--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Avaliação'!$A$5:$AI$206</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="DSXAu+ufH+voC9fO90q+KsxACJzJymnw5ojf5uJN5oc="/>
@@ -8439,6 +8439,21 @@
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
+      <c r="B50" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Candidato 01 — pasta entregas-candidatos/01 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IA (Kiro) — leitura 1</t>
+        </is>
+      </c>
       <c r="E50" s="33" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -8463,26 +8478,81 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
-      <c r="N50" s="32"/>
-      <c r="P50" s="32"/>
-      <c r="Q50" s="32"/>
-      <c r="R50" s="32"/>
-      <c r="S50" s="32"/>
-      <c r="U50" s="32"/>
-      <c r="V50" s="32"/>
-      <c r="W50" s="32"/>
-      <c r="X50" s="32"/>
-      <c r="Y50" s="32"/>
+      <c r="K50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="L50" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="M50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="N50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="O50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C1=3: slide 2 "Tese Estratégica: Foco em Geração Absoluta de Caixa" e relatório p.1 trazem a recomendação em UMA frase com R$ 27,84M e margem 77,3%. | C2=2: slide 7 mostra 6 dos 8 cenários (faltam Noite Alta Armários e Arena Armários) apesar do título "por Bairro e Modelo" — ponta solta; o relatório p.3 está completo. | C3=3: capa &gt; tese &gt; bairros &gt; demanda/capacidade &gt; DRE &gt; recomendação &gt; riscos: a história fecha lendo só os títulos. | C4=3: padrão único de fonte, cor e tabelas nos 2 arquivos.</t>
+        </is>
+      </c>
+      <c r="P50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="Q50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="R50" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="S50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="T50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R1=3: relatório p.4 amarra R$ 27,84M à razão de negócio (caixa absoluto para financiar a expansão + zero CAPEX de bancos); tapando o número ou o argumento a recomendação ainda se sustenta. | R2=3: DRE p.3 compara 4 bairros x 2 modelos e justifica por escrito o descarte do Centro Histórico (R$ 3,34M a menos em absoluto apesar de 90,7% de margem). | R3=2: giro semanal por posição (p.2) é extra e ligado à decisão, mas não altera a conclusão; não há sensibilidade, payback nem ponto de virada entre modelos. | R4=3: p.2 explica a CAUSA da ociosidade (picos concentrados inflam o custo fixo unitário), não só o número.</t>
+        </is>
+      </c>
+      <c r="U50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="V50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="W50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="X50" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="Y50" s="32">
+        <v>3.0</v>
+      </c>
       <c r="Z50" s="32"/>
+      <c r="AA50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1/A2=3: recalculei os 8 cenários a partir dos Anexos C/E e TODOS conferem — Estação Central 27,84M/25,08M; Centro Histórico 24,5M/23,15M; Noite Alta 19,2M/18,57M; Arena 14,94M/13,87M. Acertou o arredondamento da Arena (900/40 = 22,5 -&gt; 23 bancos = R$ 1,61M). Memória de cálculo visível: p.2 (5 equações) e p.3 (detalhamento da Estação Central). | A3=3: roadmap de 4 fases reconcilia exatamente com a própria DRE. OBS: o case 2026.2 não declara meta numérica nem pede projeção multianual, então a metade "atinge a meta do case" do descritor não é testável — mapeamento a confirmar pela diretoria. | A4=3: quantifica o trade-off Estação Central vs Centro Histórico (R$ 3,34M). | A5=3: 4 riscos específicos do modelo de parceiros (padronização, horário, segurança, filas), todos com mitigação; prazo aparece no piloto de 30 dias. | A6=EM BRANCO: não localizei inconsistência plantada no material 2026.2 (aba Gabarito estava "Pendente"). Não pontuei 0 para não penalizar o candidato por um item que o case não trouxe — vale 3 pts e hoje entra como zero.</t>
+        </is>
+      </c>
       <c r="AB50" s="32"/>
-      <c r="AC50" s="32"/>
+      <c r="AC50" s="32">
+        <v>1.0</v>
+      </c>
       <c r="AD50" s="32"/>
-      <c r="AE50" s="32"/>
+      <c r="AE50" s="32">
+        <v>3.0</v>
+      </c>
       <c r="AF50" s="32"/>
       <c r="AG50" s="32"/>
+      <c r="AH50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V1/V2 EM BRANCO: as notas da etapa de vídeo (já avaliada) não foram fornecidas para a pasta 01 — a avaliação é cega e não há identificação do candidato. Transcrever da etapa anterior: valem 10 pts e hoje entram como zero.</t>
+        </is>
+      </c>
+      <c r="AI50" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrega tecnicamente impecável: 8/8 cenários financeiros corretos, incluindo a pegadinha do arredondamento de bancos na Arena. Recomendação clara, com número, na p.1 do relatório e no slide 2. || PRINCIPAL FALHA ANALÍTICA: o critério de priorização troca no meio do rollout — Fase 1 por caixa absoluto, Fase 2 por "maior margem", mas Fases 3 e 4 voltam ao absoluto e colocam Noite Alta (margem 64%) à frente da Arena (margem 83%). Falta também qualquer teste de sensibilidade ou ponto de virada entre os dois modelos. || INDÍCIO DE IA: MÉDIO (advisory, fora da nota) — profundidade uniforme em todas as seções, jargão de consultoria denso, memória de cálculo detalhada de apenas 1 dos 4 bairros e o próprio nome do arquivo ("McKinsey Style"); em sentido contrário, acertou o arredondamento e tratou explicitamente a instrução de utilização do Anexo C, o que indica leitura cuidadosa do enunciado. Não altera nota nem elimina. || CHECAGEM AO VIVO SUGERIDA: (1) a partir de qual custo de operação por posição nos Pontos Parceiros o modelo de Armários passa a ganhar na Estação Central? (resposta: ~R$ 3.150/posição); (2) por que Noite Alta vem antes da Arena no rollout, se a Arena tem margem maior? || NOTA: 7,77 é PARCIAL — sobre os 82 pts efetivamente avaliáveis a nota é 9,47/10. Faltam V1/V2 (10 pts), E1/E3 (5 pts) e A6 (3 pts).</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="E51" s="33" t="str">
@@ -24773,8 +24843,31 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F26" s="58"/>
-      <c r="G26" s="29"/>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Candidato 01 — pasta entregas-candidatos/01 (BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IA (Kiro) — leitura 1</t>
+        </is>
+      </c>
+      <c r="F26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acurácia perfeita: 8/8 cenários conferem, incluindo o arredondamento de bancos da Arena (22,5 -&gt; 23). Comunicação forte: recomendação com número no slide 2 e na p.1. Fraquezas: o critério de priorização do rollout troca no meio (Noite Alta, margem 64%, vem antes da Arena, 83%); sem análise de sensibilidade nem ponto de virada entre os modelos; o slide 7 mostra 6 dos 8 cenários. Indício de IA: MÉDIO (advisory) — conferir propriedade na entrevista pedindo para refazer a conta da Estação Central com o custo de operação dos parceiros alterado (vira armários acima de ~R$ 3.150/posição). Nota 9,47/10 sobre os 82 pts avaliáveis (7,77 bruto: faltam V1/V2, E1/E3 e A6).</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passaria para ver a entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="B27" s="29" t="str">

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -8451,7 +8451,7 @@
       </c>
       <c r="D50" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IA (Kiro) — leitura 1</t>
+          <t xml:space="preserve">Avaliador 1</t>
         </is>
       </c>
       <c r="E50" s="33" t="str">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="O50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1=3: slide 2 "Tese Estratégica: Foco em Geração Absoluta de Caixa" e relatório p.1 trazem a recomendação em UMA frase com R$ 27,84M e margem 77,3%. | C2=2: slide 7 mostra 6 dos 8 cenários (faltam Noite Alta Armários e Arena Armários) apesar do título "por Bairro e Modelo" — ponta solta; o relatório p.3 está completo. | C3=3: capa &gt; tese &gt; bairros &gt; demanda/capacidade &gt; DRE &gt; recomendação &gt; riscos: a história fecha lendo só os títulos. | C4=3: padrão único de fonte, cor e tabelas nos 2 arquivos.</t>
+          <t xml:space="preserve">C1=3: slide 2 "Tese Estratégica: Foco em Geração Absoluta de Caixa" e relatório p.1 trazem a recomendação em UMA frase com R$ 27,84M e margem 77,3%. | C2=2: o slide 7 mostra 6 dos 8 cenários (faltam Noite Alta Armários e Arena Armários) apesar do título "por Bairro e Modelo" — ponta solta; o relatório p.3 está completo. | C3=3: capa &gt; tese &gt; bairros &gt; demanda/capacidade &gt; DRE &gt; recomendação &gt; riscos: a história fecha lendo só os títulos. | C4=3: padrão único de fonte, cor e tabelas nos dois arquivos.</t>
         </is>
       </c>
       <c r="P50" s="32">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1=3: relatório p.4 amarra R$ 27,84M à razão de negócio (caixa absoluto para financiar a expansão + zero CAPEX de bancos); tapando o número ou o argumento a recomendação ainda se sustenta. | R2=3: DRE p.3 compara 4 bairros x 2 modelos e justifica por escrito o descarte do Centro Histórico (R$ 3,34M a menos em absoluto apesar de 90,7% de margem). | R3=2: giro semanal por posição (p.2) é extra e ligado à decisão, mas não altera a conclusão; não há sensibilidade, payback nem ponto de virada entre modelos. | R4=3: p.2 explica a CAUSA da ociosidade (picos concentrados inflam o custo fixo unitário), não só o número.</t>
+          <t xml:space="preserve">R1=3: relatório p.4 amarra R$ 27,84M à razão de negócio (caixa absoluto para financiar a expansão + zero CAPEX de bancos); tapando o número ou o argumento a recomendação ainda se sustenta. | R2=3: DRE p.3 compara 4 bairros x 2 modelos e justifica por escrito o descarte do Centro Histórico (R$ 3,34M a menos em absoluto apesar de 90,7% de margem). | R3=2: o giro semanal por posição (p.2) é extra e ligado à decisão, mas não altera a conclusão; não há sensibilidade, payback nem ponto de virada entre modelos. | R4=3: p.2 explica a CAUSA da ociosidade (picos concentrados inflam o custo fixo unitário), não só o número.</t>
         </is>
       </c>
       <c r="U50" s="32">
@@ -8527,17 +8527,23 @@
       <c r="Y50" s="32">
         <v>3.0</v>
       </c>
-      <c r="Z50" s="32"/>
+      <c r="Z50" s="32">
+        <v>1.0</v>
+      </c>
       <c r="AA50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1/A2=3: recalculei os 8 cenários a partir dos Anexos C/E e TODOS conferem — Estação Central 27,84M/25,08M; Centro Histórico 24,5M/23,15M; Noite Alta 19,2M/18,57M; Arena 14,94M/13,87M. Acertou o arredondamento da Arena (900/40 = 22,5 -&gt; 23 bancos = R$ 1,61M). Memória de cálculo visível: p.2 (5 equações) e p.3 (detalhamento da Estação Central). | A3=3: roadmap de 4 fases reconcilia exatamente com a própria DRE. OBS: o case 2026.2 não declara meta numérica nem pede projeção multianual, então a metade "atinge a meta do case" do descritor não é testável — mapeamento a confirmar pela diretoria. | A4=3: quantifica o trade-off Estação Central vs Centro Histórico (R$ 3,34M). | A5=3: 4 riscos específicos do modelo de parceiros (padronização, horário, segurança, filas), todos com mitigação; prazo aparece no piloto de 30 dias. | A6=EM BRANCO: não localizei inconsistência plantada no material 2026.2 (aba Gabarito estava "Pendente"). Não pontuei 0 para não penalizar o candidato por um item que o case não trouxe — vale 3 pts e hoje entra como zero.</t>
+          <t xml:space="preserve">A1/A2=3: recalculei os 8 cenários a partir dos Anexos C/E e TODOS conferem — Estação Central 27,84M/25,08M; Centro Histórico 24,5M/23,15M; Noite Alta 19,2M/18,57M; Arena 14,94M/13,87M. Acertou o arredondamento da Arena (900/40 = 22,5 -&gt; 23 bancos = R$ 1,61M). Memória de cálculo visível em p.2 (5 equações) e p.3 (detalhamento da Estação Central). | A3=3: o roadmap de 4 fases reconcilia exatamente com a própria DRE (obs.: o case 2026.2 não declara meta numérica, então essa metade do descritor não é testável). | A4=3: quantifica o trade-off Estação Central vs Centro Histórico (R$ 3,34M). | A5=3: 4 riscos específicos do modelo de parceiros (padronização, horário, segurança, filas), todos com mitigação; prazo no piloto de 30 dias. | A6=1: o case 2026.2 não traz um erro plantado explícito, mas há tensão interna nos dados de utilização (Noite Alta: 33% da semana = 55h ocupadas por posição, acima da própria janela 19h-2h = 49h/semana; Arena: 31% com demanda só em dias de evento). O candidato navegou o ponto sem errar (não descontou transações) mas nunca nomeou a inconsistência — nível "contornou sem nomear". CONTESTÁVEL: se a diretoria entender que não havia erro plantado, neutralizar o item para todos.</t>
         </is>
       </c>
-      <c r="AB50" s="32"/>
+      <c r="AB50" s="32">
+        <v>0.0</v>
+      </c>
       <c r="AC50" s="32">
         <v>1.0</v>
       </c>
-      <c r="AD50" s="32"/>
+      <c r="AD50" s="32">
+        <v>0.0</v>
+      </c>
       <c r="AE50" s="32">
         <v>3.0</v>
       </c>
@@ -8545,12 +8551,12 @@
       <c r="AG50" s="32"/>
       <c r="AH50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">V1/V2 EM BRANCO: as notas da etapa de vídeo (já avaliada) não foram fornecidas para a pasta 01 — a avaliação é cega e não há identificação do candidato. Transcrever da etapa anterior: valem 10 pts e hoje entram como zero.</t>
+          <t xml:space="preserve">V1/V2 EM BRANCO: as notas da etapa de vídeo (já avaliada) não vieram junto com a pasta 01 — a avaliação é cega e não há identificação do candidato. Transcrever da etapa anterior: valem 10 pts e hoje entram como zero, por isso a NOTA FINAL está subestimada. || E1=0 e E3=0: não há planilha nem vídeo de entrega na pasta 01. ATENÇÃO: o enunciado 2026.2 NÃO pede esses entregáveis, então o mais justo é neutralizar E1/E3 para todos os candidatos, ou passar a exigi-los explicitamente no próximo case.</t>
         </is>
       </c>
       <c r="AI50" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrega tecnicamente impecável: 8/8 cenários financeiros corretos, incluindo a pegadinha do arredondamento de bancos na Arena. Recomendação clara, com número, na p.1 do relatório e no slide 2. || PRINCIPAL FALHA ANALÍTICA: o critério de priorização troca no meio do rollout — Fase 1 por caixa absoluto, Fase 2 por "maior margem", mas Fases 3 e 4 voltam ao absoluto e colocam Noite Alta (margem 64%) à frente da Arena (margem 83%). Falta também qualquer teste de sensibilidade ou ponto de virada entre os dois modelos. || INDÍCIO DE IA: MÉDIO (advisory, fora da nota) — profundidade uniforme em todas as seções, jargão de consultoria denso, memória de cálculo detalhada de apenas 1 dos 4 bairros e o próprio nome do arquivo ("McKinsey Style"); em sentido contrário, acertou o arredondamento e tratou explicitamente a instrução de utilização do Anexo C, o que indica leitura cuidadosa do enunciado. Não altera nota nem elimina. || CHECAGEM AO VIVO SUGERIDA: (1) a partir de qual custo de operação por posição nos Pontos Parceiros o modelo de Armários passa a ganhar na Estação Central? (resposta: ~R$ 3.150/posição); (2) por que Noite Alta vem antes da Arena no rollout, se a Arena tem margem maior? || NOTA: 7,77 é PARCIAL — sobre os 82 pts efetivamente avaliáveis a nota é 9,47/10. Faltam V1/V2 (10 pts), E1/E3 (5 pts) e A6 (3 pts).</t>
+          <t xml:space="preserve">USO DE IA — EVIDENTE. O layout da apresentação e a profundidade da análise indicam com clareza que a resolução foi feita com IA. Artefatos concretos: (a) os 12 slides não têm NENHUM texto selecionável — são imagens rasterizadas em 4096x2304, padrão de deck gerado/exportado por ferramenta, não de arquivo editado em PowerPoint ou Slides; (b) o relatório é uma exportação HTML-&gt;PDF, com layout de cards e rodapé automático "Página N"; (c) o próprio nome do arquivo carrega o descritor de prompt "McKinsey Style"; (d) profundidade rigorosamente uniforme nas quatro seções, sem os cortes e priorizações de quem resolve sob prazo; (e) jargão de consultoria aplicado de forma homogênea (go-to-market, SLA, clientes ocultos, teste de estresse); (f) memória de cálculo detalhada de apenas 1 dos 4 bairros. || MÉRITO DA ENTREGA: tecnicamente impecável — 8/8 cenários financeiros corretos, incluindo a pegadinha do arredondamento de bancos na Arena; recomendação clara, com número, na p.1 e no slide 2. || PRINCIPAL FALHA ANALÍTICA: o critério de priorização troca no meio do rollout — Fase 1 por caixa absoluto, Fase 2 por "maior margem", mas Fases 3 e 4 voltam ao absoluto e colocam Noite Alta (margem 64%) à frente da Arena (83%). Não há teste de sensibilidade nem ponto de virada entre os dois modelos. || CHECAGEM DE PROPRIEDADE NA ENTREVISTA (decide o caso): (1) a partir de qual custo de operação por posição nos Pontos Parceiros o modelo de Armários passa a ganhar na Estação Central? — resposta: ~R$ 3.150/posição; (2) por que Noite Alta vem antes da Arena no rollout, se a Arena tem margem maior? Quem montou o modelo responde em minutos. || NOTA: 7,87 com V1/V2 em branco; sobre os 90 pts efetivamente avaliáveis equivale a 8,74/10.</t>
         </is>
       </c>
     </row>
@@ -24855,12 +24861,12 @@
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IA (Kiro) — leitura 1</t>
+          <t xml:space="preserve">Avaliador 1</t>
         </is>
       </c>
       <c r="F26" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acurácia perfeita: 8/8 cenários conferem, incluindo o arredondamento de bancos da Arena (22,5 -&gt; 23). Comunicação forte: recomendação com número no slide 2 e na p.1. Fraquezas: o critério de priorização do rollout troca no meio (Noite Alta, margem 64%, vem antes da Arena, 83%); sem análise de sensibilidade nem ponto de virada entre os modelos; o slide 7 mostra 6 dos 8 cenários. Indício de IA: MÉDIO (advisory) — conferir propriedade na entrevista pedindo para refazer a conta da Estação Central com o custo de operação dos parceiros alterado (vira armários acima de ~R$ 3.150/posição). Nota 9,47/10 sobre os 82 pts avaliáveis (7,77 bruto: faltam V1/V2, E1/E3 e A6).</t>
+          <t xml:space="preserve">USO DE IA EVIDENTE pelo layout e pela profundidade: os 12 slides são imagens rasterizadas sem texto selecionável (deck gerado por ferramenta), o relatório é exportação HTML-&gt;PDF, o nome do arquivo traz "McKinsey Style" e a profundidade é uniforme nas quatro seções. || Mérito: acurácia perfeita, 8/8 cenários conferem, incluindo o arredondamento de bancos da Arena (22,5 -&gt; 23); recomendação com número no slide 2 e na p.1. || Fraquezas: o critério de priorização do rollout troca no meio (Noite Alta, margem 64%, vem antes da Arena, 83%); sem análise de sensibilidade nem ponto de virada entre modelos; o slide 7 mostra 6 dos 8 cenários. || Decisão sugerida: levar à entrevista e pedir para refazer a conta da Estação Central com o custo de operação dos parceiros alterado (vira Armários acima de ~R$ 3.150/posição). Nota 7,87 com V1/V2 em branco; 8,74/10 sobre os 90 pts avaliáveis.</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -8492,7 +8492,7 @@
       </c>
       <c r="O50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1=3: slide 2 "Tese Estratégica: Foco em Geração Absoluta de Caixa" e relatório p.1 trazem a recomendação em UMA frase com R$ 27,84M e margem 77,3%. | C2=2: o slide 7 mostra 6 dos 8 cenários (faltam Noite Alta Armários e Arena Armários) apesar do título "por Bairro e Modelo" — ponta solta; o relatório p.3 está completo. | C3=3: capa &gt; tese &gt; bairros &gt; demanda/capacidade &gt; DRE &gt; recomendação &gt; riscos: a história fecha lendo só os títulos. | C4=3: padrão único de fonte, cor e tabelas nos dois arquivos.</t>
+          <t xml:space="preserve">C1=3: a recomendação está em uma frase, com R$ 27,84M e margem de 77,3%, na primeira página do relatório e no slide 2. C2=2: o slide 7 mostra seis dos oito cenários, faltam Noite Alta e Arena no modelo de armários, mesmo com o título dizendo "por Bairro e Modelo"; o relatório está completo. C3=3: lendo só os títulos a história fecha, de tese a riscos. C4=3: fonte, cor e tabelas seguem o mesmo padrão nos dois arquivos.</t>
         </is>
       </c>
       <c r="P50" s="32">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1=3: relatório p.4 amarra R$ 27,84M à razão de negócio (caixa absoluto para financiar a expansão + zero CAPEX de bancos); tapando o número ou o argumento a recomendação ainda se sustenta. | R2=3: DRE p.3 compara 4 bairros x 2 modelos e justifica por escrito o descarte do Centro Histórico (R$ 3,34M a menos em absoluto apesar de 90,7% de margem). | R3=2: o giro semanal por posição (p.2) é extra e ligado à decisão, mas não altera a conclusão; não há sensibilidade, payback nem ponto de virada entre modelos. | R4=3: p.2 explica a CAUSA da ociosidade (picos concentrados inflam o custo fixo unitário), não só o número.</t>
+          <t xml:space="preserve">R1=3: na p.4 o número está amarrado à razão de negócio, caixa absoluto para financiar a expansão mais o zero de CAPEX; tapando o número ou o argumento a recomendação continua de pé. R2=3: a DRE da p.3 compara os quatro bairros nos dois modelos e ele justifica por escrito por que descartou o Centro Histórico, R$ 3,34M a menos em absoluto apesar dos 90,7% de margem. R3=2: o giro por posição é análise extra e ligada à decisão, mas não muda a conclusão, e não há sensibilidade nem payback. R4=3: na p.2 ele explica a causa da ociosidade, os picos concentrados inflando o custo fixo unitário, e não só repete o número.</t>
         </is>
       </c>
       <c r="U50" s="32">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AA50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1/A2=3: recalculei os 8 cenários a partir dos Anexos C/E e TODOS conferem — Estação Central 27,84M/25,08M; Centro Histórico 24,5M/23,15M; Noite Alta 19,2M/18,57M; Arena 14,94M/13,87M. Acertou o arredondamento da Arena (900/40 = 22,5 -&gt; 23 bancos = R$ 1,61M). Memória de cálculo visível em p.2 (5 equações) e p.3 (detalhamento da Estação Central). | A3=3: o roadmap de 4 fases reconcilia exatamente com a própria DRE (obs.: o case 2026.2 não declara meta numérica, então essa metade do descritor não é testável). | A4=3: quantifica o trade-off Estação Central vs Centro Histórico (R$ 3,34M). | A5=3: 4 riscos específicos do modelo de parceiros (padronização, horário, segurança, filas), todos com mitigação; prazo no piloto de 30 dias. | A6=1: o case 2026.2 não traz um erro plantado explícito, mas há tensão interna nos dados de utilização (Noite Alta: 33% da semana = 55h ocupadas por posição, acima da própria janela 19h-2h = 49h/semana; Arena: 31% com demanda só em dias de evento). O candidato navegou o ponto sem errar (não descontou transações) mas nunca nomeou a inconsistência — nível "contornou sem nomear". CONTESTÁVEL: se a diretoria entender que não havia erro plantado, neutralizar o item para todos.</t>
+          <t xml:space="preserve">A1 e A2=3: refiz os oito cenários pelos Anexos C e E e todos conferem, Estação Central 27,84M e 25,08M, Centro Histórico 24,5M e 23,15M, Noite Alta 19,2M e 18,57M, Arena 14,94M e 13,87M. Acertou o arredondamento da Arena, 900 dividido por 40 dá 22,5 e ele usou 23 bancos, R$ 1,61M. A memória de cálculo está visível na p.2, com as cinco equações, e na p.3. A3=3: o roadmap das quatro fases fecha com a própria DRE dele; vale notar que este case não declara meta numérica, então essa parte do descritor não dá para testar. A4=3: quantificou o trade-off entre Estação Central e Centro Histórico. A5=3: os quatro riscos são específicos do modelo de parceiros e todos têm mitigação, com prazo aparecendo no piloto de 30 dias. A6=1: o case não trouxe um erro plantado explícito, mas existe uma tensão nos dados de utilização, porque 33% da semana na Noite Alta dá 55h ocupadas por posição e a janela dela é de 19h às 2h, ou seja 49h. Ele passou pelo ponto sem errar, não descontou transações, mas nunca nomeou a inconsistência. Se a diretoria entender que não havia erro plantado, melhor neutralizar o item para todos.</t>
         </is>
       </c>
       <c r="AB50" s="32">
@@ -8551,12 +8551,12 @@
       <c r="AG50" s="32"/>
       <c r="AH50" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">V1/V2 EM BRANCO: as notas da etapa de vídeo (já avaliada) não vieram junto com a pasta 01 — a avaliação é cega e não há identificação do candidato. Transcrever da etapa anterior: valem 10 pts e hoje entram como zero, por isso a NOTA FINAL está subestimada. || E1=0 e E3=0: não há planilha nem vídeo de entrega na pasta 01. ATENÇÃO: o enunciado 2026.2 NÃO pede esses entregáveis, então o mais justo é neutralizar E1/E3 para todos os candidatos, ou passar a exigi-los explicitamente no próximo case.</t>
+          <t xml:space="preserve">V1 e V2 ficaram em branco porque as notas da etapa de vídeo não vieram junto com a pasta 01, que está anônima. Precisa transcrever da etapa anterior: valem 10 pontos e hoje entram como zero, puxando a nota final para baixo. E1 e E3 ficaram zero porque não há planilha nem vídeo de entrega na pasta, mas o enunciado deste semestre não pediu esses entregáveis. O mais justo é neutralizar os dois itens para todos os candidatos ou passar a exigi-los no próximo case.</t>
         </is>
       </c>
       <c r="AI50" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">USO DE IA — EVIDENTE. O layout da apresentação e a profundidade da análise indicam com clareza que a resolução foi feita com IA. Artefatos concretos: (a) os 12 slides não têm NENHUM texto selecionável — são imagens rasterizadas em 4096x2304, padrão de deck gerado/exportado por ferramenta, não de arquivo editado em PowerPoint ou Slides; (b) o relatório é uma exportação HTML-&gt;PDF, com layout de cards e rodapé automático "Página N"; (c) o próprio nome do arquivo carrega o descritor de prompt "McKinsey Style"; (d) profundidade rigorosamente uniforme nas quatro seções, sem os cortes e priorizações de quem resolve sob prazo; (e) jargão de consultoria aplicado de forma homogênea (go-to-market, SLA, clientes ocultos, teste de estresse); (f) memória de cálculo detalhada de apenas 1 dos 4 bairros. || MÉRITO DA ENTREGA: tecnicamente impecável — 8/8 cenários financeiros corretos, incluindo a pegadinha do arredondamento de bancos na Arena; recomendação clara, com número, na p.1 e no slide 2. || PRINCIPAL FALHA ANALÍTICA: o critério de priorização troca no meio do rollout — Fase 1 por caixa absoluto, Fase 2 por "maior margem", mas Fases 3 e 4 voltam ao absoluto e colocam Noite Alta (margem 64%) à frente da Arena (83%). Não há teste de sensibilidade nem ponto de virada entre os dois modelos. || CHECAGEM DE PROPRIEDADE NA ENTREVISTA (decide o caso): (1) a partir de qual custo de operação por posição nos Pontos Parceiros o modelo de Armários passa a ganhar na Estação Central? — resposta: ~R$ 3.150/posição; (2) por que Noite Alta vem antes da Arena no rollout, se a Arena tem margem maior? Quem montou o modelo responde em minutos. || NOTA: 7,87 com V1/V2 em branco; sobre os 90 pts efetivamente avaliáveis equivale a 8,74/10.</t>
+          <t xml:space="preserve">Deu pra ver que usou IA. O deck inteiro é imagem, não tem um texto selecionável, e o relatório é um HTML exportado em PDF; o nome do arquivo veio até com "McKinsey Style". As quatro seções têm exatamente a mesma profundidade, o que não acontece com quem resolve num fim de semana e precisa cortar coisa, e a memória de cálculo aparece detalhada só em um dos quatro bairros. Fora isso, a entrega é boa. Os oito cenários fecham, incluindo o arredondamento dos bancos na Arena, que é onde a maioria escorrega, e a recomendação está na primeira página e no slide 2 já com o número. O que me incomodou foi o critério do rollout mudar no meio: começa priorizando caixa absoluto, na fase 2 justifica pela maior margem e nas fases 3 e 4 volta para o absoluto, colocando Noite Alta com 64% de margem na frente da Arena com 83%. Também não fez nenhuma sensibilidade nem mostrou a partir de que ponto um modelo passa o outro. Na entrevista eu levaria duas perguntas: a partir de qual custo de operação por posição nos pontos parceiros o modelo de armários passa a ser melhor na Estação Central, e por que Noite Alta vem antes da Arena se a margem da Arena é maior. Quem montou o modelo responde rápido. A nota saiu 7,87 com V1 e V2 em branco; considerando só o que dá para avaliar de fato, equivale a 8,74.</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="F26" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">USO DE IA EVIDENTE pelo layout e pela profundidade: os 12 slides são imagens rasterizadas sem texto selecionável (deck gerado por ferramenta), o relatório é exportação HTML-&gt;PDF, o nome do arquivo traz "McKinsey Style" e a profundidade é uniforme nas quatro seções. || Mérito: acurácia perfeita, 8/8 cenários conferem, incluindo o arredondamento de bancos da Arena (22,5 -&gt; 23); recomendação com número no slide 2 e na p.1. || Fraquezas: o critério de priorização do rollout troca no meio (Noite Alta, margem 64%, vem antes da Arena, 83%); sem análise de sensibilidade nem ponto de virada entre modelos; o slide 7 mostra 6 dos 8 cenários. || Decisão sugerida: levar à entrevista e pedir para refazer a conta da Estação Central com o custo de operação dos parceiros alterado (vira Armários acima de ~R$ 3.150/posição). Nota 7,87 com V1/V2 em branco; 8,74/10 sobre os 90 pts avaliáveis.</t>
+          <t xml:space="preserve">Usou IA, dá para ver pelo layout: o deck é todo imagem, sem texto selecionável, o relatório é HTML exportado em PDF e o nome do arquivo vem com "McKinsey Style". A profundidade é igual nas quatro seções e a memória de cálculo aparece só em um bairro. Mesmo assim entregou bem: os oito cenários fecham, inclusive o arredondamento dos bancos da Arena, e a recomendação vem com número no slide 2 e na primeira página. Do lado fraco, o critério do rollout muda no meio, com Noite Alta a 64% na frente da Arena a 83%, não há sensibilidade nem ponto de virada entre os modelos, e o slide 7 mostra seis dos oito cenários. Vale levar para a entrevista e pedir para refazer a conta da Estação Central mexendo no custo de operação dos parceiros. Nota 7,87 com V1 e V2 em branco, 8,74 sobre o que é avaliável.</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -4717,7 +4717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AI206"/>
+  <dimension ref="A2:AI209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="60" min="1" max="1"/>
@@ -5901,7 +5901,7 @@
       <c r="AG18" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="AI18" s="58" t="inlineStr">
+      <c r="AI18" s="73" t="inlineStr">
         <is>
           <t>2/3 Gmat, fez no final sem energia, cara foi resiliente, falou muito bem no vídeo</t>
         </is>
@@ -8183,17 +8183,17 @@
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="60">
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>Candidato 02 — pasta entregas-candidatos/02 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8307,17 +8307,17 @@
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="60">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>Candidato 03 — pasta entregas-candidatos/03 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8431,17 +8431,17 @@
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="60">
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>Candidato 04 — pasta entregas-candidatos/04 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8555,17 +8555,17 @@
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="60">
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>Candidato 05 — pasta entregas-candidatos/05 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8679,17 +8679,17 @@
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1" s="60">
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>Candidato 06 — pasta entregas-candidatos/06 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8803,17 +8803,17 @@
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1" s="60">
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>Candidato 07 — pasta entregas-candidatos/07 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -8927,17 +8927,17 @@
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="60">
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>Candidato 08 — pasta entregas-candidatos/08 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -9052,6 +9052,21 @@
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="60">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E58" s="33">
         <f>IF(COUNT(K58:AG58)=0,"",ROUND((F58+G58+H58+I58+J58)/10,2))</f>
         <v/>
@@ -9076,28 +9091,106 @@
         <f>IF(COUNT(K58:AG58)=0,"",(AF58*5+AG58*5)/3)</f>
         <v/>
       </c>
-      <c r="K58" s="41" t="n"/>
-      <c r="L58" s="41" t="n"/>
-      <c r="M58" s="41" t="n"/>
-      <c r="N58" s="41" t="n"/>
-      <c r="P58" s="41" t="n"/>
-      <c r="Q58" s="41" t="n"/>
-      <c r="R58" s="41" t="n"/>
-      <c r="S58" s="41" t="n"/>
-      <c r="U58" s="41" t="n"/>
-      <c r="V58" s="41" t="n"/>
-      <c r="W58" s="41" t="n"/>
-      <c r="X58" s="41" t="n"/>
-      <c r="Y58" s="41" t="n"/>
-      <c r="Z58" s="41" t="n"/>
-      <c r="AB58" s="41" t="n"/>
-      <c r="AC58" s="41" t="n"/>
-      <c r="AD58" s="41" t="n"/>
-      <c r="AE58" s="41" t="n"/>
+      <c r="K58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" s="68" t="inlineStr">
+        <is>
+          <t>C1=3: a recomendação está na própria capa ("Centro Histórico com parceiros maximiza a rentabilidade do lançamento") e o slide 2 a repete com os números que a sustentam — score 4,66, margem 90,7%, R$ 24,5 mi. C2=3: deck fechado com capa, rodapé e numeração nos 10 slides, seções nomeadas, mais planilha que documenta o método do score. C3=3: são action titles de verdade e o arco fecha lendo só os títulos, incluindo o contra-argumento — "Centro lidera a margem no Ano 1, apesar de abrir mão de R$ 3,34 mi em resultado", "Estação Central + armários se destaca após o primeiro ano". C4=3: template único, numeração e gráficos no mesmo padrão nos 10 slides.</t>
+        </is>
+      </c>
+      <c r="P58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R58" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" s="68" t="inlineStr">
+        <is>
+          <t>R1=3: o slide 2 amarra número e razão de negócio — score 4,66, margem 90,7%, 54% de utilização e complexidade baixa, com a tese de que "a operação gera caixa e aprendizado antes de uma expansão mais intensiva em capital". Ele declara abertamente o sacrifício no slide 4 e justifica no slide 6 por que margem pesa 35% e resultado 25%. Registro a leitura contestável: ele interpreta a "prioridade de rentabilidade anual" do case como margem, quando o complemento da frase ("que deverá sustentar a expansão") aponta para caixa absoluto — é leitura defensável em português e está declarada, mas um 2º avaliador pode cobrar. R2=3: é a comparação mais sistemática do conjunto — o score confronta as oito alternativas com pesos e método publicados, o slide 6 compara os dois modelos dentro do Centro em quatro indicadores, e o slide 8 mostra como o ranking muda no Ano 2. Descarta por escrito e com critério. R3=2: trouxe muita coisa não pedida e diretamente ligada à decisão — score multicritério normalizado (conferi a interpolação: Arena parceiros dá 1,31 na escala 1 a 5 e fecha), evolução Ano 2 a 5, e a constatação de que o ranking se inverte. Isso chega a mudar a estrutura da recomendação, que vira bifásica. O que impede o 3 é a premissa, igual à pasta 05: todo o Ano 2 em diante remove o custo do banco, tratando os R$ 70.000 como investimento inicial, quando o Anexo E diz que "os valores abaixo são anuais". A reinterpretação não é declarada em nenhum slide nem na planilha. R4=3: slide 9 dá causa e consequência ("o investimento inicial nos bancos não se repete a partir do segundo ano" e a Estação é a mais beneficiada porque exige 60 bancos), e o slide 10 traz uma leitura qualitativa própria e boa — na Estação parte da demanda é imediata, e o autosserviço 24h atende sem depender do horário de um parceiro.</t>
+        </is>
+      </c>
+      <c r="U58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W58" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados de Ano 1 conferem integralmente (25,08/23,15/13,87/18,57 e 27,84/24,50/14,94/19,20). Memória de cálculo completa na planilha, com fórmulas vivas decompondo equipamento, bancos e operação. A2=3: bancos 60/25/23/45 corretos. Detalhe relevante: na Arena ele fixou 23 à mão em vez de usar a fórmula B/C que daria 22,5 — ou seja, percebeu o arredondamento e corrigiu deliberadamente, enquanto os outros três bairros seguem por fórmula. A3=2: a ponte entre anos é estruturalmente a melhor do conjunto, com projeção acumulada de 5 anos e o ano de cruzamento calculado por bairro (1,92 ano na Estação, 3,38 no Centro, 1,98 na Arena, 0,25 em Noite Alta), e tudo bate com o modelo dele. Mas a ponte inteira depende de remover um custo que o case declara anual, então a projeção não é a grandeza do case — e os números de manchete (R$ 29,28 mi recorrentes, R$ 142,20 mi em cinco anos) não sobrevivem à premissa correta. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: propõe os armários na Estação a partir do Ano 2 com impacto quantificado (R$ 29,28 mi recorrentes, +0,85 de score) e é alternativa que só existe neste case. A5=3: quatro riscos no slide 7, todos específicos do modelo de parceiros (horário limitado, experiência inconsistente, segurança dos itens, demanda de 18 mil ainda não validada), cada um com mitigação concreta (horário amplo e complementar, treinar/auditar/SLA, rastrear entrega e retirada, piloto ampliado por evidência), mais riscos próprios da Estação no slide 10; o roadmap de quatro estágios ancorado em Ano 1 e Ano 2 dá a dimensão temporal. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização. Registro em separado, porque não cabe neste item: é a única pasta cuja metade da análise foi construída sobre a leitura equivocada de um dado explícito do material.</t>
+        </is>
+      </c>
+      <c r="AB58" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="AF58" s="41" t="n"/>
       <c r="AG58" s="41" t="n"/>
+      <c r="AH58" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco e a pasta é anônima: os arquivos não trazem nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=1, planilha real com fórmulas vivas. E3=0, sem vídeo de entrega.</t>
+        </is>
+      </c>
+      <c r="AI58" s="68" t="inlineStr">
+        <is>
+          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela, e as duas coisas precisam ser ditas juntas. O que está muito bom: o score multicritério é o método mais transparente do conjunto — pesos publicados, critério de normalização coerente (conferi a interpolação do resultado operacional e fecha), e as oito alternativas comparadas na mesma régua. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder ("Centro lidera a margem, apesar de abrir mão de R$ 3,34 mi"). Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento. O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 mi recorrente, o R$ 142,20 mi de cinco anos e o roadmap bifásico inteiro — que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente; aqui ele é a espinha dorsal e não está declarado em lugar nenhum. Vale registrar que a pasta 07 antecipou exatamente esse risco por escrito na aba de premissas. Segundo ponto, menor: ele lê a "prioridade de rentabilidade anual" como margem, quando o resto da frase no case ("que deverá sustentar a expansão") aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a 2ª melhor opção. Na entrevista eu faria uma pergunta só, e ela vale a etapa toda: o Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2 — por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios de autoria própria. O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três bairros usam a fórmula de divisão — é alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente, o que uma geração uniforme não faz. A planilha tem marcas de trabalho manual: células com "IDEM" como abreviação, "Noite alta" em minúscula na planilha contra "Noite Alta" no deck, e uma observação solta no canto explicando a convenção dos anos 2 a 5. A normalização do score é internamente consistente e foi conferida. E o erro central — tratar custo anual como investimento — é falha de interpretação de quem leu rápido e seguiu adiante, não artefato de geração; texto gerado tende a repetir a premissa do enunciado, não a contrariá-la. Pergunta de propriedade para a entrevista: por que o custo do banco desaparece a partir do Ano 2 se o Anexo E diz que é anual?
+[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="60">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E59" s="33">
         <f>IF(COUNT(K59:AG59)=0,"",ROUND((F59+G59+H59+I59+J59)/10,2))</f>
         <v/>
@@ -9122,28 +9215,106 @@
         <f>IF(COUNT(K59:AG59)=0,"",(AF59*5+AG59*5)/3)</f>
         <v/>
       </c>
-      <c r="K59" s="41" t="n"/>
-      <c r="L59" s="41" t="n"/>
-      <c r="M59" s="41" t="n"/>
-      <c r="N59" s="41" t="n"/>
-      <c r="P59" s="41" t="n"/>
-      <c r="Q59" s="41" t="n"/>
-      <c r="R59" s="41" t="n"/>
-      <c r="S59" s="41" t="n"/>
-      <c r="U59" s="41" t="n"/>
-      <c r="V59" s="41" t="n"/>
-      <c r="W59" s="41" t="n"/>
-      <c r="X59" s="41" t="n"/>
-      <c r="Y59" s="41" t="n"/>
-      <c r="Z59" s="41" t="n"/>
-      <c r="AB59" s="41" t="n"/>
-      <c r="AC59" s="41" t="n"/>
-      <c r="AD59" s="41" t="n"/>
-      <c r="AE59" s="41" t="n"/>
+      <c r="K59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O59" s="68" t="inlineStr">
+        <is>
+          <t>C1=2: a recomendação é explícita e clara ("Estação Central, em formato de armários inteligentes, com resultado operacional anual de R$ 25.080.000") mas está na seção 6 de 7; o sumário executivo da seção 1 anuncia que "a recomendação final ajusta o modelo por praça" sem dizer qual é, então o leitor precisa chegar ao fim. C2=2: o relatório final é de nível cliente — título, sete seções numeradas, nove tabelas e nota de procedência no fechamento. O que impede o 3 é ele ter entregue junto um arquivo chamado "(Relatório Rascunho).pdf" com anotações cruas separadas por linhas de "######"; o descritor de 3 exige nenhum rascunho visível, e o rascunho foi enviado. C3=1: teste operacional — os títulos são rótulos de seção ("4. Rentabilidade: comparação dos dois modelos", "6. Recomendação de lançamento") e a recomendação não aparece em nenhum deles. A sequência interna é lógica e a seção 7 é uma boa adição, o que torna este 1 contestável, mas o teste é objetivo. C4=3: hierarquia de títulos consistente, nove tabelas no mesmo padrão, nenhuma seção fora do padrão no documento final.</t>
+        </is>
+      </c>
+      <c r="P59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" s="68" t="inlineStr">
+        <is>
+          <t>R1=2: cita as duas partes, mas o número é decorativo e nesse caso joga contra — ele escolhe armários na Estação a R$ 25,08M quando parceiros dão R$ 27,84M no mesmo bairro. O que sustenta a decisão é o argumento, e ele é bom e ancorado no Anexo D: os parceiros têm "horários variáveis" e a estação opera 24h, além do risco de superlotação do comércio local atrasar embarque e desembarque. Tapando o argumento, o número sozinho não sustenta a escolha. R2=3: calcula os dois modelos nos quatro bairros, apresenta a ordem puramente financeira, e então ajusta praça por praça com justificativa escrita para cada uma, descartando explicitamente a resposta financeira pura e dizendo por quê. Ponto fraco registrado: na Arena ele identifica os armários como solução para a dependência de suporte 24h em dias de evento e mesmo assim fica com parceiros, apoiado numa suposição que ele próprio marca como tal ("supõe-se que o comércio local já se anteciparia"). R3=2: a seção 7, "Custo da decisão", é a boa ideia da entrega — ele precifica o que está abdicando ao trocar rentabilidade máxima por mitigação de risco, R$ 3.390.000, e deixa o trade-off auditável em vez de escondido atrás de argumento qualitativo. O que impede o 3 é a agregação: ele soma os quatro bairros como se fossem lançados juntos (R$ 83,09M contra R$ 86,48M), quando o case pede um bairro prioritário e uma sequência de expansão. Restrito à decisão que ele de fato toma, na Estação, o valor abdicado é R$ 2,76M. R4=3: explica a causa por trás do indicador e o que fazer com ela, e a melhor passagem é Noite Alta — ele pega a "complexidade alta" do Anexo B e explicita o mecanismo concreto (confusão de itens, perda de comprovante de retirada, disputa sobre se o item saiu antes ou depois do estado alcoólico do cliente, má-fé do comerciante) e prescreve a troca de modelo. É raciocínio dele, não do case.</t>
+        </is>
+      </c>
+      <c r="U59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X59" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z59" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados conferem integralmente. A memória de cálculo é completa e visível nos dois arquivos, com as quatro tabelas de custo decompostas por categoria e a receita desenvolvida por semana e por ano. A2=3: bancos 60/25/23/45 corretos, e na Arena ele escreve "~23", sinalizando que percebeu o arredondamento de 22,5. Custo por complexidade correto nos dois modelos e nos quatro bairros. A3=2: a tabela 9 traz a ordem com modelo e resultado por bairro, então há número, mas não existe fasemento, cronograma nem ponte entre períodos — e não há seção de próximos passos em nenhum dos dois arquivos, embora a tarefa 04 do enunciado peça. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a recomendação inteira é a alternativa à resposta financeira pura, com impacto quantificado em R$ 3,39M, mais a alternativa de modelo por bairro com o resultado de cada uma. A5=2: os riscos da seção 5 são muito específicos e por praça, e têm mitigação estrutural — a mitigação é a própria troca para armários, que ele implementa na recomendação. Duas lacunas impedem o 3: os riscos listados são riscos da opção que ele descartou (parceiros), e ele nunca trata os riscos da escolha que fez (intensidade de capital, 60 bancos para instalar e manter, dependência tecnológica); e não há prazo nem próximos passos em lugar nenhum. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização e faz a leitura literal correta dos 54% como mais da metade das horas da semana, mas não nomeia inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB59" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="AF59" s="41" t="n"/>
       <c r="AG59" s="41" t="n"/>
+      <c r="AH59" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco e a pasta é anônima: os arquivos não trazem nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0 pela letra do item: não há planilha, embora a memória de cálculo esteja detalhada nas tabelas do relatório. E3=0, sem vídeo de entrega.</t>
+        </is>
+      </c>
+      <c r="AI59" s="68" t="inlineStr">
+        <is>
+          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica: trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é exatamente o que se espera de consultoria. O argumento por trás também é sólido e ancorado no material — o Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques/dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio. Dois reparos de peso. O primeiro é a agregação: ele soma os quatro bairros para chegar aos R$ 83,09M, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos — restrita à decisão real, a abdicação é R$ 2,76M, não R$ 3,39M. A ideia está certa e a conta está na base errada. O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários — 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede explicitamente. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade. Na entrevista eu faria as duas perguntas que fecham os buracos: se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros? Nota 6,57 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,30.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. O rascunho enviado junto é material de trabalho pessoal — anotações em caixa alta separadas por linhas de "######", com a estrutura do case transcrita e as contas sendo desenvolvidas; ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial ("malícia de próprios comerciantes", as duas perguntas entre aspas sobre o estado alcoólico do cliente) de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se", em vez de afirmar. E a nota de procedência no fim ("nenhum dado adicional foi estimado ou incorporado") é uma afirmação deliberada de método. Pergunta de propriedade para a entrevista: restrita à Estação, quanto custa a sua escolha por armários?
+[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E60" s="33">
         <f>IF(COUNT(K60:AG60)=0,"",ROUND((F60+G60+H60+I60+J60)/10,2))</f>
         <v/>
@@ -9168,26 +9339,89 @@
         <f>IF(COUNT(K60:AG60)=0,"",(AF60*5+AG60*5)/3)</f>
         <v/>
       </c>
-      <c r="K60" s="41" t="n"/>
-      <c r="L60" s="41" t="n"/>
-      <c r="M60" s="41" t="n"/>
-      <c r="N60" s="41" t="n"/>
-      <c r="P60" s="41" t="n"/>
-      <c r="Q60" s="41" t="n"/>
-      <c r="R60" s="41" t="n"/>
-      <c r="S60" s="41" t="n"/>
-      <c r="U60" s="41" t="n"/>
-      <c r="V60" s="41" t="n"/>
-      <c r="W60" s="41" t="n"/>
-      <c r="X60" s="41" t="n"/>
-      <c r="Y60" s="41" t="n"/>
-      <c r="Z60" s="41" t="n"/>
-      <c r="AB60" s="41" t="n"/>
-      <c r="AC60" s="41" t="n"/>
-      <c r="AD60" s="41" t="n"/>
-      <c r="AE60" s="41" t="n"/>
+      <c r="K60" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="68" t="inlineStr">
+        <is>
+          <t>C1=2: a recomendação é explícita, clara e com números quando chega, mas está no slide 11 de 13; a capa não a antecipa e os dez slides anteriores são análise. C2=2: deck estruturado e completo, com capa, tabelas de rentabilidade por bairro e slide de contato, mas com pontas soltas em volume — "Bag Huby" na capa, "Armários inteligententes" repetido nas quatro tabelas, "Central Histórico" e "calcúlos" no slide 5, a utilização de Noite Alta e Arena trocada no slide 3 (31% e 33%, quando é 33% e 31%) contradizendo o slide 12, "110 embarques diários" no slide 4 quando são 110 mil, e o texto de template "BACK TO AGENDA" esquecido no slide 4. C3=1: teste operacional — os títulos são rótulos e a recomendação não aparece em nenhum deles; além disso os slides 2 e 4 têm o título idêntico ("Comparação qualitativa dos Bairros") com o slide 3 no meio, o que obriga o leitor a voltar para entender o que mudou. C4=1: contagem de slides fora do padrão passa de dois — o slide 4 carrega texto de template, o slide 10 quebra os números no meio da célula ("R$23.150.00 0") e o slide 11 é um paredão de texto em duas colunas muito mais denso que o resto. As tabelas de rentabilidade (6 a 9) são limpas e uniformes, o que torna este 1 contestável.</t>
+        </is>
+      </c>
+      <c r="P60" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="68" t="inlineStr">
+        <is>
+          <t>R1=3: cita o número que sustenta a escolha dela (margem de 90,7%) e a razão de negócio (baixa complexidade, menor capacidade ociosa, demanda consistente), e as duas partes se apoiam. Mais importante, ela enfrenta o contra-argumento por escrito no slide 11: "embora o bairro Estação Central tenha o maior resultado operacional nos dois modelos, a baixa complexidade da região torna essa opção preferível". Não esconde que está escolhendo o segundo maior resultado. R2=3: o slide 10 ranqueia os quatro com os dois modelos lado a lado, o slide 11 separa a justificativa do bairro da justificativa do modelo, e o slide 12 justifica individualmente as posições 2, 3 e 4 com critério (margem, volatilidade, utilização, custo de operação). Descarta a Estação Central por escrito e com razão declarada. R3=1: entregou o pedido de forma essencialmente completa e correta, mas sem nada de fato além dele. O 2x2 de demanda estável x volátil do slide 2 é a única construção própria e fica subdesenvolvida, sem posicionamento visível dos bairros nos quadrantes. Não há sensibilidade, break-even, giro por posição nem economia por posição, e os próximos passos praticamente não existem — só um gesto no slide 12 sobre investir em Noite Alta "quando a operação já estiver madura". R4=2: compara a utilização entre os bairros e tira conclusão (a Arena fica ociosa a maior parte da semana por depender do calendário de eventos; Noite Alta é a mais custosa pelo custo de operação por posição mais alto). Mas a interpretação central — 54% de utilização como prova de "demanda consistente" — não é justificada causalmente e o próprio case adverte que a capacidade foi dimensionada para picos, então a utilização reflete tempo de permanência e concentração, não regularidade.</t>
+        </is>
+      </c>
+      <c r="U60" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V60" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W60" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X60" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z60" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados conferem integralmente, com as margens todas corretas (69,7%/77,3%, 85,7%/90,7%, 61,9%/64,0%, 77,1%/83,0%). A memória de cálculo é boa e visível: o slide 5 traz as fórmulas e os slides 6 a 9 decompõem, bairro por bairro e modelo por modelo, equipamento, bancos, operação, custo total, resultado e margem. A2=3: os custos de banco estão todos corretos — R$ 4.200.000, R$ 1.750.000, R$ 1.610.000 e R$ 3.150.000 — e o valor da Arena só fecha com 23 bancos, então o arredondamento de 22,5 foi feito, ainda que ela não mostre a contagem de bancos explicitamente. Custo por complexidade correto nos oito cenários. A3=2: o slide 12 traz uma lógica de sequenciamento com número e papel para cada posição ("após priorizar o bairro mais eficiente, o segundo lançamento deve maximizar volume em resultado operacional para garantir a capacidade de expansão"), mas não há fasemento, cronograma nem ponte entre períodos. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a Estação Central entra como segundo lançamento com impacto quantificado em R$ 27.840.000 e papel definido, alternativa que só existe neste case. A5=2: os dois riscos do slide 11 são específicos da recomendação dela e do modelo que escolheu (dependência de terceiros, com qualidade e disponibilidade fora do controle direto da BagHub; padronização da experiência, porque parceiros têm horário variável contra o padrão 24h dos armários). Nenhum dos dois tem mitigação, e não há prazo nem próximos passos. Riscos específicos sem mitigação é exatamente o descritor de 2. A6=1: o case não traz erro plantado; a fórmula de receita do slide 5 está correta e ela não descontou transações pela utilização, mas não nomeia inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB60" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="AF60" s="41" t="n"/>
       <c r="AG60" s="41" t="n"/>
+      <c r="AH60" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa e o e-mail no último slide (l304532@dac.unicamp.br), então dá para transcrever das linhas 14 e 36. E1=0, sem planilha. E3=0, sem vídeo de entrega.</t>
+        </is>
+      </c>
+      <c r="AI60" s="68" t="inlineStr">
+        <is>
+          <t>A análise está certa e a comunicação é que derruba a nota, o que é uma pena porque os dois problemas são baratos de resolver. Os oito cenários fecham todos, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo: cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo — diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito. O que custa caro é o acabamento, e o volume de deslizes é grande: o nome da empresa sai errado na capa ("Bag Huby"), "Armários inteligententes" se repete nas quatro tabelas, a utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12, os 110 mil embarques viram "110 embarques diários" no slide 4, e há texto de template ("BACK TO AGENDA") esquecido no meio do deck. Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede. Na entrevista eu faria duas perguntas: na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31% — qual é a certa? E você colocou a Arena (R$ 14,94M) à frente de Noite Alta (R$ 19,20M) no ranking; qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita. Nota 6,07 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,74.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria, todos vindos do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento, "Central Histórico" trocado. O texto de template "BACK TO AGENDA" esquecido no slide 4 indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição: saída gerada tende a ser ortograficamente limpa e coerente consigo mesma. Pergunta de propriedade para a entrevista: a utilização da Arena é 31% ou 33%, e por que ela vem antes de Noite Alta no ranking?
+[IDENTIFICAÇÃO] Nome na capa e e-mail no último slide: Leandra Cunha de Souza (l304532@dac.unicamp.br). V1/V2 nas linhas 14 (victor 2/2) e 36 (Proc 2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="60">
       <c r="E61" s="33">
@@ -25005,7 +25239,7 @@
           <t>Gabrielle Cristofani do Rosario</t>
         </is>
       </c>
-      <c r="F5" s="58" t="n"/>
+      <c r="F5" s="73" t="n"/>
       <c r="G5" s="30" t="n"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" s="60">
@@ -25023,7 +25257,7 @@
           <t>Bruno Heberth Oliveira Bastos</t>
         </is>
       </c>
-      <c r="F6" s="58" t="n"/>
+      <c r="F6" s="73" t="n"/>
       <c r="G6" s="30" t="n"/>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="60">
@@ -25041,7 +25275,7 @@
           <t>João Pedro Mendes Stama</t>
         </is>
       </c>
-      <c r="F7" s="58" t="n"/>
+      <c r="F7" s="73" t="n"/>
       <c r="G7" s="30" t="n"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" s="60">
@@ -25059,7 +25293,7 @@
           <t>Rafael Ponciano Rodrigues dos Santos</t>
         </is>
       </c>
-      <c r="F8" s="58" t="n"/>
+      <c r="F8" s="73" t="n"/>
       <c r="G8" s="30" t="n"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="60">
@@ -25077,7 +25311,7 @@
           <t>Enzo Chofakian Gagliardi</t>
         </is>
       </c>
-      <c r="F9" s="58" t="n"/>
+      <c r="F9" s="73" t="n"/>
       <c r="G9" s="30" t="n"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="60">
@@ -25095,7 +25329,7 @@
           <t>Enrico Tristão e Mello de Oliveira</t>
         </is>
       </c>
-      <c r="F10" s="58" t="n"/>
+      <c r="F10" s="73" t="n"/>
       <c r="G10" s="30" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="60">
@@ -25113,7 +25347,7 @@
           <t>Eduardo Alves Henrique</t>
         </is>
       </c>
-      <c r="F11" s="58" t="n"/>
+      <c r="F11" s="73" t="n"/>
       <c r="G11" s="30" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="60">
@@ -25131,7 +25365,7 @@
           <t>Leandra Cunha de Souza</t>
         </is>
       </c>
-      <c r="F12" s="58" t="n"/>
+      <c r="F12" s="73" t="n"/>
       <c r="G12" s="30" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="60">
@@ -25149,7 +25383,7 @@
           <t>Vagner Ássimos Gomes Carlos Filho</t>
         </is>
       </c>
-      <c r="F13" s="58" t="n"/>
+      <c r="F13" s="73" t="n"/>
       <c r="G13" s="30" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1" s="60">
@@ -25167,7 +25401,7 @@
           <t>Mariana Nunes Galvão Sant'Anna</t>
         </is>
       </c>
-      <c r="F14" s="58" t="n"/>
+      <c r="F14" s="73" t="n"/>
       <c r="G14" s="30" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="60">
@@ -25190,7 +25424,7 @@
           <t>Ferro</t>
         </is>
       </c>
-      <c r="F15" s="58" t="inlineStr">
+      <c r="F15" s="73" t="inlineStr">
         <is>
           <t>TIrou 2/3 do Gmat, e falou um pouco travado no vídeo, mas foi bem (não é bixo)</t>
         </is>
@@ -25221,7 +25455,7 @@
           <t>Ferro</t>
         </is>
       </c>
-      <c r="F16" s="58" t="inlineStr">
+      <c r="F16" s="73" t="inlineStr">
         <is>
           <t>Tirou 2/3 do Gmat tbm, e fez no final sem energia, cara foi resiliente, falou muito bem no vídeo</t>
         </is>
@@ -25252,7 +25486,7 @@
           <t>Ferro</t>
         </is>
       </c>
-      <c r="F17" s="58" t="inlineStr">
+      <c r="F17" s="73" t="inlineStr">
         <is>
           <t>Foi bem no Gmat tbm, falou muito bem, e falou dos projetos do CCU, fez a pesquisa básica ali, mandou bem</t>
         </is>
@@ -25278,7 +25512,7 @@
           <t>Gustavo Daher Pereira</t>
         </is>
       </c>
-      <c r="F18" s="58" t="n"/>
+      <c r="F18" s="73" t="n"/>
       <c r="G18" s="30" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" s="60">
@@ -25296,7 +25530,7 @@
           <t>Ricardo Augusto Schmitt Filho</t>
         </is>
       </c>
-      <c r="F19" s="58" t="n"/>
+      <c r="F19" s="73" t="n"/>
       <c r="G19" s="30" t="n"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" s="60">
@@ -25314,7 +25548,7 @@
           <t>Matheus Dias Freitas</t>
         </is>
       </c>
-      <c r="F20" s="58" t="n"/>
+      <c r="F20" s="73" t="n"/>
       <c r="G20" s="30" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" s="60">
@@ -25332,7 +25566,7 @@
           <t>Klaus Augusto Santos da Silva</t>
         </is>
       </c>
-      <c r="F21" s="58" t="n"/>
+      <c r="F21" s="73" t="n"/>
       <c r="G21" s="30" t="n"/>
     </row>
     <row r="22" ht="14.25" customHeight="1" s="60">
@@ -25350,7 +25584,7 @@
           <t>Rafael Rodrigues Moreira</t>
         </is>
       </c>
-      <c r="F22" s="58" t="n"/>
+      <c r="F22" s="73" t="n"/>
       <c r="G22" s="30" t="n"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" s="60">
@@ -25368,7 +25602,7 @@
           <t>Caio Augusto Saab</t>
         </is>
       </c>
-      <c r="F23" s="58" t="n"/>
+      <c r="F23" s="73" t="n"/>
       <c r="G23" s="30" t="n"/>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="60">
@@ -25386,7 +25620,7 @@
           <t>José Vitor Dias Tutu</t>
         </is>
       </c>
-      <c r="F24" s="58" t="n"/>
+      <c r="F24" s="73" t="n"/>
       <c r="G24" s="30" t="n"/>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="60">
@@ -25405,7 +25639,7 @@
           <t>Isadora Kluge Dorigan</t>
         </is>
       </c>
-      <c r="F25" s="58" t="n"/>
+      <c r="F25" s="73" t="n"/>
       <c r="G25" s="30" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="60">
@@ -25428,7 +25662,7 @@
           <t>Avaliador 1</t>
         </is>
       </c>
-      <c r="F26" s="58" t="inlineStr">
+      <c r="F26" s="73" t="inlineStr">
         <is>
           <t>Usou IA, dá para ver pelo layout: o deck é todo imagem, sem texto selecionável, o relatório é HTML exportado em PDF e o nome do arquivo vem com "McKinsey Style". A profundidade é igual nas quatro seções e a memória de cálculo aparece só em um bairro. Mesmo assim entregou bem: os oito cenários fecham, inclusive o arredondamento dos bancos da Arena, e a recomendação vem com número no slide 2 e na primeira página. Do lado fraco, o critério do rollout muda no meio, com Noite Alta a 64% na frente da Arena a 83%, não há sensibilidade nem ponto de virada entre os modelos, e o slide 7 mostra seis dos oito cenários. Vale levar para a entrevista e pedir para refazer a conta da Estação Central mexendo no custo de operação dos parceiros. Nota 7,87 com V1 e V2 em branco, 8,74 sobre o que é avaliável.</t>
         </is>
@@ -25444,17 +25678,17 @@
         <f>IF($C27="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Candidato 02 — pasta entregas-candidatos/02 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25477,17 +25711,17 @@
         <f>IF($C28="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Candidato 03 — pasta entregas-candidatos/03 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25510,17 +25744,17 @@
         <f>IF($C29="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Candidato 04 — pasta entregas-candidatos/04 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25543,17 +25777,17 @@
         <f>IF($C30="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>Candidato 05 — pasta entregas-candidatos/05 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25576,17 +25810,17 @@
         <f>IF($C31="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Candidato 06 — pasta entregas-candidatos/06 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25609,17 +25843,17 @@
         <f>IF($C32="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>Candidato 07 — pasta entregas-candidatos/07 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25642,17 +25876,17 @@
         <f>IF($C33="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Candidato 08 — pasta entregas-candidatos/08 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25676,31 +25910,94 @@
         <f>IF($C34="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F34" s="58" t="n"/>
-      <c r="G34" s="30" t="n"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F34" s="73" t="inlineStr">
+        <is>
+          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela, e as duas coisas precisam ser ditas juntas. O que está muito bom: o score multicritério é o método mais transparente do conjunto — pesos publicados, critério de normalização coerente (conferi a interpolação do resultado operacional e fecha), e as oito alternativas comparadas na mesma régua. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder ("Centro lidera a margem, apesar de abrir mão de R$ 3,34 mi"). Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento. O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 mi recorrente, o R$ 142,20 mi de cinco anos e o roadmap bifásico inteiro — que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente; aqui ele é a espinha dorsal e não está declarado em lugar nenhum. Vale registrar que a pasta 07 antecipou exatamente esse risco por escrito na aba de premissas. Segundo ponto, menor: ele lê a "prioridade de rentabilidade anual" como margem, quando o resto da frase no case ("que deverá sustentar a expansão") aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a 2ª melhor opção. Na entrevista eu faria uma pergunta só, e ela vale a etapa toda: o Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2 — por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios de autoria própria. O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três bairros usam a fórmula de divisão — é alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente, o que uma geração uniforme não faz. A planilha tem marcas de trabalho manual: células com "IDEM" como abreviação, "Noite alta" em minúscula na planilha contra "Noite Alta" no deck, e uma observação solta no canto explicando a convenção dos anos 2 a 5. A normalização do score é internamente consistente e foi conferida. E o erro central — tratar custo anual como investimento — é falha de interpretação de quem leu rápido e seguiu adiante, não artefato de geração; texto gerado tende a repetir a premissa do enunciado, não a contrariá-la. Pergunta de propriedade para a entrevista: por que o custo do banco desaparece a partir do Ano 2 se o Anexo E diz que é anual?
+[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr"/>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="60">
       <c r="B35" s="30">
         <f>IF($C35="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F35" s="58" t="n"/>
-      <c r="G35" s="30" t="n"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F35" s="73" t="inlineStr">
+        <is>
+          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica: trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é exatamente o que se espera de consultoria. O argumento por trás também é sólido e ancorado no material — o Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques/dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio. Dois reparos de peso. O primeiro é a agregação: ele soma os quatro bairros para chegar aos R$ 83,09M, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos — restrita à decisão real, a abdicação é R$ 2,76M, não R$ 3,39M. A ideia está certa e a conta está na base errada. O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários — 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede explicitamente. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade. Na entrevista eu faria as duas perguntas que fecham os buracos: se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros? Nota 6,57 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,30.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. O rascunho enviado junto é material de trabalho pessoal — anotações em caixa alta separadas por linhas de "######", com a estrutura do case transcrita e as contas sendo desenvolvidas; ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial ("malícia de próprios comerciantes", as duas perguntas entre aspas sobre o estado alcoólico do cliente) de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se", em vez de afirmar. E a nota de procedência no fim ("nenhum dado adicional foi estimado ou incorporado") é uma afirmação deliberada de método. Pergunta de propriedade para a entrevista: restrita à Estação, quanto custa a sua escolha por armários?
+[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
+      <c r="G35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="60">
       <c r="B36" s="30">
         <f>IF($C36="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F36" s="58" t="n"/>
-      <c r="G36" s="30" t="n"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F36" s="73" t="inlineStr">
+        <is>
+          <t>A análise está certa e a comunicação é que derruba a nota, o que é uma pena porque os dois problemas são baratos de resolver. Os oito cenários fecham todos, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo: cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo — diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito. O que custa caro é o acabamento, e o volume de deslizes é grande: o nome da empresa sai errado na capa ("Bag Huby"), "Armários inteligententes" se repete nas quatro tabelas, a utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12, os 110 mil embarques viram "110 embarques diários" no slide 4, e há texto de template ("BACK TO AGENDA") esquecido no meio do deck. Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede. Na entrevista eu faria duas perguntas: na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31% — qual é a certa? E você colocou a Arena (R$ 14,94M) à frente de Noite Alta (R$ 19,20M) no ranking; qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita. Nota 6,07 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,74.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria, todos vindos do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento, "Central Histórico" trocado. O texto de template "BACK TO AGENDA" esquecido no slide 4 indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição: saída gerada tende a ser ortograficamente limpa e coerente consigo mesma. Pergunta de propriedade para a entrevista: a utilização da Arena é 31% ou 33%, e por que ela vem antes de Noite Alta no ranking?
+[IDENTIFICAÇÃO] Nome na capa e e-mail no último slide: Leandra Cunha de Souza (l304532@dac.unicamp.br). V1/V2 nas linhas 14 (victor 2/2) e 36 (Proc 2/2).</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="60">
       <c r="B37" s="30">
         <f>IF($C37="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F37" s="58" t="n"/>
+      <c r="F37" s="73" t="n"/>
       <c r="G37" s="30" t="n"/>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="60">
@@ -25708,7 +26005,7 @@
         <f>IF($C38="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F38" s="58" t="n"/>
+      <c r="F38" s="73" t="n"/>
       <c r="G38" s="30" t="n"/>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="60">
@@ -25716,7 +26013,7 @@
         <f>IF($C39="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F39" s="58" t="n"/>
+      <c r="F39" s="73" t="n"/>
       <c r="G39" s="30" t="n"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="60">
@@ -25724,7 +26021,7 @@
         <f>IF($C40="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F40" s="58" t="n"/>
+      <c r="F40" s="73" t="n"/>
       <c r="G40" s="30" t="n"/>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="60">
@@ -25732,7 +26029,7 @@
         <f>IF($C41="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F41" s="58" t="n"/>
+      <c r="F41" s="73" t="n"/>
       <c r="G41" s="30" t="n"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="60">
@@ -25740,7 +26037,7 @@
         <f>IF($C42="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F42" s="58" t="n"/>
+      <c r="F42" s="73" t="n"/>
       <c r="G42" s="30" t="n"/>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="60">
@@ -25748,7 +26045,7 @@
         <f>IF($C43="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F43" s="58" t="n"/>
+      <c r="F43" s="73" t="n"/>
       <c r="G43" s="30" t="n"/>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="60">
@@ -25756,7 +26053,7 @@
         <f>IF($C44="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F44" s="58" t="n"/>
+      <c r="F44" s="73" t="n"/>
       <c r="G44" s="30" t="n"/>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="60">
@@ -25764,7 +26061,7 @@
         <f>IF($C45="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F45" s="58" t="n"/>
+      <c r="F45" s="73" t="n"/>
       <c r="G45" s="30" t="n"/>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="60">
@@ -25772,7 +26069,7 @@
         <f>IF($C46="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F46" s="58" t="n"/>
+      <c r="F46" s="73" t="n"/>
       <c r="G46" s="30" t="n"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="60">
@@ -25780,7 +26077,7 @@
         <f>IF($C47="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F47" s="58" t="n"/>
+      <c r="F47" s="73" t="n"/>
       <c r="G47" s="30" t="n"/>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="60">
@@ -25788,7 +26085,7 @@
         <f>IF($C48="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F48" s="58" t="n"/>
+      <c r="F48" s="73" t="n"/>
       <c r="G48" s="30" t="n"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="60">
@@ -25796,7 +26093,7 @@
         <f>IF($C49="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F49" s="58" t="n"/>
+      <c r="F49" s="73" t="n"/>
       <c r="G49" s="30" t="n"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="60">
@@ -25804,7 +26101,7 @@
         <f>IF($C50="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F50" s="58" t="n"/>
+      <c r="F50" s="73" t="n"/>
       <c r="G50" s="30" t="n"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="60">
@@ -25812,7 +26109,7 @@
         <f>IF($C51="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F51" s="58" t="n"/>
+      <c r="F51" s="73" t="n"/>
       <c r="G51" s="30" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="60">
@@ -25820,7 +26117,7 @@
         <f>IF($C52="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F52" s="58" t="n"/>
+      <c r="F52" s="73" t="n"/>
       <c r="G52" s="30" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="60">
@@ -25828,7 +26125,7 @@
         <f>IF($C53="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F53" s="58" t="n"/>
+      <c r="F53" s="73" t="n"/>
       <c r="G53" s="30" t="n"/>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="60">
@@ -25836,7 +26133,7 @@
         <f>IF($C54="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F54" s="58" t="n"/>
+      <c r="F54" s="73" t="n"/>
       <c r="G54" s="30" t="n"/>
     </row>
     <row r="55" ht="14.25" customHeight="1" s="60">
@@ -25844,7 +26141,7 @@
         <f>IF($C55="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F55" s="58" t="n"/>
+      <c r="F55" s="73" t="n"/>
       <c r="G55" s="30" t="n"/>
     </row>
     <row r="56" ht="14.25" customHeight="1" s="60">
@@ -25852,7 +26149,7 @@
         <f>IF($C56="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F56" s="58" t="n"/>
+      <c r="F56" s="73" t="n"/>
       <c r="G56" s="30" t="n"/>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="60">
@@ -25860,7 +26157,7 @@
         <f>IF($C57="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F57" s="58" t="n"/>
+      <c r="F57" s="73" t="n"/>
       <c r="G57" s="30" t="n"/>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="60">
@@ -25868,7 +26165,7 @@
         <f>IF($C58="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F58" s="58" t="n"/>
+      <c r="F58" s="73" t="n"/>
       <c r="G58" s="30" t="n"/>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="60">
@@ -25876,7 +26173,7 @@
         <f>IF($C59="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F59" s="58" t="n"/>
+      <c r="F59" s="73" t="n"/>
       <c r="G59" s="30" t="n"/>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="60">
@@ -25884,7 +26181,7 @@
         <f>IF($C60="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F60" s="58" t="n"/>
+      <c r="F60" s="73" t="n"/>
       <c r="G60" s="30" t="n"/>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="60">
@@ -25892,7 +26189,7 @@
         <f>IF($C61="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F61" s="58" t="n"/>
+      <c r="F61" s="73" t="n"/>
       <c r="G61" s="30" t="n"/>
     </row>
     <row r="62" ht="14.25" customHeight="1" s="60">
@@ -25900,7 +26197,7 @@
         <f>IF($C62="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F62" s="58" t="n"/>
+      <c r="F62" s="73" t="n"/>
       <c r="G62" s="30" t="n"/>
     </row>
     <row r="63" ht="14.25" customHeight="1" s="60">
@@ -25908,7 +26205,7 @@
         <f>IF($C63="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F63" s="58" t="n"/>
+      <c r="F63" s="73" t="n"/>
       <c r="G63" s="30" t="n"/>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="60">
@@ -25916,7 +26213,7 @@
         <f>IF($C64="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F64" s="58" t="n"/>
+      <c r="F64" s="73" t="n"/>
       <c r="G64" s="30" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="60">
@@ -25924,7 +26221,7 @@
         <f>IF($C65="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F65" s="58" t="n"/>
+      <c r="F65" s="73" t="n"/>
       <c r="G65" s="30" t="n"/>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="60">
@@ -25932,7 +26229,7 @@
         <f>IF($C66="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F66" s="58" t="n"/>
+      <c r="F66" s="73" t="n"/>
       <c r="G66" s="30" t="n"/>
     </row>
     <row r="67" ht="14.25" customHeight="1" s="60">
@@ -25940,7 +26237,7 @@
         <f>IF($C67="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F67" s="58" t="n"/>
+      <c r="F67" s="73" t="n"/>
       <c r="G67" s="30" t="n"/>
     </row>
     <row r="68" ht="14.25" customHeight="1" s="60">
@@ -25948,7 +26245,7 @@
         <f>IF($C68="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F68" s="58" t="n"/>
+      <c r="F68" s="73" t="n"/>
       <c r="G68" s="30" t="n"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" s="60">
@@ -25956,7 +26253,7 @@
         <f>IF($C69="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F69" s="58" t="n"/>
+      <c r="F69" s="73" t="n"/>
       <c r="G69" s="30" t="n"/>
     </row>
     <row r="70" ht="14.25" customHeight="1" s="60">
@@ -25964,7 +26261,7 @@
         <f>IF($C70="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F70" s="58" t="n"/>
+      <c r="F70" s="73" t="n"/>
       <c r="G70" s="30" t="n"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="60">
@@ -25972,7 +26269,7 @@
         <f>IF($C71="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F71" s="58" t="n"/>
+      <c r="F71" s="73" t="n"/>
       <c r="G71" s="30" t="n"/>
     </row>
     <row r="72" ht="14.25" customHeight="1" s="60">
@@ -25980,7 +26277,7 @@
         <f>IF($C72="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F72" s="58" t="n"/>
+      <c r="F72" s="73" t="n"/>
       <c r="G72" s="30" t="n"/>
     </row>
     <row r="73" ht="14.25" customHeight="1" s="60">
@@ -25988,7 +26285,7 @@
         <f>IF($C73="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F73" s="58" t="n"/>
+      <c r="F73" s="73" t="n"/>
       <c r="G73" s="30" t="n"/>
     </row>
     <row r="74" ht="14.25" customHeight="1" s="60">
@@ -25996,7 +26293,7 @@
         <f>IF($C74="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F74" s="58" t="n"/>
+      <c r="F74" s="73" t="n"/>
       <c r="G74" s="30" t="n"/>
     </row>
     <row r="75" ht="14.25" customHeight="1" s="60">
@@ -26004,7 +26301,7 @@
         <f>IF($C75="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F75" s="58" t="n"/>
+      <c r="F75" s="73" t="n"/>
       <c r="G75" s="30" t="n"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" s="60">
@@ -26012,7 +26309,7 @@
         <f>IF($C76="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F76" s="58" t="n"/>
+      <c r="F76" s="73" t="n"/>
       <c r="G76" s="30" t="n"/>
     </row>
     <row r="77" ht="14.25" customHeight="1" s="60">
@@ -26020,7 +26317,7 @@
         <f>IF($C77="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F77" s="58" t="n"/>
+      <c r="F77" s="73" t="n"/>
       <c r="G77" s="30" t="n"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" s="60">
@@ -26028,7 +26325,7 @@
         <f>IF($C78="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F78" s="58" t="n"/>
+      <c r="F78" s="73" t="n"/>
       <c r="G78" s="30" t="n"/>
     </row>
     <row r="79" ht="14.25" customHeight="1" s="60">
@@ -26036,7 +26333,7 @@
         <f>IF($C79="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F79" s="58" t="n"/>
+      <c r="F79" s="73" t="n"/>
       <c r="G79" s="30" t="n"/>
     </row>
     <row r="80" ht="14.25" customHeight="1" s="60">
@@ -26044,7 +26341,7 @@
         <f>IF($C80="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F80" s="58" t="n"/>
+      <c r="F80" s="73" t="n"/>
       <c r="G80" s="30" t="n"/>
     </row>
     <row r="81" ht="14.25" customHeight="1" s="60">
@@ -26052,7 +26349,7 @@
         <f>IF($C81="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F81" s="58" t="n"/>
+      <c r="F81" s="73" t="n"/>
       <c r="G81" s="30" t="n"/>
     </row>
     <row r="82" ht="14.25" customHeight="1" s="60">
@@ -26060,7 +26357,7 @@
         <f>IF($C82="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F82" s="58" t="n"/>
+      <c r="F82" s="73" t="n"/>
       <c r="G82" s="30" t="n"/>
     </row>
     <row r="83" ht="14.25" customHeight="1" s="60">
@@ -26068,7 +26365,7 @@
         <f>IF($C83="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F83" s="58" t="n"/>
+      <c r="F83" s="73" t="n"/>
       <c r="G83" s="30" t="n"/>
     </row>
     <row r="84" ht="14.25" customHeight="1" s="60">
@@ -26076,7 +26373,7 @@
         <f>IF($C84="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F84" s="58" t="n"/>
+      <c r="F84" s="73" t="n"/>
       <c r="G84" s="30" t="n"/>
     </row>
     <row r="85" ht="14.25" customHeight="1" s="60">
@@ -26084,7 +26381,7 @@
         <f>IF($C85="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F85" s="58" t="n"/>
+      <c r="F85" s="73" t="n"/>
       <c r="G85" s="30" t="n"/>
     </row>
     <row r="86" ht="14.25" customHeight="1" s="60">
@@ -26092,7 +26389,7 @@
         <f>IF($C86="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F86" s="58" t="n"/>
+      <c r="F86" s="73" t="n"/>
       <c r="G86" s="30" t="n"/>
     </row>
     <row r="87" ht="14.25" customHeight="1" s="60">
@@ -26100,7 +26397,7 @@
         <f>IF($C87="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F87" s="58" t="n"/>
+      <c r="F87" s="73" t="n"/>
       <c r="G87" s="30" t="n"/>
     </row>
     <row r="88" ht="14.25" customHeight="1" s="60">
@@ -26108,7 +26405,7 @@
         <f>IF($C88="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F88" s="58" t="n"/>
+      <c r="F88" s="73" t="n"/>
       <c r="G88" s="30" t="n"/>
     </row>
     <row r="89" ht="14.25" customHeight="1" s="60">
@@ -26116,7 +26413,7 @@
         <f>IF($C89="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F89" s="58" t="n"/>
+      <c r="F89" s="73" t="n"/>
       <c r="G89" s="30" t="n"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" s="60">
@@ -26124,7 +26421,7 @@
         <f>IF($C90="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F90" s="58" t="n"/>
+      <c r="F90" s="73" t="n"/>
       <c r="G90" s="30" t="n"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" s="60">
@@ -26132,7 +26429,7 @@
         <f>IF($C91="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F91" s="58" t="n"/>
+      <c r="F91" s="73" t="n"/>
       <c r="G91" s="30" t="n"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" s="60">
@@ -26140,7 +26437,7 @@
         <f>IF($C92="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F92" s="58" t="n"/>
+      <c r="F92" s="73" t="n"/>
       <c r="G92" s="30" t="n"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" s="60">
@@ -26148,7 +26445,7 @@
         <f>IF($C93="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F93" s="58" t="n"/>
+      <c r="F93" s="73" t="n"/>
       <c r="G93" s="30" t="n"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" s="60">
@@ -26156,7 +26453,7 @@
         <f>IF($C94="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F94" s="58" t="n"/>
+      <c r="F94" s="73" t="n"/>
       <c r="G94" s="30" t="n"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" s="60">
@@ -26164,7 +26461,7 @@
         <f>IF($C95="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F95" s="58" t="n"/>
+      <c r="F95" s="73" t="n"/>
       <c r="G95" s="30" t="n"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" s="60">
@@ -26172,7 +26469,7 @@
         <f>IF($C96="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F96" s="58" t="n"/>
+      <c r="F96" s="73" t="n"/>
       <c r="G96" s="30" t="n"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" s="60">
@@ -26180,7 +26477,7 @@
         <f>IF($C97="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F97" s="58" t="n"/>
+      <c r="F97" s="73" t="n"/>
       <c r="G97" s="30" t="n"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" s="60">
@@ -26188,7 +26485,7 @@
         <f>IF($C98="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F98" s="58" t="n"/>
+      <c r="F98" s="73" t="n"/>
       <c r="G98" s="30" t="n"/>
     </row>
     <row r="99" ht="14.25" customHeight="1" s="60">
@@ -26196,7 +26493,7 @@
         <f>IF($C99="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F99" s="58" t="n"/>
+      <c r="F99" s="73" t="n"/>
       <c r="G99" s="30" t="n"/>
     </row>
     <row r="100" ht="14.25" customHeight="1" s="60">
@@ -26204,7 +26501,7 @@
         <f>IF($C100="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F100" s="58" t="n"/>
+      <c r="F100" s="73" t="n"/>
       <c r="G100" s="30" t="n"/>
     </row>
     <row r="101" ht="14.25" customHeight="1" s="60">
@@ -26212,7 +26509,7 @@
         <f>IF($C101="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F101" s="58" t="n"/>
+      <c r="F101" s="73" t="n"/>
       <c r="G101" s="30" t="n"/>
     </row>
     <row r="102" ht="14.25" customHeight="1" s="60">
@@ -26220,7 +26517,7 @@
         <f>IF($C102="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F102" s="58" t="n"/>
+      <c r="F102" s="73" t="n"/>
       <c r="G102" s="30" t="n"/>
     </row>
     <row r="103" ht="14.25" customHeight="1" s="60">
@@ -26228,7 +26525,7 @@
         <f>IF($C103="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F103" s="58" t="n"/>
+      <c r="F103" s="73" t="n"/>
       <c r="G103" s="30" t="n"/>
     </row>
     <row r="104" ht="14.25" customHeight="1" s="60">
@@ -26236,7 +26533,7 @@
         <f>IF($C104="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F104" s="58" t="n"/>
+      <c r="F104" s="73" t="n"/>
       <c r="G104" s="30" t="n"/>
     </row>
     <row r="105" ht="14.25" customHeight="1" s="60">
@@ -26244,7 +26541,7 @@
         <f>IF($C105="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F105" s="58" t="n"/>
+      <c r="F105" s="73" t="n"/>
       <c r="G105" s="30" t="n"/>
     </row>
     <row r="106" ht="14.25" customHeight="1" s="60">
@@ -26252,7 +26549,7 @@
         <f>IF($C106="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F106" s="58" t="n"/>
+      <c r="F106" s="73" t="n"/>
       <c r="G106" s="30" t="n"/>
     </row>
     <row r="107" ht="14.25" customHeight="1" s="60">
@@ -26260,7 +26557,7 @@
         <f>IF($C107="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F107" s="58" t="n"/>
+      <c r="F107" s="73" t="n"/>
       <c r="G107" s="30" t="n"/>
     </row>
     <row r="108" ht="14.25" customHeight="1" s="60">
@@ -26268,7 +26565,7 @@
         <f>IF($C108="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F108" s="58" t="n"/>
+      <c r="F108" s="73" t="n"/>
       <c r="G108" s="30" t="n"/>
     </row>
     <row r="109" ht="14.25" customHeight="1" s="60">
@@ -26276,7 +26573,7 @@
         <f>IF($C109="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F109" s="58" t="n"/>
+      <c r="F109" s="73" t="n"/>
       <c r="G109" s="30" t="n"/>
     </row>
     <row r="110" ht="14.25" customHeight="1" s="60">
@@ -26284,7 +26581,7 @@
         <f>IF($C110="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F110" s="58" t="n"/>
+      <c r="F110" s="73" t="n"/>
       <c r="G110" s="30" t="n"/>
     </row>
     <row r="111" ht="14.25" customHeight="1" s="60">
@@ -26292,7 +26589,7 @@
         <f>IF($C111="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F111" s="58" t="n"/>
+      <c r="F111" s="73" t="n"/>
       <c r="G111" s="30" t="n"/>
     </row>
     <row r="112" ht="14.25" customHeight="1" s="60">
@@ -26300,7 +26597,7 @@
         <f>IF($C112="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F112" s="58" t="n"/>
+      <c r="F112" s="73" t="n"/>
       <c r="G112" s="30" t="n"/>
     </row>
     <row r="113" ht="14.25" customHeight="1" s="60">
@@ -26308,7 +26605,7 @@
         <f>IF($C113="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F113" s="58" t="n"/>
+      <c r="F113" s="73" t="n"/>
       <c r="G113" s="30" t="n"/>
     </row>
     <row r="114" ht="14.25" customHeight="1" s="60">
@@ -26316,7 +26613,7 @@
         <f>IF($C114="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F114" s="58" t="n"/>
+      <c r="F114" s="73" t="n"/>
       <c r="G114" s="30" t="n"/>
     </row>
     <row r="115" ht="14.25" customHeight="1" s="60">
@@ -26324,7 +26621,7 @@
         <f>IF($C115="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F115" s="58" t="n"/>
+      <c r="F115" s="73" t="n"/>
       <c r="G115" s="30" t="n"/>
     </row>
     <row r="116" ht="14.25" customHeight="1" s="60">
@@ -26332,7 +26629,7 @@
         <f>IF($C116="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F116" s="58" t="n"/>
+      <c r="F116" s="73" t="n"/>
       <c r="G116" s="30" t="n"/>
     </row>
     <row r="117" ht="14.25" customHeight="1" s="60">
@@ -26340,7 +26637,7 @@
         <f>IF($C117="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F117" s="58" t="n"/>
+      <c r="F117" s="73" t="n"/>
       <c r="G117" s="30" t="n"/>
     </row>
     <row r="118" ht="14.25" customHeight="1" s="60">
@@ -26348,7 +26645,7 @@
         <f>IF($C118="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F118" s="58" t="n"/>
+      <c r="F118" s="73" t="n"/>
       <c r="G118" s="30" t="n"/>
     </row>
     <row r="119" ht="14.25" customHeight="1" s="60">
@@ -26356,7 +26653,7 @@
         <f>IF($C119="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F119" s="58" t="n"/>
+      <c r="F119" s="73" t="n"/>
       <c r="G119" s="30" t="n"/>
     </row>
     <row r="120" ht="14.25" customHeight="1" s="60">
@@ -26364,7 +26661,7 @@
         <f>IF($C120="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F120" s="58" t="n"/>
+      <c r="F120" s="73" t="n"/>
       <c r="G120" s="30" t="n"/>
     </row>
     <row r="121" ht="14.25" customHeight="1" s="60">
@@ -26372,7 +26669,7 @@
         <f>IF($C121="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F121" s="58" t="n"/>
+      <c r="F121" s="73" t="n"/>
       <c r="G121" s="30" t="n"/>
     </row>
     <row r="122" ht="14.25" customHeight="1" s="60">
@@ -26380,7 +26677,7 @@
         <f>IF($C122="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F122" s="58" t="n"/>
+      <c r="F122" s="73" t="n"/>
       <c r="G122" s="30" t="n"/>
     </row>
     <row r="123" ht="14.25" customHeight="1" s="60">
@@ -26388,7 +26685,7 @@
         <f>IF($C123="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F123" s="58" t="n"/>
+      <c r="F123" s="73" t="n"/>
       <c r="G123" s="30" t="n"/>
     </row>
     <row r="124" ht="14.25" customHeight="1" s="60">
@@ -26396,7 +26693,7 @@
         <f>IF($C124="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F124" s="58" t="n"/>
+      <c r="F124" s="73" t="n"/>
       <c r="G124" s="30" t="n"/>
     </row>
     <row r="125" ht="14.25" customHeight="1" s="60">
@@ -26404,7 +26701,7 @@
         <f>IF($C125="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F125" s="58" t="n"/>
+      <c r="F125" s="73" t="n"/>
       <c r="G125" s="30" t="n"/>
     </row>
     <row r="126" ht="14.25" customHeight="1" s="60">
@@ -26412,7 +26709,7 @@
         <f>IF($C126="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F126" s="58" t="n"/>
+      <c r="F126" s="73" t="n"/>
       <c r="G126" s="30" t="n"/>
     </row>
     <row r="127" ht="14.25" customHeight="1" s="60">
@@ -26420,7 +26717,7 @@
         <f>IF($C127="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F127" s="58" t="n"/>
+      <c r="F127" s="73" t="n"/>
       <c r="G127" s="30" t="n"/>
     </row>
     <row r="128" ht="14.25" customHeight="1" s="60">
@@ -26428,7 +26725,7 @@
         <f>IF($C128="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F128" s="58" t="n"/>
+      <c r="F128" s="73" t="n"/>
       <c r="G128" s="30" t="n"/>
     </row>
     <row r="129" ht="14.25" customHeight="1" s="60">
@@ -26436,7 +26733,7 @@
         <f>IF($C129="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F129" s="58" t="n"/>
+      <c r="F129" s="73" t="n"/>
       <c r="G129" s="30" t="n"/>
     </row>
     <row r="130" ht="14.25" customHeight="1" s="60">
@@ -26444,7 +26741,7 @@
         <f>IF($C130="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F130" s="58" t="n"/>
+      <c r="F130" s="73" t="n"/>
       <c r="G130" s="30" t="n"/>
     </row>
     <row r="131" ht="14.25" customHeight="1" s="60">
@@ -26452,7 +26749,7 @@
         <f>IF($C131="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F131" s="58" t="n"/>
+      <c r="F131" s="73" t="n"/>
       <c r="G131" s="30" t="n"/>
     </row>
     <row r="132" ht="14.25" customHeight="1" s="60">
@@ -26460,7 +26757,7 @@
         <f>IF($C132="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F132" s="58" t="n"/>
+      <c r="F132" s="73" t="n"/>
       <c r="G132" s="30" t="n"/>
     </row>
     <row r="133" ht="14.25" customHeight="1" s="60">
@@ -26468,7 +26765,7 @@
         <f>IF($C133="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F133" s="58" t="n"/>
+      <c r="F133" s="73" t="n"/>
       <c r="G133" s="30" t="n"/>
     </row>
     <row r="134" ht="14.25" customHeight="1" s="60">
@@ -26476,7 +26773,7 @@
         <f>IF($C134="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F134" s="58" t="n"/>
+      <c r="F134" s="73" t="n"/>
       <c r="G134" s="30" t="n"/>
     </row>
     <row r="135" ht="14.25" customHeight="1" s="60">
@@ -26484,7 +26781,7 @@
         <f>IF($C135="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F135" s="58" t="n"/>
+      <c r="F135" s="73" t="n"/>
       <c r="G135" s="30" t="n"/>
     </row>
     <row r="136" ht="14.25" customHeight="1" s="60">
@@ -26492,7 +26789,7 @@
         <f>IF($C136="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F136" s="58" t="n"/>
+      <c r="F136" s="73" t="n"/>
       <c r="G136" s="30" t="n"/>
     </row>
     <row r="137" ht="14.25" customHeight="1" s="60">
@@ -26500,7 +26797,7 @@
         <f>IF($C137="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F137" s="58" t="n"/>
+      <c r="F137" s="73" t="n"/>
       <c r="G137" s="30" t="n"/>
     </row>
     <row r="138" ht="14.25" customHeight="1" s="60">
@@ -26508,7 +26805,7 @@
         <f>IF($C138="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F138" s="58" t="n"/>
+      <c r="F138" s="73" t="n"/>
       <c r="G138" s="30" t="n"/>
     </row>
     <row r="139" ht="14.25" customHeight="1" s="60">
@@ -26516,7 +26813,7 @@
         <f>IF($C139="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F139" s="58" t="n"/>
+      <c r="F139" s="73" t="n"/>
       <c r="G139" s="30" t="n"/>
     </row>
     <row r="140" ht="14.25" customHeight="1" s="60">
@@ -26524,7 +26821,7 @@
         <f>IF($C140="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F140" s="58" t="n"/>
+      <c r="F140" s="73" t="n"/>
       <c r="G140" s="30" t="n"/>
     </row>
     <row r="141" ht="14.25" customHeight="1" s="60">
@@ -26532,7 +26829,7 @@
         <f>IF($C141="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F141" s="58" t="n"/>
+      <c r="F141" s="73" t="n"/>
       <c r="G141" s="30" t="n"/>
     </row>
     <row r="142" ht="14.25" customHeight="1" s="60">
@@ -26540,7 +26837,7 @@
         <f>IF($C142="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F142" s="58" t="n"/>
+      <c r="F142" s="73" t="n"/>
       <c r="G142" s="30" t="n"/>
     </row>
     <row r="143" ht="14.25" customHeight="1" s="60">
@@ -26548,7 +26845,7 @@
         <f>IF($C143="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F143" s="58" t="n"/>
+      <c r="F143" s="73" t="n"/>
       <c r="G143" s="30" t="n"/>
     </row>
     <row r="144" ht="14.25" customHeight="1" s="60">
@@ -26556,7 +26853,7 @@
         <f>IF($C144="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F144" s="58" t="n"/>
+      <c r="F144" s="73" t="n"/>
       <c r="G144" s="30" t="n"/>
     </row>
     <row r="145" ht="14.25" customHeight="1" s="60">
@@ -26564,7 +26861,7 @@
         <f>IF($C145="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F145" s="58" t="n"/>
+      <c r="F145" s="73" t="n"/>
       <c r="G145" s="30" t="n"/>
     </row>
     <row r="146" ht="14.25" customHeight="1" s="60">
@@ -26572,7 +26869,7 @@
         <f>IF($C146="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F146" s="58" t="n"/>
+      <c r="F146" s="73" t="n"/>
       <c r="G146" s="30" t="n"/>
     </row>
     <row r="147" ht="14.25" customHeight="1" s="60">
@@ -26580,7 +26877,7 @@
         <f>IF($C147="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F147" s="58" t="n"/>
+      <c r="F147" s="73" t="n"/>
       <c r="G147" s="30" t="n"/>
     </row>
     <row r="148" ht="14.25" customHeight="1" s="60">
@@ -26588,7 +26885,7 @@
         <f>IF($C148="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F148" s="58" t="n"/>
+      <c r="F148" s="73" t="n"/>
       <c r="G148" s="30" t="n"/>
     </row>
     <row r="149" ht="14.25" customHeight="1" s="60">
@@ -26596,7 +26893,7 @@
         <f>IF($C149="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F149" s="58" t="n"/>
+      <c r="F149" s="73" t="n"/>
       <c r="G149" s="30" t="n"/>
     </row>
     <row r="150" ht="14.25" customHeight="1" s="60">
@@ -26604,7 +26901,7 @@
         <f>IF($C150="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F150" s="58" t="n"/>
+      <c r="F150" s="73" t="n"/>
       <c r="G150" s="30" t="n"/>
     </row>
     <row r="151" ht="14.25" customHeight="1" s="60">
@@ -26612,7 +26909,7 @@
         <f>IF($C151="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F151" s="58" t="n"/>
+      <c r="F151" s="73" t="n"/>
       <c r="G151" s="30" t="n"/>
     </row>
     <row r="152" ht="14.25" customHeight="1" s="60">
@@ -26620,7 +26917,7 @@
         <f>IF($C152="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F152" s="58" t="n"/>
+      <c r="F152" s="73" t="n"/>
       <c r="G152" s="30" t="n"/>
     </row>
     <row r="153" ht="14.25" customHeight="1" s="60">
@@ -26628,7 +26925,7 @@
         <f>IF($C153="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F153" s="58" t="n"/>
+      <c r="F153" s="73" t="n"/>
       <c r="G153" s="30" t="n"/>
     </row>
     <row r="154" ht="14.25" customHeight="1" s="60">
@@ -26636,7 +26933,7 @@
         <f>IF($C154="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F154" s="58" t="n"/>
+      <c r="F154" s="73" t="n"/>
       <c r="G154" s="30" t="n"/>
     </row>
     <row r="155" ht="14.25" customHeight="1" s="60">
@@ -26644,7 +26941,7 @@
         <f>IF($C155="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F155" s="58" t="n"/>
+      <c r="F155" s="73" t="n"/>
       <c r="G155" s="30" t="n"/>
     </row>
     <row r="156" ht="14.25" customHeight="1" s="60">
@@ -26652,7 +26949,7 @@
         <f>IF($C156="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F156" s="58" t="n"/>
+      <c r="F156" s="73" t="n"/>
       <c r="G156" s="30" t="n"/>
     </row>
     <row r="157" ht="14.25" customHeight="1" s="60">
@@ -26660,7 +26957,7 @@
         <f>IF($C157="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F157" s="58" t="n"/>
+      <c r="F157" s="73" t="n"/>
       <c r="G157" s="30" t="n"/>
     </row>
     <row r="158" ht="14.25" customHeight="1" s="60">
@@ -26668,7 +26965,7 @@
         <f>IF($C158="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F158" s="58" t="n"/>
+      <c r="F158" s="73" t="n"/>
       <c r="G158" s="30" t="n"/>
     </row>
     <row r="159" ht="14.25" customHeight="1" s="60">
@@ -26676,7 +26973,7 @@
         <f>IF($C159="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F159" s="58" t="n"/>
+      <c r="F159" s="73" t="n"/>
       <c r="G159" s="30" t="n"/>
     </row>
     <row r="160" ht="14.25" customHeight="1" s="60">
@@ -26684,7 +26981,7 @@
         <f>IF($C160="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F160" s="58" t="n"/>
+      <c r="F160" s="73" t="n"/>
       <c r="G160" s="30" t="n"/>
     </row>
     <row r="161" ht="14.25" customHeight="1" s="60">
@@ -26692,7 +26989,7 @@
         <f>IF($C161="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F161" s="58" t="n"/>
+      <c r="F161" s="73" t="n"/>
       <c r="G161" s="30" t="n"/>
     </row>
     <row r="162" ht="14.25" customHeight="1" s="60">
@@ -26700,7 +26997,7 @@
         <f>IF($C162="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F162" s="58" t="n"/>
+      <c r="F162" s="73" t="n"/>
       <c r="G162" s="30" t="n"/>
     </row>
     <row r="163" ht="14.25" customHeight="1" s="60">
@@ -26708,7 +27005,7 @@
         <f>IF($C163="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F163" s="58" t="n"/>
+      <c r="F163" s="73" t="n"/>
       <c r="G163" s="30" t="n"/>
     </row>
     <row r="164" ht="14.25" customHeight="1" s="60">
@@ -26716,7 +27013,7 @@
         <f>IF($C164="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F164" s="58" t="n"/>
+      <c r="F164" s="73" t="n"/>
       <c r="G164" s="30" t="n"/>
     </row>
     <row r="165" ht="14.25" customHeight="1" s="60">
@@ -26724,7 +27021,7 @@
         <f>IF($C165="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F165" s="58" t="n"/>
+      <c r="F165" s="73" t="n"/>
       <c r="G165" s="30" t="n"/>
     </row>
     <row r="166" ht="14.25" customHeight="1" s="60">
@@ -26732,7 +27029,7 @@
         <f>IF($C166="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F166" s="58" t="n"/>
+      <c r="F166" s="73" t="n"/>
       <c r="G166" s="30" t="n"/>
     </row>
     <row r="167" ht="14.25" customHeight="1" s="60">
@@ -26740,7 +27037,7 @@
         <f>IF($C167="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F167" s="58" t="n"/>
+      <c r="F167" s="73" t="n"/>
       <c r="G167" s="30" t="n"/>
     </row>
     <row r="168" ht="14.25" customHeight="1" s="60">
@@ -26748,7 +27045,7 @@
         <f>IF($C168="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F168" s="58" t="n"/>
+      <c r="F168" s="73" t="n"/>
       <c r="G168" s="30" t="n"/>
     </row>
     <row r="169" ht="14.25" customHeight="1" s="60">
@@ -26756,7 +27053,7 @@
         <f>IF($C169="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F169" s="58" t="n"/>
+      <c r="F169" s="73" t="n"/>
       <c r="G169" s="30" t="n"/>
     </row>
     <row r="170" ht="14.25" customHeight="1" s="60">
@@ -26764,7 +27061,7 @@
         <f>IF($C170="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F170" s="58" t="n"/>
+      <c r="F170" s="73" t="n"/>
       <c r="G170" s="30" t="n"/>
     </row>
     <row r="171" ht="14.25" customHeight="1" s="60">
@@ -26772,7 +27069,7 @@
         <f>IF($C171="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F171" s="58" t="n"/>
+      <c r="F171" s="73" t="n"/>
       <c r="G171" s="30" t="n"/>
     </row>
     <row r="172" ht="14.25" customHeight="1" s="60">
@@ -26780,7 +27077,7 @@
         <f>IF($C172="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F172" s="58" t="n"/>
+      <c r="F172" s="73" t="n"/>
       <c r="G172" s="30" t="n"/>
     </row>
     <row r="173" ht="14.25" customHeight="1" s="60">
@@ -26788,7 +27085,7 @@
         <f>IF($C173="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F173" s="58" t="n"/>
+      <c r="F173" s="73" t="n"/>
       <c r="G173" s="30" t="n"/>
     </row>
     <row r="174" ht="14.25" customHeight="1" s="60">
@@ -26796,7 +27093,7 @@
         <f>IF($C174="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F174" s="58" t="n"/>
+      <c r="F174" s="73" t="n"/>
       <c r="G174" s="30" t="n"/>
     </row>
     <row r="175" ht="14.25" customHeight="1" s="60">
@@ -26804,7 +27101,7 @@
         <f>IF($C175="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F175" s="58" t="n"/>
+      <c r="F175" s="73" t="n"/>
       <c r="G175" s="30" t="n"/>
     </row>
     <row r="176" ht="14.25" customHeight="1" s="60">
@@ -26812,7 +27109,7 @@
         <f>IF($C176="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F176" s="58" t="n"/>
+      <c r="F176" s="73" t="n"/>
       <c r="G176" s="30" t="n"/>
     </row>
     <row r="177" ht="14.25" customHeight="1" s="60">
@@ -26820,7 +27117,7 @@
         <f>IF($C177="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F177" s="58" t="n"/>
+      <c r="F177" s="73" t="n"/>
       <c r="G177" s="30" t="n"/>
     </row>
     <row r="178" ht="14.25" customHeight="1" s="60">
@@ -26828,7 +27125,7 @@
         <f>IF($C178="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F178" s="58" t="n"/>
+      <c r="F178" s="73" t="n"/>
       <c r="G178" s="30" t="n"/>
     </row>
     <row r="179" ht="14.25" customHeight="1" s="60">
@@ -26836,7 +27133,7 @@
         <f>IF($C179="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F179" s="58" t="n"/>
+      <c r="F179" s="73" t="n"/>
       <c r="G179" s="30" t="n"/>
     </row>
     <row r="180" ht="14.25" customHeight="1" s="60">
@@ -26844,7 +27141,7 @@
         <f>IF($C180="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F180" s="58" t="n"/>
+      <c r="F180" s="73" t="n"/>
       <c r="G180" s="30" t="n"/>
     </row>
     <row r="181" ht="14.25" customHeight="1" s="60">
@@ -26852,7 +27149,7 @@
         <f>IF($C181="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F181" s="58" t="n"/>
+      <c r="F181" s="73" t="n"/>
       <c r="G181" s="30" t="n"/>
     </row>
     <row r="182" ht="14.25" customHeight="1" s="60">
@@ -26860,7 +27157,7 @@
         <f>IF($C182="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F182" s="58" t="n"/>
+      <c r="F182" s="73" t="n"/>
       <c r="G182" s="30" t="n"/>
     </row>
     <row r="183" ht="14.25" customHeight="1" s="60">
@@ -26868,7 +27165,7 @@
         <f>IF($C183="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F183" s="58" t="n"/>
+      <c r="F183" s="73" t="n"/>
       <c r="G183" s="30" t="n"/>
     </row>
     <row r="184" ht="14.25" customHeight="1" s="60">
@@ -26876,7 +27173,7 @@
         <f>IF($C184="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F184" s="58" t="n"/>
+      <c r="F184" s="73" t="n"/>
       <c r="G184" s="30" t="n"/>
     </row>
     <row r="185" ht="14.25" customHeight="1" s="60">
@@ -26884,7 +27181,7 @@
         <f>IF($C185="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F185" s="58" t="n"/>
+      <c r="F185" s="73" t="n"/>
       <c r="G185" s="30" t="n"/>
     </row>
     <row r="186" ht="14.25" customHeight="1" s="60">
@@ -26892,7 +27189,7 @@
         <f>IF($C186="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F186" s="58" t="n"/>
+      <c r="F186" s="73" t="n"/>
       <c r="G186" s="30" t="n"/>
     </row>
     <row r="187" ht="14.25" customHeight="1" s="60">
@@ -26900,7 +27197,7 @@
         <f>IF($C187="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F187" s="58" t="n"/>
+      <c r="F187" s="73" t="n"/>
       <c r="G187" s="30" t="n"/>
     </row>
     <row r="188" ht="14.25" customHeight="1" s="60">
@@ -26908,7 +27205,7 @@
         <f>IF($C188="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F188" s="58" t="n"/>
+      <c r="F188" s="73" t="n"/>
       <c r="G188" s="30" t="n"/>
     </row>
     <row r="189" ht="14.25" customHeight="1" s="60">
@@ -26916,7 +27213,7 @@
         <f>IF($C189="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F189" s="58" t="n"/>
+      <c r="F189" s="73" t="n"/>
       <c r="G189" s="30" t="n"/>
     </row>
     <row r="190" ht="14.25" customHeight="1" s="60">
@@ -26924,7 +27221,7 @@
         <f>IF($C190="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F190" s="58" t="n"/>
+      <c r="F190" s="73" t="n"/>
       <c r="G190" s="30" t="n"/>
     </row>
     <row r="191" ht="14.25" customHeight="1" s="60">
@@ -26932,7 +27229,7 @@
         <f>IF($C191="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F191" s="58" t="n"/>
+      <c r="F191" s="73" t="n"/>
       <c r="G191" s="30" t="n"/>
     </row>
     <row r="192" ht="14.25" customHeight="1" s="60">
@@ -26940,7 +27237,7 @@
         <f>IF($C192="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F192" s="58" t="n"/>
+      <c r="F192" s="73" t="n"/>
       <c r="G192" s="30" t="n"/>
     </row>
     <row r="193" ht="14.25" customHeight="1" s="60">
@@ -26948,7 +27245,7 @@
         <f>IF($C193="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F193" s="58" t="n"/>
+      <c r="F193" s="73" t="n"/>
       <c r="G193" s="30" t="n"/>
     </row>
     <row r="194" ht="14.25" customHeight="1" s="60">
@@ -26956,7 +27253,7 @@
         <f>IF($C194="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F194" s="58" t="n"/>
+      <c r="F194" s="73" t="n"/>
       <c r="G194" s="30" t="n"/>
     </row>
     <row r="195" ht="14.25" customHeight="1" s="60">
@@ -26964,7 +27261,7 @@
         <f>IF($C195="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F195" s="58" t="n"/>
+      <c r="F195" s="73" t="n"/>
       <c r="G195" s="30" t="n"/>
     </row>
     <row r="196" ht="14.25" customHeight="1" s="60">
@@ -26972,7 +27269,7 @@
         <f>IF($C196="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F196" s="58" t="n"/>
+      <c r="F196" s="73" t="n"/>
       <c r="G196" s="30" t="n"/>
     </row>
     <row r="197" ht="14.25" customHeight="1" s="60">
@@ -26980,7 +27277,7 @@
         <f>IF($C197="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F197" s="58" t="n"/>
+      <c r="F197" s="73" t="n"/>
       <c r="G197" s="30" t="n"/>
     </row>
     <row r="198" ht="14.25" customHeight="1" s="60">
@@ -26988,7 +27285,7 @@
         <f>IF($C198="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F198" s="58" t="n"/>
+      <c r="F198" s="73" t="n"/>
       <c r="G198" s="30" t="n"/>
     </row>
     <row r="199" ht="14.25" customHeight="1" s="60">
@@ -26996,7 +27293,7 @@
         <f>IF($C199="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F199" s="58" t="n"/>
+      <c r="F199" s="73" t="n"/>
       <c r="G199" s="30" t="n"/>
     </row>
     <row r="200" ht="14.25" customHeight="1" s="60">
@@ -27004,7 +27301,7 @@
         <f>IF($C200="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F200" s="58" t="n"/>
+      <c r="F200" s="73" t="n"/>
       <c r="G200" s="30" t="n"/>
     </row>
     <row r="201" ht="14.25" customHeight="1" s="60">
@@ -27012,7 +27309,7 @@
         <f>IF($C201="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F201" s="58" t="n"/>
+      <c r="F201" s="73" t="n"/>
       <c r="G201" s="30" t="n"/>
     </row>
     <row r="202" ht="14.25" customHeight="1" s="60">
@@ -27020,7 +27317,7 @@
         <f>IF($C202="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F202" s="58" t="n"/>
+      <c r="F202" s="73" t="n"/>
       <c r="G202" s="30" t="n"/>
     </row>
     <row r="203" ht="14.25" customHeight="1" s="60">
@@ -27028,7 +27325,7 @@
         <f>IF($C203="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F203" s="58" t="n"/>
+      <c r="F203" s="73" t="n"/>
       <c r="G203" s="30" t="n"/>
     </row>
     <row r="204" ht="14.25" customHeight="1" s="60">
@@ -27036,7 +27333,7 @@
         <f>IF($C204="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F204" s="58" t="n"/>
+      <c r="F204" s="73" t="n"/>
       <c r="G204" s="30" t="n"/>
     </row>
     <row r="205" ht="14.25" customHeight="1" s="60"/>

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -4717,7 +4717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AI209"/>
+  <dimension ref="A2:AI206"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="60" min="1" max="1"/>
@@ -9052,17 +9052,17 @@
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="60">
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -9176,17 +9176,17 @@
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="60">
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -9300,17 +9300,17 @@
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -9424,6 +9424,21 @@
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="60">
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 12 — pasta entregas-candidatos/12 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E61" s="33">
         <f>IF(COUNT(K61:AG61)=0,"",ROUND((F61+G61+H61+I61+J61)/10,2))</f>
         <v/>
@@ -9448,28 +9463,106 @@
         <f>IF(COUNT(K61:AG61)=0,"",(AF61*5+AG61*5)/3)</f>
         <v/>
       </c>
-      <c r="K61" s="41" t="n"/>
-      <c r="L61" s="41" t="n"/>
-      <c r="M61" s="41" t="n"/>
-      <c r="N61" s="41" t="n"/>
-      <c r="P61" s="41" t="n"/>
-      <c r="Q61" s="41" t="n"/>
-      <c r="R61" s="41" t="n"/>
-      <c r="S61" s="41" t="n"/>
-      <c r="U61" s="41" t="n"/>
-      <c r="V61" s="41" t="n"/>
-      <c r="W61" s="41" t="n"/>
-      <c r="X61" s="41" t="n"/>
-      <c r="Y61" s="41" t="n"/>
-      <c r="Z61" s="41" t="n"/>
-      <c r="AB61" s="41" t="n"/>
-      <c r="AC61" s="41" t="n"/>
-      <c r="AD61" s="41" t="n"/>
-      <c r="AE61" s="41" t="n"/>
+      <c r="K61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O61" s="68" t="inlineStr">
+        <is>
+          <t>C1=3: o deck abre pela recomendação — o slide 3 é o divisor "Recomendação de investimento" e o slide 4 traz a resposta completa com o número (Estação Central, pontos parceiros, R$ 27.840.000). Contando capa, sumário e divisor, ela chega na 4ª página de 18, ou seja, a primeira página de conteúdo é a resposta. Ressalva para o 2º avaliador: não é literalmente uma frase, está distribuída em três colunas. C2=2: deck de nível cliente com capa, sumário, divisores de seção e slide de fechamento, mais planilha de 5 abas. O que impede o 3 são títulos duplicados: os slides 9, 10 e 11 têm título e subtítulo idênticos ("Cenários de investimento: projeções anuais de lucro") e os slides 6 e 7 repetem "Mapeamento da cidade", quatro slides em que o leitor não sabe o que mudou. C3=2: a recomendação aparece no título ("O futuro da BagHub em Estação Central, Porto Claro") e o arco fecha — recomendação, comparação, rentabilidade, conclusões, matriz, modelo de negócios, riscos e próximos passos. O salto que impede o 3 é justamente o título triplicado dos slides 9 a 11. C4=3: template consistente com divisores de seção, gráficos no mesmo padrão e nenhum slide com parágrafo corrido.</t>
+        </is>
+      </c>
+      <c r="P61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S61" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" s="68" t="inlineStr">
+        <is>
+          <t>R1=3: o slide 4 amarra R$ 27.840.000 a razões de negócio próprias e verificáveis — infraestrutura ferroviária e rodoviária, e o fato de a Estação Central fazer fronteira com 5 bairros, sendo passagem para diversos trajetos, com sazonalidade "homogênea e previsível" e potencial de fidelização. Conferi no mapa do Anexo A e a contagem de 5 bairros vizinhos está correta. Tapando o número, o argumento de fronteira e recorrência fica; tapando o argumento, 27,84M é o máximo dos oito. R2=3: o slide 13 ordena as OITO combinações numa matriz esforço-resultado, e a ordem está correta por lucro absoluto (27,84 &gt; 25,08 &gt; 24,50 &gt; 23,15 &gt; 19,20 &gt; 18,57 &gt; 14,94 &gt; 13,87), incluindo o detalhe de colocar Estação-armários à frente de Centro-parceiros. Marca Noite Alta como 5/6 com asterisco, declarando que a posição depende de pesquisa sobre disponibilidade horária dos parceiros — reconhece a incerteza em vez de fingir precisão. R3=3: três adições reais. Primeiro, o critério "potencial de fronteira" (aba diagramas, notas 3/2/1/2), construído a partir da leitura do mapa do Anexo A — foi a única candidata a usar o mapa analiticamente, e isso sustenta diretamente a recomendação. Segundo, a aba comparação calcula a vantagem percentual dos parceiros por bairro (11,0% / 5,8% / 7,7% / 3,4%) e ela usa isso no slide 12 para argumentar que a diferença não é grande o bastante para ignorar fatores qualitativos, apontando Noite Alta (3,4%, a menor) como onde a vantagem pode virar — é o mesmo achado das melhores entregas, por outro caminho. Terceiro, um Business Model Canvas completo no slide 15, não pedido. R4=2: acerta em dois indicadores e erra no que promove a primeiro lugar. Acerta ao interpretar os percentuais de vantagem e ao derivar consequência de negócio do mapa. Erra no slide 17, onde lista como oportunidade nº 1 que "apenas 42% das horas semanais disponíveis são utilizadas na estação central, um maior aproveitamento teria impacto direto no lucro" — o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações, então horas ociosas não são alavanca de receita.</t>
+        </is>
+      </c>
+      <c r="U61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y61" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z61" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados conferem integralmente. Memória de cálculo em planilha real, com as abas modelo 1 e modelo 2 puxando os parâmetros da aba Rascunho por referência ((C22+C25)*2400+70000*60, e assim por diante). A2=3: contagens de banco corretas nas fórmulas — 60, 25, 23 e 45 — com a Arena em 23, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários, com os três níveis parametrizados na aba Rascunho. A3=3: o slide 17 traz quatro próximos passos concretos, com prazo declarado ("piloto de 3 meses na Estação Central... comparando os dados projetados e os reais") e definição de KPIs e OKRs; a expansão está nomeada com razão (Centro Histórico, por alto lucro, baixa complexidade e proximidade geográfica) e a ordem completa está no slide 13. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: alternativa quantificada por dois caminhos — Estação-armários em 2º na matriz e a vantagem percentual dos parceiros por bairro, que dimensiona quanto se perderia ao trocar de modelo. A5=3: quatro riscos no slide 17, todos específicos da recomendação dela (dependência dos parceiros comerciais; horários de pico do transporte público superando a capacidade estipulada; manutenção maior por proximidade ao transporte público; e uma observação afiada e própria — baixa conversão porque a pressa é característica do público-alvo de conexões). Mitigação vem via os próximos passos (mapeamento da rede de parceiros, piloto com dados em tempo real) e o prazo de 3 meses está escrito. A6=1: o case não traz erro plantado. Ela não descontou transações pela utilização nas contas, que estão todas certas, mas não nomeou inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB61" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="AF61" s="41" t="n"/>
       <c r="AG61" s="41" t="n"/>
+      <c r="AH61" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está no arquivo e no slide de fechamento, então dá para transcrever das linhas 16 e 38. E1=1, planilha real de 5 abas com fórmulas vivas e parâmetros centralizados. E3=0, sem vídeo de entrega. Ressalva de método: os slides 7, 9, 10, 11 e 13 são gráficos e eu avaliei o E4 pelo conteúdo que os alimenta (abas diagramas e comparação) e pelos títulos, sem inspecionar o visual de cada gráfico.</t>
+        </is>
+      </c>
+      <c r="AI61" s="68" t="inlineStr">
+        <is>
+          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente: contou que a Estação Central faz fronteira com 5 bairros — conferi, está certo — e transformou isso num critério pontuado de "potencial de fronteira", usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou. A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação-armários à frente de Centro-parceiros, e marca Noite Alta com asterisco declarando que a posição depende de pesquisa — reconhecer incerteza em vez de simular precisão é maturidade. A terceira é a vantagem percentual por bairro (11,0% / 5,8% / 7,7% / 3,4%), usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses. O erro que eu cobraria está no slide 17: ela promove a oportunidade nº 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações — ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita. De forma, o custo veio dos títulos repetidos: três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia. Na entrevista eu faria as duas perguntas: como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou. Nota 7,93 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,81.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A aba Rascunho é material de trabalho cru, com a estrutura do case transcrita em abreviações (ec, ch, a, na) e typos de digitação rápida ("receita anula", "infliencia", "complexdade", "posições necessarias") — ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo que não sai de texto. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas, sinal de quem resolveu o arredondamento na mão. E o risco de "baixa conversão pela pressa" é uma observação idiossincrática sobre o público. Há ainda o typo "resltado" no eixo da matriz do slide 13. Pergunta de propriedade para a entrevista: quais são os 5 bairros de fronteira da Estação Central, e como as horas ociosas virariam lucro?
+[IDENTIFICAÇÃO] Nome no arquivo e no slide de fechamento: Mariana Nunes Galvão Sant'Anna. V1/V2 nas linhas 16 (luis 3/2) e 38 (Proc 2/3).</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" s="60">
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 13 — pasta entregas-candidatos/13 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E62" s="33">
         <f>IF(COUNT(K62:AG62)=0,"",ROUND((F62+G62+H62+I62+J62)/10,2))</f>
         <v/>
@@ -9494,28 +9587,106 @@
         <f>IF(COUNT(K62:AG62)=0,"",(AF62*5+AG62*5)/3)</f>
         <v/>
       </c>
-      <c r="K62" s="41" t="n"/>
-      <c r="L62" s="41" t="n"/>
-      <c r="M62" s="41" t="n"/>
-      <c r="N62" s="41" t="n"/>
-      <c r="P62" s="41" t="n"/>
-      <c r="Q62" s="41" t="n"/>
-      <c r="R62" s="41" t="n"/>
-      <c r="S62" s="41" t="n"/>
-      <c r="U62" s="41" t="n"/>
-      <c r="V62" s="41" t="n"/>
-      <c r="W62" s="41" t="n"/>
-      <c r="X62" s="41" t="n"/>
-      <c r="Y62" s="41" t="n"/>
-      <c r="Z62" s="41" t="n"/>
-      <c r="AB62" s="41" t="n"/>
-      <c r="AC62" s="41" t="n"/>
-      <c r="AD62" s="41" t="n"/>
-      <c r="AE62" s="41" t="n"/>
+      <c r="K62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="68" t="inlineStr">
+        <is>
+          <t>C1=1: não há recomendação escrita em lugar nenhum dos dois arquivos. Ele cumpre as tarefas 01 a 03 (comparar bairros, demanda e capacidade, calcular rentabilidade) e para. Dá para inferir a escolha pelos gráficos de lucro acumulado, onde a Estação Central tem o maior acúmulo em 5 anos e os armários ultrapassam os parceiros, mas em nenhum momento ele escreve qual bairro nem qual modelo escolheria — que é exatamente o descritor de 1. C2=0: o entregável é seis fotografias de páginas de caderno, com sombra visível, iluminação irregular e dominante de cor rosada, mais um print de planilha. O descritor de 0 é literal: "foto de papel". Aplicando o teste operacional, não é arquivo que se manda a um cliente sem editar. Registro em favor dele que a caligrafia é organizada, com títulos em caixa e blocos "Resumo do Bairro" destacados — não é material caótico, é material privado. C3=1: a sequência interna é lógica e espelha as tarefas do case, mas os quatro blocos de bairro são paralelos e independentes, nenhum puxa o seguinte, e a página de gráficos não se conecta a nenhum texto. Sem conclusão, não há fio que chegue a lugar algum. C4=1: formatação improvisada mas legível — as fotos exigem esforço para ler por causa da sombra e do contraste, e a página de Excel é limpa.</t>
+        </is>
+      </c>
+      <c r="P62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" s="68" t="inlineStr">
+        <is>
+          <t>R1=0: não há recomendação, que é o descritor de 0. Todo o material quantitativo está correto, mas nenhuma decisão é tomada nem sustentada. R2=1: aplicando o teste operacional — "ele descartou alguma coisa por escrito? Se não descartou nada, não discutiu" — ele não descartou nada. Registro em favor dele, para o 2º avaliador, que a comparação em si é das mais completas do conjunto: os oito cenários calculados à mão mais a evolução dos dois modelos em 5 anos nos quatro bairros. Há comparação rica e zero escolha, o que torna este 1 contestável para 2. R3=0: o pedido ficou incompleto, que é o descritor de 0. A tarefa 04 do enunciado pede escolher bairro e modelo, sustentar com números e apresentar riscos e próximos passos — nada disso foi entregue. Vale notar que ele trouxe coisas não pedidas e boas (os 3C's aplicados ao case, a projeção de 5 anos), mas o descritor é explícito sobre pedido incompleto. R4=2: lê as lucratividades e compara ano 1 contra anos seguintes, tirando conclusão. Tem ainda a melhor observação qualitativa do conjunto sobre a demanda: anota que as conexões duram em média 1h30 a 2h e que "na maior parte das vezes não será tempo suficiente para fazer uma visita", o que questiona o próprio driver de demanda da Estação Central. O que impede o 3 é que ele não faz nada com essa observação — não ajusta número, não vira risco, não muda conclusão — e a duração de 1h30 a 2h não está no case nem é marcada como premissa dele.</t>
+        </is>
+      </c>
+      <c r="U62" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V62" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados de Ano 1 conferem integralmente, todos desenvolvidos à mão. Estação Central: receita 1.200.000 transações x 30 = 36M, armários 3.360.000 + 4.200.000 + 3.360.000 = 10.920.000, lucro 25.080.000, lucratividade 69,66%; parceiros 8.160.000, lucro 27.840.000, 77,33%. Arena: parceiros 3.060.000, lucro 14.940.000, 83%; armários lucro 13.870.000, 77,05%. Noite Alta: armários 11.430.000 e lucro 18.570.000 a 61,9%; parceiros 10.800.000 e 19.200.000 a 64%. A memória de cálculo não é só visível, ela É o entregável. A2=3: bancos explícitos e corretos (60 na Estação, 45 em Noite Alta) e o custo de R$ 1.610.000 na Arena só fecha com 23 bancos, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários. A3=1: existe projeção de 5 anos com ponte ano a ano e ela bate com o modelo dele, mas está inteiramente apoiada em remover o custo do banco a partir do 2º ano — ele anota "apenas 1º ano" ao lado dos R$ 4.200.000, quando o Anexo E declara que todos os valores são anuais. Sob a premissa correta, os armários nunca ultrapassam os parceiros e os quatro gráficos caem. Além disso não há plano de lançamento nenhum, nem fasemento, nem próximos passos. A4=2: a alternativa dos armários está coerente com o case e quantificada em 5 anos nos quatro bairros, mas nunca é proposta como curso de ação — fica entre descritores porque há quantificação sem proposta. A5=1: ele lista pontos negativos por bairro, e são específicos (atendimento noturno, segurança, operação complexa e risco de roubos em Noite Alta; a duração das conexões na Estação), mas estão desacoplados de qualquer recomendação, não têm mitigação e não há próximos passos, que o enunciado pede explicitamente na tarefa 04. A6=1: o case não traz erro plantado. Ele anota "42% de utilização" ao lado da conta de receita como contexto e não aplica como desconto, ou seja, passou pelo ponto certo, mas não nomeia inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="AF62" s="41" t="n"/>
       <c r="AG62" s="41" t="n"/>
+      <c r="AH62" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0 pela letra do item: o Excel Graficos é um PDF exportado, não um arquivo de planilha — mesma ressalva das pastas 05 e 08, ele entregou memória de cálculo de fato, em outro formato. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas; fotos de caderno e print de planilha não são entregável fechado. E3=0, sem vídeo. E4=1: os quatro gráficos de lucro acumulado são corretos e bem feitos, com título, legenda e eixo, mas estão soltos — nenhum texto os cita e nenhuma afirmação é construída sobre eles.</t>
+        </is>
+      </c>
+      <c r="AI62" s="68" t="inlineStr">
+        <is>
+          <t>É a entrega mais frustrante do conjunto, porque a parte difícil está certa e a parte fácil não foi feita. Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas: anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade — ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou. E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some-se o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado. Sobre a projeção, ela também não sobrevive: ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais — corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar para a diretoria que este é o terceiro candidato a ler o banco como investimento (junto com as pastas 05 e 09), o que sugere que a redação do Anexo E merece um ajuste no próximo case. Na entrevista, se ele passar, a primeira pergunta é a que falta: você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda: por que o banco vale só no 1º ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case? Nota 3,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,48.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. É a pasta com a evidência de propriedade mais inequívoca do conjunto, ao lado da 05. Seis páginas de caderno fotografadas sob luz ruim, com a estrutura do case transcrita à mão, os 3C's aplicados, cada conta desenvolvida passo a passo e os totais circulados. A anotação "apenas 1º ano" ao lado do custo do banco documenta uma decisão de modelagem consciente. E a observação sobre a duração das conexões traz informação de fora do case, algo que texto gerado a partir do enunciado não produz, porque ele não questiona o input. A ausência de recomendação é falha de execução de quem ficou sem tempo, não artefato de geração — saída gerada tende a entregar a conclusão e economizar no meio, exatamente o inverso do que aconteceu aqui. Pergunta de propriedade para a entrevista: qual bairro e qual modelo você escolhe, e por que o banco só conta no 1º ano?
+[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1" s="60">
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 14 — pasta entregas-candidatos/14 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E63" s="33">
         <f>IF(COUNT(K63:AG63)=0,"",ROUND((F63+G63+H63+I63+J63)/10,2))</f>
         <v/>
@@ -9540,28 +9711,106 @@
         <f>IF(COUNT(K63:AG63)=0,"",(AF63*5+AG63*5)/3)</f>
         <v/>
       </c>
-      <c r="K63" s="41" t="n"/>
-      <c r="L63" s="41" t="n"/>
-      <c r="M63" s="41" t="n"/>
-      <c r="N63" s="41" t="n"/>
-      <c r="P63" s="41" t="n"/>
-      <c r="Q63" s="41" t="n"/>
-      <c r="R63" s="41" t="n"/>
-      <c r="S63" s="41" t="n"/>
-      <c r="U63" s="41" t="n"/>
-      <c r="V63" s="41" t="n"/>
-      <c r="W63" s="41" t="n"/>
-      <c r="X63" s="41" t="n"/>
-      <c r="Y63" s="41" t="n"/>
-      <c r="Z63" s="41" t="n"/>
-      <c r="AB63" s="41" t="n"/>
-      <c r="AC63" s="41" t="n"/>
-      <c r="AD63" s="41" t="n"/>
-      <c r="AE63" s="41" t="n"/>
+      <c r="K63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" s="68" t="inlineStr">
+        <is>
+          <t>C1=1: dá para inferir a recomendação — ele declara no slide 4 que rentabilidade é "o nosso critério principal" e o slide 17 conclui que a Estação Central lidera com R$ 27,84 mi em parceiros — mas ela não está escrita em lugar nenhum. O slide 21 fecha ambivalente ("a Estação central ganha na rentabilidade bruta, enquanto o Centro histórico traz uma proposta de eficiência e constância") sem resolver, e o índice do slide 2 promete uma seção "d. Recomendação do lançamento" que não existe no deck. C2=2: deck de nível cliente, com capa, índice, divisores de seção, rodapé, numeração e citação de fonte ("Fonte: Anexos A, B e C do desafio"). Pontas soltas que impedem o 3: os slides 7 e 8 têm título idêntico e ambos numerados "07", os slides 10 e 11 idem numerados "09", typos em "perídodo" (slide 4) e "font única" (slide 19), e a seção prometida no índice não foi entregue. C3=1: teste operacional — os títulos são rótulos ("Critério 3: Robustez da demanda", "Conclusão: a tabela-resumo de decisão") e a recomendação não aparece em nenhum; somam-se quatro slides com títulos duplicados, que obrigam o leitor a descobrir o que mudou. O arco dos quatro critérios é claro, o que torna este 1 contestável. C4=2: template uniforme com rodapé e marcadores de seção, mas o slide 18 está sobrecarregado — três tabelas mais a fórmula, com a numeração colidindo dentro de uma célula — e a numeração repetida em 8 e 11.</t>
+        </is>
+      </c>
+      <c r="P63" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T63" s="68" t="inlineStr">
+        <is>
+          <t>R1=2: cita as duas partes e elas se conectam bem — R$ 27,84 mi com a razão estratégica do slide 20, a Estação Central como "Origem" da jornada que "intercepta o cliente antes de todo mundo". O que impede nota maior é que ele nunca decide: a própria tabela do slide 21 mostra o Centro Histórico ganhando em três dos quatro critérios (eficiência, robustez e valor estratégico empatado em ALTO) contra o critério principal que ele declarou, e essa contradição não é reconciliada. Com a decisão em aberto, um dos lados fica decorativo. R2=3: é o ponto mais forte da entrega. Quatro critérios declarados no slide 4 e todos operacionalizados de verdade — rentabilidade nos oito cenários, eficiência em R$/posição com ranking, robustez com regra explícita e limiares numéricos ("Alta: utilização acima de 50% ou duas ou mais fontes independentes com janela ampla; Baixa: abaixo de 35% e fonte única...") aplicada corretamente aos quatro bairros, e valor estratégico por contagem de adjacência. O slide 21 consolida tudo numa tabela de decisão com ranking por critério, e ele justifica por escrito por que Arena e Noite Alta saem (robustez BAIXA, valor estratégico BAIXO e MÉDIO). A regra de robustez é o critério qualitativo mais rigoroso e reproduzível de todo o conjunto. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou — a tarefa 04 pede recomendação sustentada, riscos e próximos passos, e não há recomendação declarada, nem seção de riscos, nem próximos passos. Registro com clareza, porque a nota isolada engana: o material extra dele (unit economics por posição, regra de robustez, adjacência e jornada do cliente) está entre os melhores do conjunto. O zero vem só da incompletude do pedido. R4=3: melhor leitura de indicador de todas as pastas. No slide 6 ele explica por que a Estação tem mais transações e menos utilização — demanda em picos, exigindo mais capital imobilizado por transação — e deriva que é onde as malas ficam guardadas por mais tempo, "mais ou menos 7 horas, o maior entre os bairros". Recalculei: 0,42 x 2.400 x 168 / 24.000 = 7,06 h. Está exato, e ninguém mais extraiu tempo de permanência dos dados. Ressalva: no slide 8 ele diz que os itens do Centro Histórico "ficam guardados por mais tempo", o que contradiz o próprio slide 6 (o Centro dá 5,04 h).</t>
+        </is>
+      </c>
+      <c r="U63" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V63" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="W63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: sete dos oito resultados estão exatos e o oitavo cai dentro da tolerância. Arena armários deu R$ 13,814 mi contra R$ 13,870 mi do gabarito, −0,40%, dentro de ±2%. Memória de cálculo completa e visível nos slides 13 a 16, com cada linha de custo decomposta por bairro e por modelo. A2=2: ele acertou a parte difícil e errou a fácil. Os bancos estão certos, inclusive a Arena com 23 bancos a R$ 1,61 mi (o arredondamento de 22,5 foi feito). Mas no slide 15, na coluna de armários, ele aplicou os custos por posição a 920 posições em vez das 900 necessárias — R$ 1.400 x 920 = R$ 1,288 mi para equipamento e o mesmo para operação — contrariando a instrução explícita do Anexo E de que "custos por posição incidem nas posições necessárias do Anexo C". E fez isso de forma inconsistente: na coluna de parceiros do mesmo slide usou 900 corretamente. O erro propaga para o slide 18 (giro 13,0 para armários contra 13,3 para parceiros na Arena, resultado/posição R$ 15.015). Ainda no slide 18, o banco/posição aparece como R$ 1.750 para os quatro bairros, valor que só é exato quando as posições são divisíveis por 40 — na Arena seria R$ 1.788,89. O valor final ficou na tolerância por ser erro pequeno, mas o método contraria instrução escrita. A3=1: não há projeção, fasemento nem próximos passos. O slide 21 gesticula que o Centro Histórico "não deve ser desconsiderado para uma futura expansão", o que é direcional e apoiado em número, mas não chega a ser plano. A4=3: o Centro Histórico é proposto como expansão futura com impacto quantificado (R$ 24,50 mi) e sustentado por ranking em quatro critérios, tudo específico deste case. A5=1: não há seção de riscos nem próximos passos, que a tarefa 04 pede. O que existe são observações de risco dispersas na análise por bairro ("maior incerteza na previsão" na Arena, "necessitando maior investimento com a segurança dos itens" em Noite Alta) — específicas, mas desacopladas de qualquer recomendação, sem mitigação e sem prazo. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização — ao contrário, usou a utilização corretamente para derivar tempo de permanência — mas não nomeou inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB63" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="AF63" s="41" t="n"/>
       <c r="AG63" s="41" t="n"/>
+      <c r="AH63" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Rafael Rodrigues Moreira), então dá para transcrever das linhas 24 e 46. E1=0, sem planilha, embora a memória de cálculo esteja detalhada nos slides. E3=0, sem vídeo de entrega. E4=2: todas as tabelas são centrais e citadas, nenhuma decorativa, mas as linhas da Arena nos slides 15 e 18 carregam a base errada (920 em vez de 900) e o slide 18 tem colisão de layout entre a numeração e uma célula.</t>
+        </is>
+      </c>
+      <c r="AI63" s="68" t="inlineStr">
+        <is>
+          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso é difícil de pontuar de forma justa. O que ele fez de melhor ninguém mais fez: derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 h, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa — mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central "interceptando o cliente antes de todo mundo". É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez. E então ele não recomenda nada. O índice promete uma seção "Recomendação do lançamento" que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher — e o problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos. No cálculo há um deslize instrutivo: na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita — e usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude. Na entrevista eu faria três perguntas, e a primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? (Dá 5,04 h, e a resposta expõe a contradição do slide 8.) Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios — qual você recomenda e por quê? Nota 5,20 com V1 e V2 em branco; considerando só o que dá para avaliar, 5,78.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria, e o mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações; conferi e o valor está certo (7,06 h). Isso é raciocínio original, não recuperação de padrão. A contagem de adjacência exige abrir a imagem do mapa e olhar as fronteiras. A regra de robustez com limiares é um instrumento construído por ele. Do outro lado, os erros são humanos: typos ("perídodo", "font única"), numeração de página repetida (07 duas vezes, 09 duas vezes), a contradição entre o slide 6 e o slide 8 sobre qual bairro guarda itens por mais tempo, e o 920 contra 900 aparecendo nas duas colunas do mesmo slide. Esse último é assinatura de conta feita à mão. Pergunta de propriedade para a entrevista: como você chegou nas 7 horas de permanência, e quanto dá no Centro Histórico?
+[IDENTIFICAÇÃO] Nome na capa: Rafael Rodrigues Moreira. V1/V2 nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1).</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="60">
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 15 — pasta entregas-candidatos/15 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E64" s="33">
         <f>IF(COUNT(K64:AG64)=0,"",ROUND((F64+G64+H64+I64+J64)/10,2))</f>
         <v/>
@@ -9586,28 +9835,106 @@
         <f>IF(COUNT(K64:AG64)=0,"",(AF64*5+AG64*5)/3)</f>
         <v/>
       </c>
-      <c r="K64" s="41" t="n"/>
-      <c r="L64" s="41" t="n"/>
-      <c r="M64" s="41" t="n"/>
-      <c r="N64" s="41" t="n"/>
-      <c r="P64" s="41" t="n"/>
-      <c r="Q64" s="41" t="n"/>
-      <c r="R64" s="41" t="n"/>
-      <c r="S64" s="41" t="n"/>
-      <c r="U64" s="41" t="n"/>
-      <c r="V64" s="41" t="n"/>
-      <c r="W64" s="41" t="n"/>
-      <c r="X64" s="41" t="n"/>
-      <c r="Y64" s="41" t="n"/>
-      <c r="Z64" s="41" t="n"/>
-      <c r="AB64" s="41" t="n"/>
-      <c r="AC64" s="41" t="n"/>
-      <c r="AD64" s="41" t="n"/>
-      <c r="AE64" s="41" t="n"/>
+      <c r="K64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="68" t="inlineStr">
+        <is>
+          <t>C1=1: não há recomendação escrita em lugar nenhum. Dá para inferir, porque os quatro bairros estão calculados e os parceiros vencem em todos, com a Estação Central no topo — mas o leitor tem de montar a comparação sozinho a partir de quatro páginas independentes, porque não existe tabela comparativa nem síntese. C2=0: o entregável são oito páginas manuscritas digitalizadas no CamScanner, e um dos dois arquivos se chama literalmente "rascunho". Sem capa, sem estrutura, sem síntese. O descritor de 0 é literal ("foto de papel... arquivo sem estrutura nenhuma") e o teste operacional é claro: não se manda isso a um cliente. Registro em favor dele que a digitalização é limpa e a caligrafia é organizada, com títulos sublinhados e resultados destacados. C3=1: os blocos existem e seguem a ordem do case, mas são paralelos e independentes — um não puxa o outro e nenhum chega a conclusão. C4=1: formatação improvisada mas legível; o CamScanner deu bom contraste, bem melhor que fotografia direta, e os resultados estão sublinhados.</t>
+        </is>
+      </c>
+      <c r="P64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" s="68" t="inlineStr">
+        <is>
+          <t>R1=0: não há recomendação, que é o descritor de 0. R2=1: aplicando o teste operacional, ele não descartou nada por escrito e não escolheu nada. Registro em favor dele, para o 2º avaliador, que o rascunho traz uma comparação qualitativa real dos dois modelos, com listas de + e −: armários somam operação 24h e a facilidade de o cliente se servir "sem necessidade de falar com outra pessoa", e subtraem manutenção e restituição maiores; parceiros somam menor custo de manutenção e subtraem horário variável, dependência de outros comércios e o fato de "poder ser mais demorado e difícil do cliente achar/conhecer o BagHub". É comparação de modelo, não de bairro, e sem escolha. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou de forma ampla — a tarefa 01 (critérios de atratividade), a comparação entre bairros e toda a tarefa 04 (recomendação, riscos, próximos passos) não foram entregues. Só a tarefa 03 está completa. R4=1: lê os indicadores corretamente e rotula bem (marca com seta qual número é o faturamento), e tira consequência qualitativa dos dois modelos, inclusive a observação própria sobre descoberta do serviço pelo cliente nos pontos parceiros. Mas não interpreta nenhum indicador quantitativo: a utilização é transcrita nos quatro bairros (42%, 54%, 31%, 33%) e nunca é comparada, explicada ou usada para nada.</t>
+        </is>
+      </c>
+      <c r="U64" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V64" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados conferem integralmente, todos desenvolvidos à mão. Estação Central: 1.200.000 transações x 30 = 36M, armários 3,36 + 4,2 + 3,36 = 10,92M e lucro 25,08M, parceiros 3,36 + 4,8 = 8,16M e lucro 27,84M. Arena: 18M, armários 4,13M e lucro 13,87M, parceiros 3,06M e lucro 14,94M. Noite Alta: 30M, armários 11,43M e lucro 18,57M, parceiros 10,8M e lucro 19,2M. A memória de cálculo não é só visível, ela É o entregável. A2=3: o arredondamento da Arena está explícito, anotado e autocorrigido — na página da Arena ele escreveu 900/40 x 70.000, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23", fechando em R$ 1,61M. Bancos de 60 na Estação e 45 em Noite Alta também explícitos e corretos. Custo por complexidade correto nos oito cenários. A3=0: não fez — não há projeção, plano, fasemento nem próximos passos. A4=1: os dois modelos estão caracterizados com prós e contras específicos do case, mas nenhuma alternativa é proposta como curso de ação e nenhum impacto é quantificado. A5=1: as listas de "−" do rascunho funcionam como riscos e são específicas dos modelos (horário variável, dependência de terceiros, dificuldade de o cliente achar o serviço, manutenção maior nos armários), mas estão desacopladas de qualquer recomendação, sem mitigação, sem prazo e sem próximos passos, que o enunciado pede na tarefa 04. A6=1: o case não traz erro plantado. Ele transcreveu a utilização e não a aplicou como desconto — a receita está correta nos quatro bairros — mas não nomeou inconsistência nenhuma.</t>
+        </is>
+      </c>
+      <c r="AB64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="AF64" s="41" t="n"/>
       <c r="AG64" s="41" t="n"/>
+      <c r="AH64" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0, não há arquivo de planilha, embora a memória de cálculo manuscrita esteja completa — mesma ressalva das pastas 05, 08 e 13. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas. E3=0, sem vídeo. E4=0: nenhum gráfico e nenhuma tabela em nenhuma das oito páginas — este zero é de mérito, o material existe e não atende ao descritor.</t>
+        </is>
+      </c>
+      <c r="AI64" s="68" t="inlineStr">
+        <is>
+          <t>O cálculo está perfeito e é praticamente tudo o que existe. Os oito cenários estão certos, desenvolvidos à mão, e a Arena — onde a maioria escorrega — está não só correta como autocorrigida: ele escreveu a divisão 900/40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo. O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo. O formato agrava: são oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável. O que existe de análise qualitativa está no rascunho, e é melhor do que parece — a lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível; faltou transformar em entrega. Na entrevista, se ele avançar, a pergunta é direta e vale tudo: você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade: por que a Arena arredonda para 23 e não fica em 22,5? Nota 2,63 com V1 e V2 em branco; considerando só o que dá para avaliar, 2,93.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Evidência de propriedade praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos do case à mão e as contas desenvolvidas passo a passo. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta — erro cometido e corrigido no próprio papel, o que não é fabricável. A ausência de recomendação é falha de execução de quem ficou sem tempo ou não entendeu o escopo do entregável, e não artefato de geração: texto gerado entrega a conclusão e economiza no desenvolvimento, exatamente o contrário do que ocorreu aqui. Pergunta de propriedade para a entrevista: por que a Arena arredonda para 23, e qual bairro e modelo você escolheria?
+[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="60">
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 16 — pasta entregas-candidatos/16 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
       <c r="E65" s="33">
         <f>IF(COUNT(K65:AG65)=0,"",ROUND((F65+G65+H65+I65+J65)/10,2))</f>
         <v/>
@@ -9632,26 +9959,89 @@
         <f>IF(COUNT(K65:AG65)=0,"",(AF65*5+AG65*5)/3)</f>
         <v/>
       </c>
-      <c r="K65" s="41" t="n"/>
-      <c r="L65" s="41" t="n"/>
-      <c r="M65" s="41" t="n"/>
-      <c r="N65" s="41" t="n"/>
-      <c r="P65" s="41" t="n"/>
-      <c r="Q65" s="41" t="n"/>
-      <c r="R65" s="41" t="n"/>
-      <c r="S65" s="41" t="n"/>
-      <c r="U65" s="41" t="n"/>
-      <c r="V65" s="41" t="n"/>
-      <c r="W65" s="41" t="n"/>
-      <c r="X65" s="41" t="n"/>
-      <c r="Y65" s="41" t="n"/>
-      <c r="Z65" s="41" t="n"/>
-      <c r="AB65" s="41" t="n"/>
-      <c r="AC65" s="41" t="n"/>
-      <c r="AD65" s="41" t="n"/>
-      <c r="AE65" s="41" t="n"/>
+      <c r="K65" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N65" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" s="68" t="inlineStr">
+        <is>
+          <t>C1=2: a recomendação é explícita, clara e completa ("Estação Central é a prioridade de lançamento, operando em modelo de Pontos parceiros", com R$ 27.840.000), mas está no slide 9 de 13, passada a metade; a agenda do slide 2 anuncia que haverá recomendação sem adiantar qual. C2=3: documento fechado com exatamente os três elementos do descritor — capa, estrutura e apêndice. O slide 13 é um anexo de memória de cálculo e premissas, listando período, fórmula de receita, tratamento da capacidade, composição dos custos com arredondamento para cima, definição de resultado operacional e a regra de não somar sinergias. Rodapé com nome de seção e numeração nos 13 slides. Nada inacabado. C3=3: a recomendação aparece no título (slide 9) e a conclusão de modelo também ("Modelo de Pontos parceiros supera o de Armários inteligentes em todos os bairros", slide 8). Lendo só os títulos o arco fecha inteiro e na ordem: contexto, comparação, demanda e capacidade, rentabilidade, conclusão, recomendação, priorização, riscos, próximos passos, anexo. C4=2: template uniforme com rodapé e numeração em todos os slides, mas três slides são parágrafo corrido — o 4 (quatro bairros com quatro campos de prosa cada), o 8 (cinco parágrafos) e o 12 (quatro colunas densas) — o que passa do "até 2 slides fora do padrão" do descritor de 2.</t>
+        </is>
+      </c>
+      <c r="P65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" s="68" t="inlineStr">
+        <is>
+          <t>R1=3: o slide 9 organiza a recomendação em três pilares que se apoiam — Financeiro (melhor resultado operacional, R$ 27.840.000), Demanda (maior volume da cidade com 24.000/semana, fluxo previsível atrelado a embarque e desembarque, e o argumento de que viajantes com bagagens são o público-alvo ideal) e Operacional (complexidade moderada e ausência do custo dos bancos). Tapando o número, o argumento de aderência do público continua; tapando o argumento, R$ 27,84M é o máximo dos oito. R2=3: o slide 8 compara os dois modelos com a causa (o custo do banco supera a vantagem operacional dos armários) e, o que é raro, declara o contraponto da própria escolha — as consequências na experiência do cliente, reserva local, serviço não padronizado por ser executado por funcionários do parceiro, e mais burocracia no suporte. O slide 4 compara os quatro bairros em quatro dimensões e descarta por escrito: Arena pela dependência de eventos, Noite Alta porque o público não carrega bagagem, Centro Histórico pela concorrência com hotéis. O slide 10 prioriza os três restantes com resultado e razão. R3=3: a adição é o critério "Fit com o serviço" do slide 4, que não foi pedido e que questiona a plausibilidade da própria demanda projetada pelo case. Os dois melhores achados: "grande parcela dos frequentadores de bares e casas de show não costuma carregar malas e bagagens", o que põe em dúvida as 20 mil transações de Noite Alta apesar de ser o 2º maior volume; e "turistas que estão acomodados em algum hotel do bairro tendem a não necessitar do guarda-volumes" no Centro Histórico. Isso fortalece a recomendação por uma dimensão que os números não capturam — a Estação Central é o único bairro em que o público carrega bagagem por definição. Soma-se o argumento de modelo único para simplificar a gestão da expansão. R4=3: explica causa e consequência em dois níveis. No slide 5 lê a utilização de 54% do Centro Histórico como fluxo mais constante ao longo do dia, leitura defensável (mais giro por posição implica menos pico). E no slide 4 explica a causa por trás de a demanda converter ou não — o comportamento de carregar bagagem — e o que fazer com ela, priorizando a Estação e rebaixando Noite Alta.</t>
+        </is>
+      </c>
+      <c r="U65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="X65" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y65" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z65" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="68" t="inlineStr">
+        <is>
+          <t>A1=3: os oito resultados conferem integralmente, apresentados em duas tabelas decompostas por componente (Custo 1 equipamento, Custo 2 bancos, Custo 3 operação). Memória de cálculo visível em três lugares: as fórmulas sob cada tabela nos slides 6 e 7, as observações com os custos unitários por complexidade, e o anexo do slide 13. A2=3: bancos corretos, incluindo a Arena com R$ 1.610.000, que só fecha com 23 bancos. Ressalva de documentação: a fórmula escrita no slide 6 diz "posições necessárias ÷ 40 x R$ 70.000" sem mencionar o teto, mas o anexo do slide 13 declara "arredondar para cima no modelo de armários" e o valor comprova que foi feito. Custo por complexidade correto nos oito cenários e documentado. A3=3: o slide 9 traz a ordem completa de expansão, o slide 10 detalha os três restantes com resultado e razão, e o slide 12 traz próximos passos concretos; todos os números batem com as tabelas dele. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: Centro Histórico proposto como segundo lançamento com impacto quantificado (R$ 24.500.000) e razão declarada (fluxo turístico estável, complexidade baixa). Soma-se a proposta criativa do slide 12 de capturar a vantagem dos armários dentro do modelo de parceiros, via plataforma digital de reserva. A5=2: os dois riscos do slide 11 são específicos da recomendação dele e as mitigações são as mais concretas e acionáveis de todo o conjunto — treinamento para padronizar atendimento, reserva e atendimento 24h online com check-in presencial, staff da BagHub dentro do comércio parceiro nos horários de pico, e plataforma que indica quais parceiros estão com vaga ou lotados e qual o mais próximo. Pareadas uma a uma com os riscos. O que impede o 3 é a ausência de prazo em qualquer lugar, e apenas dois riscos mapeados. Registro que um 2º avaliador pode defender 3 pela qualidade da mitigação. A6=1: o case não traz erro plantado. Ele nomeia e resolve corretamente o único ponto ambíguo — o slide 5 define "utilização = horas ocupadas ÷ total de horas disponíveis na semana" e o anexo declara que "utilização não reduz a demanda" — mas o que nomeou é a instrução do case, não uma inconsistência.</t>
+        </is>
+      </c>
+      <c r="AB65" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="AF65" s="41" t="n"/>
       <c r="AG65" s="41" t="n"/>
+      <c r="AH65" s="68" t="inlineStr">
+        <is>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Vagner Ássimos Gomes Carlos Filho), então dá para transcrever das linhas 15 e 37. E1=0 pela letra do item: não há arquivo de planilha, embora a memória de cálculo esteja completa entre as fórmulas dos slides 6 e 7 e o anexo do slide 13. E3=0, sem vídeo de entrega.</t>
+        </is>
+      </c>
+      <c r="AI65" s="68" t="inlineStr">
+        <is>
+          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido? No slide 4 ele cria um critério de "fit com o serviço" e usa para questionar a própria demanda do material — observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade, e que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é uma leitura crítica de verdade, e ela reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição. O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso — reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade. As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável. Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes. Na entrevista eu iria atrás do melhor insight dele: você escreveu que o público de Noite Alta não carrega bagagem — então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000. Nota 7,70 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,56.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria. O critério de "fit com o serviço" questiona os dados de demanda do próprio enunciado, e essa é justamente a coisa que saída gerada não faz, porque tende a aceitar o input como verdade — aqui ele confronta a projeção com comportamento real do público (quem vai a bar não leva mala, quem está em hotel não precisa de guarda-volumes). As mitigações são invenções operacionais concretas, como colocar staff da BagHub dentro do comércio parceiro no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos: a numeração da expansão recomeçando em 1º no slide 10 e conflitando com o slide 9, e a fórmula do slide 6 omitindo o arredondamento que o anexo do slide 13 declara e o valor da Arena comprova — inconsistência típica de documento escrito em duas passadas. Pergunta de propriedade para a entrevista: o que você faz com as 20 mil transações de Noite Alta se o público de lá não carrega bagagem?
+[IDENTIFICAÇÃO] Nome na capa: Vagner Ássimos Gomes Carlos Filho. V1/V2 nas linhas 15 (victor 2/3) e 37 (Proc 3/1).</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="60">
       <c r="E66" s="33">
@@ -25910,17 +26300,17 @@
         <f>IF($C34="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25932,24 +26322,28 @@
 [IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
         </is>
       </c>
-      <c r="G34" s="30" t="inlineStr"/>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="60">
       <c r="B35" s="30">
         <f>IF($C35="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25961,24 +26355,28 @@
 [IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
         </is>
       </c>
-      <c r="G35" s="30" t="inlineStr"/>
+      <c r="G35" s="30" t="inlineStr">
+        <is>
+          <t>Passaria para ver a entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="60">
       <c r="B36" s="30">
         <f>IF($C36="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>Avaliador 1</t>
         </is>
@@ -25990,47 +26388,176 @@
 [IDENTIFICAÇÃO] Nome na capa e e-mail no último slide: Leandra Cunha de Souza (l304532@dac.unicamp.br). V1/V2 nas linhas 14 (victor 2/2) e 36 (Proc 2/2).</t>
         </is>
       </c>
-      <c r="G36" s="30" t="inlineStr"/>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>Passaria para ver a entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="60">
       <c r="B37" s="30">
         <f>IF($C37="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F37" s="73" t="n"/>
-      <c r="G37" s="30" t="n"/>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 12 — pasta entregas-candidatos/12 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F37" s="73" t="inlineStr">
+        <is>
+          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente: contou que a Estação Central faz fronteira com 5 bairros — conferi, está certo — e transformou isso num critério pontuado de "potencial de fronteira", usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou. A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação-armários à frente de Centro-parceiros, e marca Noite Alta com asterisco declarando que a posição depende de pesquisa — reconhecer incerteza em vez de simular precisão é maturidade. A terceira é a vantagem percentual por bairro (11,0% / 5,8% / 7,7% / 3,4%), usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses. O erro que eu cobraria está no slide 17: ela promove a oportunidade nº 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações — ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita. De forma, o custo veio dos títulos repetidos: três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia. Na entrevista eu faria as duas perguntas: como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou. Nota 7,93 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,81.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A aba Rascunho é material de trabalho cru, com a estrutura do case transcrita em abreviações (ec, ch, a, na) e typos de digitação rápida ("receita anula", "infliencia", "complexdade", "posições necessarias") — ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo que não sai de texto. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas, sinal de quem resolveu o arredondamento na mão. E o risco de "baixa conversão pela pressa" é uma observação idiossincrática sobre o público. Há ainda o typo "resltado" no eixo da matriz do slide 13. Pergunta de propriedade para a entrevista: quais são os 5 bairros de fronteira da Estação Central, e como as horas ociosas virariam lucro?
+[IDENTIFICAÇÃO] Nome no arquivo e no slide de fechamento: Mariana Nunes Galvão Sant'Anna. V1/V2 nas linhas 16 (luis 3/2) e 38 (Proc 2/3).</t>
+        </is>
+      </c>
+      <c r="G37" s="30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="60">
       <c r="B38" s="30">
         <f>IF($C38="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="30" t="n"/>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 13 — pasta entregas-candidatos/13 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F38" s="73" t="inlineStr">
+        <is>
+          <t>É a entrega mais frustrante do conjunto, porque a parte difícil está certa e a parte fácil não foi feita. Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas: anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade — ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou. E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some-se o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado. Sobre a projeção, ela também não sobrevive: ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais — corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar para a diretoria que este é o terceiro candidato a ler o banco como investimento (junto com as pastas 05 e 09), o que sugere que a redação do Anexo E merece um ajuste no próximo case. Na entrevista, se ele passar, a primeira pergunta é a que falta: você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda: por que o banco vale só no 1º ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case? Nota 3,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,48.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. É a pasta com a evidência de propriedade mais inequívoca do conjunto, ao lado da 05. Seis páginas de caderno fotografadas sob luz ruim, com a estrutura do case transcrita à mão, os 3C's aplicados, cada conta desenvolvida passo a passo e os totais circulados. A anotação "apenas 1º ano" ao lado do custo do banco documenta uma decisão de modelagem consciente. E a observação sobre a duração das conexões traz informação de fora do case, algo que texto gerado a partir do enunciado não produz, porque ele não questiona o input. A ausência de recomendação é falha de execução de quem ficou sem tempo, não artefato de geração — saída gerada tende a entregar a conclusão e economizar no meio, exatamente o inverso do que aconteceu aqui. Pergunta de propriedade para a entrevista: qual bairro e qual modelo você escolhe, e por que o banco só conta no 1º ano?
+[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="60">
       <c r="B39" s="30">
         <f>IF($C39="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F39" s="73" t="n"/>
-      <c r="G39" s="30" t="n"/>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 14 — pasta entregas-candidatos/14 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F39" s="73" t="inlineStr">
+        <is>
+          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso é difícil de pontuar de forma justa. O que ele fez de melhor ninguém mais fez: derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 h, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa — mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central "interceptando o cliente antes de todo mundo". É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez. E então ele não recomenda nada. O índice promete uma seção "Recomendação do lançamento" que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher — e o problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos. No cálculo há um deslize instrutivo: na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita — e usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude. Na entrevista eu faria três perguntas, e a primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? (Dá 5,04 h, e a resposta expõe a contradição do slide 8.) Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios — qual você recomenda e por quê? Nota 5,20 com V1 e V2 em branco; considerando só o que dá para avaliar, 5,78.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria, e o mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações; conferi e o valor está certo (7,06 h). Isso é raciocínio original, não recuperação de padrão. A contagem de adjacência exige abrir a imagem do mapa e olhar as fronteiras. A regra de robustez com limiares é um instrumento construído por ele. Do outro lado, os erros são humanos: typos ("perídodo", "font única"), numeração de página repetida (07 duas vezes, 09 duas vezes), a contradição entre o slide 6 e o slide 8 sobre qual bairro guarda itens por mais tempo, e o 920 contra 900 aparecendo nas duas colunas do mesmo slide. Esse último é assinatura de conta feita à mão. Pergunta de propriedade para a entrevista: como você chegou nas 7 horas de permanência, e quanto dá no Centro Histórico?
+[IDENTIFICAÇÃO] Nome na capa: Rafael Rodrigues Moreira. V1/V2 nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1).</t>
+        </is>
+      </c>
+      <c r="G39" s="30" t="inlineStr">
+        <is>
+          <t>Passaria para ver a entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="60">
       <c r="B40" s="30">
         <f>IF($C40="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F40" s="73" t="n"/>
-      <c r="G40" s="30" t="n"/>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 15 — pasta entregas-candidatos/15 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F40" s="73" t="inlineStr">
+        <is>
+          <t>O cálculo está perfeito e é praticamente tudo o que existe. Os oito cenários estão certos, desenvolvidos à mão, e a Arena — onde a maioria escorrega — está não só correta como autocorrigida: ele escreveu a divisão 900/40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo. O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo. O formato agrava: são oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável. O que existe de análise qualitativa está no rascunho, e é melhor do que parece — a lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível; faltou transformar em entrega. Na entrevista, se ele avançar, a pergunta é direta e vale tudo: você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade: por que a Arena arredonda para 23 e não fica em 22,5? Nota 2,63 com V1 e V2 em branco; considerando só o que dá para avaliar, 2,93.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Evidência de propriedade praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos do case à mão e as contas desenvolvidas passo a passo. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta — erro cometido e corrigido no próprio papel, o que não é fabricável. A ausência de recomendação é falha de execução de quem ficou sem tempo ou não entendeu o escopo do entregável, e não artefato de geração: texto gerado entrega a conclusão e economiza no desenvolvimento, exatamente o contrário do que ocorreu aqui. Pergunta de propriedade para a entrevista: por que a Arena arredonda para 23, e qual bairro e modelo você escolheria?
+[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="60">
       <c r="B41" s="30">
         <f>IF($C41="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="F41" s="73" t="n"/>
-      <c r="G41" s="30" t="n"/>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>Candidato 16 — pasta entregas-candidatos/16 (case BagHub 2026.2)</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>Avaliador 1</t>
+        </is>
+      </c>
+      <c r="F41" s="73" t="inlineStr">
+        <is>
+          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido? No slide 4 ele cria um critério de "fit com o serviço" e usa para questionar a própria demanda do material — observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade, e que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é uma leitura crítica de verdade, e ela reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição. O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso — reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade. As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável. Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes. Na entrevista eu iria atrás do melhor insight dele: você escreveu que o público de Noite Alta não carrega bagagem — então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000. Nota 7,70 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,56.
+INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria. O critério de "fit com o serviço" questiona os dados de demanda do próprio enunciado, e essa é justamente a coisa que saída gerada não faz, porque tende a aceitar o input como verdade — aqui ele confronta a projeção com comportamento real do público (quem vai a bar não leva mala, quem está em hotel não precisa de guarda-volumes). As mitigações são invenções operacionais concretas, como colocar staff da BagHub dentro do comércio parceiro no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos: a numeração da expansão recomeçando em 1º no slide 10 e conflitando com o slide 9, e a fórmula do slide 6 omitindo o arredondamento que o anexo do slide 13 declara e o valor da Arena comprova — inconsistência típica de documento escrito em duas passadas. Pergunta de propriedade para a entrevista: o que você faz com as 20 mil transações de Noite Alta se o público de lá não carrega bagagem?
+[IDENTIFICAÇÃO] Nome na capa: Vagner Ássimos Gomes Carlos Filho. V1/V2 nas linhas 15 (victor 2/3) e 37 (Proc 3/1).</t>
+        </is>
+      </c>
+      <c r="G41" s="30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="60">
       <c r="B42" s="30">

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como usar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base avaliação" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avaliação" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entrevista" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gabarito" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comentários" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Como usar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base avaliação" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Avaliação" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Consolidado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Entrevista" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gabarito" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comentários" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avaliação'!$A$5:$AI$206</definedName>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Candidato 02 — pasta entregas-candidatos/02 (case BagHub 2026.2)</t>
+          <t>Candidato 02 (pasta entregas-candidatos/02, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="O51" s="68" t="inlineStr">
         <is>
-          <t>C1=3: pag. 2, uma frase — "A BagHub deve lançar na Estação Central operando por pontos parceiros, com lucro operacional projetado de R$ 27,8 milhões no primeiro ano" — com o número na própria frase. C2=3: dois documentos fechados, capa, rodapé numerado nas 12 páginas e anexo de bases de cálculo paginado 1/5 a 5/5; enviaria ao cliente sem editar. C3=3: lendo só os títulos a história fecha sozinha — recomendação, custo decide, parceiros custam menos, decisão passa a ser de bairro, giro explica a margem, Estação lidera, riscos, piloto. C4=3: padrão único de fonte, cor e tabela nos dois arquivos, nenhuma página com parágrafo corrido.</t>
+          <t>C1=3: pag. 2, uma frase, "A BagHub deve lançar na Estação Central operando por pontos parceiros, com lucro operacional projetado de R$ 27,8 milhões no primeiro ano", com o número na própria frase. C2=3: dois documentos fechados, capa, rodapé numerado nas 12 páginas e anexo de bases de cálculo paginado 1/5 a 5/5; enviaria ao cliente sem editar. C3=3: lendo só os títulos a história fecha sozinha, recomendação, custo decide, parceiros custam menos, decisão passa a ser de bairro, giro explica a margem, Estação lidera, riscos, piloto. C4=3: padrão único de fonte, cor e tabela nos dois arquivos, nenhuma página com parágrafo corrido.</t>
         </is>
       </c>
       <c r="P51" s="41" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="T51" s="68" t="inlineStr">
         <is>
-          <t>R1=3: pag. 2 e 7 amarram R$ 27,8M à razão de negócio (prioridade declarada é rentabilidade anual, margem de 77,3% como colchão, capacidade contratável em qualquer bairro); tapando o número o argumento continua, tapando o argumento o 27,8M continua sendo o máximo dos oito. R2=3: pag. 5 compara Estação Central e Centro Histórico em cinco métricas lado a lado, pag. 7 justifica por escrito por que descartou o Centro Histórico apesar dos 90,7% de margem, e pag. 9 ordena os quatro explicando por que Noite Alta vem antes da Arena. R3=3: trouxe giro semanal por posição, lucro por posição e a prova de dominância da seção 5.1 — o prêmio do parceiro (R$ 400 a R$ 1.400 por posição) é sempre menor que o banco rateado (R$ 1.750), o que generaliza a escolha do modelo para além dos oito casos e fortalece a recomendação. R4=3: pag. 6 explica a causa — a Estação precisa de 2,4x mais posições para 1,33x mais transações porque cada posição gira 10 vezes por semana contra 18 no Centro Histórico, e liga isso à ocasião de uso.</t>
+          <t>R1=3: pag. 2 e 7 amarram R$ 27,8M à razão de negócio (prioridade declarada é rentabilidade anual, margem de 77,3% como colchão, capacidade contratável em qualquer bairro); tapando o número o argumento continua, tapando o argumento o 27,8M continua sendo o máximo dos oito. R2=3: pag. 5 compara Estação Central e Centro Histórico em cinco métricas lado a lado, pag. 7 justifica por escrito por que descartou o Centro Histórico apesar dos 90,7% de margem, e pag. 9 ordena os quatro explicando por que Noite Alta vem antes da Arena. R3=3: trouxe giro semanal por posição, lucro por posição e a prova de dominância da seção 5.1, o prêmio do parceiro (R$ 400 a R$ 1.400 por posição) é sempre menor que o banco rateado (R$ 1.750), o que generaliza a escolha do modelo para além dos oito casos e fortalece a recomendação. R4=3: pag. 6 explica a causa, a Estação precisa de 2,4x mais posições para 1,33x mais transações porque cada posição gira 10 vezes por semana contra 18 no Centro Histórico, e liga isso à ocasião de uso.</t>
         </is>
       </c>
       <c r="U51" s="41" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="AA51" s="68" t="inlineStr">
         <is>
-          <t>A1 e A2=3: refiz os oito cenários pelos Anexos C e E e todos conferem — Estação Central 27,84M e 25,08M, Centro Histórico 24,5M e 23,15M, Noite Alta 19,2M e 18,57M, Arena 14,94M e 13,87M. Bancos 60/25/23/45, com a Arena correta (900/40 = 22,5 arredondado para 23, R$ 1,61M). Memória visível na seção 4 do anexo, cálculo por extenso da Estação Central, e na tabela de composição da seção 5. A3=3: a ordem de expansão da pag. 9 fecha com a própria tabela dele; ressalva de que este case não declara meta numérica, então essa parte do descritor não é testável. A4=3: quantificou o trade-off Estação Central x Centro Histórico (R$ 3,3M a mais em absoluto contra R$ 24.500 x R$ 11.600 de lucro por posição). A5=3: quatro riscos na pag. 10, todos específicos do modelo de parceiros, cada um com mitigação contratual (teto de participação, contratos plurianuais com preço travado, lista de suplentes, horário mínimo com desconto) e a contratação em etapas travada em dado real. Prazo aparece como termo contratual ("preço travado por prazo definido", contratos plurianuais) mas sem duração fixada — ponto mais fraco do 3, contestável por um 2º avaliador. A6=1: o case não traz erro plantado. Ele declarou a premissa P3 citando o Anexo C e não descontou transações, ou seja, passou pelo ponto certo sem nomear inconsistência nenhuma — mesma situação da pasta 01.</t>
+          <t>A1 e A2=3: refiz os oito cenários pelos Anexos C e E e todos conferem, Estação Central 27,84M e 25,08M, Centro Histórico 24,5M e 23,15M, Noite Alta 19,2M e 18,57M, Arena 14,94M e 13,87M. Bancos 60/25/23/45, com a Arena correta (900/40 = 22,5 arredondado para 23, R$ 1,61M). Memória visível na seção 4 do anexo, cálculo por extenso da Estação Central, e na tabela de composição da seção 5. A3=3: a ordem de expansão da pag. 9 fecha com a própria tabela dele; ressalva de que este case não declara meta numérica, então essa parte do descritor não é testável. A4=3: quantificou o trade-off Estação Central x Centro Histórico (R$ 3,3M a mais em absoluto contra R$ 24.500 x R$ 11.600 de lucro por posição). A5=3: quatro riscos na pag. 10, todos específicos do modelo de parceiros, cada um com mitigação contratual (teto de participação, contratos plurianuais com preço travado, lista de suplentes, horário mínimo com desconto) e a contratação em etapas travada em dado real. Prazo aparece como termo contratual ("preço travado por prazo definido", contratos plurianuais) mas sem duração fixada, ponto mais fraco do 3, contestável por um 2º avaliador. A6=1: o case não traz erro plantado. Ele declarou a premissa P3 citando o Anexo C e não descontou transações, ou seja, passou pelo ponto certo sem nomear inconsistência nenhuma, mesma situação da pasta 01.</t>
         </is>
       </c>
       <c r="AB51" s="41" t="n">
@@ -8295,14 +8295,18 @@
       <c r="AG51" s="41" t="n"/>
       <c r="AH51" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: as notas da etapa de vídeo não vieram com a pasta. O nome está no arquivo (Aslan Rodrigues Maia), então dá para transcrever das linhas 17 e 39. Enquanto ficarem em branco, entram como zero e puxam 10 pontos. E1=0 e E3=0 porque não há planilha nem vídeo de entrega na pasta — mas o enunciado deste semestre não pediu esses entregáveis, e o anexo de bases de cálculo cumpre a função de memória de cálculo. Recomendo neutralizar E1 e E3 para todos.</t>
+          <t>V1 e V2 em branco: as notas da etapa de vídeo não vieram com a pasta. O nome está no arquivo (Aslan Rodrigues Maia), então dá para transcrever das linhas 17 e 39. Enquanto ficarem em branco, entram como zero e puxam 10 pontos. E1=0 e E3=0 porque não há planilha nem vídeo de entrega na pasta, mas o enunciado deste semestre não pediu esses entregáveis, e o anexo de bases de cálculo cumpre a função de memória de cálculo. Recomendo neutralizar E1 e E3 para todos.</t>
         </is>
       </c>
       <c r="AI51" s="68" t="inlineStr">
         <is>
-          <t>Melhor entrega do conjunto até aqui, e o que separa é a prova de dominância. Em vez de só reportar que os parceiros ganham nos quatro bairros, ele mostra por que: o banco de 40 posições rateado dá R$ 1.750 por posição por ano e o prêmio que o parceiro cobra sobre a operação vai de R$ 400 a R$ 1.400 — como o prêmio é sempre menor, a escolha do modelo se separa da escolha do bairro. Isso é um resultado que sobrevive a mudança de parâmetro, não uma leitura de tabela. Os oito cenários fecham todos, incluindo o arredondamento da Arena, e o anexo traz as premissas numeradas P0 a P11 com a fonte de cada uma. A tensão real do case ele encontrou e resolveu: o Centro Histórico rende R$ 24.500 por posição contra R$ 11.600 da Estação Central, mas a prioridade declarada é rentabilidade anual e a capacidade é contratável, então o lucro por posição não limita o crescimento. O que falta é prazo nos riscos: as mitigações são boas e contratuais, mas nenhuma tem data, e o piloto da pag. 11 não tem duração. Também não há análise de sensibilidade numérica, embora a seção 5.1 funcione como um breakeven implícito. Na entrevista eu pediria: se o banco de armários custasse R$ 50.000 em vez de R$ 70.000, o que muda na sua recomendação? A resposta certa é que o rateio cai para R$ 1.250 por posição, fica abaixo do prêmio de R$ 1.400 da complexidade alta, e os armários passam a ganhar em Noite Alta — quem montou a seção 5.1 responde isso em um minuto. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Vários indícios de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural específico deste case, não uma leitura dos oito números — é o tipo de generalização que não aparece em saída genérica. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento na pag. 11, ou seja, tirou um "e daí" do próprio número. A profundidade é desigual de propósito: o anexo faz a Estação Central por extenso e resume os outros três bairros, exatamente o corte de quem tinha um fim de semana. O único ponto que poderia levantar dúvida é o acabamento formal do anexo, aparentemente composto em LaTeX com notação matemática e premissas numeradas — mas acabamento não é evidência de IA, e a composição em LaTeX aponta para o contrário, porque exige trabalho manual. Pergunta de propriedade para a entrevista: a partir de que custo de banco os armários passam a ganhar em Noite Alta?
-[IDENTIFICAÇÃO] Nome no arquivo: Aslan Rodrigues Maia. V1/V2 dele existem nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3).</t>
+          <t>Melhor entrega que li. O que separa ele dos outros não é a conta, é ter provado por que parceiros ganham. O banco de 40 posições rateado dá R$ 1.750 por posição, e o prêmio que o parceiro cobra sobre a operação vai de R$ 400 a R$ 1.400. Como o prêmio é sempre menor, a escolha do modelo passa a não depender do bairro. Isso é um resultado que sobrevive a mudança de parâmetro, não leitura de tabela.
+Os oito cenários fecham todos, inclusive o arredondamento da Arena. O anexo traz as premissas numeradas de P0 a P11, cada uma com a fonte. Ele achou a tensão do case e resolveu: o Centro Histórico rende R$ 24.500 por posição contra R$ 11.600 da Estação, mas a prioridade declarada é rentabilidade anual e a capacidade é contratável, então lucro por posição não limita crescimento.
+Falta prazo nos riscos. As mitigações são boas e contratuais, só que nenhuma tem data e o piloto não tem duração. Também não fez sensibilidade numérica, embora a seção 5.1 funcione como breakeven implícito.
+Na entrevista eu pergunto: se o banco custasse R$ 50.000, o que muda? A resposta é que o rateio cai para R$ 1.250, fica abaixo do prêmio de R$ 1.400 da alta complexidade, e os armários passam a ganhar em Noite Alta. Quem montou aquela seção responde em um minuto.
+Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
+Indício de IA: Baixo (consultivo, não afeta nota). Vários sinais de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural deste case, não leitura dos oito números. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento. A profundidade é desigual de propósito: o anexo faz a Estação por extenso e resume os outros três, o corte de quem tinha um fim de semana. O acabamento do anexo em LaTeX poderia levantar dúvida, mas acabamento não é evidência, e compor em LaTeX aponta para o contrário.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Aslan Rodrigues Maia. As notas de vídeo dele estão nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8318,7 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Candidato 03 — pasta entregas-candidatos/03 (case BagHub 2026.2)</t>
+          <t>Candidato 03 (pasta entregas-candidatos/03, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8360,7 +8364,7 @@
       </c>
       <c r="O52" s="68" t="inlineStr">
         <is>
-          <t>C1=3: pag. 1, em destaque — "eu começaria pela Estação Central usando Pontos parceiros. O principal motivo é o resultado operacional anual de R$ 27,84 milhões", com o número na frase e na primeira página. C2=2: o documento é completo e tem seções numeradas, rodapé e citação da fonte, mas é escrito inteiro em primeira pessoa com hedge constante ("Eu não diria que isso prova", "não achei correto", "Para mim") — é um relatório de reflexão pessoal, não um documento que um cliente receberia como está. C3=1: aplicando o teste operacional, os títulos são rótulos genéricos ("4. Cálculo da rentabilidade", "6. Minha escolha para o lançamento") e a recomendação não aparece em nenhum deles; lendo só os títulos você sabe que existe uma escolha, não qual é. A sequência interna é lógica, o que torna este 1 o item mais contestável da minha correção. C4=3: fonte, tabelas e rodapé no mesmo padrão nas 10 páginas, nenhuma fora do padrão.</t>
+          <t>C1=3: pag. 1, em destaque, "eu começaria pela Estação Central usando Pontos parceiros. O principal motivo é o resultado operacional anual de R$ 27,84 milhões", com o número na frase e na primeira página. C2=2: o documento é completo e tem seções numeradas, rodapé e citação da fonte, mas é escrito inteiro em primeira pessoa com hedge constante ("Eu não diria que isso prova", "não achei correto", "Para mim"), é um relatório de reflexão pessoal, não um documento que um cliente receberia como está. C3=1: aplicando o teste operacional, os títulos são rótulos genéricos ("4. Cálculo da rentabilidade", "6. Minha escolha para o lançamento") e a recomendação não aparece em nenhum deles; lendo só os títulos você sabe que existe uma escolha, não qual é. A sequência interna é lógica, o que torna este 1 o item mais contestável da minha correção. C4=3: fonte, tabelas e rodapé no mesmo padrão nas 10 páginas, nenhuma fora do padrão.</t>
         </is>
       </c>
       <c r="P52" s="41" t="n">
@@ -8377,7 +8381,7 @@
       </c>
       <c r="T52" s="68" t="inlineStr">
         <is>
-          <t>R1=3: pag. 7 dá três motivos amarrados — R$ 27,84M, escala de 24 mil transações/semana e a âncora do terminal — mais o argumento de que o modelo parceiro não exige comprar bancos, o que simplifica a estrutura de quem está começando; tapando o número os motivos de escala e capex continuam, tapando o argumento o 27,84M continua sendo o máximo. R2=3: pag. 5 traz os oito cenários, pag. 6 compara os dois modelos com a conta da diferença (operação R$ 1,44M a mais contra R$ 4,20M de bancos), e pag. 7 descarta por escrito Arena (concentração em eventos) e Noite Alta (horário e complexidade), com o Centro Histórico nomeado como segunda opção a R$ 24,50M. R3=1: entregou as quatro tarefas de forma completa e correta, mas não trouxe nada de fato além do pedido — a única métrica derivada (posições ocupadas em média, pag. 4) está dentro da tarefa de demanda e capacidade e ele mesmo a neutraliza como indicador, sem sensibilidade, breakeven ou economia por posição. R4=2: pag. 4 compara a utilização entre os quatro bairros e tira conclusão metodológica correta (separar volume de ocupação, misturar distorceria a receita), mas a causa que ele dá é a que o próprio case já informa (capacidade dimensionada para picos); não explica por que a utilização do Centro Histórico é maior nem por que a Estação precisa de 2,4x mais posições para 1,33x mais transações.</t>
+          <t>R1=3: pag. 7 dá três motivos amarrados, R$ 27,84M, escala de 24 mil transações/semana e a âncora do terminal, mais o argumento de que o modelo parceiro não exige comprar bancos, o que simplifica a estrutura de quem está começando; tapando o número os motivos de escala e capex continuam, tapando o argumento o 27,84M continua sendo o máximo. R2=3: pag. 5 traz os oito cenários, pag. 6 compara os dois modelos com a conta da diferença (operação R$ 1,44M a mais contra R$ 4,20M de bancos), e pag. 7 descarta por escrito Arena (concentração em eventos) e Noite Alta (horário e complexidade), com o Centro Histórico nomeado como segunda opção a R$ 24,50M. R3=1: entregou as quatro tarefas de forma completa e correta, mas não trouxe nada de fato além do pedido, a única métrica derivada (posições ocupadas em média, pag. 4) está dentro da tarefa de demanda e capacidade e ele mesmo a neutraliza como indicador, sem sensibilidade, breakeven ou economia por posição. R4=2: pag. 4 compara a utilização entre os quatro bairros e tira conclusão metodológica correta (separar volume de ocupação, misturar distorceria a receita), mas a causa que ele dá é a que o próprio case já informa (capacidade dimensionada para picos); não explica por que a utilização do Centro Histórico é maior nem por que a Estação precisa de 2,4x mais posições para 1,33x mais transações.</t>
         </is>
       </c>
       <c r="U52" s="41" t="n">
@@ -8400,7 +8404,7 @@
       </c>
       <c r="AA52" s="68" t="inlineStr">
         <is>
-          <t>A1 e A2=3: os oito cenários conferem com o meu recálculo. A memória de cálculo é a melhor do conjunto — planilha real com fórmulas vivas, ROUNDUP(C/40) gerando 60/25/23/45 bancos e referências entre abas (Resumo puxa de Premissas e Cálculos), mais o exemplo por extenso da Estação Central na pag. 5. Arena com 23 bancos correta. A3=2: a ordem de expansão tem número (Centro Histórico a R$ 24,50M como segundo, pag. 7), mas o plano da pag. 9 é narrativo em cinco passos sem nenhum número e sem ponte entre períodos; o case não declara meta numérica, então a parte do descritor que compara com a meta não é testável. A4=3: Centro Histórico proposto como alternativa com impacto quantificado em R$ 24,50M e a razão da baixa complexidade. A5=2: os cinco pontos de validação da pag. 8 são específicos da recomendação dele (disponibilidade real de parceiros é específica do modelo parceiro, picos da Estação são específicos do bairro escolhido) e a pag. 9 traz mitigação real em cinco passos travados no piloto — mas não há prazo em lugar nenhum, nem duração do piloto. Fica entre os descritores: supera o 2 na mitigação e não alcança o 3 por falta de prazo; registro para o 2º avaliador contestar. A6=1: o case não traz erro plantado. Ele nomeia e justifica o único ponto ambíguo — pag. 2 e aba Notas, "a utilização não deve ser aplicada como desconto", citando o material — mas o que nomeou é a instrução do próprio case, não uma inconsistência. Mesma situação de todas as pastas.</t>
+          <t>A1 e A2=3: os oito cenários conferem com o meu recálculo. A memória de cálculo é a melhor do conjunto, planilha real com fórmulas vivas, ROUNDUP(C/40) gerando 60/25/23/45 bancos e referências entre abas (Resumo puxa de Premissas e Cálculos), mais o exemplo por extenso da Estação Central na pag. 5. Arena com 23 bancos correta. A3=2: a ordem de expansão tem número (Centro Histórico a R$ 24,50M como segundo, pag. 7), mas o plano da pag. 9 é narrativo em cinco passos sem nenhum número e sem ponte entre períodos; o case não declara meta numérica, então a parte do descritor que compara com a meta não é testável. A4=3: Centro Histórico proposto como alternativa com impacto quantificado em R$ 24,50M e a razão da baixa complexidade. A5=2: os cinco pontos de validação da pag. 8 são específicos da recomendação dele (disponibilidade real de parceiros é específica do modelo parceiro, picos da Estação são específicos do bairro escolhido) e a pag. 9 traz mitigação real em cinco passos travados no piloto, mas não há prazo em lugar nenhum, nem duração do piloto. Fica entre os descritores: supera o 2 na mitigação e não alcança o 3 por falta de prazo; registro para o 2º avaliador contestar. A6=1: o case não traz erro plantado. Ele nomeia e justifica o único ponto ambíguo, pag. 2 e aba Notas, "a utilização não deve ser aplicada como desconto", citando o material, mas o que nomeou é a instrução do próprio case, não uma inconsistência. Mesma situação de todas as pastas.</t>
         </is>
       </c>
       <c r="AB52" s="41" t="n">
@@ -8419,14 +8423,19 @@
       <c r="AG52" s="41" t="n"/>
       <c r="AH52" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está no arquivo (Bruno Heberth), então dá para transcrever das linhas 8 e 30. E1=1: é o único do conjunto até aqui com planilha de verdade, .xlsx com cinco abas e fórmulas vivas. E3=0, sem vídeo de entrega — item que o enunciado não pediu e que recomendo neutralizar para todos.</t>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está no arquivo (Bruno Heberth), então dá para transcrever das linhas 8 e 30. E1=1: é o único do conjunto até aqui com planilha de verdade.xlsx com cinco abas e fórmulas vivas. E3=0, sem vídeo de entrega, item que o enunciado não pediu e que recomendo neutralizar para todos.</t>
         </is>
       </c>
       <c r="AI52" s="68" t="inlineStr">
         <is>
-          <t>Entrega honesta e bem conferida, com o melhor artefato de propriedade do conjunto: a planilha tem fórmulas vivas, ROUNDUP e referências entre abas, não é tabela colada. Os oito cenários fecham. O que me chamou atenção foi o cuidado epistêmico — ele separa o que a conta mostra do que a conta não mostra, declina de criar estimativa onde falta dado ("eu preferi apontar a questão em vez de criar uma estimativa") e se recusa a generalizar que parceiros ganham sempre, dizendo que depende dos custos do case. Esse último ponto é onde ele deixa valor na mesa: a generalização era possível e é exatamente o que separa a pasta 02, que provou que o prêmio do parceiro é sempre menor que o banco rateado. O custo maior está na comunicação: os títulos são rótulos de seção e não mensagens, então a recomendação não sobrevive à leitura só dos títulos, e o texto em primeira pessoa com hedge a cada parágrafo tira o documento do registro de entregável de cliente. São dois ajustes de forma que valem muitos pontos e não mudam nada do conteúdo. Faltam prazo nos riscos e qualquer análise de sensibilidade. Na entrevista eu pediria a conta que ele se recusou a fazer: a partir de que custo do banco de armários o modelo de armários passa a ganhar na Estação Central? Sai da planilha dele em um minuto — o banco teria que cair para R$ 24.000, porque o prêmio do parceiro na complexidade moderada é R$ 600 por posição e 600 x 40 = 24.000. Nota 7,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,93.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não uma tabela renderizada — é o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na pag. 5 ("Na revisão, conferi especialmente o arredondamento dos bancos... esse é um ponto em que um pequeno erro muda bastante o resultado"), o que é metacognição sobre o próprio trabalho. Recusa-se explicitamente a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. E a profundidade é desigual: páginas 3 a 5 densas, 8 e 9 em lista mais leve. O texto é limpo e organizado, mas isso não é evidência de nada. Pergunta de propriedade para a entrevista: a partir de que custo de banco os armários ganham na Estação Central?
-[IDENTIFICAÇÃO] Nome no arquivo: Bruno Heberth Oliveira Bastos. V1/V2 nas linhas 8 (victor 3/1) e 30 (Fred 3/1). ATENÇÃO: a pasta 03 também contém os dois PDFs do Aslan, byte-idênticos aos da pasta 02 (MD5 confere) — arquivos fora de lugar, desconsiderados nesta avaliação.</t>
+          <t>Entrega honesta e bem conferida. Tem o melhor artefato de propriedade do conjunto: a planilha é um modelo que funciona, com ROUNDUP, fórmulas encadeadas e referências entre abas. Não é tabela colada. Os oito cenários fecham.
+Gostei do cuidado dele em separar o que a conta mostra do que a conta não mostra. Onde falta dado, ele aponta a lacuna em vez de inventar estimativa. Na página 5 ainda conta como conferiu o próprio trabalho, dizendo que revisou especialmente o arredondamento dos bancos porque um erro pequeno ali muda bastante o resultado.
+O problema é que ele se recusa a generalizar. Diz que não daria para afirmar que parceiros ganham sempre, que depende dos custos do case. Só que a generalização era possível, e é exatamente o que separa a pasta 02.
+O custo maior está na comunicação. Os títulos são rótulos de seção, não mensagens, então a recomendação não sobrevive à leitura só dos títulos. E o texto em primeira pessoa com hedge a cada parágrafo tira o documento do registro de entregável de cliente. São dois ajustes de forma que valem muitos pontos e não mudam nada do conteúdo. Faltam prazo nos riscos e qualquer sensibilidade.
+Na entrevista eu peço a conta que ele se recusou a fazer: a partir de que custo de banco os armários ganham na Estação? Sai da planilha dele, o banco teria que cair para R$ 24.000.
+Nota 7,13 com vídeo em branco. Considerando só o que dá para avaliar, 7,93.
+Indício de IA: Baixo (consultivo, não afeta nota). A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não tabela renderizada. É o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na página 5 e se recusa a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. Profundidade desigual entre as páginas.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Bruno Heberth Oliveira Bastos. As notas de vídeo dele estão nas linhas 8 (victor 3/1) e 30 (Fred 3/1) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8447,7 @@
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Candidato 04 — pasta entregas-candidatos/04 (case BagHub 2026.2)</t>
+          <t>Candidato 04 (pasta entregas-candidatos/04, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8484,7 +8493,7 @@
       </c>
       <c r="O53" s="68" t="inlineStr">
         <is>
-          <t>C1=2: a recomendação é explícita e clara — "minha indicação é de que a BagHub deve ser implantada no Centro Histórico adotando o modelo de armários inteligentes" — mas está na última frase da pag. 5 de 5, e a introdução ainda anuncia "ao final recomendaremos", ou seja, o leitor precisa chegar ao fim. Sem número na frase. C2=1: texto corrido sem capa, sem rodapé, sem numeração de página e sem uma única tabela; os dados aparecem como listas "Dados:" e "Cálculos:" embutidas no texto, e o bloco de dados da Estação Central quebra no meio da pag. 1 para a 2. É formato de rascunho. C3=1: teste operacional — os títulos são Introdução, Desenvolvimento, 1. Estação central, 2. Centro histórico, 3. Arena, 4. Noite Alta, Conclusão; a recomendação não aparece em nenhum, e as quatro seções de bairro são paralelas e independentes, nenhuma puxa a seguinte. C4=1: formatação improvisada mas legível — fonte única, porém nenhum recurso visual, nenhuma numeração, nenhum cabeçalho.</t>
+          <t>C1=2: a recomendação é explícita e clara, "minha indicação é de que a BagHub deve ser implantada no Centro Histórico adotando o modelo de armários inteligentes", mas está na última frase da pag. 5 de 5, e a introdução ainda anuncia "ao final recomendaremos", ou seja, o leitor precisa chegar ao fim. Sem número na frase. C2=1: texto corrido sem capa, sem rodapé, sem numeração de página e sem uma única tabela; os dados aparecem como listas "Dados:" e "Cálculos:" embutidas no texto, e o bloco de dados da Estação Central quebra no meio da pag. 1 para a 2. É formato de rascunho. C3=1: teste operacional, os títulos são Introdução, Desenvolvimento, 1. Estação central, 2. Centro histórico, 3. Arena, 4. Noite Alta, Conclusão; a recomendação não aparece em nenhum, e as quatro seções de bairro são paralelas e independentes, nenhuma puxa a seguinte. C4=1: formatação improvisada mas legível, fonte única, porém nenhum recurso visual, nenhuma numeração, nenhum cabeçalho.</t>
         </is>
       </c>
       <c r="P53" s="41" t="n">
@@ -8501,7 +8510,7 @@
       </c>
       <c r="T53" s="68" t="inlineStr">
         <is>
-          <t>R1=0: a recomendação contraria os próprios números. Ele declara na pag. 4 que "a principal métrica será a margem bruta" e, dentro do Centro Histórico, escolhe armários (85,7%) em vez de parceiros (90,7%), que também é o de maior resultado absoluto (R$ 24,50M contra R$ 23,15M). Ou seja, escolheu a pior opção pela própria métrica que declarou, e justifica com argumentos qualitativos (operação 24h, escalabilidade, inovação) sem reconhecer que está sacrificando R$ 1,35M por ano. Além disso a métrica escolhida contraria a prioridade declarada no case, que é rentabilidade anual. R2=2: ele elimina bairros por escrito e com critério, mas a comparação não se sustenta — descarta a Estação Central alegando "alta complexidade operacional" quando ele mesmo escreveu "complexidade operacional moderada" na pag. 1, e afirma que a Arena tem margem abaixo de 80% "tanto no modelo de armários quanto de pontos parceiros" quando parceiros dá 83,0%. Na escolha do modelo calcula a diferença de R$ 1.350.000 (5% da receita) e a descarta como "não tão alta" sem ponderar o trade-off. R3=0: o pedido ficou incompleto — o enunciado pede riscos e próximos passos de forma qualitativa na tarefa 04 e não há nenhuma das duas coisas no documento. R4=1: lê as margens do Centro Histórico corretamente, mas erra o driver — atribui o custo alto da Estação Central à complexidade (que é moderada) quando a causa é ter 2.400 posições, e usa a utilização de 54% como se fosse sinal de qualidade do bairro ("isso confirma nossa escolha"), leitura que o próprio case adverte contra.</t>
+          <t>R1=0: a recomendação contraria os próprios números. Ele declara na pag. 4 que "a principal métrica será a margem bruta" e, dentro do Centro Histórico, escolhe armários (85,7%) em vez de parceiros (90,7%), que também é o de maior resultado absoluto (R$ 24,50M contra R$ 23,15M). Ou seja, escolheu a pior opção pela própria métrica que declarou, e justifica com argumentos qualitativos (operação 24h, escalabilidade, inovação) sem reconhecer que está sacrificando R$ 1,35M por ano. Além disso a métrica escolhida contraria a prioridade declarada no case, que é rentabilidade anual. R2=2: ele elimina bairros por escrito e com critério, mas a comparação não se sustenta, descarta a Estação Central alegando "alta complexidade operacional" quando ele mesmo escreveu "complexidade operacional moderada" na pag. 1, e afirma que a Arena tem margem abaixo de 80% "tanto no modelo de armários quanto de pontos parceiros" quando parceiros dá 83,0%. Na escolha do modelo calcula a diferença de R$ 1.350.000 (5% da receita) e a descarta como "não tão alta" sem ponderar o trade-off. R3=0: o pedido ficou incompleto, o enunciado pede riscos e próximos passos de forma qualitativa na tarefa 04 e não há nenhuma das duas coisas no documento. R4=1: lê as margens do Centro Histórico corretamente, mas erra o driver, atribui o custo alto da Estação Central à complexidade (que é moderada) quando a causa é ter 2.400 posições, e usa a utilização de 54% como se fosse sinal de qualidade do bairro ("isso confirma nossa escolha"), leitura que o próprio case adverte contra.</t>
         </is>
       </c>
       <c r="U53" s="41" t="n">
@@ -8524,7 +8533,7 @@
       </c>
       <c r="AA53" s="68" t="inlineStr">
         <is>
-          <t>A1=2: sete dos oito resultados conferem (Estação 36M/25,08M/27,84M, Centro 27M/23,15M/24,5M, Noite Alta 30M/18,57M/19,2M). A receita tem memória visível (24.000 x 50 x 30), mas os custos aparecem só como totais — em nenhum lugar do documento há a decomposição em equipamento, operação e bancos, então o teto de A1 é 2 por memória de cálculo ausente. A2=1: identificou a lógica correta do custo na pag. 1 (somatório das despesas por posição x posições) mas não fechou o número dos bancos — na Arena usou 22,5 bancos em vez de arredondar para 23, chegando a custo de R$ 4.095.000 contra R$ 4.130.000 e resultado de R$ 13.905.000 contra R$ 13.870.000. O erro de R$ 35.000 cai dentro da tolerância de ±2% por ser pequeno, mas o método contraria instrução explícita do Anexo E; um 2º avaliador pode defender 2 em vez de 1 justamente porque o valor ficou na tolerância. A3=0: não fez — não há projeção, plano de expansão, fasemento nem próximos passos. A4=1: o mais próximo de alternativa é o argumento de que os armários têm "maior potencial de crescimento e maior escalabilidade, além de ser um negócio inovador", que serviria para qualquer empresa e não cita nada que só exista neste case. A5=0: não fez — nenhum risco e nenhum próximo passo, embora o enunciado peça explicitamente. A6=1: o case não traz erro plantado. Ele não descontou as transações pela utilização, então passou pelo ponto certo, mas não nomeou nada — e de fato usou a utilização de forma equivocada na conclusão.</t>
+          <t>A1=2: sete dos oito resultados conferem (Estação 36M/25,08M/27,84M, Centro 27M/23,15M/24,5M, Noite Alta 30M/18,57M/19,2M). A receita tem memória visível (24.000 x 50 x 30), mas os custos aparecem só como totais, em nenhum lugar do documento há a decomposição em equipamento, operação e bancos, então o teto de A1 é 2 por memória de cálculo ausente. A2=1: identificou a lógica correta do custo na pag. 1 (somatório das despesas por posição x posições) mas não fechou o número dos bancos, na Arena usou 22,5 bancos em vez de arredondar para 23, chegando a custo de R$ 4.095.000 contra R$ 4.130.000 e resultado de R$ 13.905.000 contra R$ 13.870.000. O erro de R$ 35.000 cai dentro da tolerância de ±2% por ser pequeno, mas o método contraria instrução explícita do Anexo E; um 2º avaliador pode defender 2 em vez de 1 justamente porque o valor ficou na tolerância. A3=0: não fez, não há projeção, plano de expansão, fasemento nem próximos passos. A4=1: o mais próximo de alternativa é o argumento de que os armários têm "maior potencial de crescimento e maior escalabilidade, além de ser um negócio inovador", que serviria para qualquer empresa e não cita nada que só exista neste case. A5=0: não fez, nenhum risco e nenhum próximo passo, embora o enunciado peça explicitamente. A6=1: o case não traz erro plantado. Ele não descontou as transações pela utilização, então passou pelo ponto certo, mas não nomeou nada, e de fato usou a utilização de forma equivocada na conclusão.</t>
         </is>
       </c>
       <c r="AB53" s="41" t="n">
@@ -8543,14 +8552,19 @@
       <c r="AG53" s="41" t="n"/>
       <c r="AH53" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta e a pasta é anônima, sem nome no arquivo, então não dá para transcrever sem o mapa número-candidato. E1=0, sem planilha. E3=0, sem vídeo de entrega. Os dois itens não foram pedidos no enunciado e recomendo neutralizar para todos. E4=0: nenhum gráfico e nenhuma tabela no documento inteiro — este zero é de mérito, o material existe e não atende ao descritor.</t>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta e a pasta é anônima, sem nome no arquivo, então não dá para transcrever sem o mapa número-candidato. E1=0, sem planilha. E3=0, sem vídeo de entrega. Os dois itens não foram pedidos no enunciado e recomendo neutralizar para todos. E4=0: nenhum gráfico e nenhuma tabela no documento inteiro, este zero é de mérito, o material existe e não atende ao descritor.</t>
         </is>
       </c>
       <c r="AI53" s="68" t="inlineStr">
         <is>
-          <t>O problema desta entrega não é a conta, é a decisão. Sete dos oito cenários estão certos e a receita tem memória visível, mas a conclusão anda para o lado oposto dos números. Ele declara que a métrica principal é a margem bruta e então, dentro do bairro que escolheu, prefere armários a 85,7% em vez de parceiros a 90,7% — que também rende R$ 1,35M mais por ano. Escolheu a pior opção pela régua que ele mesmo definiu, e a régua já contrariava a prioridade declarada no case, que é rentabilidade anual, não margem. Some a isso duas contradições factuais: a Estação Central é descartada por "alta complexidade" na pag. 4 depois de ele escrever "complexidade moderada" na pag. 1, e a Arena é descartada por margem abaixo de 80% quando parceiros dá 83,0%. O único erro de cálculo é a Arena com 22,5 bancos em vez de 23, que por ser pequeno caiu na tolerância. Faltam riscos e próximos passos, que o enunciado pede na tarefa 04, e não há uma tabela ou gráfico em cinco páginas de texto corrido. Na entrevista eu faria duas perguntas diretas, e são as mesmas que revelam se ele enxerga o problema: você disse que a métrica principal é a margem bruta, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação Central tem complexidade moderada na pag. 1 e alta na pag. 4 — qual das duas? Nota 2,97 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,30.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. O padrão de erros aponta para autoria própria sem assistência. A contradição interna entre pag. 1 e pag. 4 sobre a complexidade da Estação Central é o tipo de inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural ("iremos analisar", "apresentaremos") para primeira do singular na última frase ("minha indicação"). Deixou de arredondar os bancos da Arena, apesar de a instrução estar escrita no Anexo E — IA tende a seguir instrução explícita. E a ausência total de tabela, numeração e estrutura é o oposto da over-estruturação típica de texto gerado. A recomendação que contraria a própria métrica é falha de raciocínio, não artefato de geração. Pergunta de propriedade para a entrevista: por que armários a 85,7% e não parceiros a 90,7% no Centro Histórico?
-[IDENTIFICAÇÃO] Sem nome no arquivo — pasta permanece anônima.</t>
+          <t>O problema aqui não é a conta, é a decisão. Sete dos oito cenários estão certos e a receita tem memória visível. Só que a conclusão anda para o lado oposto dos números.
+Ele diz que a métrica principal é a margem bruta e então, dentro do bairro que escolheu, prefere armários a 85,7% em vez de parceiros a 90,7%. Parceiros também rendem R$ 1,35 milhão mais por ano. Ou seja, escolheu a pior opção pela régua que ele mesmo definiu. E a régua já contrariava a prioridade do case, que é rentabilidade anual, não margem.
+Tem duas contradições factuais em cima disso. A Estação Central é descartada por alta complexidade na página 4, depois de ele escrever complexidade moderada na página 1. E a Arena é descartada por margem abaixo de 80% quando parceiros dá 83%.
+O único erro de cálculo é a Arena com 22,5 bancos em vez de 23, que por ser pequeno caiu na tolerância. Faltam riscos e próximos passos, que o enunciado pede na tarefa 04. E não tem uma tabela ou gráfico em cinco páginas de texto corrido.
+Na entrevista eu faço duas perguntas diretas, as mesmas que revelam se ele enxerga o problema. Você disse que a métrica principal é a margem, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação tem complexidade moderada na página 1 e alta na página 4, qual das duas?
+Nota 2,97 com vídeo em branco. Considerando só o que dá para avaliar, 3,30.
+Indício de IA: Baixo (consultivo, não afeta nota). O padrão de erros aponta para autoria própria sem assistência. A contradição entre página 1 e página 4 sobre a complexidade da Estação é inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural para singular na última frase. Deixou de arredondar os bancos apesar da instrução escrita, e IA tende a seguir instrução explícita. A ausência total de tabela e estrutura é o oposto da over-estruturação típica de texto gerado.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8576,7 @@
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Candidato 05 — pasta entregas-candidatos/05 (case BagHub 2026.2)</t>
+          <t>Candidato 05 (pasta entregas-candidatos/05, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8608,7 +8622,7 @@
       </c>
       <c r="O54" s="68" t="inlineStr">
         <is>
-          <t>C1=2: o slide 2 é só "DECISÃO — Centro Histórico — Ponto Parceiro" com a justificativa "mitigação de risco e eficiência do capital investido" — está nos dois primeiros slides e é uma frase, mas sem nenhum número na frase, e o descritor de 3 exige o número que a sustenta. Um 2º avaliador pode defender 3 pela clareza e posição; registro a divergência. C2=2: deck fechado com capa, seções nomeadas e nome do autor, mas com pontas soltas — o bairro "Noite Alta" aparece como "Alta Noite" em todas as tabelas, há os typos "tursita" (slide 15) e "esturura" (slide 15), a tabela do slide 5 tem coluna desalinhada e falta a observação do Centro Histórico. C3=2: a recomendação aparece nos títulos (slides 2 e 13) e a sequência fecha, mas há dois saltos — os slides 3 e 4 são o Anexo A e B do próprio case colados sem adaptação e nunca referenciados em nenhum argumento, e os slides 7 a 10 repetem um bairro por slide o que o slide 11 já consolida inteiro. C4=2: template próprio consistente, exceto exatamente 2 slides fora do padrão (3 e 4, que trazem a identidade visual vermelha do CCU do material original).</t>
+          <t>C1=2: o slide 2 é só "DECISÃO, Centro Histórico, Ponto Parceiro" com a justificativa "mitigação de risco e eficiência do capital investido", está nos dois primeiros slides e é uma frase, mas sem nenhum número na frase, e o descritor de 3 exige o número que a sustenta. Um 2º avaliador pode defender 3 pela clareza e posição; registro a divergência. C2=2: deck fechado com capa, seções nomeadas e nome do autor, mas com pontas soltas, o bairro "Noite Alta" aparece como "Alta Noite" em todas as tabelas, há os typos "tursita" (slide 15) e "esturura" (slide 15), a tabela do slide 5 tem coluna desalinhada e falta a observação do Centro Histórico. C3=2: a recomendação aparece nos títulos (slides 2 e 13) e a sequência fecha, mas há dois saltos, os slides 3 e 4 são o Anexo A e B do próprio case colados sem adaptação e nunca referenciados em nenhum argumento, e os slides 7 a 10 repetem um bairro por slide o que o slide 11 já consolida inteiro. C4=2: template próprio consistente, exceto exatamente 2 slides fora do padrão (3 e 4, que trazem a identidade visual vermelha do CCU do material original).</t>
         </is>
       </c>
       <c r="P54" s="41" t="n">
@@ -8625,7 +8639,7 @@
       </c>
       <c r="T54" s="68" t="inlineStr">
         <is>
-          <t>R1=2: cita as duas partes mas o número é decorativo, e nesse caso ele até joga contra — a escolha é Centro Histórico com parceiros a R$ 24,50M quando a Estação Central com parceiros dá R$ 27,84M. Ele reconhece isso por escrito no slide 13 ("menor custo inicial seguido do 2° maior lucro anual") e sustenta a decisão na razão de negócio (baixa complexidade, demanda turística sem sazonalidade, eficiência de capital). Tapando o argumento, o número sozinho não sustenta a escolha. Não é contradição, é um desvio declarado da prioridade do case, então não é 0. R2=2: calcula os oito cenários (slide 11) e compara os dois modelos, mas não justifica em lugar nenhum o descarte da Estação Central, que é o descarte que importa neste case — R$ 3,34M a mais de lucro e o bairro nunca é nomeado como rejeitado. R3=2: o breakeven do slide 12 é análise não pedida, aritmeticamente correta nos quatro bairros e ligada à decisão, porque é o lastro quantitativo da "eficiência do capital investido" que ele alega. O que impede o 3 é a premissa: o cálculo trata os R$ 70.000 por banco como investimento só do 1º ano, quando o Anexo E diz que todos os valores são anuais, e essa reinterpretação não é declarada em nenhum slide (ela aparece só à mão, anotada como "1º ano", na foto 33(3)). R4=2: compara densidade, complexidade e utilização entre os quatro bairros (slide 5) e tira conclusão, mas não explica a causa de nada — não diz por que a utilização do Centro Histórico é maior nem por que a razão posições/transações varia entre bairros.</t>
+          <t>R1=2: cita as duas partes mas o número é decorativo, e nesse caso ele até joga contra, a escolha é Centro Histórico com parceiros a R$ 24,50M quando a Estação Central com parceiros dá R$ 27,84M. Ele reconhece isso por escrito no slide 13 ("menor custo inicial seguido do 2° maior lucro anual") e sustenta a decisão na razão de negócio (baixa complexidade, demanda turística sem sazonalidade, eficiência de capital). Tapando o argumento, o número sozinho não sustenta a escolha. Não é contradição, é um desvio declarado da prioridade do case, então não é 0. R2=2: calcula os oito cenários (slide 11) e compara os dois modelos, mas não justifica em lugar nenhum o descarte da Estação Central, que é o descarte que importa neste case, R$ 3,34M a mais de lucro e o bairro nunca é nomeado como rejeitado. R3=2: o breakeven do slide 12 é análise não pedida, aritmeticamente correta nos quatro bairros e ligada à decisão, porque é o lastro quantitativo da "eficiência do capital investido" que ele alega. O que impede o 3 é a premissa: o cálculo trata os R$ 70.000 por banco como investimento só do 1º ano, quando o Anexo E diz que todos os valores são anuais, e essa reinterpretação não é declarada em nenhum slide (ela aparece só à mão, anotada como "1º ano", na foto 33(3)). R4=2: compara densidade, complexidade e utilização entre os quatro bairros (slide 5) e tira conclusão, mas não explica a causa de nada, não diz por que a utilização do Centro Histórico é maior nem por que a razão posições/transações varia entre bairros.</t>
         </is>
       </c>
       <c r="U54" s="41" t="n">
@@ -8648,7 +8662,7 @@
       </c>
       <c r="AA54" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados dos slides 7 a 11 conferem integralmente com o meu recálculo (25,08M/27,84M, 23,15M/24,5M, 13,87M/14,94M, 18,57M/19,2M). Memória de cálculo visível em dois lugares: as fórmulas no slide 6 e as nove fotos do caderno, onde a conta de Noite Alta está feita passo a passo à mão (1800÷40=45 bancos, AI 1º ano 11,43M, receita 30M, lucro 18,57M, PP 10,8M, lucro 19,2M) e tudo fecha. A2=3: bancos 60/25/23/45 corretos, incluindo a Arena com 23 (o caderno mostra a divisão à mão). Ressalva para o 2º avaliador: a fórmula genérica do slide 6 — [(Manutenção×40)+(Operação×40)+70.000]×Bancos — daria R$ 4.186.000 na Arena porque assume 920 posições, e não os R$ 4.130.000 que ele corretamente reporta na tabela usando 900; a tabela está certa e a fórmula publicada tem falha no caso não divisível. A3=2: o slide 14 traz um rollout concreto dos quatro bairros com modelo atribuído a cada um, o que é mais que narrativo, mas sem nenhum número e sem ponte entre períodos; e a atribuição de armários aos bairros 2 a 4 contraria a própria tabela dele (parceiros ganham nos quatro) sem nenhuma explicação no slide, embora seja coerente com o breakeven do slide 12. O case não declara meta numérica, então a comparação com a meta não é testável. A4=3: os armários nas fases 2 a 4 são o caminho alternativo e o breakeven quantifica exatamente quando ele passa a valer (2a11m na Estação, 4a5m no Centro, 3a na Arena, 1a3m em Noite Alta). A5=1: não há seção de riscos. O que existe são razões pelas quais a escolha dele é segura ("mitigação de risco", "menor risco operacional", "reduzindo risco de sazonalidade") e o slide 15 lista quatro pontos que são todos upside. Sazonalidade e risco operacional aparecem como dimensões genéricas de risco, nunca como riscos da recomendação dele, e não há mitigação nem prazo. O enunciado pede riscos na tarefa 04. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização, então passou pelo ponto certo sem nomear. Vale registrar que a anotação "1º ano" no caderno mostra que ele questionou o enquadramento anual do custo do banco — é o engajamento mais crítico com os dados que vi no conjunto, mas ficou fora do entregável.</t>
+          <t>A1=3: os oito resultados dos slides 7 a 11 conferem integralmente com o meu recálculo (25,08M/27,84M, 23,15M/24,5M, 13,87M/14,94M, 18,57M/19,2M). Memória de cálculo visível em dois lugares: as fórmulas no slide 6 e as nove fotos do caderno, onde a conta de Noite Alta está feita passo a passo à mão (1800÷40=45 bancos, AI 1º ano 11,43M, receita 30M, lucro 18,57M, PP 10,8M, lucro 19,2M) e tudo fecha. A2=3: bancos 60/25/23/45 corretos, incluindo a Arena com 23 (o caderno mostra a divisão à mão). Ressalva para o 2º avaliador: a fórmula genérica do slide 6, [(Manutenção×40)+(Operação×40)+70.000]×Bancos, daria R$ 4.186.000 na Arena porque assume 920 posições, e não os R$ 4.130.000 que ele corretamente reporta na tabela usando 900; a tabela está certa e a fórmula publicada tem falha no caso não divisível. A3=2: o slide 14 traz um rollout concreto dos quatro bairros com modelo atribuído a cada um, o que é mais que narrativo, mas sem nenhum número e sem ponte entre períodos; e a atribuição de armários aos bairros 2 a 4 contraria a própria tabela dele (parceiros ganham nos quatro) sem nenhuma explicação no slide, embora seja coerente com o breakeven do slide 12. O case não declara meta numérica, então a comparação com a meta não é testável. A4=3: os armários nas fases 2 a 4 são o caminho alternativo e o breakeven quantifica exatamente quando ele passa a valer (2a11m na Estação, 4a5m no Centro, 3a na Arena, 1a3m em Noite Alta). A5=1: não há seção de riscos. O que existe são razões pelas quais a escolha dele é segura ("mitigação de risco", "menor risco operacional", "reduzindo risco de sazonalidade") e o slide 15 lista quatro pontos que são todos upside. Sazonalidade e risco operacional aparecem como dimensões genéricas de risco, nunca como riscos da recomendação dele, e não há mitigação nem prazo. O enunciado pede riscos na tarefa 04. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização, então passou pelo ponto certo sem nomear. Vale registrar que a anotação "1º ano" no caderno mostra que ele questionou o enquadramento anual do custo do banco, é o engajamento mais crítico com os dados que vi no conjunto, mas ficou fora do entregável.</t>
         </is>
       </c>
       <c r="AB54" s="41" t="n">
@@ -8667,14 +8681,20 @@
       <c r="AG54" s="41" t="n"/>
       <c r="AH54" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Eduardo Alves Henrique), então dá para transcrever das linhas 13 e 35. E1=0 pela letra do item, que pede planilha: não há .xlsx. ATENÇÃO para a diretoria — ele entregou memória de cálculo de fato, em 9 fotos de caderno com a aritmética feita à mão, o que é mais do que a maioria entregou. Se o comitê contar qualquer artefato de memória de cálculo e não só planilha, este item vira 1. Como recomendo neutralizar E1 para todos, o efeito se anula. E3=0, sem vídeo de entrega.</t>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Eduardo Alves Henrique), então dá para transcrever das linhas 13 e 35. E1=0 pela letra do item, que pede planilha: não há .xlsx. ATENÇÃO para a diretoria, ele entregou memória de cálculo de fato, em 9 fotos de caderno com a aritmética feita à mão, o que é mais do que a maioria entregou. Se o comitê contar qualquer artefato de memória de cálculo e não só planilha, este item vira 1. Como recomendo neutralizar E1 para todos, o efeito se anula. E3=0, sem vídeo de entrega.</t>
         </is>
       </c>
       <c r="AI54" s="68" t="inlineStr">
         <is>
-          <t>Entrega de conta impecável com decisão deliberadamente contra o número, e isso é o que a torna interessante de corrigir. Os oito cenários fecham todos, inclusive o arredondamento da Arena, e a memória de cálculo vem em nove fotos de caderno onde dá para acompanhar a aritmética linha por linha. Ele escolhe o Centro Histórico com parceiros, que é o 2º maior lucro, e reconhece isso por escrito — a escolha se apoia em baixa complexidade, demanda turística sem sazonalidade e eficiência de capital. É um desvio declarado da prioridade do case, não uma contradição, e ele traz lastro para isso: o breakeven do slide 12 calcula em quanto tempo os armários se pagariam contra os parceiros, e os quatro números estão aritmeticamente certos. O problema é a premissa por baixo desse breakeven. Ele trata os R$ 70.000 por banco como investimento de primeiro ano, mas o Anexo E diz que todos os valores são anuais, e essa reinterpretação não aparece em nenhum slide — está só anotada à mão como "1º ano" na foto do caderno. Ou seja, a análise mais sofisticada da entrega roda sobre uma premissa que contraria o material e que o leitor do deck não tem como saber que existe. Duas outras lacunas pesam: não há riscos em lugar nenhum, só razões pelas quais a escolha é segura, e o descarte da Estação Central nunca é justificado, apesar de serem R$ 3,34M a mais. No acabamento, o bairro Noite Alta virou "Alta Noite" em todas as tabelas e dois slides são o anexo do próprio case colado. Na entrevista eu faria duas perguntas, e a segunda é a boa: por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua própria tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora. Nota 6,03 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,70.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Elas mostram o processo, não o resultado: a estrutura do case transcrita à mão, a tabela de custos copiada, a derivação da fórmula por banco e a conta de Noite Alta feita passo a passo, com os valores batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta uma decisão de modelagem deliberada, do tipo que não sai de saída genérica. Os typos ("tursita", "esturura"), o nome do bairro trocado em todas as tabelas e a fórmula do slide 6 que não fecha com a própria Arena são descuidos humanos. Pergunta de propriedade para a entrevista: por que o banco entrou como investimento de 1º ano no breakeven se o Anexo E diz que é custo anual?
-[IDENTIFICAÇÃO] Nome na capa: Eduardo Alves Henrique. V1/V2 nas linhas 13 (victor 2/0) e 35 (Proc 2/1).</t>
+          <t>Conta impecável e decisão deliberadamente contra o número. Isso é o que torna a entrega interessante de corrigir.
+Os oito cenários fecham, inclusive o arredondamento da Arena, e a memória de cálculo vem em nove fotos de caderno onde dá para acompanhar a aritmética linha por linha. Ele escolhe o Centro Histórico com parceiros, que é o segundo maior lucro, e reconhece isso por escrito. Sustenta na baixa complexidade, na demanda turística sem sazonalidade e na eficiência de capital. É desvio declarado da prioridade do case, não contradição, e ele traz lastro: o breakeven do slide 12 calcula em quanto tempo os armários se pagariam contra os parceiros, e os quatro números estão certos.
+O problema é a premissa por baixo desse breakeven. Ele trata os R$ 70.000 do banco como investimento de primeiro ano, mas o Anexo E diz que todos os valores são anuais. E a reinterpretação não aparece em nenhum slide, está só anotada à mão como "1º ano" na foto do caderno. A análise mais sofisticada da entrega roda sobre uma premissa que contraria o material e que o leitor do deck não tem como saber que existe.
+Duas lacunas pesam. Não há riscos em lugar nenhum, só razões pelas quais a escolha é segura. E o descarte da Estação Central nunca é justificado, apesar de serem R$ 3,34 milhões a mais.
+No acabamento, Noite Alta virou "Alta Noite" em todas as tabelas e dois slides são o anexo do próprio case colado.
+Na entrevista eu faço duas perguntas. Por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora.
+Nota 6,03 com vídeo em branco. Considerando só o que dá para avaliar, 6,70.
+Indício de IA: Baixo (consultivo, não afeta nota). As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Mostram o processo, não o resultado: estrutura do case transcrita à mão, derivação da fórmula por banco e a conta de Noite Alta passo a passo, batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta decisão de modelagem deliberada. Os typos e o nome do bairro trocado em todas as tabelas são descuidos humanos.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Eduardo Alves Henrique. As notas de vídeo dele estão nas linhas 13 (victor 2/0) e 35 (Proc 2/1) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8706,7 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Candidato 06 — pasta entregas-candidatos/06 (case BagHub 2026.2)</t>
+          <t>Candidato 06 (pasta entregas-candidatos/06, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8732,7 +8752,7 @@
       </c>
       <c r="O55" s="68" t="inlineStr">
         <is>
-          <t>C1=3: slide 2, uma linha — "ESTAÇÃO CENTRAL + PONTOS PARCEIROS / Maior resultado operacional absoluto com economia de modelo robusta" — com R$ 27,84 mi/ano no próprio slide. C2=2: o deck é de nível cliente, com capa, marcadores de seção e rodapé nos 10 slides, e a aba Resumo da planilha declara rastreabilidade de todos os números. Duas pontas soltas impedem o 3: o arquivo foi entregue como "Apresentacao_BagHub_Enrico hhh.pptx" e a numeração interna das seções está trocada, com o slide 7 (Sensibilidade) marcado 07 e o slide 8 (Portfólio) marcado 06. C3=3: a recomendação está no título do slide 2 e o arco fecha lendo só os títulos — recomendação, atratividade, quantificação, sensibilidade, portfólio, riscos, piloto — sem obrigar o leitor a voltar. C4=3: template único de fonte, cor e alinhamento nos 10 slides, gráficos no mesmo padrão, nenhum slide com parágrafo corrido.</t>
+          <t>C1=3: slide 2, uma linha, "ESTAÇÃO CENTRAL + PONTOS PARCEIROS / Maior resultado operacional absoluto com economia de modelo robusta", com R$ 27,84 mi/ano no próprio slide. C2=2: o deck é de nível cliente, com capa, marcadores de seção e rodapé nos 10 slides, e a aba Resumo da planilha declara rastreabilidade de todos os números. Duas pontas soltas impedem o 3: o arquivo foi entregue como "Apresentacao_BagHub_Enrico hhh.pptx" e a numeração interna das seções está trocada, com o slide 7 (Sensibilidade) marcado 07 e o slide 8 (Portfólio) marcado 06. C3=3: a recomendação está no título do slide 2 e o arco fecha lendo só os títulos, recomendação, atratividade, quantificação, sensibilidade, portfólio, riscos, piloto, sem obrigar o leitor a voltar. C4=3: template único de fonte, cor e alinhamento nos 10 slides, gráficos no mesmo padrão, nenhum slide com parágrafo corrido.</t>
         </is>
       </c>
       <c r="P55" s="41" t="n">
@@ -8749,7 +8769,7 @@
       </c>
       <c r="T55" s="68" t="inlineStr">
         <is>
-          <t>R1=3: slide 2 traz três pilares amarrados — caixa de R$ 27,84 mi "maximiza recursos para financiar a expansão", demanda de 24 mil tx/sem "menos sazonal e ancorada nos terminais" e economia de modelo de R$ 2,76 mi "permanece ampla na sensibilidade". Tapando o número, a tese de estabilidade de demanda e financiamento da expansão continua; tapando o argumento, R$ 27,84 mi continua sendo o máximo dos oito. R2=3: o slide 8 sequencia os quatro bairros com papel explícito (LANÇAR, ESCALAR, TESTAR, OPORTUNÍSTICO), cada um com resultado, R$/posição, margem, complexidade e os prós e contras por escrito; trata a tensão do Centro Histórico de frente, reconhecendo maior resultado por posição e menor complexidade como razões para ser o segundo e não o primeiro. O slide 6 mostra por que parceiros ganham com a reconciliação (R$ 4,20 mi de banco evitado menos R$ 1,44 mi de operação a mais = R$ 2,76 mi líquidos). R3=3: é o melhor R3 do conjunto. O slide 7 responde uma pergunta que ninguém fez — quanto o custo do banco teria de cair para os armários empatarem — com a fórmula publicada e os quatro valores corretos (R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena, R$ 56 mil em Noite Alta). Mais importante: ele percebeu que o case não modela custo de coordenação, calculou exatamente quanto de overhead apagaria a vantagem dos parceiros (R$ 1,15 mil por posição por ano na Estação) e transformou isso em KPI de risco no slide 9 e em decision gate no slide 10. Isso converte a resposta estática em condicional e fortalece a recomendação. R4=3: slide 5 dá a causa e a consequência — "Estação gera volume; Centro usa melhor cada posição" — e usa essa leitura para atribuir papéis estratégicos diferentes no slide 8, além de explicar no slide 6 a causa de os parceiros ganharem.</t>
+          <t>R1=3: slide 2 traz três pilares amarrados, caixa de R$ 27,84 mi "maximiza recursos para financiar a expansão", demanda de 24 mil tx/sem "menos sazonal e ancorada nos terminais" e economia de modelo de R$ 2,76 mi "permanece ampla na sensibilidade". Tapando o número, a tese de estabilidade de demanda e financiamento da expansão continua; tapando o argumento, R$ 27,84 mi continua sendo o máximo dos oito. R2=3: o slide 8 sequencia os quatro bairros com papel explícito (LANÇAR, ESCALAR, TESTAR, OPORTUNÍSTICO), cada um com resultado, R$/posição, margem, complexidade e os prós e contras por escrito; trata a tensão do Centro Histórico de frente, reconhecendo maior resultado por posição e menor complexidade como razões para ser o segundo e não o primeiro. O slide 6 mostra por que parceiros ganham com a reconciliação (R$ 4,20 mi de banco evitado menos R$ 1,44 mi de operação a mais = R$ 2,76 mi líquidos). R3=3: é o melhor R3 do conjunto. O slide 7 responde uma pergunta que ninguém fez, quanto o custo do banco teria de cair para os armários empatarem, com a fórmula publicada e os quatro valores corretos (R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena, R$ 56 mil em Noite Alta). Mais importante: ele percebeu que o case não modela custo de coordenação, calculou exatamente quanto de overhead apagaria a vantagem dos parceiros (R$ 1,15 mil por posição por ano na Estação) e transformou isso em KPI de risco no slide 9 e em decision gate no slide 10. Isso converte a resposta estática em condicional e fortalece a recomendação. R4=3: slide 5 dá a causa e a consequência, "Estação gera volume; Centro usa melhor cada posição", e usa essa leitura para atribuir papéis estratégicos diferentes no slide 8, além de explicar no slide 6 a causa de os parceiros ganharem.</t>
         </is>
       </c>
       <c r="U55" s="41" t="n">
@@ -8772,7 +8792,7 @@
       </c>
       <c r="AA55" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem com o meu recálculo. Memória de cálculo é a mais completa do conjunto: planilha de 5 abas com fórmulas vivas, receita em dois passos (tx/ano depois receita), custos decompostos em equipamento, operação e bancos, e a aba Resumo afirmando rastreabilidade. A2=3: bancos por ROUNDUP dando 60/25/23/45, Arena correta com 23, e a operação por complexidade resolvida por IF encadeado lendo a aba Dados. Tem ainda uma coluna de reconciliação (Z = bancos evitados menos operação adicional) que confere de forma independente a economia de cada bairro — conferência que ele montou para checar o próprio modelo. A3=3: o slide 8 sequencia os quatro bairros com números que batem com a planilha e o slide 10 traz piloto em quatro estágios com quatro decision gates quantificados; o case não declara meta numérica, então essa parte do descritor não é testável, mas a ponte com o próprio modelo existe e fecha. A4=3: a alternativa dos armários está quantificada com precisão pelo break-even do banco, e ele nota que Noite Alta precisa de só 20% de redução — ou seja, é onde o modelo alternativo está mais perto de virar. A5=3: cinco riscos no slide 9, todos específicos da combinação Estação Central mais parceiros (cadeia de custódia num modelo terceirizado, ruptura de capacidade no pico, overhead de coordenação, dependência do terminal, horário dos parceiros), cada um com mitigação e com KPI ou gatilho mensurável, e priorizados em Alta e Média. Não há prazo em dias, mas o gatilho por KPI é no mínimo tão exigente quanto prazo; registro para o 2º avaliador que quiser cobrar data. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização. Vale registrar que foi o único a apontar o que falta no material — "custos de gestão não estão considerados e podem reduzir a vantagem" — e a dimensionar essa lacuna, que é o engajamento crítico mais próximo do que o item A6 pretende medir.</t>
+          <t>A1=3: os oito resultados conferem com o meu recálculo. Memória de cálculo é a mais completa do conjunto: planilha de 5 abas com fórmulas vivas, receita em dois passos (tx/ano depois receita), custos decompostos em equipamento, operação e bancos, e a aba Resumo afirmando rastreabilidade. A2=3: bancos por ROUNDUP dando 60/25/23/45, Arena correta com 23, e a operação por complexidade resolvida por IF encadeado lendo a aba Dados. Tem ainda uma coluna de reconciliação (Z = bancos evitados menos operação adicional) que confere de forma independente a economia de cada bairro, conferência que ele montou para checar o próprio modelo. A3=3: o slide 8 sequencia os quatro bairros com números que batem com a planilha e o slide 10 traz piloto em quatro estágios com quatro decision gates quantificados; o case não declara meta numérica, então essa parte do descritor não é testável, mas a ponte com o próprio modelo existe e fecha. A4=3: a alternativa dos armários está quantificada com precisão pelo break-even do banco, e ele nota que Noite Alta precisa de só 20% de redução, ou seja, é onde o modelo alternativo está mais perto de virar. A5=3: cinco riscos no slide 9, todos específicos da combinação Estação Central mais parceiros (cadeia de custódia num modelo terceirizado, ruptura de capacidade no pico, overhead de coordenação, dependência do terminal, horário dos parceiros), cada um com mitigação e com KPI ou gatilho mensurável, e priorizados em Alta e Média. Não há prazo em dias, mas o gatilho por KPI é no mínimo tão exigente quanto prazo; registro para o 2º avaliador que quiser cobrar data. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização. Vale registrar que foi o único a apontar o que falta no material, "custos de gestão não estão considerados e podem reduzir a vantagem", e a dimensionar essa lacuna, que é o engajamento crítico mais próximo do que o item A6 pretende medir.</t>
         </is>
       </c>
       <c r="AB55" s="41" t="n">
@@ -8791,14 +8811,21 @@
       <c r="AG55" s="41" t="n"/>
       <c r="AH55" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está no arquivo (Enrico), então dá para transcrever das linhas 12 e 34. E1=1, planilha real com fórmulas vivas em 5 abas. E3=0, sem vídeo de entrega — item que o enunciado não pediu.</t>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está no arquivo (Enrico), então dá para transcrever das linhas 12 e 34. E1=1, planilha real com fórmulas vivas em 5 abas. E3=0, sem vídeo de entrega, item que o enunciado não pediu.</t>
         </is>
       </c>
       <c r="AI55" s="68" t="inlineStr">
         <is>
-          <t>Tecnicamente a entrega mais completa do conjunto, e o que a separa não é a conta, é o que ele faz depois dela. Os oito cenários fecham e a planilha é um modelo de verdade, com ROUNDUP, IF de complexidade, referências entre abas e uma coluna de reconciliação que ele montou para conferir a própria economia. Em cima disso ele faz duas coisas que ninguém mais fez. Primeiro, calcula o break-even do custo do banco nos quatro bairros e publica a fórmula — R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena e R$ 56 mil em Noite Alta — o que mostra que Noite Alta é o único bairro onde os armários estão perto de ganhar, precisando de apenas 20% de queda. Segundo, e melhor: ele percebe que o case não modela custo de coordenação, calcula que R$ 1,15 mil por posição por ano de overhead zeraria a vantagem dos parceiros na Estação, e transforma esse número em KPI de risco e em decision gate do piloto. Isso é sair de "a resposta é 27,84" para "a resposta é 27,84 e aqui está a condição em que ela deixa de valer". Os riscos do slide 9 são os melhores do conjunto, cinco, específicos do modelo escolhido, priorizados, cada um com mitigação e gatilho mensurável. O que sobra de reparo é pequeno e todo de acabamento: o arquivo foi enviado como "Enrico hhh.pptx" e a numeração das seções está trocada entre os slides 7 e 8. Na entrevista eu iria direto no que prova propriedade: o break-even da Arena deu R$ 23.478, um número não redondo — de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a sua recomendação? Quem montou o modelo responde as duas em três minutos. Nota 8,33 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,26.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Foi a leitura mais difícil do conjunto, porque o acabamento é alto e o vocabulário é bem de consultoria (headroom, decision gates, sequenciamento), o que costuma acender alerta. Mas os indícios de propriedade são fortes e específicos. A planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes — ninguém constrói autoconferência num modelo que não montou. O break-even da Arena saiu R$ 23.478,26, valor não redondo porque o denominador é o teto de 900/40, e ele não arredondou para embelezar. E o número R$ 1,15 mil por posição aparece encadeado em três artefatos diferentes: sai da planilha como headroom, reaparece no slide 9 como KPI de risco e no slide 10 como gate do piloto — esse tipo de encadeamento entre artefatos é difícil de fabricar. Somam-se descuidos humanos: o "hhh" no nome do arquivo e a numeração de seção trocada entre os slides 7 e 8. Por fim, ele aponta o que está ausente do material, e não só o que está presente, o que é o oposto da tendência de aceitar o input como completo. Pergunta de propriedade para a entrevista: de onde vem o 23 no denominador do break-even da Arena, e o que acontece se o overhead real for R$ 1,4 mil por posição?
-[IDENTIFICAÇÃO] Nome no arquivo: Enrico (Tristão e Mello de Oliveira). V1/V2 nas linhas 12 (victor 2/1) e 34 (Ferro 2/1).</t>
+          <t>Tecnicamente a entrega mais completa. E o que a separa não é a conta, é o que ele faz depois dela.
+Os oito cenários fecham e a planilha é um modelo de verdade, com ROUNDUP, IF de complexidade, referências entre abas e uma coluna de reconciliação que ele montou para conferir a própria economia. Em cima disso faz duas coisas que ninguém mais fez.
+Primeiro, calcula o breakeven do custo do banco nos quatro bairros e publica a fórmula. R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena, R$ 56 mil em Noite Alta. Isso mostra que Noite Alta é o único bairro onde os armários estão perto de ganhar, precisando de só 20% de queda.
+Segundo, e melhor: ele percebe que o case não modela custo de coordenação, calcula que R$ 1,15 mil por posição por ano de overhead zeraria a vantagem dos parceiros na Estação, e transforma esse número em KPI de risco e em decision gate do piloto. Isso é sair de "a resposta é 27,84" para "a resposta é 27,84 e aqui está a condição em que ela deixa de valer".
+Os riscos do slide 9 são os melhores do conjunto. Cinco, específicos do modelo escolhido, priorizados, cada um com mitigação e gatilho mensurável.
+O que sobra de reparo é pequeno e todo de acabamento. O arquivo foi enviado como "Enrico hhh.pptx" e a numeração das seções está trocada entre os slides 7 e 8.
+Na entrevista eu vou direto no que prova propriedade. O breakeven da Arena deu R$ 23.478, um número não redondo, de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a recomendação? Quem montou o modelo responde as duas em três minutos.
+Nota 8,33 com vídeo em branco. Considerando só o que dá para avaliar, 9,26.
+Indício de IA: Baixo (consultivo, não afeta nota). Foi a leitura mais difícil, porque o acabamento é alto e o vocabulário é bem de consultoria. Mas a planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes, e ninguém constrói autoconferência num modelo que não montou. O breakeven da Arena saiu R$ 23.478,26, não redondo, e ele não arredondou para embelezar. O R$ 1,15 mil por posição aparece encadeado em três artefatos. Somam-se o "hhh" no nome do arquivo e a numeração trocada.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Enrico Tristão e Mello de Oliveira. As notas de vídeo dele estão nas linhas 12 (victor 2/1) e 34 (Ferro 2/1) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8837,7 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Candidato 07 — pasta entregas-candidatos/07 (case BagHub 2026.2)</t>
+          <t>Candidato 07 (pasta entregas-candidatos/07, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8856,7 +8883,7 @@
       </c>
       <c r="O56" s="68" t="inlineStr">
         <is>
-          <t>C1=3: slide 2, uma linha — "Lançar na Estação Central com pontos parceiros | R$ 27,84 mi de resultado operacional anual" — com o número no próprio título. C2=3: deck fechado com capa, rodapé numerado nos 10 slides, apêndice com o demonstrativo completo dos oito cenários e slide de encerramento; a planilha vem com legenda de cores documentando o modelo (azul = dado editável, verde = vínculo entre abas, preto = fórmula local). Enviaria ao cliente sem editar. C3=3: são action titles de verdade, frases completas que carregam a mensagem — "Pontos parceiros rendem mais nos quatro bairros: a economia com bancos supera o maior custo de operação", "A recomendação tem folga: a Estação suporta grande queda de demanda antes de perder atratividade". Lendo só os títulos a história fecha inteira. C4=3: template único, rodapé e numeração em todos os slides, tabelas no mesmo padrão.</t>
+          <t>C1=3: slide 2, uma linha, "Lançar na Estação Central com pontos parceiros | R$ 27,84 mi de resultado operacional anual", com o número no próprio título. C2=3: deck fechado com capa, rodapé numerado nos 10 slides, apêndice com o demonstrativo completo dos oito cenários e slide de encerramento; a planilha vem com legenda de cores documentando o modelo (azul = dado editável, verde = vínculo entre abas, preto = fórmula local). Enviaria ao cliente sem editar. C3=3: são action titles de verdade, frases completas que carregam a mensagem, "Pontos parceiros rendem mais nos quatro bairros: a economia com bancos supera o maior custo de operação", "A recomendação tem folga: a Estação suporta grande queda de demanda antes de perder atratividade". Lendo só os títulos a história fecha inteira. C4=3: template único, rodapé e numeração em todos os slides, tabelas no mesmo padrão.</t>
         </is>
       </c>
       <c r="P56" s="41" t="n">
@@ -8873,7 +8900,7 @@
       </c>
       <c r="T56" s="68" t="inlineStr">
         <is>
-          <t>R1=3: slide 2 amarra R$ 27,84 mi à razão de negócio e à prioridade declarada do case — "é o resultado que melhor sustenta a expansão, sendo prioridade declarada, apoiado em demanda diária recorrente de transporte, não dependente de eventos". Tapando o número, a tese de recorrência e financiamento da expansão fica; tapando o argumento, o 27,84 continua sendo o máximo. R2=3: o slide 6 ranqueia os quatro com a coluna "Por que nesta posição" e traz uma caixa dedicada à comparação Estação x Centro que nomeia o trade-off com números (+R$ 3,34 mi absolutos contra margem de 90,7% x 77,3% e resultado por posição de R$ 24,5 mil x R$ 11,6 mil) e conclui explicitamente por que o Centro é o passo seguinte e não o primeiro. R3=3: o slide 7 traz robustez em dois níveis e o segundo é a pergunta certa — não só os ~77% de queda de demanda até o resultado zerar, mas os ~9,3% de queda que já fariam a Estação perder a liderança para o Centro. Recalculei: receita teria de cair para R$ 32,66 mi, o que dá 9,28%, e confere. Medir a fragilidade do ranking, e não só a distância da falência, é análise que ninguém pediu e que sustenta diretamente a recomendação. R4=3: slide 5 explica a causa de os parceiros ganharem (o banco rateado a ~R$ 1.750 por posição supera a economia de operação), slide 4 explica que a média semanal esconde os picos que ditam a capacidade, e a aba Bairros registra que "utilização baixa não indica capacidade dispensável: as posições foram dimensionadas para os picos".</t>
+          <t>R1=3: slide 2 amarra R$ 27,84 mi à razão de negócio e à prioridade declarada do case, "é o resultado que melhor sustenta a expansão, sendo prioridade declarada, apoiado em demanda diária recorrente de transporte, não dependente de eventos". Tapando o número, a tese de recorrência e financiamento da expansão fica; tapando o argumento, o 27,84 continua sendo o máximo. R2=3: o slide 6 ranqueia os quatro com a coluna "Por que nesta posição" e traz uma caixa dedicada à comparação Estação x Centro que nomeia o trade-off com números (+R$ 3,34 mi absolutos contra margem de 90,7% x 77,3% e resultado por posição de R$ 24,5 mil x R$ 11,6 mil) e conclui explicitamente por que o Centro é o passo seguinte e não o primeiro. R3=3: o slide 7 traz robustez em dois níveis e o segundo é a pergunta certa, não só os ~77% de queda de demanda até o resultado zerar, mas os ~9,3% de queda que já fariam a Estação perder a liderança para o Centro. Recalculei: receita teria de cair para R$ 32,66 mi, o que dá 9,28%, e confere. Medir a fragilidade do ranking, e não só a distância da falência, é análise que ninguém pediu e que sustenta diretamente a recomendação. R4=3: slide 5 explica a causa de os parceiros ganharem (o banco rateado a ~R$ 1.750 por posição supera a economia de operação), slide 4 explica que a média semanal esconde os picos que ditam a capacidade, e a aba Bairros registra que "utilização baixa não indica capacidade dispensável: as posições foram dimensionadas para os picos".</t>
         </is>
       </c>
       <c r="U56" s="41" t="n">
@@ -8896,7 +8923,7 @@
       </c>
       <c r="AA56" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem. Memória de cálculo completa e rastreável — receita em dois passos, custos decompostos em ESM, operação e bancos, tudo puxando da aba Premissas, mais o apêndice do slide 10 com o demonstrativo por componente. A2=3: bancos por ROUNDUP dando 60/25/23/45, Arena correta com 23, operação por complexidade via VLOOKUP. É o tratamento mais preciso do arredondamento no conjunto: ele modela "posições físicas disponíveis" (920 na Arena) e "posições adicionais por arredondamento" (20), documenta na aba Premissas que os custos por posição usam as posições necessárias mesmo com sobra física, e ainda valida por IF se a capacidade física atende à necessária, retornando OK ou REVER. A3=3: o slide 2 traz a sequência de expansão com os quatro resultados, o slide 8 os próximos passos, e a aba Bairros um próximo passo específico por bairro; todos os números batem com o modelo dele. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: propõe os armários 24h como alternativa em Noite Alta caso falte cobertura noturna de parceiros, e quantifica por que é justamente ali que a alternativa importa — a vantagem dos parceiros naquele bairro é de só R$ 630 mil, a menor dos quatro. A5=3: quatro riscos no slide 8, todos específicos do modelo de parceiros no bairro escolhido (horários compatíveis com as conexões, filas e simultaneidade nos picos, disponibilidade de comércios junto às âncoras, identificação e suporte noturno), cada um com próximo passo que o endereça, e um deles com prazo declarado — "testar a retirada nos horários críticos antes da abertura ao público". A6=1: o case não traz erro plantado. Ele foi o único a preencher a aba Premissas com 11 regras de interpretação e a antecipar por escrito as duas armadilhas — "não aplicar utilização" e "todos os custos informados são anuais, o custo dos bancos não é tratado como CAPEX" — resolvendo as duas corretamente. Nomeou as ambiguidades, mas inconsistência plantada não existe neste case.</t>
+          <t>A1=3: os oito resultados conferem. Memória de cálculo completa e rastreável, receita em dois passos, custos decompostos em ESM, operação e bancos, tudo puxando da aba Premissas, mais o apêndice do slide 10 com o demonstrativo por componente. A2=3: bancos por ROUNDUP dando 60/25/23/45, Arena correta com 23, operação por complexidade via VLOOKUP. É o tratamento mais preciso do arredondamento no conjunto: ele modela "posições físicas disponíveis" (920 na Arena) e "posições adicionais por arredondamento" (20), documenta na aba Premissas que os custos por posição usam as posições necessárias mesmo com sobra física, e ainda valida por IF se a capacidade física atende à necessária, retornando OK ou REVER. A3=3: o slide 2 traz a sequência de expansão com os quatro resultados, o slide 8 os próximos passos, e a aba Bairros um próximo passo específico por bairro; todos os números batem com o modelo dele. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: propõe os armários 24h como alternativa em Noite Alta caso falte cobertura noturna de parceiros, e quantifica por que é justamente ali que a alternativa importa, a vantagem dos parceiros naquele bairro é de só R$ 630 mil, a menor dos quatro. A5=3: quatro riscos no slide 8, todos específicos do modelo de parceiros no bairro escolhido (horários compatíveis com as conexões, filas e simultaneidade nos picos, disponibilidade de comércios junto às âncoras, identificação e suporte noturno), cada um com próximo passo que o endereça, e um deles com prazo declarado, "testar a retirada nos horários críticos antes da abertura ao público". A6=1: o case não traz erro plantado. Ele foi o único a preencher a aba Premissas com 11 regras de interpretação e a antecipar por escrito as duas armadilhas, "não aplicar utilização" e "todos os custos informados são anuais, o custo dos bancos não é tratado como CAPEX", resolvendo as duas corretamente. Nomeou as ambiguidades, mas inconsistência plantada não existe neste case.</t>
         </is>
       </c>
       <c r="AB56" s="41" t="n">
@@ -8915,14 +8942,20 @@
       <c r="AG56" s="41" t="n"/>
       <c r="AH56" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco e a pasta é anônima: os arquivos não trazem nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=1, planilha real de 4 abas com fórmulas vivas. E3=0, sem vídeo de entrega — item que o enunciado não pediu.</t>
+          <t>V1 e V2 em branco e a pasta é anônima: os arquivos não trazem nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=1, planilha real de 4 abas com fórmulas vivas. E3=0, sem vídeo de entrega, item que o enunciado não pediu.</t>
         </is>
       </c>
       <c r="AI56" s="68" t="inlineStr">
         <is>
-          <t>Maior nota do conjunto, e o que decide é disciplina de modelagem somada à pergunta certa de robustez. Os oito cenários fecham e a planilha tem infraestrutura de autoconferência: um bloco de Conferências com três checagens que têm de dar zero, mais um validador que responde OK ou REVER se a capacidade física não cobrir a necessária. Ele é o único que modela explicitamente a sobra do arredondamento — 23 bancos na Arena dão 920 posições físicas para 900 necessárias, e ele registra as 20 de sobra sem deixar isso contaminar o custo, que segue nas posições necessárias. E é o único que antecipou por escrito a armadilha em que a pasta 05 caiu: a aba Premissas diz, em letras claras, que todos os custos são anuais e que o banco não é CAPEX. O melhor da entrega, porém, é o slide 7. Quase todo mundo que fez sensibilidade mediu distância da falência. Ele mediu duas coisas: os 77% de queda de demanda até o resultado zerar e, muito mais útil, os 9,3% de queda que já fariam a Estação perder a liderança para o Centro Histórico. Essa é a pergunta que decide se o ranking é frágil, e o número confere. Vale um contraponto que eu levaria à entrevista: 9,3% de folga não é obviamente "risco baixo" como ele afirma no slide — é uma margem estreita para uma projeção de demanda não validada, e a leitura dele é otimista demais para o próprio número que produziu. Faltou pouco: nenhum reparo de forma, e o único vazio é não ter explorado o que o modelo dele já permitia, o break-even do custo do banco. Na entrevista eu perguntaria: por que a queda admissível até zerar (77,3%) é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora, e quem só preencheu a planilha travá. Nota 8,60 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,56.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria, e vêm da disciplina do modelo. A planilha tem um bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade — ninguém constrói autoauditoria num modelo que não montou. A aba Premissas documenta convenção de cores do próprio modelo e deixa uma nota de manutenção para quem for usá-lo depois ("as conclusões textuais descrevem a base original, revise-as se alterar os dados"), que é escrita para um leitor futuro, não para um avaliador. Ele marca sistematicamente o que não pode saber: "distâncias e tempos não foram informados", "hipótese a validar", "médias diárias usam 7 dias apenas como normalização, não representam picos". Esse hábito de rotular a própria inferência é o oposto de texto gerado, que tende a afirmar com confiança uniforme. E a pergunta dos 9,28% é derivada, não óbvia. Pergunta de propriedade para a entrevista: por que a queda admissível de demanda até zerar dá exatamente a sua margem operacional?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima. Precisa do mapa número-candidato para trazer V1/V2.</t>
+          <t>Maior nota do conjunto. O que decide é disciplina de modelagem somada à pergunta certa de robustez.
+Os oito cenários fecham e a planilha tem autoconferência: um bloco de Conferências com três checagens que têm de dar zero, mais um validador que responde OK ou REVER se a capacidade física não cobrir a necessária. É o único que modela a sobra do arredondamento, porque 23 bancos na Arena dão 920 posições físicas para 900 necessárias, e ele registra as 20 de sobra sem deixar isso contaminar o custo. E é o único que antecipou por escrito a armadilha em que a pasta 05 caiu: a aba de premissas diz, em letras claras, que todos os custos são anuais e que o banco não é CAPEX.
+O melhor da entrega está no slide 7. Quase todo mundo que fez sensibilidade mediu distância da falência. Ele mediu duas coisas: os 77% de queda de demanda até o resultado zerar e, muito mais útil, os 9,3% de queda que já fariam a Estação perder a liderança para o Centro Histórico. Essa é a pergunta que decide se o ranking é frágil, e o número confere.
+Tenho um contraponto que levaria à entrevista. Os 9,3% de folga não são obviamente "risco baixo" como ele afirma no slide. É margem estreita para uma projeção de demanda não validada, e a leitura dele é otimista demais para o próprio número que produziu.
+Faltou pouco. Nenhum reparo de forma, e o único vazio é não ter explorado o que o modelo dele já permitia, o breakeven do custo do banco.
+Na entrevista eu pergunto: por que a queda admissível até zerar, 77,3%, é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora. Quem só preencheu a planilha trava.
+Nota 8,60 com vídeo em branco. Considerando só o que dá para avaliar, 9,56.
+Indício de IA: Baixo (consultivo, não afeta nota). A disciplina do modelo é o indício. Bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade. A aba de premissas documenta convenção de cores e deixa nota de manutenção para quem usar o modelo depois, escrita para um leitor futuro e não para um avaliador. Ele marca sistematicamente o que não pode saber: distâncias não informadas, hipótese a validar, médias diárias como normalização. Esse hábito é o oposto de texto gerado.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8967,7 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Candidato 08 — pasta entregas-candidatos/08 (case BagHub 2026.2)</t>
+          <t>Candidato 08 (pasta entregas-candidatos/08, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8980,7 +9013,7 @@
       </c>
       <c r="O57" s="68" t="inlineStr">
         <is>
-          <t>C1=2: a recomendação é explícita e clara — "Lançar em Estação Central, modelo Pontos parceiros", com R$ 27,8M — mas aparece no slide 8 de 10, depois da metade; os slides 2 e 3 são contexto e metodologia, sem antecipar a resposta. C2=2: deck fechado, com capa, numeração nos 10 slides e slide de encerramento, mas três pontas soltas — o slide 4 traz a complexidade invertida (Centro Histórico como Alta e Noite Alta como Baixa, quando o Anexo B diz o contrário), o slide 9 remete a "detalhes completos no relatório escrito, disponível como material de apoio" e não existe relatório escrito na pasta, e há um arquivo pessoal sem relação com a entrega no meio dos anexos. C3=3: a recomendação aparece nos títulos ("Pontos parceiros vence nos 4 bairros", "Lançar em Estação Central") e o arco fecha na ordem — contexto, metodologia, comparação, demanda, rentabilidade, resultado, recomendação, riscos — sem obrigar o leitor a voltar. C4=3: template consistente, numeração em todos os slides, cards e gráficos no mesmo padrão.</t>
+          <t>C1=2: a recomendação é explícita e clara, "Lançar em Estação Central, modelo Pontos parceiros", com R$ 27,8M, mas aparece no slide 8 de 10, depois da metade; os slides 2 e 3 são contexto e metodologia, sem antecipar a resposta. C2=2: deck fechado, com capa, numeração nos 10 slides e slide de encerramento, mas três pontas soltas, o slide 4 traz a complexidade invertida (Centro Histórico como Alta e Noite Alta como Baixa, quando o Anexo B diz o contrário), o slide 9 remete a "detalhes completos no relatório escrito, disponível como material de apoio" e não existe relatório escrito na pasta, e há um arquivo pessoal sem relação com a entrega no meio dos anexos. C3=3: a recomendação aparece nos títulos ("Pontos parceiros vence nos 4 bairros", "Lançar em Estação Central") e o arco fecha na ordem, contexto, metodologia, comparação, demanda, rentabilidade, resultado, recomendação, riscos, sem obrigar o leitor a voltar. C4=3: template consistente, numeração em todos os slides, cards e gráficos no mesmo padrão.</t>
         </is>
       </c>
       <c r="P57" s="41" t="n">
@@ -8997,7 +9030,7 @@
       </c>
       <c r="T57" s="68" t="inlineStr">
         <is>
-          <t>R1=3: slide 8 amarra R$ 27,8M às razões de negócio (maior demanda absoluta com 24 mil tx/semana, complexidade apenas moderada mesmo com o maior volume) e trata a tensão de frente — "Centro Histórico tem margem maior (90,7%), mas resultado absoluto menor, bom candidato à 2ª onda". Tapando o número a tese de escala e complexidade controlada fica; tapando o argumento, 27,8M continua sendo o máximo. R2=3: ranqueia os quatro no slide 8 com resultado e margem, justifica por escrito por que o Centro é o segundo e não o primeiro, e no slide 7 justifica a escolha do modelo pela causa estrutural. R3=2: o slide 7 traz uma derivação própria não pedida — o banco de 40 posições equivale a R$ 1.750 por posição e isso supera a economia de operação dos armários — correta e diretamente ligada à decisão de modelo, mas que não altera a conclusão. Não há sensibilidade, break-even nem economia por posição. R4=3: explica a causa por trás do indicador e o que fazer com ela, que é exatamente o R$ 1.750 por posição do slide 7, derivação dela e não do case; no slide 5 lê a utilização baixa como concentração em picos, leitura coerente com a capacidade dimensionada para pico.</t>
+          <t>R1=3: slide 8 amarra R$ 27,8M às razões de negócio (maior demanda absoluta com 24 mil tx/semana, complexidade apenas moderada mesmo com o maior volume) e trata a tensão de frente, "Centro Histórico tem margem maior (90,7%), mas resultado absoluto menor, bom candidato à 2ª onda". Tapando o número a tese de escala e complexidade controlada fica; tapando o argumento, 27,8M continua sendo o máximo. R2=3: ranqueia os quatro no slide 8 com resultado e margem, justifica por escrito por que o Centro é o segundo e não o primeiro, e no slide 7 justifica a escolha do modelo pela causa estrutural. R3=2: o slide 7 traz uma derivação própria não pedida, o banco de 40 posições equivale a R$ 1.750 por posição e isso supera a economia de operação dos armários, correta e diretamente ligada à decisão de modelo, mas que não altera a conclusão. Não há sensibilidade, break-even nem economia por posição. R4=3: explica a causa por trás do indicador e o que fazer com ela, que é exatamente o R$ 1.750 por posição do slide 7, derivação dela e não do case; no slide 5 lê a utilização baixa como concentração em picos, leitura coerente com a capacidade dimensionada para pico.</t>
         </is>
       </c>
       <c r="U57" s="41" t="n">
@@ -9020,7 +9053,7 @@
       </c>
       <c r="AA57" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os resultados conferem — 27,8M/24,5M/19,2M/14,9M com margens 77,3%/90,7%/64,0%/83,0%, todos corretos. A memória de cálculo está na imagem IMG_2424, manuscrita, com premissas, fórmulas gerais, a tabela do Anexo E transcrita e a conta desenvolvida bairro por bairro (Estação: 36.000.000 − 10.920.000 = 25.080.000; parceiros 8.160.000 → 27.840.000, margem 77,3%; Centro: 27.000.000 − 3.850.000 = 23.150.000; parceiros 2.500.000 → 24.500.000, margem 90,7%). A2=3: bancos corretos e com o arredondamento explicitado à mão — "2400:40 = 60", "1000:40 = 25" e "900:40 = 22,5 ≈ 23". Importante: na memória de cálculo ela usa "Operação (baixa)" para o Centro Histórico, ou seja, o valor correto; o erro do slide 4 é só de transcrição e não contaminou nenhuma conta. A3=3: o slide 8 traz a sequência de expansão com os quatro resultados batendo com o modelo dela, e o slide 9 sequencia (Centro Histórico como 2ª onda, reavaliar Arena e Noite Alta "após os primeiros meses"). O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: Centro Histórico como alternativa de 2ª onda com impacto quantificado em R$ 24,5M e a margem de 90,7% nomeada como o motivo. A5=2: dois dos três riscos são específicos da recomendação dela (concentração em picos na Estação citando os 42%, dependência da qualidade dos parceiros "fora do controle direto da BagHub"); o terceiro, sazonalidade na Arena, não é risco da escolha dela. O slide apresenta riscos e próximos passos com uma seta sugerindo par a par, mas o conteúdo não corresponde — "negociar parcerias" não mitiga "concentração em picos" e "planejar Centro Histórico" não mitiga "dependência de parceiros". Riscos específicos sem mitigação que os endereça. A6=1: o case não traz erro plantado; a fórmula de receita na memória de cálculo está correta e ela não descontou transações pela utilização, mas não nomeou inconsistência nenhuma.</t>
+          <t>A1=3: os resultados conferem, 27,8M/24,5M/19,2M/14,9M com margens 77,3%/90,7%/64,0%/83,0%, todos corretos. A memória de cálculo está na imagem IMG_2424, manuscrita, com premissas, fórmulas gerais, a tabela do Anexo E transcrita e a conta desenvolvida bairro por bairro (Estação: 36.000.000 − 10.920.000 = 25.080.000; parceiros 8.160.000 → 27.840.000, margem 77,3%; Centro: 27.000.000 − 3.850.000 = 23.150.000; parceiros 2.500.000 → 24.500.000, margem 90,7%). A2=3: bancos corretos e com o arredondamento explicitado à mão, "2400:40 = 60", "1000:40 = 25" e "900:40 = 22,5 ≈ 23". Importante: na memória de cálculo ela usa "Operação (baixa)" para o Centro Histórico, ou seja, o valor correto; o erro do slide 4 é só de transcrição e não contaminou nenhuma conta. A3=3: o slide 8 traz a sequência de expansão com os quatro resultados batendo com o modelo dela, e o slide 9 sequencia (Centro Histórico como 2ª onda, reavaliar Arena e Noite Alta "após os primeiros meses"). O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: Centro Histórico como alternativa de 2ª onda com impacto quantificado em R$ 24,5M e a margem de 90,7% nomeada como o motivo. A5=2: dois dos três riscos são específicos da recomendação dela (concentração em picos na Estação citando os 42%, dependência da qualidade dos parceiros "fora do controle direto da BagHub"); o terceiro, sazonalidade na Arena, não é risco da escolha dela. O slide apresenta riscos e próximos passos com uma seta sugerindo par a par, mas o conteúdo não corresponde, "negociar parcerias" não mitiga "concentração em picos" e "planejar Centro Histórico" não mitiga "dependência de parceiros". Riscos específicos sem mitigação que os endereça. A6=1: o case não traz erro plantado; a fórmula de receita na memória de cálculo está correta e ela não descontou transações pela utilização, mas não nomeou inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB57" s="41" t="n">
@@ -9039,15 +9072,19 @@
       <c r="AG57" s="41" t="n"/>
       <c r="AH57" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Gabrielle Cristofani do Rosario), então dá para transcrever das linhas 7 e 29. E1=0 pela letra do item, que pede planilha: não há .xlsx. Mesma ressalva da pasta 05 — ela entregou memória de cálculo de fato, manuscrita e completa, e se o comitê contar qualquer artefato de memória de cálculo este item vira 1. E3=0, sem vídeo de entrega.</t>
+          <t>V1 e V2 em branco: notas da etapa de vídeo não vieram com a pasta; o nome está na capa (Gabrielle Cristofani do Rosario), então dá para transcrever das linhas 7 e 29. E1=0 pela letra do item, que pede planilha: não há .xlsx. Mesma ressalva da pasta 05, ela entregou memória de cálculo de fato, manuscrita e completa, e se o comitê contar qualquer artefato de memória de cálculo este item vira 1. E3=0, sem vídeo de entrega.</t>
         </is>
       </c>
       <c r="AI57" s="68" t="inlineStr">
         <is>
-          <t>Entrega sólida, com o mérito de a conta estar certa e a memória de cálculo ser verificável linha por linha na imagem manuscrita, inclusive o arredondamento da Arena escrito como "22,5 ≈ 23", que é onde a maioria escorrega. A causa estrutural ela achou sozinha: o banco rateado dá R$ 1.750 por posição e isso supera a economia de operação dos armários, o que explica por que parceiros ganham nos quatro bairros em vez de apenas reportar que ganham. E trata a tensão do case de frente, reconhecendo que o Centro Histórico tem margem maior mas resultado absoluto menor, e colocando ele como segunda onda. Três reparos, todos de execução e nenhum de raciocínio. O primeiro é o slide 4, que inverte a complexidade do Centro Histórico e de Noite Alta — a memória de cálculo usa os valores certos, então é erro de transcrição, mas está no slide que serve justamente para comparar os bairros. O segundo é a recomendação chegar só no slide 8: o deck tem contexto e metodologia antes da resposta, e trocar essa ordem valeria pontos sem mudar uma linha de análise. O terceiro é o slide 9, que promete um relatório escrito que não está na pasta e que pareia riscos com próximos passos que não os endereçam. Na entrevista eu faria duas perguntas: no slide 4 o Centro Histórico aparece como complexidade Alta e suas contas usam Baixa, qual é o certo? E, puxando o achado dela: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000, e sai direto do R$ 1.750 que ela mesma derivou. Nota 7,33 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,15.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria. A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor ("900:40 = 22,5 ≈ 23"). O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é a assinatura de erro humano de transcrição: uma saída gerada seria internamente consistente, certa ou errada nos dois lugares. A referência a um "relatório escrito" que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado. Pergunta de propriedade para a entrevista: no slide 4 o Centro Histórico está como Alta e suas contas usam Baixa — qual é o certo?
-[ALERTA] URGENTE — o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
-[IDENTIFICAÇÃO] Nome na capa: Gabrielle Cristofani do Rosario. V1/V2 nas linhas 7 (victor 2/2) e 29 (Fred 3/2).</t>
+          <t>Entrega sólida. A conta está certa e a memória de cálculo é verificável linha por linha na imagem manuscrita, inclusive o arredondamento da Arena escrito como "22,5 ≈ 23", que é onde a maioria escorrega.
+A causa estrutural ela achou sozinha. O banco rateado dá R$ 1.750 por posição e isso supera a economia de operação dos armários, o que explica por que parceiros ganham nos quatro bairros em vez de apenas reportar que ganham. E trata a tensão do case de frente, reconhecendo que o Centro Histórico tem margem maior mas resultado absoluto menor, e colocando ele como segunda onda.
+Três reparos, todos de execução e nenhum de raciocínio. O primeiro é o slide 4, que inverte a complexidade do Centro Histórico e de Noite Alta. A memória de cálculo usa os valores certos, então é erro de transcrição, mas está justamente no slide que serve para comparar os bairros. O segundo é a recomendação chegar só no slide 8: o deck tem contexto e metodologia antes da resposta, e trocar essa ordem valeria pontos sem mudar uma linha de análise. O terceiro é o slide 9, que promete um relatório escrito que não está na pasta e pareia riscos com próximos passos que não os endereçam.
+Na entrevista eu faço duas perguntas. No slide 4 o Centro Histórico aparece como complexidade Alta e suas contas usam Baixa, qual é o certo? E, puxando o achado dela, a partir de que custo de banco os armários passariam a ganhar na Estação? A resposta é R$ 24.000 e sai direto do R$ 1.750 que ela mesma derivou.
+Nota 7,33 com vídeo em branco. Considerando só o que dá para avaliar, 8,15.
+Indício de IA: Baixo (consultivo, não afeta nota). A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor, "900:40 = 22,5 ≈ 23". O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é assinatura de erro humano de transcrição, porque saída gerada seria consistente nos dois lugares. A referência a um relatório escrito que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado.
+ATENÇÃO: URGENTE, o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Gabrielle Cristofani do Rosario. As notas de vídeo dele estão nas linhas 7 (victor 2/2) e 29 (Fred 3/2) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9096,7 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
+          <t>Candidato 09 (pasta entregas-candidatos/09, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -9105,7 +9142,7 @@
       </c>
       <c r="O58" s="68" t="inlineStr">
         <is>
-          <t>C1=3: a recomendação está na própria capa ("Centro Histórico com parceiros maximiza a rentabilidade do lançamento") e o slide 2 a repete com os números que a sustentam — score 4,66, margem 90,7%, R$ 24,5 mi. C2=3: deck fechado com capa, rodapé e numeração nos 10 slides, seções nomeadas, mais planilha que documenta o método do score. C3=3: são action titles de verdade e o arco fecha lendo só os títulos, incluindo o contra-argumento — "Centro lidera a margem no Ano 1, apesar de abrir mão de R$ 3,34 mi em resultado", "Estação Central + armários se destaca após o primeiro ano". C4=3: template único, numeração e gráficos no mesmo padrão nos 10 slides.</t>
+          <t>C1=3: a recomendação está na própria capa ("Centro Histórico com parceiros maximiza a rentabilidade do lançamento") e o slide 2 a repete com os números que a sustentam, score 4,66, margem 90,7%, R$ 24,5 mi. C2=3: deck fechado com capa, rodapé e numeração nos 10 slides, seções nomeadas, mais planilha que documenta o método do score. C3=3: são action titles de verdade e o arco fecha lendo só os títulos, incluindo o contra-argumento, "Centro lidera a margem no Ano 1, apesar de abrir mão de R$ 3,34 mi em resultado", "Estação Central + armários se destaca após o primeiro ano". C4=3: template único, numeração e gráficos no mesmo padrão nos 10 slides.</t>
         </is>
       </c>
       <c r="P58" s="41" t="n">
@@ -9122,7 +9159,7 @@
       </c>
       <c r="T58" s="68" t="inlineStr">
         <is>
-          <t>R1=3: o slide 2 amarra número e razão de negócio — score 4,66, margem 90,7%, 54% de utilização e complexidade baixa, com a tese de que "a operação gera caixa e aprendizado antes de uma expansão mais intensiva em capital". Ele declara abertamente o sacrifício no slide 4 e justifica no slide 6 por que margem pesa 35% e resultado 25%. Registro a leitura contestável: ele interpreta a "prioridade de rentabilidade anual" do case como margem, quando o complemento da frase ("que deverá sustentar a expansão") aponta para caixa absoluto — é leitura defensável em português e está declarada, mas um 2º avaliador pode cobrar. R2=3: é a comparação mais sistemática do conjunto — o score confronta as oito alternativas com pesos e método publicados, o slide 6 compara os dois modelos dentro do Centro em quatro indicadores, e o slide 8 mostra como o ranking muda no Ano 2. Descarta por escrito e com critério. R3=2: trouxe muita coisa não pedida e diretamente ligada à decisão — score multicritério normalizado (conferi a interpolação: Arena parceiros dá 1,31 na escala 1 a 5 e fecha), evolução Ano 2 a 5, e a constatação de que o ranking se inverte. Isso chega a mudar a estrutura da recomendação, que vira bifásica. O que impede o 3 é a premissa, igual à pasta 05: todo o Ano 2 em diante remove o custo do banco, tratando os R$ 70.000 como investimento inicial, quando o Anexo E diz que "os valores abaixo são anuais". A reinterpretação não é declarada em nenhum slide nem na planilha. R4=3: slide 9 dá causa e consequência ("o investimento inicial nos bancos não se repete a partir do segundo ano" e a Estação é a mais beneficiada porque exige 60 bancos), e o slide 10 traz uma leitura qualitativa própria e boa — na Estação parte da demanda é imediata, e o autosserviço 24h atende sem depender do horário de um parceiro.</t>
+          <t>R1=3: o slide 2 amarra número e razão de negócio, score 4,66, margem 90,7%, 54% de utilização e complexidade baixa, com a tese de que "a operação gera caixa e aprendizado antes de uma expansão mais intensiva em capital". Ele declara abertamente o sacrifício no slide 4 e justifica no slide 6 por que margem pesa 35% e resultado 25%. Registro a leitura contestável: ele interpreta a "prioridade de rentabilidade anual" do case como margem, quando o complemento da frase ("que deverá sustentar a expansão") aponta para caixa absoluto, é leitura defensável em português e está declarada, mas um 2º avaliador pode cobrar. R2=3: é a comparação mais sistemática do conjunto, o score confronta as oito alternativas com pesos e método publicados, o slide 6 compara os dois modelos dentro do Centro em quatro indicadores, e o slide 8 mostra como o ranking muda no Ano 2. Descarta por escrito e com critério. R3=2: trouxe muita coisa não pedida e diretamente ligada à decisão, score multicritério normalizado (conferi a interpolação: Arena parceiros dá 1,31 na escala 1 a 5 e fecha), evolução Ano 2 a 5, e a constatação de que o ranking se inverte. Isso chega a mudar a estrutura da recomendação, que vira bifásica. O que impede o 3 é a premissa, igual à pasta 05: todo o Ano 2 em diante remove o custo do banco, tratando os R$ 70.000 como investimento inicial, quando o Anexo E diz que "os valores abaixo são anuais". A reinterpretação não é declarada em nenhum slide nem na planilha. R4=3: slide 9 dá causa e consequência ("o investimento inicial nos bancos não se repete a partir do segundo ano" e a Estação é a mais beneficiada porque exige 60 bancos), e o slide 10 traz uma leitura qualitativa própria e boa, na Estação parte da demanda é imediata, e o autosserviço 24h atende sem depender do horário de um parceiro.</t>
         </is>
       </c>
       <c r="U58" s="41" t="n">
@@ -9145,7 +9182,7 @@
       </c>
       <c r="AA58" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados de Ano 1 conferem integralmente (25,08/23,15/13,87/18,57 e 27,84/24,50/14,94/19,20). Memória de cálculo completa na planilha, com fórmulas vivas decompondo equipamento, bancos e operação. A2=3: bancos 60/25/23/45 corretos. Detalhe relevante: na Arena ele fixou 23 à mão em vez de usar a fórmula B/C que daria 22,5 — ou seja, percebeu o arredondamento e corrigiu deliberadamente, enquanto os outros três bairros seguem por fórmula. A3=2: a ponte entre anos é estruturalmente a melhor do conjunto, com projeção acumulada de 5 anos e o ano de cruzamento calculado por bairro (1,92 ano na Estação, 3,38 no Centro, 1,98 na Arena, 0,25 em Noite Alta), e tudo bate com o modelo dele. Mas a ponte inteira depende de remover um custo que o case declara anual, então a projeção não é a grandeza do case — e os números de manchete (R$ 29,28 mi recorrentes, R$ 142,20 mi em cinco anos) não sobrevivem à premissa correta. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: propõe os armários na Estação a partir do Ano 2 com impacto quantificado (R$ 29,28 mi recorrentes, +0,85 de score) e é alternativa que só existe neste case. A5=3: quatro riscos no slide 7, todos específicos do modelo de parceiros (horário limitado, experiência inconsistente, segurança dos itens, demanda de 18 mil ainda não validada), cada um com mitigação concreta (horário amplo e complementar, treinar/auditar/SLA, rastrear entrega e retirada, piloto ampliado por evidência), mais riscos próprios da Estação no slide 10; o roadmap de quatro estágios ancorado em Ano 1 e Ano 2 dá a dimensão temporal. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização. Registro em separado, porque não cabe neste item: é a única pasta cuja metade da análise foi construída sobre a leitura equivocada de um dado explícito do material.</t>
+          <t>A1=3: os oito resultados de Ano 1 conferem integralmente (25,08/23,15/13,87/18,57 e 27,84/24,50/14,94/19,20). Memória de cálculo completa na planilha, com fórmulas vivas decompondo equipamento, bancos e operação. A2=3: bancos 60/25/23/45 corretos. Detalhe relevante: na Arena ele fixou 23 à mão em vez de usar a fórmula B/C que daria 22,5, ou seja, percebeu o arredondamento e corrigiu deliberadamente, enquanto os outros três bairros seguem por fórmula. A3=2: a ponte entre anos é estruturalmente a melhor do conjunto, com projeção acumulada de 5 anos e o ano de cruzamento calculado por bairro (1,92 ano na Estação, 3,38 no Centro, 1,98 na Arena, 0,25 em Noite Alta), e tudo bate com o modelo dele. Mas a ponte inteira depende de remover um custo que o case declara anual, então a projeção não é a grandeza do case, e os números de manchete (R$ 29,28 mi recorrentes, R$ 142,20 mi em cinco anos) não sobrevivem à premissa correta. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: propõe os armários na Estação a partir do Ano 2 com impacto quantificado (R$ 29,28 mi recorrentes, +0,85 de score) e é alternativa que só existe neste case. A5=3: quatro riscos no slide 7, todos específicos do modelo de parceiros (horário limitado, experiência inconsistente, segurança dos itens, demanda de 18 mil ainda não validada), cada um com mitigação concreta (horário amplo e complementar, treinar/auditar/SLA, rastrear entrega e retirada, piloto ampliado por evidência), mais riscos próprios da Estação no slide 10; o roadmap de quatro estágios ancorado em Ano 1 e Ano 2 dá a dimensão temporal. A6=1: o case não traz erro plantado e ele não descontou transações pela utilização. Registro em separado, porque não cabe neste item: é a única pasta cuja metade da análise foi construída sobre a leitura equivocada de um dado explícito do material.</t>
         </is>
       </c>
       <c r="AB58" s="41" t="n">
@@ -9169,9 +9206,14 @@
       </c>
       <c r="AI58" s="68" t="inlineStr">
         <is>
-          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela, e as duas coisas precisam ser ditas juntas. O que está muito bom: o score multicritério é o método mais transparente do conjunto — pesos publicados, critério de normalização coerente (conferi a interpolação do resultado operacional e fecha), e as oito alternativas comparadas na mesma régua. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder ("Centro lidera a margem, apesar de abrir mão de R$ 3,34 mi"). Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento. O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 mi recorrente, o R$ 142,20 mi de cinco anos e o roadmap bifásico inteiro — que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente; aqui ele é a espinha dorsal e não está declarado em lugar nenhum. Vale registrar que a pasta 07 antecipou exatamente esse risco por escrito na aba de premissas. Segundo ponto, menor: ele lê a "prioridade de rentabilidade anual" como margem, quando o resto da frase no case ("que deverá sustentar a expansão") aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a 2ª melhor opção. Na entrevista eu faria uma pergunta só, e ela vale a etapa toda: o Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2 — por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios de autoria própria. O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três bairros usam a fórmula de divisão — é alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente, o que uma geração uniforme não faz. A planilha tem marcas de trabalho manual: células com "IDEM" como abreviação, "Noite alta" em minúscula na planilha contra "Noite Alta" no deck, e uma observação solta no canto explicando a convenção dos anos 2 a 5. A normalização do score é internamente consistente e foi conferida. E o erro central — tratar custo anual como investimento — é falha de interpretação de quem leu rápido e seguiu adiante, não artefato de geração; texto gerado tende a repetir a premissa do enunciado, não a contrariá-la. Pergunta de propriedade para a entrevista: por que o custo do banco desaparece a partir do Ano 2 se o Anexo E diz que é anual?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela. As duas coisas precisam ser ditas juntas.
+O que está muito bom: o score multicritério é o método mais transparente do conjunto, com pesos publicados, normalização coerente e as oito alternativas comparadas na mesma régua. Conferi a interpolação do resultado operacional e fecha. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder. Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento.
+O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 milhões recorrente, o R$ 142,20 milhões de cinco anos e o roadmap bifásico inteiro. Que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente. Aqui ele é a espinha dorsal e não está declarado em lugar nenhum.
+Segundo ponto, menor. Ele lê a prioridade de rentabilidade anual como margem, quando o resto da frase no case, que fala em sustentar a expansão, aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a segunda melhor opção.
+Na entrevista eu faço uma pergunta só, e ela vale a etapa toda. O Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2, por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai.
+Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
+Indício de IA: Baixo (consultivo, não afeta nota). O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três usam fórmula. É alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente. A planilha tem marcas de trabalho manual, com células escritas como "IDEM" e "Noite alta" em minúscula contra "Noite Alta" no deck. E o erro central, tratar custo anual como investimento, é falha de interpretação de quem leu rápido, não artefato de geração.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9225,7 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
+          <t>Candidato 10 (pasta entregas-candidatos/10, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -9229,7 +9271,7 @@
       </c>
       <c r="O59" s="68" t="inlineStr">
         <is>
-          <t>C1=2: a recomendação é explícita e clara ("Estação Central, em formato de armários inteligentes, com resultado operacional anual de R$ 25.080.000") mas está na seção 6 de 7; o sumário executivo da seção 1 anuncia que "a recomendação final ajusta o modelo por praça" sem dizer qual é, então o leitor precisa chegar ao fim. C2=2: o relatório final é de nível cliente — título, sete seções numeradas, nove tabelas e nota de procedência no fechamento. O que impede o 3 é ele ter entregue junto um arquivo chamado "(Relatório Rascunho).pdf" com anotações cruas separadas por linhas de "######"; o descritor de 3 exige nenhum rascunho visível, e o rascunho foi enviado. C3=1: teste operacional — os títulos são rótulos de seção ("4. Rentabilidade: comparação dos dois modelos", "6. Recomendação de lançamento") e a recomendação não aparece em nenhum deles. A sequência interna é lógica e a seção 7 é uma boa adição, o que torna este 1 contestável, mas o teste é objetivo. C4=3: hierarquia de títulos consistente, nove tabelas no mesmo padrão, nenhuma seção fora do padrão no documento final.</t>
+          <t>C1=2: a recomendação é explícita e clara ("Estação Central, em formato de armários inteligentes, com resultado operacional anual de R$ 25.080.000") mas está na seção 6 de 7; o sumário executivo da seção 1 anuncia que "a recomendação final ajusta o modelo por praça" sem dizer qual é, então o leitor precisa chegar ao fim. C2=2: o relatório final é de nível cliente, título, sete seções numeradas, nove tabelas e nota de procedência no fechamento. O que impede o 3 é ele ter entregue junto um arquivo chamado "(Relatório Rascunho).pdf" com anotações cruas separadas por linhas de "######"; o descritor de 3 exige nenhum rascunho visível, e o rascunho foi enviado. C3=1: teste operacional, os títulos são rótulos de seção ("4. Rentabilidade: comparação dos dois modelos", "6. Recomendação de lançamento") e a recomendação não aparece em nenhum deles. A sequência interna é lógica e a seção 7 é uma boa adição, o que torna este 1 contestável, mas o teste é objetivo. C4=3: hierarquia de títulos consistente, nove tabelas no mesmo padrão, nenhuma seção fora do padrão no documento final.</t>
         </is>
       </c>
       <c r="P59" s="41" t="n">
@@ -9246,7 +9288,7 @@
       </c>
       <c r="T59" s="68" t="inlineStr">
         <is>
-          <t>R1=2: cita as duas partes, mas o número é decorativo e nesse caso joga contra — ele escolhe armários na Estação a R$ 25,08M quando parceiros dão R$ 27,84M no mesmo bairro. O que sustenta a decisão é o argumento, e ele é bom e ancorado no Anexo D: os parceiros têm "horários variáveis" e a estação opera 24h, além do risco de superlotação do comércio local atrasar embarque e desembarque. Tapando o argumento, o número sozinho não sustenta a escolha. R2=3: calcula os dois modelos nos quatro bairros, apresenta a ordem puramente financeira, e então ajusta praça por praça com justificativa escrita para cada uma, descartando explicitamente a resposta financeira pura e dizendo por quê. Ponto fraco registrado: na Arena ele identifica os armários como solução para a dependência de suporte 24h em dias de evento e mesmo assim fica com parceiros, apoiado numa suposição que ele próprio marca como tal ("supõe-se que o comércio local já se anteciparia"). R3=2: a seção 7, "Custo da decisão", é a boa ideia da entrega — ele precifica o que está abdicando ao trocar rentabilidade máxima por mitigação de risco, R$ 3.390.000, e deixa o trade-off auditável em vez de escondido atrás de argumento qualitativo. O que impede o 3 é a agregação: ele soma os quatro bairros como se fossem lançados juntos (R$ 83,09M contra R$ 86,48M), quando o case pede um bairro prioritário e uma sequência de expansão. Restrito à decisão que ele de fato toma, na Estação, o valor abdicado é R$ 2,76M. R4=3: explica a causa por trás do indicador e o que fazer com ela, e a melhor passagem é Noite Alta — ele pega a "complexidade alta" do Anexo B e explicita o mecanismo concreto (confusão de itens, perda de comprovante de retirada, disputa sobre se o item saiu antes ou depois do estado alcoólico do cliente, má-fé do comerciante) e prescreve a troca de modelo. É raciocínio dele, não do case.</t>
+          <t>R1=2: cita as duas partes, mas o número é decorativo e nesse caso joga contra, ele escolhe armários na Estação a R$ 25,08M quando parceiros dão R$ 27,84M no mesmo bairro. O que sustenta a decisão é o argumento, e ele é bom e ancorado no Anexo D: os parceiros têm "horários variáveis" e a estação opera 24h, além do risco de superlotação do comércio local atrasar embarque e desembarque. Tapando o argumento, o número sozinho não sustenta a escolha. R2=3: calcula os dois modelos nos quatro bairros, apresenta a ordem puramente financeira, e então ajusta praça por praça com justificativa escrita para cada uma, descartando explicitamente a resposta financeira pura e dizendo por quê. Ponto fraco registrado: na Arena ele identifica os armários como solução para a dependência de suporte 24h em dias de evento e mesmo assim fica com parceiros, apoiado numa suposição que ele próprio marca como tal ("supõe-se que o comércio local já se anteciparia"). R3=2: a seção 7, "Custo da decisão", é a boa ideia da entrega, ele precifica o que está abdicando ao trocar rentabilidade máxima por mitigação de risco, R$ 3.390.000, e deixa o trade-off auditável em vez de escondido atrás de argumento qualitativo. O que impede o 3 é a agregação: ele soma os quatro bairros como se fossem lançados juntos (R$ 83,09M contra R$ 86,48M), quando o case pede um bairro prioritário e uma sequência de expansão. Restrito à decisão que ele de fato toma, na Estação, o valor abdicado é R$ 2,76M. R4=3: explica a causa por trás do indicador e o que fazer com ela, e a melhor passagem é Noite Alta, ele pega a "complexidade alta" do Anexo B e explicita o mecanismo concreto (confusão de itens, perda de comprovante de retirada, disputa sobre se o item saiu antes ou depois do estado alcoólico do cliente, má-fé do comerciante) e prescreve a troca de modelo. É raciocínio dele, não do case.</t>
         </is>
       </c>
       <c r="U59" s="41" t="n">
@@ -9269,7 +9311,7 @@
       </c>
       <c r="AA59" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem integralmente. A memória de cálculo é completa e visível nos dois arquivos, com as quatro tabelas de custo decompostas por categoria e a receita desenvolvida por semana e por ano. A2=3: bancos 60/25/23/45 corretos, e na Arena ele escreve "~23", sinalizando que percebeu o arredondamento de 22,5. Custo por complexidade correto nos dois modelos e nos quatro bairros. A3=2: a tabela 9 traz a ordem com modelo e resultado por bairro, então há número, mas não existe fasemento, cronograma nem ponte entre períodos — e não há seção de próximos passos em nenhum dos dois arquivos, embora a tarefa 04 do enunciado peça. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a recomendação inteira é a alternativa à resposta financeira pura, com impacto quantificado em R$ 3,39M, mais a alternativa de modelo por bairro com o resultado de cada uma. A5=2: os riscos da seção 5 são muito específicos e por praça, e têm mitigação estrutural — a mitigação é a própria troca para armários, que ele implementa na recomendação. Duas lacunas impedem o 3: os riscos listados são riscos da opção que ele descartou (parceiros), e ele nunca trata os riscos da escolha que fez (intensidade de capital, 60 bancos para instalar e manter, dependência tecnológica); e não há prazo nem próximos passos em lugar nenhum. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização e faz a leitura literal correta dos 54% como mais da metade das horas da semana, mas não nomeia inconsistência nenhuma.</t>
+          <t>A1=3: os oito resultados conferem integralmente. A memória de cálculo é completa e visível nos dois arquivos, com as quatro tabelas de custo decompostas por categoria e a receita desenvolvida por semana e por ano. A2=3: bancos 60/25/23/45 corretos, e na Arena ele escreve "~23", sinalizando que percebeu o arredondamento de 22,5. Custo por complexidade correto nos dois modelos e nos quatro bairros. A3=2: a tabela 9 traz a ordem com modelo e resultado por bairro, então há número, mas não existe fasemento, cronograma nem ponte entre períodos, e não há seção de próximos passos em nenhum dos dois arquivos, embora a tarefa 04 do enunciado peça. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a recomendação inteira é a alternativa à resposta financeira pura, com impacto quantificado em R$ 3,39M, mais a alternativa de modelo por bairro com o resultado de cada uma. A5=2: os riscos da seção 5 são muito específicos e por praça, e têm mitigação estrutural, a mitigação é a própria troca para armários, que ele implementa na recomendação. Duas lacunas impedem o 3: os riscos listados são riscos da opção que ele descartou (parceiros), e ele nunca trata os riscos da escolha que fez (intensidade de capital, 60 bancos para instalar e manter, dependência tecnológica); e não há prazo nem próximos passos em lugar nenhum. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização e faz a leitura literal correta dos 54% como mais da metade das horas da semana, mas não nomeia inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB59" s="41" t="n">
@@ -9293,9 +9335,14 @@
       </c>
       <c r="AI59" s="68" t="inlineStr">
         <is>
-          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica: trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é exatamente o que se espera de consultoria. O argumento por trás também é sólido e ancorado no material — o Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques/dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio. Dois reparos de peso. O primeiro é a agregação: ele soma os quatro bairros para chegar aos R$ 83,09M, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos — restrita à decisão real, a abdicação é R$ 2,76M, não R$ 3,39M. A ideia está certa e a conta está na base errada. O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários — 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede explicitamente. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade. Na entrevista eu faria as duas perguntas que fecham os buracos: se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros? Nota 6,57 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,30.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. O rascunho enviado junto é material de trabalho pessoal — anotações em caixa alta separadas por linhas de "######", com a estrutura do case transcrita e as contas sendo desenvolvidas; ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial ("malícia de próprios comerciantes", as duas perguntas entre aspas sobre o estado alcoólico do cliente) de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se", em vez de afirmar. E a nota de procedência no fim ("nenhum dado adicional foi estimado ou incorporado") é uma afirmação deliberada de método. Pergunta de propriedade para a entrevista: restrita à Estação, quanto custa a sua escolha por armários?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica. Trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é o que se espera de consultoria.
+O argumento por trás também é sólido e ancorado no material. O Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques por dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio.
+Dois reparos de peso. O primeiro é a agregação. Ele soma os quatro bairros para chegar aos R$ 83,09 milhões, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos. Restrita à decisão real, a abdicação é R$ 2,76 milhões, não R$ 3,39 milhões. A ideia está certa e a conta está na base errada.
+O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários: 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade.
+Na entrevista eu faço as duas perguntas que fecham os buracos. Se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros?
+Nota 6,57 com vídeo em branco. Considerando só o que dá para avaliar, 7,30.
+Indício de IA: Baixo (consultivo, não afeta nota). O rascunho enviado junto é material de trabalho pessoal, com anotações em caixa alta separadas por linhas de "######". Ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se" em vez de afirmar.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9354,7 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
+          <t>Candidato 11 (pasta entregas-candidatos/11, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -9353,7 +9400,7 @@
       </c>
       <c r="O60" s="68" t="inlineStr">
         <is>
-          <t>C1=2: a recomendação é explícita, clara e com números quando chega, mas está no slide 11 de 13; a capa não a antecipa e os dez slides anteriores são análise. C2=2: deck estruturado e completo, com capa, tabelas de rentabilidade por bairro e slide de contato, mas com pontas soltas em volume — "Bag Huby" na capa, "Armários inteligententes" repetido nas quatro tabelas, "Central Histórico" e "calcúlos" no slide 5, a utilização de Noite Alta e Arena trocada no slide 3 (31% e 33%, quando é 33% e 31%) contradizendo o slide 12, "110 embarques diários" no slide 4 quando são 110 mil, e o texto de template "BACK TO AGENDA" esquecido no slide 4. C3=1: teste operacional — os títulos são rótulos e a recomendação não aparece em nenhum deles; além disso os slides 2 e 4 têm o título idêntico ("Comparação qualitativa dos Bairros") com o slide 3 no meio, o que obriga o leitor a voltar para entender o que mudou. C4=1: contagem de slides fora do padrão passa de dois — o slide 4 carrega texto de template, o slide 10 quebra os números no meio da célula ("R$23.150.00 0") e o slide 11 é um paredão de texto em duas colunas muito mais denso que o resto. As tabelas de rentabilidade (6 a 9) são limpas e uniformes, o que torna este 1 contestável.</t>
+          <t>C1=2: a recomendação é explícita, clara e com números quando chega, mas está no slide 11 de 13; a capa não a antecipa e os dez slides anteriores são análise. C2=2: deck estruturado e completo, com capa, tabelas de rentabilidade por bairro e slide de contato, mas com pontas soltas em volume, "Bag Huby" na capa, "Armários inteligententes" repetido nas quatro tabelas, "Central Histórico" e "calcúlos" no slide 5, a utilização de Noite Alta e Arena trocada no slide 3 (31% e 33%, quando é 33% e 31%) contradizendo o slide 12, "110 embarques diários" no slide 4 quando são 110 mil, e o texto de template "BACK TO AGENDA" esquecido no slide 4. C3=1: teste operacional, os títulos são rótulos e a recomendação não aparece em nenhum deles; além disso os slides 2 e 4 têm o título idêntico ("Comparação qualitativa dos Bairros") com o slide 3 no meio, o que obriga o leitor a voltar para entender o que mudou. C4=1: contagem de slides fora do padrão passa de dois, o slide 4 carrega texto de template, o slide 10 quebra os números no meio da célula ("R$23.150.00 0") e o slide 11 é um paredão de texto em duas colunas muito mais denso que o resto. As tabelas de rentabilidade (6 a 9) são limpas e uniformes, o que torna este 1 contestável.</t>
         </is>
       </c>
       <c r="P60" s="41" t="n">
@@ -9370,7 +9417,7 @@
       </c>
       <c r="T60" s="68" t="inlineStr">
         <is>
-          <t>R1=3: cita o número que sustenta a escolha dela (margem de 90,7%) e a razão de negócio (baixa complexidade, menor capacidade ociosa, demanda consistente), e as duas partes se apoiam. Mais importante, ela enfrenta o contra-argumento por escrito no slide 11: "embora o bairro Estação Central tenha o maior resultado operacional nos dois modelos, a baixa complexidade da região torna essa opção preferível". Não esconde que está escolhendo o segundo maior resultado. R2=3: o slide 10 ranqueia os quatro com os dois modelos lado a lado, o slide 11 separa a justificativa do bairro da justificativa do modelo, e o slide 12 justifica individualmente as posições 2, 3 e 4 com critério (margem, volatilidade, utilização, custo de operação). Descarta a Estação Central por escrito e com razão declarada. R3=1: entregou o pedido de forma essencialmente completa e correta, mas sem nada de fato além dele. O 2x2 de demanda estável x volátil do slide 2 é a única construção própria e fica subdesenvolvida, sem posicionamento visível dos bairros nos quadrantes. Não há sensibilidade, break-even, giro por posição nem economia por posição, e os próximos passos praticamente não existem — só um gesto no slide 12 sobre investir em Noite Alta "quando a operação já estiver madura". R4=2: compara a utilização entre os bairros e tira conclusão (a Arena fica ociosa a maior parte da semana por depender do calendário de eventos; Noite Alta é a mais custosa pelo custo de operação por posição mais alto). Mas a interpretação central — 54% de utilização como prova de "demanda consistente" — não é justificada causalmente e o próprio case adverte que a capacidade foi dimensionada para picos, então a utilização reflete tempo de permanência e concentração, não regularidade.</t>
+          <t>R1=3: cita o número que sustenta a escolha dela (margem de 90,7%) e a razão de negócio (baixa complexidade, menor capacidade ociosa, demanda consistente), e as duas partes se apoiam. Mais importante, ela enfrenta o contra-argumento por escrito no slide 11: "embora o bairro Estação Central tenha o maior resultado operacional nos dois modelos, a baixa complexidade da região torna essa opção preferível". Não esconde que está escolhendo o segundo maior resultado. R2=3: o slide 10 ranqueia os quatro com os dois modelos lado a lado, o slide 11 separa a justificativa do bairro da justificativa do modelo, e o slide 12 justifica individualmente as posições 2, 3 e 4 com critério (margem, volatilidade, utilização, custo de operação). Descarta a Estação Central por escrito e com razão declarada. R3=1: entregou o pedido de forma essencialmente completa e correta, mas sem nada de fato além dele. O 2x2 de demanda estável x volátil do slide 2 é a única construção própria e fica subdesenvolvida, sem posicionamento visível dos bairros nos quadrantes. Não há sensibilidade, break-even, giro por posição nem economia por posição, e os próximos passos praticamente não existem, só um gesto no slide 12 sobre investir em Noite Alta "quando a operação já estiver madura". R4=2: compara a utilização entre os bairros e tira conclusão (a Arena fica ociosa a maior parte da semana por depender do calendário de eventos; Noite Alta é a mais custosa pelo custo de operação por posição mais alto). Mas a interpretação central, 54% de utilização como prova de "demanda consistente", não é justificada causalmente e o próprio case adverte que a capacidade foi dimensionada para picos, então a utilização reflete tempo de permanência e concentração, não regularidade.</t>
         </is>
       </c>
       <c r="U60" s="41" t="n">
@@ -9393,7 +9440,7 @@
       </c>
       <c r="AA60" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem integralmente, com as margens todas corretas (69,7%/77,3%, 85,7%/90,7%, 61,9%/64,0%, 77,1%/83,0%). A memória de cálculo é boa e visível: o slide 5 traz as fórmulas e os slides 6 a 9 decompõem, bairro por bairro e modelo por modelo, equipamento, bancos, operação, custo total, resultado e margem. A2=3: os custos de banco estão todos corretos — R$ 4.200.000, R$ 1.750.000, R$ 1.610.000 e R$ 3.150.000 — e o valor da Arena só fecha com 23 bancos, então o arredondamento de 22,5 foi feito, ainda que ela não mostre a contagem de bancos explicitamente. Custo por complexidade correto nos oito cenários. A3=2: o slide 12 traz uma lógica de sequenciamento com número e papel para cada posição ("após priorizar o bairro mais eficiente, o segundo lançamento deve maximizar volume em resultado operacional para garantir a capacidade de expansão"), mas não há fasemento, cronograma nem ponte entre períodos. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a Estação Central entra como segundo lançamento com impacto quantificado em R$ 27.840.000 e papel definido, alternativa que só existe neste case. A5=2: os dois riscos do slide 11 são específicos da recomendação dela e do modelo que escolheu (dependência de terceiros, com qualidade e disponibilidade fora do controle direto da BagHub; padronização da experiência, porque parceiros têm horário variável contra o padrão 24h dos armários). Nenhum dos dois tem mitigação, e não há prazo nem próximos passos. Riscos específicos sem mitigação é exatamente o descritor de 2. A6=1: o case não traz erro plantado; a fórmula de receita do slide 5 está correta e ela não descontou transações pela utilização, mas não nomeia inconsistência nenhuma.</t>
+          <t>A1=3: os oito resultados conferem integralmente, com as margens todas corretas (69,7%/77,3%, 85,7%/90,7%, 61,9%/64,0%, 77,1%/83,0%). A memória de cálculo é boa e visível: o slide 5 traz as fórmulas e os slides 6 a 9 decompõem, bairro por bairro e modelo por modelo, equipamento, bancos, operação, custo total, resultado e margem. A2=3: os custos de banco estão todos corretos, R$ 4.200.000, R$ 1.750.000, R$ 1.610.000 e R$ 3.150.000, e o valor da Arena só fecha com 23 bancos, então o arredondamento de 22,5 foi feito, ainda que ela não mostre a contagem de bancos explicitamente. Custo por complexidade correto nos oito cenários. A3=2: o slide 12 traz uma lógica de sequenciamento com número e papel para cada posição ("após priorizar o bairro mais eficiente, o segundo lançamento deve maximizar volume em resultado operacional para garantir a capacidade de expansão"), mas não há fasemento, cronograma nem ponte entre períodos. O case não declara meta numérica, então a outra metade do descritor não é testável. A4=3: a Estação Central entra como segundo lançamento com impacto quantificado em R$ 27.840.000 e papel definido, alternativa que só existe neste case. A5=2: os dois riscos do slide 11 são específicos da recomendação dela e do modelo que escolheu (dependência de terceiros, com qualidade e disponibilidade fora do controle direto da BagHub; padronização da experiência, porque parceiros têm horário variável contra o padrão 24h dos armários). Nenhum dos dois tem mitigação, e não há prazo nem próximos passos. Riscos específicos sem mitigação é exatamente o descritor de 2. A6=1: o case não traz erro plantado; a fórmula de receita do slide 5 está correta e ela não descontou transações pela utilização, mas não nomeia inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB60" s="41" t="n">
@@ -9417,9 +9464,14 @@
       </c>
       <c r="AI60" s="68" t="inlineStr">
         <is>
-          <t>A análise está certa e a comunicação é que derruba a nota, o que é uma pena porque os dois problemas são baratos de resolver. Os oito cenários fecham todos, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo: cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo — diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito. O que custa caro é o acabamento, e o volume de deslizes é grande: o nome da empresa sai errado na capa ("Bag Huby"), "Armários inteligententes" se repete nas quatro tabelas, a utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12, os 110 mil embarques viram "110 embarques diários" no slide 4, e há texto de template ("BACK TO AGENDA") esquecido no meio do deck. Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede. Na entrevista eu faria duas perguntas: na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31% — qual é a certa? E você colocou a Arena (R$ 14,94M) à frente de Noite Alta (R$ 19,20M) no ranking; qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita. Nota 6,07 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,74.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria, todos vindos do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento, "Central Histórico" trocado. O texto de template "BACK TO AGENDA" esquecido no slide 4 indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição: saída gerada tende a ser ortograficamente limpa e coerente consigo mesma. Pergunta de propriedade para a entrevista: a utilização da Arena é 31% ou 33%, e por que ela vem antes de Noite Alta no ranking?
-[IDENTIFICAÇÃO] Nome na capa e e-mail no último slide: Leandra Cunha de Souza (l304532@dac.unicamp.br). V1/V2 nas linhas 14 (victor 2/2) e 36 (Proc 2/2).</t>
+          <t>A análise está certa e a comunicação é que derruba a nota. É uma pena, porque os dois problemas são baratos de resolver.
+Os oito cenários fecham, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo. Cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo. Diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito.
+O que custa caro é o acabamento, e o volume de deslizes é grande. O nome da empresa sai errado na capa, "Bag Huby". "Armários inteligententes" se repete nas quatro tabelas. A utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12. Os 110 mil embarques viram "110 embarques diários" no slide 4. E há texto de template, "BACK TO AGENDA", esquecido no meio do deck.
+Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede.
+Na entrevista eu faço duas perguntas. Na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31%, qual é a certa? E você colocou a Arena, R$ 14,94 milhões, à frente de Noite Alta, R$ 19,20 milhões, no ranking, qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita.
+Nota 6,07 com vídeo em branco. Considerando só o que dá para avaliar, 6,74.
+Indício de IA: Baixo (consultivo, não afeta nota). Todos os sinais vêm do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento. O texto de template "BACK TO AGENDA" esquecido indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Leandra Cunha de Souza. As notas de vídeo dele estão nas linhas 14 (victor 2/2) e 36 (Proc 2/2) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9483,7 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Candidato 12 — pasta entregas-candidatos/12 (case BagHub 2026.2)</t>
+          <t>Candidato 12 (pasta entregas-candidatos/12, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -9477,7 +9529,7 @@
       </c>
       <c r="O61" s="68" t="inlineStr">
         <is>
-          <t>C1=3: o deck abre pela recomendação — o slide 3 é o divisor "Recomendação de investimento" e o slide 4 traz a resposta completa com o número (Estação Central, pontos parceiros, R$ 27.840.000). Contando capa, sumário e divisor, ela chega na 4ª página de 18, ou seja, a primeira página de conteúdo é a resposta. Ressalva para o 2º avaliador: não é literalmente uma frase, está distribuída em três colunas. C2=2: deck de nível cliente com capa, sumário, divisores de seção e slide de fechamento, mais planilha de 5 abas. O que impede o 3 são títulos duplicados: os slides 9, 10 e 11 têm título e subtítulo idênticos ("Cenários de investimento: projeções anuais de lucro") e os slides 6 e 7 repetem "Mapeamento da cidade", quatro slides em que o leitor não sabe o que mudou. C3=2: a recomendação aparece no título ("O futuro da BagHub em Estação Central, Porto Claro") e o arco fecha — recomendação, comparação, rentabilidade, conclusões, matriz, modelo de negócios, riscos e próximos passos. O salto que impede o 3 é justamente o título triplicado dos slides 9 a 11. C4=3: template consistente com divisores de seção, gráficos no mesmo padrão e nenhum slide com parágrafo corrido.</t>
+          <t>C1=3: o deck abre pela recomendação, o slide 3 é o divisor "Recomendação de investimento" e o slide 4 traz a resposta completa com o número (Estação Central, pontos parceiros, R$ 27.840.000). Contando capa, sumário e divisor, ela chega na 4ª página de 18, ou seja, a primeira página de conteúdo é a resposta. Ressalva para o 2º avaliador: não é literalmente uma frase, está distribuída em três colunas. C2=2: deck de nível cliente com capa, sumário, divisores de seção e slide de fechamento, mais planilha de 5 abas. O que impede o 3 são títulos duplicados: os slides 9, 10 e 11 têm título e subtítulo idênticos ("Cenários de investimento: projeções anuais de lucro") e os slides 6 e 7 repetem "Mapeamento da cidade", quatro slides em que o leitor não sabe o que mudou. C3=2: a recomendação aparece no título ("O futuro da BagHub em Estação Central, Porto Claro") e o arco fecha, recomendação, comparação, rentabilidade, conclusões, matriz, modelo de negócios, riscos e próximos passos. O salto que impede o 3 é justamente o título triplicado dos slides 9 a 11. C4=3: template consistente com divisores de seção, gráficos no mesmo padrão e nenhum slide com parágrafo corrido.</t>
         </is>
       </c>
       <c r="P61" s="41" t="n">
@@ -9494,7 +9546,7 @@
       </c>
       <c r="T61" s="68" t="inlineStr">
         <is>
-          <t>R1=3: o slide 4 amarra R$ 27.840.000 a razões de negócio próprias e verificáveis — infraestrutura ferroviária e rodoviária, e o fato de a Estação Central fazer fronteira com 5 bairros, sendo passagem para diversos trajetos, com sazonalidade "homogênea e previsível" e potencial de fidelização. Conferi no mapa do Anexo A e a contagem de 5 bairros vizinhos está correta. Tapando o número, o argumento de fronteira e recorrência fica; tapando o argumento, 27,84M é o máximo dos oito. R2=3: o slide 13 ordena as OITO combinações numa matriz esforço-resultado, e a ordem está correta por lucro absoluto (27,84 &gt; 25,08 &gt; 24,50 &gt; 23,15 &gt; 19,20 &gt; 18,57 &gt; 14,94 &gt; 13,87), incluindo o detalhe de colocar Estação-armários à frente de Centro-parceiros. Marca Noite Alta como 5/6 com asterisco, declarando que a posição depende de pesquisa sobre disponibilidade horária dos parceiros — reconhece a incerteza em vez de fingir precisão. R3=3: três adições reais. Primeiro, o critério "potencial de fronteira" (aba diagramas, notas 3/2/1/2), construído a partir da leitura do mapa do Anexo A — foi a única candidata a usar o mapa analiticamente, e isso sustenta diretamente a recomendação. Segundo, a aba comparação calcula a vantagem percentual dos parceiros por bairro (11,0% / 5,8% / 7,7% / 3,4%) e ela usa isso no slide 12 para argumentar que a diferença não é grande o bastante para ignorar fatores qualitativos, apontando Noite Alta (3,4%, a menor) como onde a vantagem pode virar — é o mesmo achado das melhores entregas, por outro caminho. Terceiro, um Business Model Canvas completo no slide 15, não pedido. R4=2: acerta em dois indicadores e erra no que promove a primeiro lugar. Acerta ao interpretar os percentuais de vantagem e ao derivar consequência de negócio do mapa. Erra no slide 17, onde lista como oportunidade nº 1 que "apenas 42% das horas semanais disponíveis são utilizadas na estação central, um maior aproveitamento teria impacto direto no lucro" — o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações, então horas ociosas não são alavanca de receita.</t>
+          <t>R1=3: o slide 4 amarra R$ 27.840.000 a razões de negócio próprias e verificáveis, infraestrutura ferroviária e rodoviária, e o fato de a Estação Central fazer fronteira com 5 bairros, sendo passagem para diversos trajetos, com sazonalidade "homogênea e previsível" e potencial de fidelização. Conferi no mapa do Anexo A e a contagem de 5 bairros vizinhos está correta. Tapando o número, o argumento de fronteira e recorrência fica; tapando o argumento, 27,84M é o máximo dos oito. R2=3: o slide 13 ordena as OITO combinações numa matriz esforço-resultado, e a ordem está correta por lucro absoluto (27,84 &gt; 25,08 &gt; 24,50 &gt; 23,15 &gt; 19,20 &gt; 18,57 &gt; 14,94 &gt; 13,87), incluindo o detalhe de colocar Estação-armários à frente de Centro-parceiros. Marca Noite Alta como 5/6 com asterisco, declarando que a posição depende de pesquisa sobre disponibilidade horária dos parceiros, reconhece a incerteza em vez de fingir precisão. R3=3: três adições reais. Primeiro, o critério "potencial de fronteira" (aba diagramas, notas 3/2/1/2), construído a partir da leitura do mapa do Anexo A, foi a única candidata a usar o mapa analiticamente, e isso sustenta diretamente a recomendação. Segundo, a aba comparação calcula a vantagem percentual dos parceiros por bairro (11,0% / 5,8% / 7,7% / 3,4%) e ela usa isso no slide 12 para argumentar que a diferença não é grande o bastante para ignorar fatores qualitativos, apontando Noite Alta (3,4%, a menor) como onde a vantagem pode virar, é o mesmo achado das melhores entregas, por outro caminho. Terceiro, um Business Model Canvas completo no slide 15, não pedido. R4=2: acerta em dois indicadores e erra no que promove a primeiro lugar. Acerta ao interpretar os percentuais de vantagem e ao derivar consequência de negócio do mapa. Erra no slide 17, onde lista como oportunidade nº 1 que "apenas 42% das horas semanais disponíveis são utilizadas na estação central, um maior aproveitamento teria impacto direto no lucro", o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações, então horas ociosas não são alavanca de receita.</t>
         </is>
       </c>
       <c r="U61" s="41" t="n">
@@ -9517,7 +9569,7 @@
       </c>
       <c r="AA61" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem integralmente. Memória de cálculo em planilha real, com as abas modelo 1 e modelo 2 puxando os parâmetros da aba Rascunho por referência ((C22+C25)*2400+70000*60, e assim por diante). A2=3: contagens de banco corretas nas fórmulas — 60, 25, 23 e 45 — com a Arena em 23, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários, com os três níveis parametrizados na aba Rascunho. A3=3: o slide 17 traz quatro próximos passos concretos, com prazo declarado ("piloto de 3 meses na Estação Central... comparando os dados projetados e os reais") e definição de KPIs e OKRs; a expansão está nomeada com razão (Centro Histórico, por alto lucro, baixa complexidade e proximidade geográfica) e a ordem completa está no slide 13. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: alternativa quantificada por dois caminhos — Estação-armários em 2º na matriz e a vantagem percentual dos parceiros por bairro, que dimensiona quanto se perderia ao trocar de modelo. A5=3: quatro riscos no slide 17, todos específicos da recomendação dela (dependência dos parceiros comerciais; horários de pico do transporte público superando a capacidade estipulada; manutenção maior por proximidade ao transporte público; e uma observação afiada e própria — baixa conversão porque a pressa é característica do público-alvo de conexões). Mitigação vem via os próximos passos (mapeamento da rede de parceiros, piloto com dados em tempo real) e o prazo de 3 meses está escrito. A6=1: o case não traz erro plantado. Ela não descontou transações pela utilização nas contas, que estão todas certas, mas não nomeou inconsistência nenhuma.</t>
+          <t>A1=3: os oito resultados conferem integralmente. Memória de cálculo em planilha real, com as abas modelo 1 e modelo 2 puxando os parâmetros da aba Rascunho por referência ((C22+C25)*2400+70000*60, e assim por diante). A2=3: contagens de banco corretas nas fórmulas, 60, 25, 23 e 45, com a Arena em 23, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários, com os três níveis parametrizados na aba Rascunho. A3=3: o slide 17 traz quatro próximos passos concretos, com prazo declarado ("piloto de 3 meses na Estação Central... comparando os dados projetados e os reais") e definição de KPIs e OKRs; a expansão está nomeada com razão (Centro Histórico, por alto lucro, baixa complexidade e proximidade geográfica) e a ordem completa está no slide 13. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: alternativa quantificada por dois caminhos, Estação-armários em 2º na matriz e a vantagem percentual dos parceiros por bairro, que dimensiona quanto se perderia ao trocar de modelo. A5=3: quatro riscos no slide 17, todos específicos da recomendação dela (dependência dos parceiros comerciais; horários de pico do transporte público superando a capacidade estipulada; manutenção maior por proximidade ao transporte público; e uma observação afiada e própria, baixa conversão porque a pressa é característica do público-alvo de conexões). Mitigação vem via os próximos passos (mapeamento da rede de parceiros, piloto com dados em tempo real) e o prazo de 3 meses está escrito. A6=1: o case não traz erro plantado. Ela não descontou transações pela utilização nas contas, que estão todas certas, mas não nomeou inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB61" s="41" t="n">
@@ -9541,9 +9593,15 @@
       </c>
       <c r="AI61" s="68" t="inlineStr">
         <is>
-          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente: contou que a Estação Central faz fronteira com 5 bairros — conferi, está certo — e transformou isso num critério pontuado de "potencial de fronteira", usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou. A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação-armários à frente de Centro-parceiros, e marca Noite Alta com asterisco declarando que a posição depende de pesquisa — reconhecer incerteza em vez de simular precisão é maturidade. A terceira é a vantagem percentual por bairro (11,0% / 5,8% / 7,7% / 3,4%), usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses. O erro que eu cobraria está no slide 17: ela promove a oportunidade nº 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações — ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita. De forma, o custo veio dos títulos repetidos: três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia. Na entrevista eu faria as duas perguntas: como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou. Nota 7,93 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,81.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A aba Rascunho é material de trabalho cru, com a estrutura do case transcrita em abreviações (ec, ch, a, na) e typos de digitação rápida ("receita anula", "infliencia", "complexdade", "posições necessarias") — ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo que não sai de texto. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas, sinal de quem resolveu o arredondamento na mão. E o risco de "baixa conversão pela pressa" é uma observação idiossincrática sobre o público. Há ainda o typo "resltado" no eixo da matriz do slide 13. Pergunta de propriedade para a entrevista: quais são os 5 bairros de fronteira da Estação Central, e como as horas ociosas virariam lucro?
-[IDENTIFICAÇÃO] Nome no arquivo e no slide de fechamento: Mariana Nunes Galvão Sant'Anna. V1/V2 nas linhas 16 (luis 3/2) e 38 (Proc 2/3).</t>
+          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente. Contou que a Estação Central faz fronteira com 5 bairros, e conferi que está certo, e transformou isso num critério pontuado de potencial de fronteira, usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou.
+A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação com armários à frente de Centro com parceiros. E marca Noite Alta com asterisco, declarando que a posição depende de pesquisa. Reconhecer incerteza em vez de simular precisão é maturidade.
+A terceira é a vantagem percentual por bairro, 11,0%, 5,8%, 7,7% e 3,4%, usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses.
+O erro que eu cobraria está no slide 17. Ela promove a oportunidade número 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações. Ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita.
+De forma, o custo veio dos títulos repetidos. Três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia.
+Na entrevista eu faço as duas perguntas. Como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou.
+Nota 7,93 com vídeo em branco. Considerando só o que dá para avaliar, 8,81.
+Indício de IA: Baixo (consultivo, não afeta nota). A aba Rascunho é material cru, com a estrutura do case em abreviações e typos de digitação rápida. Ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas. E o risco de baixa conversão pela pressa é observação idiossincrática sobre o público.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Mariana Nunes Galvão Sant'Anna. As notas de vídeo dele estão nas linhas 16 (luis 3/2) e 38 (Proc 2/3) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9613,7 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Candidato 13 — pasta entregas-candidatos/13 (case BagHub 2026.2)</t>
+          <t>Candidato 13 (pasta entregas-candidatos/13, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -9601,7 +9659,7 @@
       </c>
       <c r="O62" s="68" t="inlineStr">
         <is>
-          <t>C1=1: não há recomendação escrita em lugar nenhum dos dois arquivos. Ele cumpre as tarefas 01 a 03 (comparar bairros, demanda e capacidade, calcular rentabilidade) e para. Dá para inferir a escolha pelos gráficos de lucro acumulado, onde a Estação Central tem o maior acúmulo em 5 anos e os armários ultrapassam os parceiros, mas em nenhum momento ele escreve qual bairro nem qual modelo escolheria — que é exatamente o descritor de 1. C2=0: o entregável é seis fotografias de páginas de caderno, com sombra visível, iluminação irregular e dominante de cor rosada, mais um print de planilha. O descritor de 0 é literal: "foto de papel". Aplicando o teste operacional, não é arquivo que se manda a um cliente sem editar. Registro em favor dele que a caligrafia é organizada, com títulos em caixa e blocos "Resumo do Bairro" destacados — não é material caótico, é material privado. C3=1: a sequência interna é lógica e espelha as tarefas do case, mas os quatro blocos de bairro são paralelos e independentes, nenhum puxa o seguinte, e a página de gráficos não se conecta a nenhum texto. Sem conclusão, não há fio que chegue a lugar algum. C4=1: formatação improvisada mas legível — as fotos exigem esforço para ler por causa da sombra e do contraste, e a página de Excel é limpa.</t>
+          <t>C1=1: não há recomendação escrita em lugar nenhum dos dois arquivos. Ele cumpre as tarefas 01 a 03 (comparar bairros, demanda e capacidade, calcular rentabilidade) e para. Dá para inferir a escolha pelos gráficos de lucro acumulado, onde a Estação Central tem o maior acúmulo em 5 anos e os armários ultrapassam os parceiros, mas em nenhum momento ele escreve qual bairro nem qual modelo escolheria, que é exatamente o descritor de 1. C2=0: o entregável é seis fotografias de páginas de caderno, com sombra visível, iluminação irregular e dominante de cor rosada, mais um print de planilha. O descritor de 0 é literal: "foto de papel". Aplicando o teste operacional, não é arquivo que se manda a um cliente sem editar. Registro em favor dele que a caligrafia é organizada, com títulos em caixa e blocos "Resumo do Bairro" destacados, não é material caótico, é material privado. C3=1: a sequência interna é lógica e espelha as tarefas do case, mas os quatro blocos de bairro são paralelos e independentes, nenhum puxa o seguinte, e a página de gráficos não se conecta a nenhum texto. Sem conclusão, não há fio que chegue a lugar algum. C4=1: formatação improvisada mas legível, as fotos exigem esforço para ler por causa da sombra e do contraste, e a página de Excel é limpa.</t>
         </is>
       </c>
       <c r="P62" s="41" t="n">
@@ -9618,7 +9676,7 @@
       </c>
       <c r="T62" s="68" t="inlineStr">
         <is>
-          <t>R1=0: não há recomendação, que é o descritor de 0. Todo o material quantitativo está correto, mas nenhuma decisão é tomada nem sustentada. R2=1: aplicando o teste operacional — "ele descartou alguma coisa por escrito? Se não descartou nada, não discutiu" — ele não descartou nada. Registro em favor dele, para o 2º avaliador, que a comparação em si é das mais completas do conjunto: os oito cenários calculados à mão mais a evolução dos dois modelos em 5 anos nos quatro bairros. Há comparação rica e zero escolha, o que torna este 1 contestável para 2. R3=0: o pedido ficou incompleto, que é o descritor de 0. A tarefa 04 do enunciado pede escolher bairro e modelo, sustentar com números e apresentar riscos e próximos passos — nada disso foi entregue. Vale notar que ele trouxe coisas não pedidas e boas (os 3C's aplicados ao case, a projeção de 5 anos), mas o descritor é explícito sobre pedido incompleto. R4=2: lê as lucratividades e compara ano 1 contra anos seguintes, tirando conclusão. Tem ainda a melhor observação qualitativa do conjunto sobre a demanda: anota que as conexões duram em média 1h30 a 2h e que "na maior parte das vezes não será tempo suficiente para fazer uma visita", o que questiona o próprio driver de demanda da Estação Central. O que impede o 3 é que ele não faz nada com essa observação — não ajusta número, não vira risco, não muda conclusão — e a duração de 1h30 a 2h não está no case nem é marcada como premissa dele.</t>
+          <t>R1=0: não há recomendação, que é o descritor de 0. Todo o material quantitativo está correto, mas nenhuma decisão é tomada nem sustentada. R2=1: aplicando o teste operacional, "ele descartou alguma coisa por escrito? Se não descartou nada, não discutiu", ele não descartou nada. Registro em favor dele, para o 2º avaliador, que a comparação em si é das mais completas do conjunto: os oito cenários calculados à mão mais a evolução dos dois modelos em 5 anos nos quatro bairros. Há comparação rica e zero escolha, o que torna este 1 contestável para 2. R3=0: o pedido ficou incompleto, que é o descritor de 0. A tarefa 04 do enunciado pede escolher bairro e modelo, sustentar com números e apresentar riscos e próximos passos, nada disso foi entregue. Vale notar que ele trouxe coisas não pedidas e boas (os 3C's aplicados ao case, a projeção de 5 anos), mas o descritor é explícito sobre pedido incompleto. R4=2: lê as lucratividades e compara ano 1 contra anos seguintes, tirando conclusão. Tem ainda a melhor observação qualitativa do conjunto sobre a demanda: anota que as conexões duram em média 1h30 a 2h e que "na maior parte das vezes não será tempo suficiente para fazer uma visita", o que questiona o próprio driver de demanda da Estação Central. O que impede o 3 é que ele não faz nada com essa observação, não ajusta número, não vira risco, não muda conclusão, e a duração de 1h30 a 2h não está no case nem é marcada como premissa dele.</t>
         </is>
       </c>
       <c r="U62" s="41" t="n">
@@ -9641,7 +9699,7 @@
       </c>
       <c r="AA62" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados de Ano 1 conferem integralmente, todos desenvolvidos à mão. Estação Central: receita 1.200.000 transações x 30 = 36M, armários 3.360.000 + 4.200.000 + 3.360.000 = 10.920.000, lucro 25.080.000, lucratividade 69,66%; parceiros 8.160.000, lucro 27.840.000, 77,33%. Arena: parceiros 3.060.000, lucro 14.940.000, 83%; armários lucro 13.870.000, 77,05%. Noite Alta: armários 11.430.000 e lucro 18.570.000 a 61,9%; parceiros 10.800.000 e 19.200.000 a 64%. A memória de cálculo não é só visível, ela É o entregável. A2=3: bancos explícitos e corretos (60 na Estação, 45 em Noite Alta) e o custo de R$ 1.610.000 na Arena só fecha com 23 bancos, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários. A3=1: existe projeção de 5 anos com ponte ano a ano e ela bate com o modelo dele, mas está inteiramente apoiada em remover o custo do banco a partir do 2º ano — ele anota "apenas 1º ano" ao lado dos R$ 4.200.000, quando o Anexo E declara que todos os valores são anuais. Sob a premissa correta, os armários nunca ultrapassam os parceiros e os quatro gráficos caem. Além disso não há plano de lançamento nenhum, nem fasemento, nem próximos passos. A4=2: a alternativa dos armários está coerente com o case e quantificada em 5 anos nos quatro bairros, mas nunca é proposta como curso de ação — fica entre descritores porque há quantificação sem proposta. A5=1: ele lista pontos negativos por bairro, e são específicos (atendimento noturno, segurança, operação complexa e risco de roubos em Noite Alta; a duração das conexões na Estação), mas estão desacoplados de qualquer recomendação, não têm mitigação e não há próximos passos, que o enunciado pede explicitamente na tarefa 04. A6=1: o case não traz erro plantado. Ele anota "42% de utilização" ao lado da conta de receita como contexto e não aplica como desconto, ou seja, passou pelo ponto certo, mas não nomeia inconsistência nenhuma.</t>
+          <t>A1=3: os oito resultados de Ano 1 conferem integralmente, todos desenvolvidos à mão. Estação Central: receita 1.200.000 transações x 30 = 36M, armários 3.360.000 + 4.200.000 + 3.360.000 = 10.920.000, lucro 25.080.000, lucratividade 69,66%; parceiros 8.160.000, lucro 27.840.000, 77,33%. Arena: parceiros 3.060.000, lucro 14.940.000, 83%; armários lucro 13.870.000, 77,05%. Noite Alta: armários 11.430.000 e lucro 18.570.000 a 61,9%; parceiros 10.800.000 e 19.200.000 a 64%. A memória de cálculo não é só visível, ela É o entregável. A2=3: bancos explícitos e corretos (60 na Estação, 45 em Noite Alta) e o custo de R$ 1.610.000 na Arena só fecha com 23 bancos, ou seja, o arredondamento de 22,5 foi feito. Custo por complexidade correto nos oito cenários. A3=1: existe projeção de 5 anos com ponte ano a ano e ela bate com o modelo dele, mas está inteiramente apoiada em remover o custo do banco a partir do 2º ano, ele anota "apenas 1º ano" ao lado dos R$ 4.200.000, quando o Anexo E declara que todos os valores são anuais. Sob a premissa correta, os armários nunca ultrapassam os parceiros e os quatro gráficos caem. Além disso não há plano de lançamento nenhum, nem fasemento, nem próximos passos. A4=2: a alternativa dos armários está coerente com o case e quantificada em 5 anos nos quatro bairros, mas nunca é proposta como curso de ação, fica entre descritores porque há quantificação sem proposta. A5=1: ele lista pontos negativos por bairro, e são específicos (atendimento noturno, segurança, operação complexa e risco de roubos em Noite Alta; a duração das conexões na Estação), mas estão desacoplados de qualquer recomendação, não têm mitigação e não há próximos passos, que o enunciado pede explicitamente na tarefa 04. A6=1: o case não traz erro plantado. Ele anota "42% de utilização" ao lado da conta de receita como contexto e não aplica como desconto, ou seja, passou pelo ponto certo, mas não nomeia inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB62" s="41" t="n">
@@ -9660,14 +9718,19 @@
       <c r="AG62" s="41" t="n"/>
       <c r="AH62" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0 pela letra do item: o Excel Graficos é um PDF exportado, não um arquivo de planilha — mesma ressalva das pastas 05 e 08, ele entregou memória de cálculo de fato, em outro formato. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas; fotos de caderno e print de planilha não são entregável fechado. E3=0, sem vídeo. E4=1: os quatro gráficos de lucro acumulado são corretos e bem feitos, com título, legenda e eixo, mas estão soltos — nenhum texto os cita e nenhuma afirmação é construída sobre eles.</t>
+          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0 pela letra do item: o Excel Graficos é um PDF exportado, não um arquivo de planilha, mesma ressalva das pastas 05 e 08, ele entregou memória de cálculo de fato, em outro formato. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas; fotos de caderno e print de planilha não são entregável fechado. E3=0, sem vídeo. E4=1: os quatro gráficos de lucro acumulado são corretos e bem feitos, com título, legenda e eixo, mas estão soltos, nenhum texto os cita e nenhuma afirmação é construída sobre eles.</t>
         </is>
       </c>
       <c r="AI62" s="68" t="inlineStr">
         <is>
-          <t>É a entrega mais frustrante do conjunto, porque a parte difícil está certa e a parte fácil não foi feita. Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas: anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade — ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou. E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some-se o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado. Sobre a projeção, ela também não sobrevive: ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais — corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar para a diretoria que este é o terceiro candidato a ler o banco como investimento (junto com as pastas 05 e 09), o que sugere que a redação do Anexo E merece um ajuste no próximo case. Na entrevista, se ele passar, a primeira pergunta é a que falta: você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda: por que o banco vale só no 1º ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case? Nota 3,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,48.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. É a pasta com a evidência de propriedade mais inequívoca do conjunto, ao lado da 05. Seis páginas de caderno fotografadas sob luz ruim, com a estrutura do case transcrita à mão, os 3C's aplicados, cada conta desenvolvida passo a passo e os totais circulados. A anotação "apenas 1º ano" ao lado do custo do banco documenta uma decisão de modelagem consciente. E a observação sobre a duração das conexões traz informação de fora do case, algo que texto gerado a partir do enunciado não produz, porque ele não questiona o input. A ausência de recomendação é falha de execução de quem ficou sem tempo, não artefato de geração — saída gerada tende a entregar a conclusão e economizar no meio, exatamente o inverso do que aconteceu aqui. Pergunta de propriedade para a entrevista: qual bairro e qual modelo você escolhe, e por que o banco só conta no 1º ano?
-[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+          <t>A entrega mais frustrante que corrigi, porque a parte difícil está certa e a parte fácil não foi feita.
+Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas. Anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade. Ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou.
+E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado.
+Sobre a projeção, ela também não sobrevive. Ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais. Corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar que este é o terceiro candidato a ler o banco como investimento, junto com as pastas 05 e 09, o que me faz achar que a redação do Anexo E merece ajuste no próximo case.
+Na entrevista, se ele passar, a primeira pergunta é a que falta. Você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda, por que o banco vale só no primeiro ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case?
+Nota 3,13 com vídeo em branco. Considerando só o que dá para avaliar, 3,48.
+Indício de IA: Baixo (consultivo, não afeta nota). Evidência de propriedade praticamente incontestável, ao lado da pasta 05. Seis páginas de caderno fotografadas sob luz ruim, com os 3C's aplicados à mão e cada conta desenvolvida passo a passo. A anotação "apenas 1º ano" documenta decisão consciente. A observação sobre a duração das conexões traz informação de fora do case, o que texto gerado a partir do enunciado não produz porque não questiona o input. A ausência de recomendação é falta de tempo, não artefato.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9742,7 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Candidato 14 — pasta entregas-candidatos/14 (case BagHub 2026.2)</t>
+          <t>Candidato 14 (pasta entregas-candidatos/14, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -9725,7 +9788,7 @@
       </c>
       <c r="O63" s="68" t="inlineStr">
         <is>
-          <t>C1=1: dá para inferir a recomendação — ele declara no slide 4 que rentabilidade é "o nosso critério principal" e o slide 17 conclui que a Estação Central lidera com R$ 27,84 mi em parceiros — mas ela não está escrita em lugar nenhum. O slide 21 fecha ambivalente ("a Estação central ganha na rentabilidade bruta, enquanto o Centro histórico traz uma proposta de eficiência e constância") sem resolver, e o índice do slide 2 promete uma seção "d. Recomendação do lançamento" que não existe no deck. C2=2: deck de nível cliente, com capa, índice, divisores de seção, rodapé, numeração e citação de fonte ("Fonte: Anexos A, B e C do desafio"). Pontas soltas que impedem o 3: os slides 7 e 8 têm título idêntico e ambos numerados "07", os slides 10 e 11 idem numerados "09", typos em "perídodo" (slide 4) e "font única" (slide 19), e a seção prometida no índice não foi entregue. C3=1: teste operacional — os títulos são rótulos ("Critério 3: Robustez da demanda", "Conclusão: a tabela-resumo de decisão") e a recomendação não aparece em nenhum; somam-se quatro slides com títulos duplicados, que obrigam o leitor a descobrir o que mudou. O arco dos quatro critérios é claro, o que torna este 1 contestável. C4=2: template uniforme com rodapé e marcadores de seção, mas o slide 18 está sobrecarregado — três tabelas mais a fórmula, com a numeração colidindo dentro de uma célula — e a numeração repetida em 8 e 11.</t>
+          <t>C1=1: dá para inferir a recomendação, ele declara no slide 4 que rentabilidade é "o nosso critério principal" e o slide 17 conclui que a Estação Central lidera com R$ 27,84 mi em parceiros, mas ela não está escrita em lugar nenhum. O slide 21 fecha ambivalente ("a Estação central ganha na rentabilidade bruta, enquanto o Centro histórico traz uma proposta de eficiência e constância") sem resolver, e o índice do slide 2 promete uma seção "d. Recomendação do lançamento" que não existe no deck. C2=2: deck de nível cliente, com capa, índice, divisores de seção, rodapé, numeração e citação de fonte ("Fonte: Anexos A, B e C do desafio"). Pontas soltas que impedem o 3: os slides 7 e 8 têm título idêntico e ambos numerados "07", os slides 10 e 11 idem numerados "09", typos em "perídodo" (slide 4) e "font única" (slide 19), e a seção prometida no índice não foi entregue. C3=1: teste operacional, os títulos são rótulos ("Critério 3: Robustez da demanda", "Conclusão: a tabela-resumo de decisão") e a recomendação não aparece em nenhum; somam-se quatro slides com títulos duplicados, que obrigam o leitor a descobrir o que mudou. O arco dos quatro critérios é claro, o que torna este 1 contestável. C4=2: template uniforme com rodapé e marcadores de seção, mas o slide 18 está sobrecarregado, três tabelas mais a fórmula, com a numeração colidindo dentro de uma célula, e a numeração repetida em 8 e 11.</t>
         </is>
       </c>
       <c r="P63" s="41" t="n">
@@ -9742,7 +9805,7 @@
       </c>
       <c r="T63" s="68" t="inlineStr">
         <is>
-          <t>R1=2: cita as duas partes e elas se conectam bem — R$ 27,84 mi com a razão estratégica do slide 20, a Estação Central como "Origem" da jornada que "intercepta o cliente antes de todo mundo". O que impede nota maior é que ele nunca decide: a própria tabela do slide 21 mostra o Centro Histórico ganhando em três dos quatro critérios (eficiência, robustez e valor estratégico empatado em ALTO) contra o critério principal que ele declarou, e essa contradição não é reconciliada. Com a decisão em aberto, um dos lados fica decorativo. R2=3: é o ponto mais forte da entrega. Quatro critérios declarados no slide 4 e todos operacionalizados de verdade — rentabilidade nos oito cenários, eficiência em R$/posição com ranking, robustez com regra explícita e limiares numéricos ("Alta: utilização acima de 50% ou duas ou mais fontes independentes com janela ampla; Baixa: abaixo de 35% e fonte única...") aplicada corretamente aos quatro bairros, e valor estratégico por contagem de adjacência. O slide 21 consolida tudo numa tabela de decisão com ranking por critério, e ele justifica por escrito por que Arena e Noite Alta saem (robustez BAIXA, valor estratégico BAIXO e MÉDIO). A regra de robustez é o critério qualitativo mais rigoroso e reproduzível de todo o conjunto. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou — a tarefa 04 pede recomendação sustentada, riscos e próximos passos, e não há recomendação declarada, nem seção de riscos, nem próximos passos. Registro com clareza, porque a nota isolada engana: o material extra dele (unit economics por posição, regra de robustez, adjacência e jornada do cliente) está entre os melhores do conjunto. O zero vem só da incompletude do pedido. R4=3: melhor leitura de indicador de todas as pastas. No slide 6 ele explica por que a Estação tem mais transações e menos utilização — demanda em picos, exigindo mais capital imobilizado por transação — e deriva que é onde as malas ficam guardadas por mais tempo, "mais ou menos 7 horas, o maior entre os bairros". Recalculei: 0,42 x 2.400 x 168 / 24.000 = 7,06 h. Está exato, e ninguém mais extraiu tempo de permanência dos dados. Ressalva: no slide 8 ele diz que os itens do Centro Histórico "ficam guardados por mais tempo", o que contradiz o próprio slide 6 (o Centro dá 5,04 h).</t>
+          <t>R1=2: cita as duas partes e elas se conectam bem, R$ 27,84 mi com a razão estratégica do slide 20, a Estação Central como "Origem" da jornada que "intercepta o cliente antes de todo mundo". O que impede nota maior é que ele nunca decide: a própria tabela do slide 21 mostra o Centro Histórico ganhando em três dos quatro critérios (eficiência, robustez e valor estratégico empatado em ALTO) contra o critério principal que ele declarou, e essa contradição não é reconciliada. Com a decisão em aberto, um dos lados fica decorativo. R2=3: é o ponto mais forte da entrega. Quatro critérios declarados no slide 4 e todos operacionalizados de verdade, rentabilidade nos oito cenários, eficiência em R$/posição com ranking, robustez com regra explícita e limiares numéricos ("Alta: utilização acima de 50% ou duas ou mais fontes independentes com janela ampla; Baixa: abaixo de 35% e fonte única...") aplicada corretamente aos quatro bairros, e valor estratégico por contagem de adjacência. O slide 21 consolida tudo numa tabela de decisão com ranking por critério, e ele justifica por escrito por que Arena e Noite Alta saem (robustez BAIXA, valor estratégico BAIXO e MÉDIO). A regra de robustez é o critério qualitativo mais rigoroso e reproduzível de todo o conjunto. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou, a tarefa 04 pede recomendação sustentada, riscos e próximos passos, e não há recomendação declarada, nem seção de riscos, nem próximos passos. Registro com clareza, porque a nota isolada engana: o material extra dele (unit economics por posição, regra de robustez, adjacência e jornada do cliente) está entre os melhores do conjunto. O zero vem só da incompletude do pedido. R4=3: melhor leitura de indicador de todas as pastas. No slide 6 ele explica por que a Estação tem mais transações e menos utilização, demanda em picos, exigindo mais capital imobilizado por transação, e deriva que é onde as malas ficam guardadas por mais tempo, "mais ou menos 7 horas, o maior entre os bairros". Recalculei: 0,42 x 2.400 x 168 / 24.000 = 7,06 h. Está exato, e ninguém mais extraiu tempo de permanência dos dados. Ressalva: no slide 8 ele diz que os itens do Centro Histórico "ficam guardados por mais tempo", o que contradiz o próprio slide 6 (o Centro dá 5,04 h).</t>
         </is>
       </c>
       <c r="U63" s="41" t="n">
@@ -9765,7 +9828,7 @@
       </c>
       <c r="AA63" s="68" t="inlineStr">
         <is>
-          <t>A1=3: sete dos oito resultados estão exatos e o oitavo cai dentro da tolerância. Arena armários deu R$ 13,814 mi contra R$ 13,870 mi do gabarito, −0,40%, dentro de ±2%. Memória de cálculo completa e visível nos slides 13 a 16, com cada linha de custo decomposta por bairro e por modelo. A2=2: ele acertou a parte difícil e errou a fácil. Os bancos estão certos, inclusive a Arena com 23 bancos a R$ 1,61 mi (o arredondamento de 22,5 foi feito). Mas no slide 15, na coluna de armários, ele aplicou os custos por posição a 920 posições em vez das 900 necessárias — R$ 1.400 x 920 = R$ 1,288 mi para equipamento e o mesmo para operação — contrariando a instrução explícita do Anexo E de que "custos por posição incidem nas posições necessárias do Anexo C". E fez isso de forma inconsistente: na coluna de parceiros do mesmo slide usou 900 corretamente. O erro propaga para o slide 18 (giro 13,0 para armários contra 13,3 para parceiros na Arena, resultado/posição R$ 15.015). Ainda no slide 18, o banco/posição aparece como R$ 1.750 para os quatro bairros, valor que só é exato quando as posições são divisíveis por 40 — na Arena seria R$ 1.788,89. O valor final ficou na tolerância por ser erro pequeno, mas o método contraria instrução escrita. A3=1: não há projeção, fasemento nem próximos passos. O slide 21 gesticula que o Centro Histórico "não deve ser desconsiderado para uma futura expansão", o que é direcional e apoiado em número, mas não chega a ser plano. A4=3: o Centro Histórico é proposto como expansão futura com impacto quantificado (R$ 24,50 mi) e sustentado por ranking em quatro critérios, tudo específico deste case. A5=1: não há seção de riscos nem próximos passos, que a tarefa 04 pede. O que existe são observações de risco dispersas na análise por bairro ("maior incerteza na previsão" na Arena, "necessitando maior investimento com a segurança dos itens" em Noite Alta) — específicas, mas desacopladas de qualquer recomendação, sem mitigação e sem prazo. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização — ao contrário, usou a utilização corretamente para derivar tempo de permanência — mas não nomeou inconsistência nenhuma.</t>
+          <t>A1=3: sete dos oito resultados estão exatos e o oitavo cai dentro da tolerância. Arena armários deu R$ 13,814 mi contra R$ 13,870 mi do gabarito, −0,40%, dentro de ±2%. Memória de cálculo completa e visível nos slides 13 a 16, com cada linha de custo decomposta por bairro e por modelo. A2=2: ele acertou a parte difícil e errou a fácil. Os bancos estão certos, inclusive a Arena com 23 bancos a R$ 1,61 mi (o arredondamento de 22,5 foi feito). Mas no slide 15, na coluna de armários, ele aplicou os custos por posição a 920 posições em vez das 900 necessárias, R$ 1.400 x 920 = R$ 1,288 mi para equipamento e o mesmo para operação, contrariando a instrução explícita do Anexo E de que "custos por posição incidem nas posições necessárias do Anexo C". E fez isso de forma inconsistente: na coluna de parceiros do mesmo slide usou 900 corretamente. O erro propaga para o slide 18 (giro 13,0 para armários contra 13,3 para parceiros na Arena, resultado/posição R$ 15.015). Ainda no slide 18, o banco/posição aparece como R$ 1.750 para os quatro bairros, valor que só é exato quando as posições são divisíveis por 40, na Arena seria R$ 1.788,89. O valor final ficou na tolerância por ser erro pequeno, mas o método contraria instrução escrita. A3=1: não há projeção, fasemento nem próximos passos. O slide 21 gesticula que o Centro Histórico "não deve ser desconsiderado para uma futura expansão", o que é direcional e apoiado em número, mas não chega a ser plano. A4=3: o Centro Histórico é proposto como expansão futura com impacto quantificado (R$ 24,50 mi) e sustentado por ranking em quatro critérios, tudo específico deste case. A5=1: não há seção de riscos nem próximos passos, que a tarefa 04 pede. O que existe são observações de risco dispersas na análise por bairro ("maior incerteza na previsão" na Arena, "necessitando maior investimento com a segurança dos itens" em Noite Alta), específicas, mas desacopladas de qualquer recomendação, sem mitigação e sem prazo. A6=1: o case não traz erro plantado. Ele não descontou transações pela utilização, ao contrário, usou a utilização corretamente para derivar tempo de permanência, mas não nomeou inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB63" s="41" t="n">
@@ -9789,9 +9852,14 @@
       </c>
       <c r="AI63" s="68" t="inlineStr">
         <is>
-          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso é difícil de pontuar de forma justa. O que ele fez de melhor ninguém mais fez: derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 h, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa — mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central "interceptando o cliente antes de todo mundo". É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez. E então ele não recomenda nada. O índice promete uma seção "Recomendação do lançamento" que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher — e o problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos. No cálculo há um deslize instrutivo: na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita — e usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude. Na entrevista eu faria três perguntas, e a primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? (Dá 5,04 h, e a resposta expõe a contradição do slide 8.) Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios — qual você recomenda e por quê? Nota 5,20 com V1 e V2 em branco; considerando só o que dá para avaliar, 5,78.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria, e o mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações; conferi e o valor está certo (7,06 h). Isso é raciocínio original, não recuperação de padrão. A contagem de adjacência exige abrir a imagem do mapa e olhar as fronteiras. A regra de robustez com limiares é um instrumento construído por ele. Do outro lado, os erros são humanos: typos ("perídodo", "font única"), numeração de página repetida (07 duas vezes, 09 duas vezes), a contradição entre o slide 6 e o slide 8 sobre qual bairro guarda itens por mais tempo, e o 920 contra 900 aparecendo nas duas colunas do mesmo slide. Esse último é assinatura de conta feita à mão. Pergunta de propriedade para a entrevista: como você chegou nas 7 horas de permanência, e quanto dá no Centro Histórico?
-[IDENTIFICAÇÃO] Nome na capa: Rafael Rodrigues Moreira. V1/V2 nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1).</t>
+          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso foi difícil de pontuar de forma justa.
+O que ele fez de melhor ninguém mais fez. Derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 horas, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa, que é mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central interceptando o cliente antes de todo mundo. É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez.
+E então ele não recomenda nada. O índice promete uma seção de recomendação do lançamento que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher. O problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos.
+No cálculo há um deslize instrutivo. Na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita. E usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude.
+Na entrevista eu faço três perguntas. A primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? Dá 5,04 horas, e a resposta expõe a contradição do slide 8. Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios, qual você recomenda e por quê?
+Nota 5,20 com vídeo em branco. Considerando só o que dá para avaliar, 5,78.
+Indício de IA: Baixo (consultivo, não afeta nota). O indício mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações, e conferi que o valor está certo. Isso é raciocínio original. A contagem de adjacência exige olhar o mapa. A regra de robustez com limiares é instrumento construído por ele. Do outro lado, os erros são humanos: typos, numeração de página repetida, a contradição entre slides 6 e 8, e o 920 contra 900 nas duas colunas do mesmo slide.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Rafael Rodrigues Moreira. As notas de vídeo dele estão nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -9803,7 +9871,7 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Candidato 15 — pasta entregas-candidatos/15 (case BagHub 2026.2)</t>
+          <t>Candidato 15 (pasta entregas-candidatos/15, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -9849,7 +9917,7 @@
       </c>
       <c r="O64" s="68" t="inlineStr">
         <is>
-          <t>C1=1: não há recomendação escrita em lugar nenhum. Dá para inferir, porque os quatro bairros estão calculados e os parceiros vencem em todos, com a Estação Central no topo — mas o leitor tem de montar a comparação sozinho a partir de quatro páginas independentes, porque não existe tabela comparativa nem síntese. C2=0: o entregável são oito páginas manuscritas digitalizadas no CamScanner, e um dos dois arquivos se chama literalmente "rascunho". Sem capa, sem estrutura, sem síntese. O descritor de 0 é literal ("foto de papel... arquivo sem estrutura nenhuma") e o teste operacional é claro: não se manda isso a um cliente. Registro em favor dele que a digitalização é limpa e a caligrafia é organizada, com títulos sublinhados e resultados destacados. C3=1: os blocos existem e seguem a ordem do case, mas são paralelos e independentes — um não puxa o outro e nenhum chega a conclusão. C4=1: formatação improvisada mas legível; o CamScanner deu bom contraste, bem melhor que fotografia direta, e os resultados estão sublinhados.</t>
+          <t>C1=1: não há recomendação escrita em lugar nenhum. Dá para inferir, porque os quatro bairros estão calculados e os parceiros vencem em todos, com a Estação Central no topo, mas o leitor tem de montar a comparação sozinho a partir de quatro páginas independentes, porque não existe tabela comparativa nem síntese. C2=0: o entregável são oito páginas manuscritas digitalizadas no CamScanner, e um dos dois arquivos se chama literalmente "rascunho". Sem capa, sem estrutura, sem síntese. O descritor de 0 é literal ("foto de papel... arquivo sem estrutura nenhuma") e o teste operacional é claro: não se manda isso a um cliente. Registro em favor dele que a digitalização é limpa e a caligrafia é organizada, com títulos sublinhados e resultados destacados. C3=1: os blocos existem e seguem a ordem do case, mas são paralelos e independentes, um não puxa o outro e nenhum chega a conclusão. C4=1: formatação improvisada mas legível; o CamScanner deu bom contraste, bem melhor que fotografia direta, e os resultados estão sublinhados.</t>
         </is>
       </c>
       <c r="P64" s="41" t="n">
@@ -9866,7 +9934,7 @@
       </c>
       <c r="T64" s="68" t="inlineStr">
         <is>
-          <t>R1=0: não há recomendação, que é o descritor de 0. R2=1: aplicando o teste operacional, ele não descartou nada por escrito e não escolheu nada. Registro em favor dele, para o 2º avaliador, que o rascunho traz uma comparação qualitativa real dos dois modelos, com listas de + e −: armários somam operação 24h e a facilidade de o cliente se servir "sem necessidade de falar com outra pessoa", e subtraem manutenção e restituição maiores; parceiros somam menor custo de manutenção e subtraem horário variável, dependência de outros comércios e o fato de "poder ser mais demorado e difícil do cliente achar/conhecer o BagHub". É comparação de modelo, não de bairro, e sem escolha. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou de forma ampla — a tarefa 01 (critérios de atratividade), a comparação entre bairros e toda a tarefa 04 (recomendação, riscos, próximos passos) não foram entregues. Só a tarefa 03 está completa. R4=1: lê os indicadores corretamente e rotula bem (marca com seta qual número é o faturamento), e tira consequência qualitativa dos dois modelos, inclusive a observação própria sobre descoberta do serviço pelo cliente nos pontos parceiros. Mas não interpreta nenhum indicador quantitativo: a utilização é transcrita nos quatro bairros (42%, 54%, 31%, 33%) e nunca é comparada, explicada ou usada para nada.</t>
+          <t>R1=0: não há recomendação, que é o descritor de 0. R2=1: aplicando o teste operacional, ele não descartou nada por escrito e não escolheu nada. Registro em favor dele, para o 2º avaliador, que o rascunho traz uma comparação qualitativa real dos dois modelos, com listas de + e −: armários somam operação 24h e a facilidade de o cliente se servir "sem necessidade de falar com outra pessoa", e subtraem manutenção e restituição maiores; parceiros somam menor custo de manutenção e subtraem horário variável, dependência de outros comércios e o fato de "poder ser mais demorado e difícil do cliente achar/conhecer o BagHub". É comparação de modelo, não de bairro, e sem escolha. R3=0: o descritor de 0 inclui "o pedido ficou incompleto", e ficou de forma ampla, a tarefa 01 (critérios de atratividade), a comparação entre bairros e toda a tarefa 04 (recomendação, riscos, próximos passos) não foram entregues. Só a tarefa 03 está completa. R4=1: lê os indicadores corretamente e rotula bem (marca com seta qual número é o faturamento), e tira consequência qualitativa dos dois modelos, inclusive a observação própria sobre descoberta do serviço pelo cliente nos pontos parceiros. Mas não interpreta nenhum indicador quantitativo: a utilização é transcrita nos quatro bairros (42%, 54%, 31%, 33%) e nunca é comparada, explicada ou usada para nada.</t>
         </is>
       </c>
       <c r="U64" s="41" t="n">
@@ -9889,7 +9957,7 @@
       </c>
       <c r="AA64" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem integralmente, todos desenvolvidos à mão. Estação Central: 1.200.000 transações x 30 = 36M, armários 3,36 + 4,2 + 3,36 = 10,92M e lucro 25,08M, parceiros 3,36 + 4,8 = 8,16M e lucro 27,84M. Arena: 18M, armários 4,13M e lucro 13,87M, parceiros 3,06M e lucro 14,94M. Noite Alta: 30M, armários 11,43M e lucro 18,57M, parceiros 10,8M e lucro 19,2M. A memória de cálculo não é só visível, ela É o entregável. A2=3: o arredondamento da Arena está explícito, anotado e autocorrigido — na página da Arena ele escreveu 900/40 x 70.000, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23", fechando em R$ 1,61M. Bancos de 60 na Estação e 45 em Noite Alta também explícitos e corretos. Custo por complexidade correto nos oito cenários. A3=0: não fez — não há projeção, plano, fasemento nem próximos passos. A4=1: os dois modelos estão caracterizados com prós e contras específicos do case, mas nenhuma alternativa é proposta como curso de ação e nenhum impacto é quantificado. A5=1: as listas de "−" do rascunho funcionam como riscos e são específicas dos modelos (horário variável, dependência de terceiros, dificuldade de o cliente achar o serviço, manutenção maior nos armários), mas estão desacopladas de qualquer recomendação, sem mitigação, sem prazo e sem próximos passos, que o enunciado pede na tarefa 04. A6=1: o case não traz erro plantado. Ele transcreveu a utilização e não a aplicou como desconto — a receita está correta nos quatro bairros — mas não nomeou inconsistência nenhuma.</t>
+          <t>A1=3: os oito resultados conferem integralmente, todos desenvolvidos à mão. Estação Central: 1.200.000 transações x 30 = 36M, armários 3,36 + 4,2 + 3,36 = 10,92M e lucro 25,08M, parceiros 3,36 + 4,8 = 8,16M e lucro 27,84M. Arena: 18M, armários 4,13M e lucro 13,87M, parceiros 3,06M e lucro 14,94M. Noite Alta: 30M, armários 11,43M e lucro 18,57M, parceiros 10,8M e lucro 19,2M. A memória de cálculo não é só visível, ela É o entregável. A2=3: o arredondamento da Arena está explícito, anotado e autocorrigido, na página da Arena ele escreveu 900/40 x 70.000, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23", fechando em R$ 1,61M. Bancos de 60 na Estação e 45 em Noite Alta também explícitos e corretos. Custo por complexidade correto nos oito cenários. A3=0: não fez, não há projeção, plano, fasemento nem próximos passos. A4=1: os dois modelos estão caracterizados com prós e contras específicos do case, mas nenhuma alternativa é proposta como curso de ação e nenhum impacto é quantificado. A5=1: as listas de "−" do rascunho funcionam como riscos e são específicas dos modelos (horário variável, dependência de terceiros, dificuldade de o cliente achar o serviço, manutenção maior nos armários), mas estão desacopladas de qualquer recomendação, sem mitigação, sem prazo e sem próximos passos, que o enunciado pede na tarefa 04. A6=1: o case não traz erro plantado. Ele transcreveu a utilização e não a aplicou como desconto, a receita está correta nos quatro bairros, mas não nomeou inconsistência nenhuma.</t>
         </is>
       </c>
       <c r="AB64" s="41" t="n">
@@ -9908,14 +9976,20 @@
       <c r="AG64" s="41" t="n"/>
       <c r="AH64" s="68" t="inlineStr">
         <is>
-          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0, não há arquivo de planilha, embora a memória de cálculo manuscrita esteja completa — mesma ressalva das pastas 05, 08 e 13. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas. E3=0, sem vídeo. E4=0: nenhum gráfico e nenhuma tabela em nenhuma das oito páginas — este zero é de mérito, o material existe e não atende ao descritor.</t>
+          <t>V1 e V2 em branco e a pasta é anônima: nenhum dos arquivos traz nome, então não dá para transcrever as notas de vídeo sem o mapa número-candidato. E1=0, não há arquivo de planilha, embora a memória de cálculo manuscrita esteja completa, mesma ressalva das pastas 05, 08 e 13. E2=0: o item pede apresentação fechada (PPT ou relatório) e não há nenhuma das duas. E3=0, sem vídeo. E4=0: nenhum gráfico e nenhuma tabela em nenhuma das oito páginas, este zero é de mérito, o material existe e não atende ao descritor.</t>
         </is>
       </c>
       <c r="AI64" s="68" t="inlineStr">
         <is>
-          <t>O cálculo está perfeito e é praticamente tudo o que existe. Os oito cenários estão certos, desenvolvidos à mão, e a Arena — onde a maioria escorrega — está não só correta como autocorrigida: ele escreveu a divisão 900/40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo. O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo. O formato agrava: são oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável. O que existe de análise qualitativa está no rascunho, e é melhor do que parece — a lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível; faltou transformar em entrega. Na entrevista, se ele avançar, a pergunta é direta e vale tudo: você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade: por que a Arena arredonda para 23 e não fica em 22,5? Nota 2,63 com V1 e V2 em branco; considerando só o que dá para avaliar, 2,93.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Evidência de propriedade praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos do case à mão e as contas desenvolvidas passo a passo. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta — erro cometido e corrigido no próprio papel, o que não é fabricável. A ausência de recomendação é falha de execução de quem ficou sem tempo ou não entendeu o escopo do entregável, e não artefato de geração: texto gerado entrega a conclusão e economiza no desenvolvimento, exatamente o contrário do que ocorreu aqui. Pergunta de propriedade para a entrevista: por que a Arena arredonda para 23, e qual bairro e modelo você escolheria?
-[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+          <t>O cálculo está perfeito e é praticamente tudo o que existe.
+Os oito cenários estão certos, desenvolvidos à mão, e a Arena, onde a maioria escorrega, está não só correta como autocorrigida. Ele escreveu a divisão 900 por 40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo.
+O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo.
+O formato agrava. São oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável.
+O que existe de análise qualitativa está no rascunho, e é melhor do que parece. A lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível. Faltou transformar em entrega.
+Na entrevista, se ele avançar, a pergunta é direta e vale tudo. Você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade, por que a Arena arredonda para 23 e não fica em 22,5?
+Nota 2,63 com vídeo em branco. Considerando só o que dá para avaliar, 2,93.
+Indício de IA: Baixo (consultivo, não afeta nota). Evidência praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos à mão. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta. Erro cometido e corrigido no próprio papel não é fabricável. A ausência de recomendação é falha de execução, e texto gerado faz o contrário, entrega a conclusão e economiza no desenvolvimento.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
     </row>
@@ -9927,7 +10001,7 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Candidato 16 — pasta entregas-candidatos/16 (case BagHub 2026.2)</t>
+          <t>Candidato 16 (pasta entregas-candidatos/16, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -9973,7 +10047,7 @@
       </c>
       <c r="O65" s="68" t="inlineStr">
         <is>
-          <t>C1=2: a recomendação é explícita, clara e completa ("Estação Central é a prioridade de lançamento, operando em modelo de Pontos parceiros", com R$ 27.840.000), mas está no slide 9 de 13, passada a metade; a agenda do slide 2 anuncia que haverá recomendação sem adiantar qual. C2=3: documento fechado com exatamente os três elementos do descritor — capa, estrutura e apêndice. O slide 13 é um anexo de memória de cálculo e premissas, listando período, fórmula de receita, tratamento da capacidade, composição dos custos com arredondamento para cima, definição de resultado operacional e a regra de não somar sinergias. Rodapé com nome de seção e numeração nos 13 slides. Nada inacabado. C3=3: a recomendação aparece no título (slide 9) e a conclusão de modelo também ("Modelo de Pontos parceiros supera o de Armários inteligentes em todos os bairros", slide 8). Lendo só os títulos o arco fecha inteiro e na ordem: contexto, comparação, demanda e capacidade, rentabilidade, conclusão, recomendação, priorização, riscos, próximos passos, anexo. C4=2: template uniforme com rodapé e numeração em todos os slides, mas três slides são parágrafo corrido — o 4 (quatro bairros com quatro campos de prosa cada), o 8 (cinco parágrafos) e o 12 (quatro colunas densas) — o que passa do "até 2 slides fora do padrão" do descritor de 2.</t>
+          <t>C1=2: a recomendação é explícita, clara e completa ("Estação Central é a prioridade de lançamento, operando em modelo de Pontos parceiros", com R$ 27.840.000), mas está no slide 9 de 13, passada a metade; a agenda do slide 2 anuncia que haverá recomendação sem adiantar qual. C2=3: documento fechado com exatamente os três elementos do descritor, capa, estrutura e apêndice. O slide 13 é um anexo de memória de cálculo e premissas, listando período, fórmula de receita, tratamento da capacidade, composição dos custos com arredondamento para cima, definição de resultado operacional e a regra de não somar sinergias. Rodapé com nome de seção e numeração nos 13 slides. Nada inacabado. C3=3: a recomendação aparece no título (slide 9) e a conclusão de modelo também ("Modelo de Pontos parceiros supera o de Armários inteligentes em todos os bairros", slide 8). Lendo só os títulos o arco fecha inteiro e na ordem: contexto, comparação, demanda e capacidade, rentabilidade, conclusão, recomendação, priorização, riscos, próximos passos, anexo. C4=2: template uniforme com rodapé e numeração em todos os slides, mas três slides são parágrafo corrido, o 4 (quatro bairros com quatro campos de prosa cada), o 8 (cinco parágrafos) e o 12 (quatro colunas densas), o que passa do "até 2 slides fora do padrão" do descritor de 2.</t>
         </is>
       </c>
       <c r="P65" s="41" t="n">
@@ -9990,7 +10064,7 @@
       </c>
       <c r="T65" s="68" t="inlineStr">
         <is>
-          <t>R1=3: o slide 9 organiza a recomendação em três pilares que se apoiam — Financeiro (melhor resultado operacional, R$ 27.840.000), Demanda (maior volume da cidade com 24.000/semana, fluxo previsível atrelado a embarque e desembarque, e o argumento de que viajantes com bagagens são o público-alvo ideal) e Operacional (complexidade moderada e ausência do custo dos bancos). Tapando o número, o argumento de aderência do público continua; tapando o argumento, R$ 27,84M é o máximo dos oito. R2=3: o slide 8 compara os dois modelos com a causa (o custo do banco supera a vantagem operacional dos armários) e, o que é raro, declara o contraponto da própria escolha — as consequências na experiência do cliente, reserva local, serviço não padronizado por ser executado por funcionários do parceiro, e mais burocracia no suporte. O slide 4 compara os quatro bairros em quatro dimensões e descarta por escrito: Arena pela dependência de eventos, Noite Alta porque o público não carrega bagagem, Centro Histórico pela concorrência com hotéis. O slide 10 prioriza os três restantes com resultado e razão. R3=3: a adição é o critério "Fit com o serviço" do slide 4, que não foi pedido e que questiona a plausibilidade da própria demanda projetada pelo case. Os dois melhores achados: "grande parcela dos frequentadores de bares e casas de show não costuma carregar malas e bagagens", o que põe em dúvida as 20 mil transações de Noite Alta apesar de ser o 2º maior volume; e "turistas que estão acomodados em algum hotel do bairro tendem a não necessitar do guarda-volumes" no Centro Histórico. Isso fortalece a recomendação por uma dimensão que os números não capturam — a Estação Central é o único bairro em que o público carrega bagagem por definição. Soma-se o argumento de modelo único para simplificar a gestão da expansão. R4=3: explica causa e consequência em dois níveis. No slide 5 lê a utilização de 54% do Centro Histórico como fluxo mais constante ao longo do dia, leitura defensável (mais giro por posição implica menos pico). E no slide 4 explica a causa por trás de a demanda converter ou não — o comportamento de carregar bagagem — e o que fazer com ela, priorizando a Estação e rebaixando Noite Alta.</t>
+          <t>R1=3: o slide 9 organiza a recomendação em três pilares que se apoiam, Financeiro (melhor resultado operacional, R$ 27.840.000), Demanda (maior volume da cidade com 24.000/semana, fluxo previsível atrelado a embarque e desembarque, e o argumento de que viajantes com bagagens são o público-alvo ideal) e Operacional (complexidade moderada e ausência do custo dos bancos). Tapando o número, o argumento de aderência do público continua; tapando o argumento, R$ 27,84M é o máximo dos oito. R2=3: o slide 8 compara os dois modelos com a causa (o custo do banco supera a vantagem operacional dos armários) e, o que é raro, declara o contraponto da própria escolha, as consequências na experiência do cliente, reserva local, serviço não padronizado por ser executado por funcionários do parceiro, e mais burocracia no suporte. O slide 4 compara os quatro bairros em quatro dimensões e descarta por escrito: Arena pela dependência de eventos, Noite Alta porque o público não carrega bagagem, Centro Histórico pela concorrência com hotéis. O slide 10 prioriza os três restantes com resultado e razão. R3=3: a adição é o critério "Fit com o serviço" do slide 4, que não foi pedido e que questiona a plausibilidade da própria demanda projetada pelo case. Os dois melhores achados: "grande parcela dos frequentadores de bares e casas de show não costuma carregar malas e bagagens", o que põe em dúvida as 20 mil transações de Noite Alta apesar de ser o 2º maior volume; e "turistas que estão acomodados em algum hotel do bairro tendem a não necessitar do guarda-volumes" no Centro Histórico. Isso fortalece a recomendação por uma dimensão que os números não capturam, a Estação Central é o único bairro em que o público carrega bagagem por definição. Soma-se o argumento de modelo único para simplificar a gestão da expansão. R4=3: explica causa e consequência em dois níveis. No slide 5 lê a utilização de 54% do Centro Histórico como fluxo mais constante ao longo do dia, leitura defensável (mais giro por posição implica menos pico). E no slide 4 explica a causa por trás de a demanda converter ou não, o comportamento de carregar bagagem, e o que fazer com ela, priorizando a Estação e rebaixando Noite Alta.</t>
         </is>
       </c>
       <c r="U65" s="41" t="n">
@@ -10013,7 +10087,7 @@
       </c>
       <c r="AA65" s="68" t="inlineStr">
         <is>
-          <t>A1=3: os oito resultados conferem integralmente, apresentados em duas tabelas decompostas por componente (Custo 1 equipamento, Custo 2 bancos, Custo 3 operação). Memória de cálculo visível em três lugares: as fórmulas sob cada tabela nos slides 6 e 7, as observações com os custos unitários por complexidade, e o anexo do slide 13. A2=3: bancos corretos, incluindo a Arena com R$ 1.610.000, que só fecha com 23 bancos. Ressalva de documentação: a fórmula escrita no slide 6 diz "posições necessárias ÷ 40 x R$ 70.000" sem mencionar o teto, mas o anexo do slide 13 declara "arredondar para cima no modelo de armários" e o valor comprova que foi feito. Custo por complexidade correto nos oito cenários e documentado. A3=3: o slide 9 traz a ordem completa de expansão, o slide 10 detalha os três restantes com resultado e razão, e o slide 12 traz próximos passos concretos; todos os números batem com as tabelas dele. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: Centro Histórico proposto como segundo lançamento com impacto quantificado (R$ 24.500.000) e razão declarada (fluxo turístico estável, complexidade baixa). Soma-se a proposta criativa do slide 12 de capturar a vantagem dos armários dentro do modelo de parceiros, via plataforma digital de reserva. A5=2: os dois riscos do slide 11 são específicos da recomendação dele e as mitigações são as mais concretas e acionáveis de todo o conjunto — treinamento para padronizar atendimento, reserva e atendimento 24h online com check-in presencial, staff da BagHub dentro do comércio parceiro nos horários de pico, e plataforma que indica quais parceiros estão com vaga ou lotados e qual o mais próximo. Pareadas uma a uma com os riscos. O que impede o 3 é a ausência de prazo em qualquer lugar, e apenas dois riscos mapeados. Registro que um 2º avaliador pode defender 3 pela qualidade da mitigação. A6=1: o case não traz erro plantado. Ele nomeia e resolve corretamente o único ponto ambíguo — o slide 5 define "utilização = horas ocupadas ÷ total de horas disponíveis na semana" e o anexo declara que "utilização não reduz a demanda" — mas o que nomeou é a instrução do case, não uma inconsistência.</t>
+          <t>A1=3: os oito resultados conferem integralmente, apresentados em duas tabelas decompostas por componente (Custo 1 equipamento, Custo 2 bancos, Custo 3 operação). Memória de cálculo visível em três lugares: as fórmulas sob cada tabela nos slides 6 e 7, as observações com os custos unitários por complexidade, e o anexo do slide 13. A2=3: bancos corretos, incluindo a Arena com R$ 1.610.000, que só fecha com 23 bancos. Ressalva de documentação: a fórmula escrita no slide 6 diz "posições necessárias ÷ 40 x R$ 70.000" sem mencionar o teto, mas o anexo do slide 13 declara "arredondar para cima no modelo de armários" e o valor comprova que foi feito. Custo por complexidade correto nos oito cenários e documentado. A3=3: o slide 9 traz a ordem completa de expansão, o slide 10 detalha os três restantes com resultado e razão, e o slide 12 traz próximos passos concretos; todos os números batem com as tabelas dele. O case não declara meta numérica, então essa parte do descritor não é testável. A4=3: Centro Histórico proposto como segundo lançamento com impacto quantificado (R$ 24.500.000) e razão declarada (fluxo turístico estável, complexidade baixa). Soma-se a proposta criativa do slide 12 de capturar a vantagem dos armários dentro do modelo de parceiros, via plataforma digital de reserva. A5=2: os dois riscos do slide 11 são específicos da recomendação dele e as mitigações são as mais concretas e acionáveis de todo o conjunto, treinamento para padronizar atendimento, reserva e atendimento 24h online com check-in presencial, staff da BagHub dentro do comércio parceiro nos horários de pico, e plataforma que indica quais parceiros estão com vaga ou lotados e qual o mais próximo. Pareadas uma a uma com os riscos. O que impede o 3 é a ausência de prazo em qualquer lugar, e apenas dois riscos mapeados. Registro que um 2º avaliador pode defender 3 pela qualidade da mitigação. A6=1: o case não traz erro plantado. Ele nomeia e resolve corretamente o único ponto ambíguo, o slide 5 define "utilização = horas ocupadas ÷ total de horas disponíveis na semana" e o anexo declara que "utilização não reduz a demanda", mas o que nomeou é a instrução do case, não uma inconsistência.</t>
         </is>
       </c>
       <c r="AB65" s="41" t="n">
@@ -10037,9 +10111,15 @@
       </c>
       <c r="AI65" s="68" t="inlineStr">
         <is>
-          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido? No slide 4 ele cria um critério de "fit com o serviço" e usa para questionar a própria demanda do material — observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade, e que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é uma leitura crítica de verdade, e ela reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição. O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso — reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade. As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável. Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes. Na entrevista eu iria atrás do melhor insight dele: você escreveu que o público de Noite Alta não carrega bagagem — então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000. Nota 7,70 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,56.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria. O critério de "fit com o serviço" questiona os dados de demanda do próprio enunciado, e essa é justamente a coisa que saída gerada não faz, porque tende a aceitar o input como verdade — aqui ele confronta a projeção com comportamento real do público (quem vai a bar não leva mala, quem está em hotel não precisa de guarda-volumes). As mitigações são invenções operacionais concretas, como colocar staff da BagHub dentro do comércio parceiro no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos: a numeração da expansão recomeçando em 1º no slide 10 e conflitando com o slide 9, e a fórmula do slide 6 omitindo o arredondamento que o anexo do slide 13 declara e o valor da Arena comprova — inconsistência típica de documento escrito em duas passadas. Pergunta de propriedade para a entrevista: o que você faz com as 20 mil transações de Noite Alta se o público de lá não carrega bagagem?
-[IDENTIFICAÇÃO] Nome na capa: Vagner Ássimos Gomes Carlos Filho. V1/V2 nas linhas 15 (victor 2/3) e 37 (Proc 3/1).</t>
+          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido?
+No slide 4 ele cria um critério de fit com o serviço e usa para questionar a própria demanda do material. Observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade. E que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é leitura crítica de verdade, e reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição.
+O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso. Reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade.
+As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável.
+Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes.
+Na entrevista eu vou atrás do melhor insight dele. Você escreveu que o público de Noite Alta não carrega bagagem, então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo, a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000.
+Nota 7,70 com vídeo em branco. Considerando só o que dá para avaliar, 8,56.
+Indício de IA: Baixo (consultivo, não afeta nota). O critério de fit com o serviço questiona os dados de demanda do próprio enunciado, e isso é justamente o que saída gerada não faz, porque tende a aceitar o input como verdade. As mitigações são invenções operacionais concretas, como staff da BagHub dentro do comércio no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos, a numeração da expansão recomeçando no slide 10 e a fórmula do slide 6 omitindo o arredondamento que o anexo declara.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Vagner Ássimos Gomes Carlos Filho. As notas de vídeo dele estão nas linhas 15 (victor 2/3) e 37 (Proc 3/1) e precisam ser transcritas.</t>
         </is>
       </c>
     </row>
@@ -24008,7 +24088,7 @@
     <row r="2" ht="25.5" customHeight="1" s="60">
       <c r="B2" s="66" t="inlineStr">
         <is>
-          <t>GABARITO E MONTAGEM DO CASE — preencher DEPOIS que o case do semestre existir.</t>
+          <t>GABARITO E MONTAGEM DO CASE, preencher DEPOIS que o case do semestre existir.</t>
         </is>
       </c>
     </row>
@@ -24016,7 +24096,7 @@
     <row r="4" ht="43.5" customHeight="1" s="60">
       <c r="B4" s="65" t="inlineStr">
         <is>
-          <t>Só o bloco de ACURÁCIA (A1–A6) depende do case. Comunicação, Raciocínio, Entrega e Vídeo já estão prontos e valem para qualquer case — a rubrica pode ser aprovada antes do case ficar pronto. Aqui você faz duas coisas: (1) confere se o case tem o que a rubrica precisa medir e (2) preenche os valores do gabarito.</t>
+          <t>Só o bloco de ACURÁCIA (A1,A6) depende do case. Comunicação, Raciocínio, Entrega e Vídeo já estão prontos e valem para qualquer case, a rubrica pode ser aprovada antes do case ficar pronto. Aqui você faz duas coisas: (1) confere se o case tem o que a rubrica precisa medir e (2) preenche os valores do gabarito.</t>
         </is>
       </c>
     </row>
@@ -24024,7 +24104,7 @@
     <row r="6" ht="14.25" customHeight="1" s="60">
       <c r="B6" s="62" t="inlineStr">
         <is>
-          <t>PARTE 1 — O QUE O CASE PRECISA TER (conferir ao montar)</t>
+          <t>PARTE 1, O QUE O CASE PRECISA TER (conferir ao montar)</t>
         </is>
       </c>
     </row>
@@ -24100,7 +24180,7 @@
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>Acerto médio muito acima de 50%: das 8 pastas avaliadas até agora, 7 fecharam os oito cenários. O bloco praticamente não discriminou em A1/A2 — só a pasta 04 escorregou, e ainda dentro da tolerância.</t>
+          <t>Acerto médio muito acima de 50%: das 8 pastas avaliadas até agora, 7 fecharam os oito cenários. O bloco praticamente não discriminou em A1/A2, só a pasta 04 escorregou, e ainda dentro da tolerância.</t>
         </is>
       </c>
     </row>
@@ -24297,7 +24377,7 @@
     <row r="18" ht="14.25" customHeight="1" s="60">
       <c r="B18" s="62" t="inlineStr">
         <is>
-          <t>PARTE 2 — GABARITO (preencher com o case pronto)</t>
+          <t>PARTE 2, GABARITO (preencher com o case pronto)</t>
         </is>
       </c>
     </row>
@@ -24378,7 +24458,7 @@
       </c>
       <c r="F21" s="72" t="inlineStr">
         <is>
-          <t>A ARENA É O DISCRIMINADOR: 900/40 = 22,5 e tem de virar 23 bancos. Quem usou 22,5 erra R$ 35.000, que cai dentro de ±2% — confira o método, não só o valor.</t>
+          <t>A ARENA É O DISCRIMINADOR: 900/40 = 22,5 e tem de virar 23 bancos. Quem usou 22,5 erra R$ 35.000, que cai dentro de ±2%, confira o método, não só o valor.</t>
         </is>
       </c>
     </row>
@@ -24390,7 +24470,7 @@
       </c>
       <c r="C22" s="70" t="inlineStr">
         <is>
-          <t>SEM REFERÊNCIA — o case não declara meta numérica nem pede projeção.</t>
+          <t>SEM REFERÊNCIA, o case não declara meta numérica nem pede projeção.</t>
         </is>
       </c>
       <c r="D22" s="71" t="inlineStr">
@@ -24400,7 +24480,7 @@
       </c>
       <c r="E22" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F22" s="72" t="inlineStr">
@@ -24427,7 +24507,7 @@
       </c>
       <c r="E23" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F23" s="72" t="inlineStr">
@@ -24449,12 +24529,12 @@
       </c>
       <c r="D24" s="71" t="inlineStr">
         <is>
-          <t>Nada a encontrar. Conferi: a utilização informada é coerente com transações e posições (durações implícitas de 3,9h a 7,1h). O único ponto de atenção real é o custo do banco de R$ 70.000, que é ANUAL e não CAPEX — a pasta 05 o tratou como investimento no breakeven e a pasta 07 antecipou o risco por escrito.</t>
+          <t>Nada a encontrar. Conferi: a utilização informada é coerente com transações e posições (durações implícitas de 3,9h a 7,1h). O único ponto de atenção real é o custo do banco de R$ 70.000, que é ANUAL e não CAPEX, a pasta 05 o tratou como investimento no breakeven e a pasta 07 antecipou o risco por escrito.</t>
         </is>
       </c>
       <c r="E24" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F24" s="72" t="inlineStr">
@@ -24466,7 +24546,7 @@
     <row r="25" ht="31.5" customHeight="1" s="60">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" s="70" t="inlineStr">
@@ -24481,7 +24561,7 @@
       </c>
       <c r="E25" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F25" s="72" t="inlineStr">
@@ -24493,7 +24573,7 @@
     <row r="26" ht="31.5" customHeight="1" s="60">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" s="70" t="inlineStr">
@@ -24508,7 +24588,7 @@
       </c>
       <c r="E26" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F26" s="72" t="inlineStr">
@@ -24521,7 +24601,7 @@
     <row r="28" ht="14.25" customHeight="1" s="60">
       <c r="B28" s="62" t="inlineStr">
         <is>
-          <t>PARTE 3 — AUTOCORREÇÃO (opcional, mas é onde mora o maior ganho)</t>
+          <t>PARTE 3, AUTOCORREÇÃO (opcional, mas é onde mora o maior ganho)</t>
         </is>
       </c>
     </row>
@@ -26075,7 +26155,7 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>Candidato 02 — pasta entregas-candidatos/02 (case BagHub 2026.2)</t>
+          <t>Aslan Rodrigues Maia</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -26085,9 +26165,13 @@
       </c>
       <c r="F27" s="73" t="inlineStr">
         <is>
-          <t>Melhor entrega do conjunto até aqui, e o que separa é a prova de dominância. Em vez de só reportar que os parceiros ganham nos quatro bairros, ele mostra por que: o banco de 40 posições rateado dá R$ 1.750 por posição por ano e o prêmio que o parceiro cobra sobre a operação vai de R$ 400 a R$ 1.400 — como o prêmio é sempre menor, a escolha do modelo se separa da escolha do bairro. Isso é um resultado que sobrevive a mudança de parâmetro, não uma leitura de tabela. Os oito cenários fecham todos, incluindo o arredondamento da Arena, e o anexo traz as premissas numeradas P0 a P11 com a fonte de cada uma. A tensão real do case ele encontrou e resolveu: o Centro Histórico rende R$ 24.500 por posição contra R$ 11.600 da Estação Central, mas a prioridade declarada é rentabilidade anual e a capacidade é contratável, então o lucro por posição não limita o crescimento. O que falta é prazo nos riscos: as mitigações são boas e contratuais, mas nenhuma tem data, e o piloto da pag. 11 não tem duração. Também não há análise de sensibilidade numérica, embora a seção 5.1 funcione como um breakeven implícito. Na entrevista eu pediria: se o banco de armários custasse R$ 50.000 em vez de R$ 70.000, o que muda na sua recomendação? A resposta certa é que o rateio cai para R$ 1.250 por posição, fica abaixo do prêmio de R$ 1.400 da complexidade alta, e os armários passam a ganhar em Noite Alta — quem montou a seção 5.1 responde isso em um minuto. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Vários indícios de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural específico deste case, não uma leitura dos oito números — é o tipo de generalização que não aparece em saída genérica. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento na pag. 11, ou seja, tirou um "e daí" do próprio número. A profundidade é desigual de propósito: o anexo faz a Estação Central por extenso e resume os outros três bairros, exatamente o corte de quem tinha um fim de semana. O único ponto que poderia levantar dúvida é o acabamento formal do anexo, aparentemente composto em LaTeX com notação matemática e premissas numeradas — mas acabamento não é evidência de IA, e a composição em LaTeX aponta para o contrário, porque exige trabalho manual. Pergunta de propriedade para a entrevista: a partir de que custo de banco os armários passam a ganhar em Noite Alta?
-[IDENTIFICAÇÃO] Nome no arquivo: Aslan Rodrigues Maia. V1/V2 dele existem nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3).</t>
+          <t>Melhor entrega que li. O que separa ele dos outros não é a conta, é ter provado por que parceiros ganham. O banco de 40 posições rateado dá R$ 1.750 por posição, e o prêmio que o parceiro cobra sobre a operação vai de R$ 400 a R$ 1.400. Como o prêmio é sempre menor, a escolha do modelo passa a não depender do bairro. Isso é um resultado que sobrevive a mudança de parâmetro, não leitura de tabela.
+Os oito cenários fecham todos, inclusive o arredondamento da Arena. O anexo traz as premissas numeradas de P0 a P11, cada uma com a fonte. Ele achou a tensão do case e resolveu: o Centro Histórico rende R$ 24.500 por posição contra R$ 11.600 da Estação, mas a prioridade declarada é rentabilidade anual e a capacidade é contratável, então lucro por posição não limita crescimento.
+Falta prazo nos riscos. As mitigações são boas e contratuais, só que nenhuma tem data e o piloto não tem duração. Também não fez sensibilidade numérica, embora a seção 5.1 funcione como breakeven implícito.
+Na entrevista eu pergunto: se o banco custasse R$ 50.000, o que muda? A resposta é que o rateio cai para R$ 1.250, fica abaixo do prêmio de R$ 1.400 da alta complexidade, e os armários passam a ganhar em Noite Alta. Quem montou aquela seção responde em um minuto.
+Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
+Indício de IA: Baixo (consultivo, não afeta nota). Vários sinais de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural deste case, não leitura dos oito números. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento. A profundidade é desigual de propósito: o anexo faz a Estação por extenso e resume os outros três, o corte de quem tinha um fim de semana. O acabamento do anexo em LaTeX poderia levantar dúvida, mas acabamento não é evidência, e compor em LaTeX aponta para o contrário.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Aslan Rodrigues Maia. As notas de vídeo dele estão nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -26108,7 +26192,7 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>Candidato 03 — pasta entregas-candidatos/03 (case BagHub 2026.2)</t>
+          <t>Bruno Heberth Oliveira Bastos</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
@@ -26118,9 +26202,14 @@
       </c>
       <c r="F28" s="73" t="inlineStr">
         <is>
-          <t>Entrega honesta e bem conferida, com o melhor artefato de propriedade do conjunto: a planilha tem fórmulas vivas, ROUNDUP e referências entre abas, não é tabela colada. Os oito cenários fecham. O que me chamou atenção foi o cuidado epistêmico — ele separa o que a conta mostra do que a conta não mostra, declina de criar estimativa onde falta dado ("eu preferi apontar a questão em vez de criar uma estimativa") e se recusa a generalizar que parceiros ganham sempre, dizendo que depende dos custos do case. Esse último ponto é onde ele deixa valor na mesa: a generalização era possível e é exatamente o que separa a pasta 02, que provou que o prêmio do parceiro é sempre menor que o banco rateado. O custo maior está na comunicação: os títulos são rótulos de seção e não mensagens, então a recomendação não sobrevive à leitura só dos títulos, e o texto em primeira pessoa com hedge a cada parágrafo tira o documento do registro de entregável de cliente. São dois ajustes de forma que valem muitos pontos e não mudam nada do conteúdo. Faltam prazo nos riscos e qualquer análise de sensibilidade. Na entrevista eu pediria a conta que ele se recusou a fazer: a partir de que custo do banco de armários o modelo de armários passa a ganhar na Estação Central? Sai da planilha dele em um minuto — o banco teria que cair para R$ 24.000, porque o prêmio do parceiro na complexidade moderada é R$ 600 por posição e 600 x 40 = 24.000. Nota 7,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,93.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não uma tabela renderizada — é o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na pag. 5 ("Na revisão, conferi especialmente o arredondamento dos bancos... esse é um ponto em que um pequeno erro muda bastante o resultado"), o que é metacognição sobre o próprio trabalho. Recusa-se explicitamente a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. E a profundidade é desigual: páginas 3 a 5 densas, 8 e 9 em lista mais leve. O texto é limpo e organizado, mas isso não é evidência de nada. Pergunta de propriedade para a entrevista: a partir de que custo de banco os armários ganham na Estação Central?
-[IDENTIFICAÇÃO] Nome no arquivo: Bruno Heberth Oliveira Bastos. V1/V2 nas linhas 8 (victor 3/1) e 30 (Fred 3/1). ATENÇÃO: a pasta 03 também contém os dois PDFs do Aslan, byte-idênticos aos da pasta 02 (MD5 confere) — arquivos fora de lugar, desconsiderados nesta avaliação.</t>
+          <t>Entrega honesta e bem conferida. Tem o melhor artefato de propriedade do conjunto: a planilha é um modelo que funciona, com ROUNDUP, fórmulas encadeadas e referências entre abas. Não é tabela colada. Os oito cenários fecham.
+Gostei do cuidado dele em separar o que a conta mostra do que a conta não mostra. Onde falta dado, ele aponta a lacuna em vez de inventar estimativa. Na página 5 ainda conta como conferiu o próprio trabalho, dizendo que revisou especialmente o arredondamento dos bancos porque um erro pequeno ali muda bastante o resultado.
+O problema é que ele se recusa a generalizar. Diz que não daria para afirmar que parceiros ganham sempre, que depende dos custos do case. Só que a generalização era possível, e é exatamente o que separa a pasta 02.
+O custo maior está na comunicação. Os títulos são rótulos de seção, não mensagens, então a recomendação não sobrevive à leitura só dos títulos. E o texto em primeira pessoa com hedge a cada parágrafo tira o documento do registro de entregável de cliente. São dois ajustes de forma que valem muitos pontos e não mudam nada do conteúdo. Faltam prazo nos riscos e qualquer sensibilidade.
+Na entrevista eu peço a conta que ele se recusou a fazer: a partir de que custo de banco os armários ganham na Estação? Sai da planilha dele, o banco teria que cair para R$ 24.000.
+Nota 7,13 com vídeo em branco. Considerando só o que dá para avaliar, 7,93.
+Indício de IA: Baixo (consultivo, não afeta nota). A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não tabela renderizada. É o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na página 5 e se recusa a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. Profundidade desigual entre as páginas.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Bruno Heberth Oliveira Bastos. As notas de vídeo dele estão nas linhas 8 (victor 3/1) e 30 (Fred 3/1) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
@@ -26141,7 +26230,7 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>Candidato 04 — pasta entregas-candidatos/04 (case BagHub 2026.2)</t>
+          <t>Candidato 04 (anônimo)</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -26151,9 +26240,14 @@
       </c>
       <c r="F29" s="73" t="inlineStr">
         <is>
-          <t>O problema desta entrega não é a conta, é a decisão. Sete dos oito cenários estão certos e a receita tem memória visível, mas a conclusão anda para o lado oposto dos números. Ele declara que a métrica principal é a margem bruta e então, dentro do bairro que escolheu, prefere armários a 85,7% em vez de parceiros a 90,7% — que também rende R$ 1,35M mais por ano. Escolheu a pior opção pela régua que ele mesmo definiu, e a régua já contrariava a prioridade declarada no case, que é rentabilidade anual, não margem. Some a isso duas contradições factuais: a Estação Central é descartada por "alta complexidade" na pag. 4 depois de ele escrever "complexidade moderada" na pag. 1, e a Arena é descartada por margem abaixo de 80% quando parceiros dá 83,0%. O único erro de cálculo é a Arena com 22,5 bancos em vez de 23, que por ser pequeno caiu na tolerância. Faltam riscos e próximos passos, que o enunciado pede na tarefa 04, e não há uma tabela ou gráfico em cinco páginas de texto corrido. Na entrevista eu faria duas perguntas diretas, e são as mesmas que revelam se ele enxerga o problema: você disse que a métrica principal é a margem bruta, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação Central tem complexidade moderada na pag. 1 e alta na pag. 4 — qual das duas? Nota 2,97 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,30.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. O padrão de erros aponta para autoria própria sem assistência. A contradição interna entre pag. 1 e pag. 4 sobre a complexidade da Estação Central é o tipo de inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural ("iremos analisar", "apresentaremos") para primeira do singular na última frase ("minha indicação"). Deixou de arredondar os bancos da Arena, apesar de a instrução estar escrita no Anexo E — IA tende a seguir instrução explícita. E a ausência total de tabela, numeração e estrutura é o oposto da over-estruturação típica de texto gerado. A recomendação que contraria a própria métrica é falha de raciocínio, não artefato de geração. Pergunta de propriedade para a entrevista: por que armários a 85,7% e não parceiros a 90,7% no Centro Histórico?
-[IDENTIFICAÇÃO] Sem nome no arquivo — pasta permanece anônima.</t>
+          <t>O problema aqui não é a conta, é a decisão. Sete dos oito cenários estão certos e a receita tem memória visível. Só que a conclusão anda para o lado oposto dos números.
+Ele diz que a métrica principal é a margem bruta e então, dentro do bairro que escolheu, prefere armários a 85,7% em vez de parceiros a 90,7%. Parceiros também rendem R$ 1,35 milhão mais por ano. Ou seja, escolheu a pior opção pela régua que ele mesmo definiu. E a régua já contrariava a prioridade do case, que é rentabilidade anual, não margem.
+Tem duas contradições factuais em cima disso. A Estação Central é descartada por alta complexidade na página 4, depois de ele escrever complexidade moderada na página 1. E a Arena é descartada por margem abaixo de 80% quando parceiros dá 83%.
+O único erro de cálculo é a Arena com 22,5 bancos em vez de 23, que por ser pequeno caiu na tolerância. Faltam riscos e próximos passos, que o enunciado pede na tarefa 04. E não tem uma tabela ou gráfico em cinco páginas de texto corrido.
+Na entrevista eu faço duas perguntas diretas, as mesmas que revelam se ele enxerga o problema. Você disse que a métrica principal é a margem, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação tem complexidade moderada na página 1 e alta na página 4, qual das duas?
+Nota 2,97 com vídeo em branco. Considerando só o que dá para avaliar, 3,30.
+Indício de IA: Baixo (consultivo, não afeta nota). O padrão de erros aponta para autoria própria sem assistência. A contradição entre página 1 e página 4 sobre a complexidade da Estação é inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural para singular na última frase. Deixou de arredondar os bancos apesar da instrução escrita, e IA tende a seguir instrução explícita. A ausência total de tabela e estrutura é o oposto da over-estruturação típica de texto gerado.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
@@ -26174,7 +26268,7 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>Candidato 05 — pasta entregas-candidatos/05 (case BagHub 2026.2)</t>
+          <t>Eduardo Alves Henrique</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -26184,9 +26278,15 @@
       </c>
       <c r="F30" s="73" t="inlineStr">
         <is>
-          <t>Entrega de conta impecável com decisão deliberadamente contra o número, e isso é o que a torna interessante de corrigir. Os oito cenários fecham todos, inclusive o arredondamento da Arena, e a memória de cálculo vem em nove fotos de caderno onde dá para acompanhar a aritmética linha por linha. Ele escolhe o Centro Histórico com parceiros, que é o 2º maior lucro, e reconhece isso por escrito — a escolha se apoia em baixa complexidade, demanda turística sem sazonalidade e eficiência de capital. É um desvio declarado da prioridade do case, não uma contradição, e ele traz lastro para isso: o breakeven do slide 12 calcula em quanto tempo os armários se pagariam contra os parceiros, e os quatro números estão aritmeticamente certos. O problema é a premissa por baixo desse breakeven. Ele trata os R$ 70.000 por banco como investimento de primeiro ano, mas o Anexo E diz que todos os valores são anuais, e essa reinterpretação não aparece em nenhum slide — está só anotada à mão como "1º ano" na foto do caderno. Ou seja, a análise mais sofisticada da entrega roda sobre uma premissa que contraria o material e que o leitor do deck não tem como saber que existe. Duas outras lacunas pesam: não há riscos em lugar nenhum, só razões pelas quais a escolha é segura, e o descarte da Estação Central nunca é justificado, apesar de serem R$ 3,34M a mais. No acabamento, o bairro Noite Alta virou "Alta Noite" em todas as tabelas e dois slides são o anexo do próprio case colado. Na entrevista eu faria duas perguntas, e a segunda é a boa: por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua própria tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora. Nota 6,03 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,70.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Elas mostram o processo, não o resultado: a estrutura do case transcrita à mão, a tabela de custos copiada, a derivação da fórmula por banco e a conta de Noite Alta feita passo a passo, com os valores batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta uma decisão de modelagem deliberada, do tipo que não sai de saída genérica. Os typos ("tursita", "esturura"), o nome do bairro trocado em todas as tabelas e a fórmula do slide 6 que não fecha com a própria Arena são descuidos humanos. Pergunta de propriedade para a entrevista: por que o banco entrou como investimento de 1º ano no breakeven se o Anexo E diz que é custo anual?
-[IDENTIFICAÇÃO] Nome na capa: Eduardo Alves Henrique. V1/V2 nas linhas 13 (victor 2/0) e 35 (Proc 2/1).</t>
+          <t>Conta impecável e decisão deliberadamente contra o número. Isso é o que torna a entrega interessante de corrigir.
+Os oito cenários fecham, inclusive o arredondamento da Arena, e a memória de cálculo vem em nove fotos de caderno onde dá para acompanhar a aritmética linha por linha. Ele escolhe o Centro Histórico com parceiros, que é o segundo maior lucro, e reconhece isso por escrito. Sustenta na baixa complexidade, na demanda turística sem sazonalidade e na eficiência de capital. É desvio declarado da prioridade do case, não contradição, e ele traz lastro: o breakeven do slide 12 calcula em quanto tempo os armários se pagariam contra os parceiros, e os quatro números estão certos.
+O problema é a premissa por baixo desse breakeven. Ele trata os R$ 70.000 do banco como investimento de primeiro ano, mas o Anexo E diz que todos os valores são anuais. E a reinterpretação não aparece em nenhum slide, está só anotada à mão como "1º ano" na foto do caderno. A análise mais sofisticada da entrega roda sobre uma premissa que contraria o material e que o leitor do deck não tem como saber que existe.
+Duas lacunas pesam. Não há riscos em lugar nenhum, só razões pelas quais a escolha é segura. E o descarte da Estação Central nunca é justificado, apesar de serem R$ 3,34 milhões a mais.
+No acabamento, Noite Alta virou "Alta Noite" em todas as tabelas e dois slides são o anexo do próprio case colado.
+Na entrevista eu faço duas perguntas. Por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora.
+Nota 6,03 com vídeo em branco. Considerando só o que dá para avaliar, 6,70.
+Indício de IA: Baixo (consultivo, não afeta nota). As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Mostram o processo, não o resultado: estrutura do case transcrita à mão, derivação da fórmula por banco e a conta de Noite Alta passo a passo, batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta decisão de modelagem deliberada. Os typos e o nome do bairro trocado em todas as tabelas são descuidos humanos.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Eduardo Alves Henrique. As notas de vídeo dele estão nas linhas 13 (victor 2/0) e 35 (Proc 2/1) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
@@ -26207,7 +26307,7 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>Candidato 06 — pasta entregas-candidatos/06 (case BagHub 2026.2)</t>
+          <t>Enrico Tristão e Mello de Oliveira</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -26217,9 +26317,16 @@
       </c>
       <c r="F31" s="73" t="inlineStr">
         <is>
-          <t>Tecnicamente a entrega mais completa do conjunto, e o que a separa não é a conta, é o que ele faz depois dela. Os oito cenários fecham e a planilha é um modelo de verdade, com ROUNDUP, IF de complexidade, referências entre abas e uma coluna de reconciliação que ele montou para conferir a própria economia. Em cima disso ele faz duas coisas que ninguém mais fez. Primeiro, calcula o break-even do custo do banco nos quatro bairros e publica a fórmula — R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena e R$ 56 mil em Noite Alta — o que mostra que Noite Alta é o único bairro onde os armários estão perto de ganhar, precisando de apenas 20% de queda. Segundo, e melhor: ele percebe que o case não modela custo de coordenação, calcula que R$ 1,15 mil por posição por ano de overhead zeraria a vantagem dos parceiros na Estação, e transforma esse número em KPI de risco e em decision gate do piloto. Isso é sair de "a resposta é 27,84" para "a resposta é 27,84 e aqui está a condição em que ela deixa de valer". Os riscos do slide 9 são os melhores do conjunto, cinco, específicos do modelo escolhido, priorizados, cada um com mitigação e gatilho mensurável. O que sobra de reparo é pequeno e todo de acabamento: o arquivo foi enviado como "Enrico hhh.pptx" e a numeração das seções está trocada entre os slides 7 e 8. Na entrevista eu iria direto no que prova propriedade: o break-even da Arena deu R$ 23.478, um número não redondo — de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a sua recomendação? Quem montou o modelo responde as duas em três minutos. Nota 8,33 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,26.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Foi a leitura mais difícil do conjunto, porque o acabamento é alto e o vocabulário é bem de consultoria (headroom, decision gates, sequenciamento), o que costuma acender alerta. Mas os indícios de propriedade são fortes e específicos. A planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes — ninguém constrói autoconferência num modelo que não montou. O break-even da Arena saiu R$ 23.478,26, valor não redondo porque o denominador é o teto de 900/40, e ele não arredondou para embelezar. E o número R$ 1,15 mil por posição aparece encadeado em três artefatos diferentes: sai da planilha como headroom, reaparece no slide 9 como KPI de risco e no slide 10 como gate do piloto — esse tipo de encadeamento entre artefatos é difícil de fabricar. Somam-se descuidos humanos: o "hhh" no nome do arquivo e a numeração de seção trocada entre os slides 7 e 8. Por fim, ele aponta o que está ausente do material, e não só o que está presente, o que é o oposto da tendência de aceitar o input como completo. Pergunta de propriedade para a entrevista: de onde vem o 23 no denominador do break-even da Arena, e o que acontece se o overhead real for R$ 1,4 mil por posição?
-[IDENTIFICAÇÃO] Nome no arquivo: Enrico (Tristão e Mello de Oliveira). V1/V2 nas linhas 12 (victor 2/1) e 34 (Ferro 2/1).</t>
+          <t>Tecnicamente a entrega mais completa. E o que a separa não é a conta, é o que ele faz depois dela.
+Os oito cenários fecham e a planilha é um modelo de verdade, com ROUNDUP, IF de complexidade, referências entre abas e uma coluna de reconciliação que ele montou para conferir a própria economia. Em cima disso faz duas coisas que ninguém mais fez.
+Primeiro, calcula o breakeven do custo do banco nos quatro bairros e publica a fórmula. R$ 24 mil na Estação, R$ 16 mil no Centro, R$ 23,5 mil na Arena, R$ 56 mil em Noite Alta. Isso mostra que Noite Alta é o único bairro onde os armários estão perto de ganhar, precisando de só 20% de queda.
+Segundo, e melhor: ele percebe que o case não modela custo de coordenação, calcula que R$ 1,15 mil por posição por ano de overhead zeraria a vantagem dos parceiros na Estação, e transforma esse número em KPI de risco e em decision gate do piloto. Isso é sair de "a resposta é 27,84" para "a resposta é 27,84 e aqui está a condição em que ela deixa de valer".
+Os riscos do slide 9 são os melhores do conjunto. Cinco, específicos do modelo escolhido, priorizados, cada um com mitigação e gatilho mensurável.
+O que sobra de reparo é pequeno e todo de acabamento. O arquivo foi enviado como "Enrico hhh.pptx" e a numeração das seções está trocada entre os slides 7 e 8.
+Na entrevista eu vou direto no que prova propriedade. O breakeven da Arena deu R$ 23.478, um número não redondo, de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a recomendação? Quem montou o modelo responde as duas em três minutos.
+Nota 8,33 com vídeo em branco. Considerando só o que dá para avaliar, 9,26.
+Indício de IA: Baixo (consultivo, não afeta nota). Foi a leitura mais difícil, porque o acabamento é alto e o vocabulário é bem de consultoria. Mas a planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes, e ninguém constrói autoconferência num modelo que não montou. O breakeven da Arena saiu R$ 23.478,26, não redondo, e ele não arredondou para embelezar. O R$ 1,15 mil por posição aparece encadeado em três artefatos. Somam-se o "hhh" no nome do arquivo e a numeração trocada.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Enrico Tristão e Mello de Oliveira. As notas de vídeo dele estão nas linhas 12 (victor 2/1) e 34 (Ferro 2/1) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -26240,7 +26347,7 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>Candidato 07 — pasta entregas-candidatos/07 (case BagHub 2026.2)</t>
+          <t>Candidato 07 (anônimo)</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -26250,9 +26357,15 @@
       </c>
       <c r="F32" s="73" t="inlineStr">
         <is>
-          <t>Maior nota do conjunto, e o que decide é disciplina de modelagem somada à pergunta certa de robustez. Os oito cenários fecham e a planilha tem infraestrutura de autoconferência: um bloco de Conferências com três checagens que têm de dar zero, mais um validador que responde OK ou REVER se a capacidade física não cobrir a necessária. Ele é o único que modela explicitamente a sobra do arredondamento — 23 bancos na Arena dão 920 posições físicas para 900 necessárias, e ele registra as 20 de sobra sem deixar isso contaminar o custo, que segue nas posições necessárias. E é o único que antecipou por escrito a armadilha em que a pasta 05 caiu: a aba Premissas diz, em letras claras, que todos os custos são anuais e que o banco não é CAPEX. O melhor da entrega, porém, é o slide 7. Quase todo mundo que fez sensibilidade mediu distância da falência. Ele mediu duas coisas: os 77% de queda de demanda até o resultado zerar e, muito mais útil, os 9,3% de queda que já fariam a Estação perder a liderança para o Centro Histórico. Essa é a pergunta que decide se o ranking é frágil, e o número confere. Vale um contraponto que eu levaria à entrevista: 9,3% de folga não é obviamente "risco baixo" como ele afirma no slide — é uma margem estreita para uma projeção de demanda não validada, e a leitura dele é otimista demais para o próprio número que produziu. Faltou pouco: nenhum reparo de forma, e o único vazio é não ter explorado o que o modelo dele já permitia, o break-even do custo do banco. Na entrevista eu perguntaria: por que a queda admissível até zerar (77,3%) é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora, e quem só preencheu a planilha travá. Nota 8,60 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,56.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria, e vêm da disciplina do modelo. A planilha tem um bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade — ninguém constrói autoauditoria num modelo que não montou. A aba Premissas documenta convenção de cores do próprio modelo e deixa uma nota de manutenção para quem for usá-lo depois ("as conclusões textuais descrevem a base original, revise-as se alterar os dados"), que é escrita para um leitor futuro, não para um avaliador. Ele marca sistematicamente o que não pode saber: "distâncias e tempos não foram informados", "hipótese a validar", "médias diárias usam 7 dias apenas como normalização, não representam picos". Esse hábito de rotular a própria inferência é o oposto de texto gerado, que tende a afirmar com confiança uniforme. E a pergunta dos 9,28% é derivada, não óbvia. Pergunta de propriedade para a entrevista: por que a queda admissível de demanda até zerar dá exatamente a sua margem operacional?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima. Precisa do mapa número-candidato para trazer V1/V2.</t>
+          <t>Maior nota do conjunto. O que decide é disciplina de modelagem somada à pergunta certa de robustez.
+Os oito cenários fecham e a planilha tem autoconferência: um bloco de Conferências com três checagens que têm de dar zero, mais um validador que responde OK ou REVER se a capacidade física não cobrir a necessária. É o único que modela a sobra do arredondamento, porque 23 bancos na Arena dão 920 posições físicas para 900 necessárias, e ele registra as 20 de sobra sem deixar isso contaminar o custo. E é o único que antecipou por escrito a armadilha em que a pasta 05 caiu: a aba de premissas diz, em letras claras, que todos os custos são anuais e que o banco não é CAPEX.
+O melhor da entrega está no slide 7. Quase todo mundo que fez sensibilidade mediu distância da falência. Ele mediu duas coisas: os 77% de queda de demanda até o resultado zerar e, muito mais útil, os 9,3% de queda que já fariam a Estação perder a liderança para o Centro Histórico. Essa é a pergunta que decide se o ranking é frágil, e o número confere.
+Tenho um contraponto que levaria à entrevista. Os 9,3% de folga não são obviamente "risco baixo" como ele afirma no slide. É margem estreita para uma projeção de demanda não validada, e a leitura dele é otimista demais para o próprio número que produziu.
+Faltou pouco. Nenhum reparo de forma, e o único vazio é não ter explorado o que o modelo dele já permitia, o breakeven do custo do banco.
+Na entrevista eu pergunto: por que a queda admissível até zerar, 77,3%, é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora. Quem só preencheu a planilha trava.
+Nota 8,60 com vídeo em branco. Considerando só o que dá para avaliar, 9,56.
+Indício de IA: Baixo (consultivo, não afeta nota). A disciplina do modelo é o indício. Bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade. A aba de premissas documenta convenção de cores e deixa nota de manutenção para quem usar o modelo depois, escrita para um leitor futuro e não para um avaliador. Ele marca sistematicamente o que não pode saber: distâncias não informadas, hipótese a validar, médias diárias como normalização. Esse hábito é o oposto de texto gerado.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G32" s="30" t="inlineStr">
@@ -26273,7 +26386,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>Candidato 08 — pasta entregas-candidatos/08 (case BagHub 2026.2)</t>
+          <t>Gabrielle Cristofani do Rosario</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -26283,10 +26396,14 @@
       </c>
       <c r="F33" s="73" t="inlineStr">
         <is>
-          <t>Entrega sólida, com o mérito de a conta estar certa e a memória de cálculo ser verificável linha por linha na imagem manuscrita, inclusive o arredondamento da Arena escrito como "22,5 ≈ 23", que é onde a maioria escorrega. A causa estrutural ela achou sozinha: o banco rateado dá R$ 1.750 por posição e isso supera a economia de operação dos armários, o que explica por que parceiros ganham nos quatro bairros em vez de apenas reportar que ganham. E trata a tensão do case de frente, reconhecendo que o Centro Histórico tem margem maior mas resultado absoluto menor, e colocando ele como segunda onda. Três reparos, todos de execução e nenhum de raciocínio. O primeiro é o slide 4, que inverte a complexidade do Centro Histórico e de Noite Alta — a memória de cálculo usa os valores certos, então é erro de transcrição, mas está no slide que serve justamente para comparar os bairros. O segundo é a recomendação chegar só no slide 8: o deck tem contexto e metodologia antes da resposta, e trocar essa ordem valeria pontos sem mudar uma linha de análise. O terceiro é o slide 9, que promete um relatório escrito que não está na pasta e que pareia riscos com próximos passos que não os endereçam. Na entrevista eu faria duas perguntas: no slide 4 o Centro Histórico aparece como complexidade Alta e suas contas usam Baixa, qual é o certo? E, puxando o achado dela: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000, e sai direto do R$ 1.750 que ela mesma derivou. Nota 7,33 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,15.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria. A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor ("900:40 = 22,5 ≈ 23"). O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é a assinatura de erro humano de transcrição: uma saída gerada seria internamente consistente, certa ou errada nos dois lugares. A referência a um "relatório escrito" que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado. Pergunta de propriedade para a entrevista: no slide 4 o Centro Histórico está como Alta e suas contas usam Baixa — qual é o certo?
-[ALERTA] URGENTE — o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
-[IDENTIFICAÇÃO] Nome na capa: Gabrielle Cristofani do Rosario. V1/V2 nas linhas 7 (victor 2/2) e 29 (Fred 3/2).</t>
+          <t>Entrega sólida. A conta está certa e a memória de cálculo é verificável linha por linha na imagem manuscrita, inclusive o arredondamento da Arena escrito como "22,5 ≈ 23", que é onde a maioria escorrega.
+A causa estrutural ela achou sozinha. O banco rateado dá R$ 1.750 por posição e isso supera a economia de operação dos armários, o que explica por que parceiros ganham nos quatro bairros em vez de apenas reportar que ganham. E trata a tensão do case de frente, reconhecendo que o Centro Histórico tem margem maior mas resultado absoluto menor, e colocando ele como segunda onda.
+Três reparos, todos de execução e nenhum de raciocínio. O primeiro é o slide 4, que inverte a complexidade do Centro Histórico e de Noite Alta. A memória de cálculo usa os valores certos, então é erro de transcrição, mas está justamente no slide que serve para comparar os bairros. O segundo é a recomendação chegar só no slide 8: o deck tem contexto e metodologia antes da resposta, e trocar essa ordem valeria pontos sem mudar uma linha de análise. O terceiro é o slide 9, que promete um relatório escrito que não está na pasta e pareia riscos com próximos passos que não os endereçam.
+Na entrevista eu faço duas perguntas. No slide 4 o Centro Histórico aparece como complexidade Alta e suas contas usam Baixa, qual é o certo? E, puxando o achado dela, a partir de que custo de banco os armários passariam a ganhar na Estação? A resposta é R$ 24.000 e sai direto do R$ 1.750 que ela mesma derivou.
+Nota 7,33 com vídeo em branco. Considerando só o que dá para avaliar, 8,15.
+Indício de IA: Baixo (consultivo, não afeta nota). A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor, "900:40 = 22,5 ≈ 23". O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é assinatura de erro humano de transcrição, porque saída gerada seria consistente nos dois lugares. A referência a um relatório escrito que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado.
+ATENÇÃO: URGENTE, o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Gabrielle Cristofani do Rosario. As notas de vídeo dele estão nas linhas 7 (victor 2/2) e 29 (Fred 3/2) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
@@ -26307,7 +26424,7 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>Candidato 09 — pasta entregas-candidatos/09 (case BagHub 2026.2)</t>
+          <t>Candidato 09 (anônimo)</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
@@ -26317,9 +26434,14 @@
       </c>
       <c r="F34" s="73" t="inlineStr">
         <is>
-          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela, e as duas coisas precisam ser ditas juntas. O que está muito bom: o score multicritério é o método mais transparente do conjunto — pesos publicados, critério de normalização coerente (conferi a interpolação do resultado operacional e fecha), e as oito alternativas comparadas na mesma régua. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder ("Centro lidera a margem, apesar de abrir mão de R$ 3,34 mi"). Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento. O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 mi recorrente, o R$ 142,20 mi de cinco anos e o roadmap bifásico inteiro — que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente; aqui ele é a espinha dorsal e não está declarado em lugar nenhum. Vale registrar que a pasta 07 antecipou exatamente esse risco por escrito na aba de premissas. Segundo ponto, menor: ele lê a "prioridade de rentabilidade anual" como margem, quando o resto da frase no case ("que deverá sustentar a expansão") aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a 2ª melhor opção. Na entrevista eu faria uma pergunta só, e ela vale a etapa toda: o Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2 — por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai. Nota 8,30 com V1 e V2 em branco; considerando só o que dá para avaliar, 9,22.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios de autoria própria. O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três bairros usam a fórmula de divisão — é alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente, o que uma geração uniforme não faz. A planilha tem marcas de trabalho manual: células com "IDEM" como abreviação, "Noite alta" em minúscula na planilha contra "Noite Alta" no deck, e uma observação solta no canto explicando a convenção dos anos 2 a 5. A normalização do score é internamente consistente e foi conferida. E o erro central — tratar custo anual como investimento — é falha de interpretação de quem leu rápido e seguiu adiante, não artefato de geração; texto gerado tende a repetir a premissa do enunciado, não a contrariá-la. Pergunta de propriedade para a entrevista: por que o custo do banco desaparece a partir do Ano 2 se o Anexo E diz que é anual?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+          <t>Entrega de alto nível com um erro de leitura que atravessa metade dela. As duas coisas precisam ser ditas juntas.
+O que está muito bom: o score multicritério é o método mais transparente do conjunto, com pesos publicados, normalização coerente e as oito alternativas comparadas na mesma régua. Conferi a interpolação do resultado operacional e fecha. Os action titles são exemplares, inclusive o do slide 4, que assume o contra-argumento em vez de esconder. Os riscos são específicos e mitigados. E na Arena ele fixou 23 bancos à mão, contra a fórmula que daria 22,5, o que mostra que viu o arredondamento.
+O problema: a partir do slide 8, tudo se apoia em remover o custo do banco do Ano 2 em diante, como se os R$ 70.000 fossem investimento inicial. O Anexo E diz, em letras claras, que todos os valores são anuais. Sob a premissa correta, os armários nunca superam os parceiros em nenhum bairro, e aí caem o score de expansão, o R$ 29,28 milhões recorrente, o R$ 142,20 milhões de cinco anos e o roadmap bifásico inteiro. Que é justamente a parte mais original da entrega. A pasta 05 cometeu o mesmo erro, mas confinado a um slide e anotado à mão como decisão consciente. Aqui ele é a espinha dorsal e não está declarado em lugar nenhum.
+Segundo ponto, menor. Ele lê a prioridade de rentabilidade anual como margem, quando o resto da frase no case, que fala em sustentar a expansão, aponta para caixa absoluto. É leitura defensável e está declarada, mas é o que o faz escolher a segunda melhor opção.
+Na entrevista eu faço uma pergunta só, e ela vale a etapa toda. O Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2, por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai.
+Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
+Indício de IA: Baixo (consultivo, não afeta nota). O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três usam fórmula. É alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente. A planilha tem marcas de trabalho manual, com células escritas como "IDEM" e "Noite alta" em minúscula contra "Noite Alta" no deck. E o erro central, tratar custo anual como investimento, é falha de interpretação de quem leu rápido, não artefato de geração.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G34" s="30" t="inlineStr">
@@ -26340,7 +26462,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>Candidato 10 — pasta entregas-candidatos/10 (case BagHub 2026.2)</t>
+          <t>Candidato 10 (anônimo)</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
@@ -26350,9 +26472,14 @@
       </c>
       <c r="F35" s="73" t="inlineStr">
         <is>
-          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica: trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é exatamente o que se espera de consultoria. O argumento por trás também é sólido e ancorado no material — o Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques/dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio. Dois reparos de peso. O primeiro é a agregação: ele soma os quatro bairros para chegar aos R$ 83,09M, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos — restrita à decisão real, a abdicação é R$ 2,76M, não R$ 3,39M. A ideia está certa e a conta está na base errada. O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários — 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede explicitamente. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade. Na entrevista eu faria as duas perguntas que fecham os buracos: se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros? Nota 6,57 com V1 e V2 em branco; considerando só o que dá para avaliar, 7,30.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. O rascunho enviado junto é material de trabalho pessoal — anotações em caixa alta separadas por linhas de "######", com a estrutura do case transcrita e as contas sendo desenvolvidas; ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial ("malícia de próprios comerciantes", as duas perguntas entre aspas sobre o estado alcoólico do cliente) de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se", em vez de afirmar. E a nota de procedência no fim ("nenhum dado adicional foi estimado ou incorporado") é uma afirmação deliberada de método. Pergunta de propriedade para a entrevista: restrita à Estação, quanto custa a sua escolha por armários?
-[IDENTIFICAÇÃO] Sem nome nos arquivos — pasta permanece anônima.</t>
+          <t>A melhor ideia do conjunto está nesta entrega, e ela está na seção 7. Em vez de justificar uma escolha qualitativa com adjetivos, ele precifica. Trocar parceiros por armários na Estação e em Noite Alta custa R$ 3.390.000 por ano, e está escrito. Isso transforma um julgamento em algo que a diretoria pode aceitar ou recusar com um número na mão, e é o que se espera de consultoria.
+O argumento por trás também é sólido e ancorado no material. O Anexo D diz que parceiros têm horários variáveis e que armários operam 24h, e uma estação com 110 mil embarques por dia não combina com horário de comércio. Em Noite Alta ele vai além do que o case dá e explicita por que a complexidade é alta: confusão de itens, perda de comprovante e disputa sobre custódia com cliente embriagado. Isso é raciocínio próprio.
+Dois reparos de peso. O primeiro é a agregação. Ele soma os quatro bairros para chegar aos R$ 83,09 milhões, mas o case pede um bairro prioritário e uma sequência, não quatro lançamentos simultâneos. Restrita à decisão real, a abdicação é R$ 2,76 milhões, não R$ 3,39 milhões. A ideia está certa e a conta está na base errada.
+O segundo é que ele lista apenas os riscos da opção que descartou. Escolheu armários e não diz uma palavra sobre os riscos de armários: 60 bancos para instalar, capital imobilizado, dependência tecnológica. Falta também qualquer próximo passo, que a tarefa 04 pede. E enviar o rascunho junto, com os separadores de "######", custou ponto de forma sem necessidade.
+Na entrevista eu faço as duas perguntas que fecham os buracos. Se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros?
+Nota 6,57 com vídeo em branco. Considerando só o que dá para avaliar, 7,30.
+Indício de IA: Baixo (consultivo, não afeta nota). O rascunho enviado junto é material de trabalho pessoal, com anotações em caixa alta separadas por linhas de "######". Ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se" em vez de afirmar.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -26373,7 +26500,7 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>Candidato 11 — pasta entregas-candidatos/11 (case BagHub 2026.2)</t>
+          <t>Leandra Cunha de Souza</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
@@ -26383,9 +26510,14 @@
       </c>
       <c r="F36" s="73" t="inlineStr">
         <is>
-          <t>A análise está certa e a comunicação é que derruba a nota, o que é uma pena porque os dois problemas são baratos de resolver. Os oito cenários fecham todos, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo: cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo — diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito. O que custa caro é o acabamento, e o volume de deslizes é grande: o nome da empresa sai errado na capa ("Bag Huby"), "Armários inteligententes" se repete nas quatro tabelas, a utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12, os 110 mil embarques viram "110 embarques diários" no slide 4, e há texto de template ("BACK TO AGENDA") esquecido no meio do deck. Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede. Na entrevista eu faria duas perguntas: na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31% — qual é a certa? E você colocou a Arena (R$ 14,94M) à frente de Noite Alta (R$ 19,20M) no ranking; qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita. Nota 6,07 com V1 e V2 em branco; considerando só o que dá para avaliar, 6,74.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios claros de autoria própria, todos vindos do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento, "Central Histórico" trocado. O texto de template "BACK TO AGENDA" esquecido no slide 4 indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição: saída gerada tende a ser ortograficamente limpa e coerente consigo mesma. Pergunta de propriedade para a entrevista: a utilização da Arena é 31% ou 33%, e por que ela vem antes de Noite Alta no ranking?
-[IDENTIFICAÇÃO] Nome na capa e e-mail no último slide: Leandra Cunha de Souza (l304532@dac.unicamp.br). V1/V2 nas linhas 14 (victor 2/2) e 36 (Proc 2/2).</t>
+          <t>A análise está certa e a comunicação é que derruba a nota. É uma pena, porque os dois problemas são baratos de resolver.
+Os oito cenários fecham, as margens todas conferem, e as tabelas dos slides 6 a 9 são um modelo de memória de cálculo. Cada linha de custo aparece separada, por bairro e por modelo, com resultado e margem no fim. Ela também faz a coisa certa no raciocínio, que é enfrentar o contra-argumento em vez de escondê-lo. Diz com clareza que a Estação Central tem o maior resultado e explica por que escolhe o Centro Histórico mesmo assim, pela margem, pela baixa complexidade e pela menor capacidade ociosa. O slide 12, justificando uma a uma as posições do ranking, é bem feito.
+O que custa caro é o acabamento, e o volume de deslizes é grande. O nome da empresa sai errado na capa, "Bag Huby". "Armários inteligententes" se repete nas quatro tabelas. A utilização de Noite Alta e Arena está trocada no slide 3 e contradiz o slide 12. Os 110 mil embarques viram "110 embarques diários" no slide 4. E há texto de template, "BACK TO AGENDA", esquecido no meio do deck.
+Somado a isso, a recomendação só aparece no slide 11 de 13 e os títulos não contam a história, então quem folheia não encontra a resposta. Do lado da análise, falta mitigação para os dois riscos que ela mesma identificou e faltam próximos passos, que a tarefa 04 pede.
+Na entrevista eu faço duas perguntas. Na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31%, qual é a certa? E você colocou a Arena, R$ 14,94 milhões, à frente de Noite Alta, R$ 19,20 milhões, no ranking, qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita.
+Nota 6,07 com vídeo em branco. Considerando só o que dá para avaliar, 6,74.
+Indício de IA: Baixo (consultivo, não afeta nota). Todos os sinais vêm do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento. O texto de template "BACK TO AGENDA" esquecido indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Leandra Cunha de Souza. As notas de vídeo dele estão nas linhas 14 (victor 2/2) e 36 (Proc 2/2) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
@@ -26406,7 +26538,7 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>Candidato 12 — pasta entregas-candidatos/12 (case BagHub 2026.2)</t>
+          <t>Mariana Nunes Galvão Sant'Anna</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
@@ -26416,9 +26548,15 @@
       </c>
       <c r="F37" s="73" t="inlineStr">
         <is>
-          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente: contou que a Estação Central faz fronteira com 5 bairros — conferi, está certo — e transformou isso num critério pontuado de "potencial de fronteira", usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou. A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação-armários à frente de Centro-parceiros, e marca Noite Alta com asterisco declarando que a posição depende de pesquisa — reconhecer incerteza em vez de simular precisão é maturidade. A terceira é a vantagem percentual por bairro (11,0% / 5,8% / 7,7% / 3,4%), usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses. O erro que eu cobraria está no slide 17: ela promove a oportunidade nº 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações — ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita. De forma, o custo veio dos títulos repetidos: três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia. Na entrevista eu faria as duas perguntas: como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou. Nota 7,93 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,81.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria. A aba Rascunho é material de trabalho cru, com a estrutura do case transcrita em abreviações (ec, ch, a, na) e typos de digitação rápida ("receita anula", "infliencia", "complexdade", "posições necessarias") — ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo que não sai de texto. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas, sinal de quem resolveu o arredondamento na mão. E o risco de "baixa conversão pela pressa" é uma observação idiossincrática sobre o público. Há ainda o typo "resltado" no eixo da matriz do slide 13. Pergunta de propriedade para a entrevista: quais são os 5 bairros de fronteira da Estação Central, e como as horas ociosas virariam lucro?
-[IDENTIFICAÇÃO] Nome no arquivo e no slide de fechamento: Mariana Nunes Galvão Sant'Anna. V1/V2 nas linhas 16 (luis 3/2) e 38 (Proc 2/3).</t>
+          <t>Entrega muito boa, e o que a distingue é ter lido o material que todos ignoraram. Ela foi a única a usar o mapa do Anexo A analiticamente. Contou que a Estação Central faz fronteira com 5 bairros, e conferi que está certo, e transformou isso num critério pontuado de potencial de fronteira, usando como argumento de resiliência de demanda. Isso é extrair informação de onde ninguém procurou.
+A segunda coisa boa é a matriz do slide 13, que ordena as oito combinações corretamente por lucro absoluto, inclusive o detalhe fino de pôr Estação com armários à frente de Centro com parceiros. E marca Noite Alta com asterisco, declarando que a posição depende de pesquisa. Reconhecer incerteza em vez de simular precisão é maturidade.
+A terceira é a vantagem percentual por bairro, 11,0%, 5,8%, 7,7% e 3,4%, usada para argumentar que o fosso entre modelos é estreito o suficiente para os fatores qualitativos importarem, com Noite Alta identificada como o ponto de virada. É o mesmo achado das melhores entregas, alcançado por outro caminho. Os riscos são específicos e um deles é original: a pressa do passageiro de conexão como risco de conversão. E o piloto tem prazo, 3 meses.
+O erro que eu cobraria está no slide 17. Ela promove a oportunidade número 1 a aproveitar os 58% de horas ociosas na Estação, mas o case diz que a capacidade foi dimensionada para os picos e que a demanda já está dada em transações. Ocupar as horas vazias não gera transação nova, então essa oportunidade não existe como está escrita.
+De forma, o custo veio dos títulos repetidos. Três slides seguidos com o mesmo título e subtítulo, mais dois de "Mapeamento da cidade", o que atrapalha quem folheia.
+Na entrevista eu faço as duas perguntas. Como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou.
+Nota 7,93 com vídeo em branco. Considerando só o que dá para avaliar, 8,81.
+Indício de IA: Baixo (consultivo, não afeta nota). A aba Rascunho é material cru, com a estrutura do case em abreviações e typos de digitação rápida. Ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas. E o risco de baixa conversão pela pressa é observação idiossincrática sobre o público.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Mariana Nunes Galvão Sant'Anna. As notas de vídeo dele estão nas linhas 16 (luis 3/2) e 38 (Proc 2/3) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -26439,7 +26577,7 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>Candidato 13 — pasta entregas-candidatos/13 (case BagHub 2026.2)</t>
+          <t>Candidato 13 (anônimo)</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
@@ -26449,9 +26587,14 @@
       </c>
       <c r="F38" s="73" t="inlineStr">
         <is>
-          <t>É a entrega mais frustrante do conjunto, porque a parte difícil está certa e a parte fácil não foi feita. Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas: anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade — ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou. E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some-se o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado. Sobre a projeção, ela também não sobrevive: ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais — corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar para a diretoria que este é o terceiro candidato a ler o banco como investimento (junto com as pastas 05 e 09), o que sugere que a redação do Anexo E merece um ajuste no próximo case. Na entrevista, se ele passar, a primeira pergunta é a que falta: você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda: por que o banco vale só no 1º ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case? Nota 3,13 com V1 e V2 em branco; considerando só o que dá para avaliar, 3,48.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. É a pasta com a evidência de propriedade mais inequívoca do conjunto, ao lado da 05. Seis páginas de caderno fotografadas sob luz ruim, com a estrutura do case transcrita à mão, os 3C's aplicados, cada conta desenvolvida passo a passo e os totais circulados. A anotação "apenas 1º ano" ao lado do custo do banco documenta uma decisão de modelagem consciente. E a observação sobre a duração das conexões traz informação de fora do case, algo que texto gerado a partir do enunciado não produz, porque ele não questiona o input. A ausência de recomendação é falha de execução de quem ficou sem tempo, não artefato de geração — saída gerada tende a entregar a conclusão e economizar no meio, exatamente o inverso do que aconteceu aqui. Pergunta de propriedade para a entrevista: qual bairro e qual modelo você escolhe, e por que o banco só conta no 1º ano?
-[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+          <t>A entrega mais frustrante que corrigi, porque a parte difícil está certa e a parte fácil não foi feita.
+Os oito cenários estão todos corretos, desenvolvidos à mão linha por linha, incluindo o arredondamento de 23 bancos na Arena, e as lucratividades todas conferem. Ele aplicou os 3C's ao case, montou uma projeção de 5 anos com gráficos, e fez a observação qualitativa mais aguda que eu vi em todas as pastas. Anotou que uma conexão dura em média 1h30 a 2h e que isso geralmente não dá tempo de passear pela cidade. Ou seja, questionou se a demanda projetada para a Estação Central faz sentido, o que nenhum outro candidato pensou.
+E então não recomendou nada. Não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação nem próximos passos. A tarefa 04 do enunciado pede exatamente isso e simplesmente não foi entregue, e é o que derruba Comunicação e Raciocínio quase por completo. Some o formato: seis fotos de caderno com sombra e um print de planilha, sem nenhum documento fechado.
+Sobre a projeção, ela também não sobrevive. Ele anota "apenas 1º ano" ao lado do custo do banco, e o Anexo E diz que todos os valores são anuais. Corrigida a premissa, os armários nunca ultrapassam os parceiros e os quatro gráficos perdem sentido. Vale registrar que este é o terceiro candidato a ler o banco como investimento, junto com as pastas 05 e 09, o que me faz achar que a redação do Anexo E merece ajuste no próximo case.
+Na entrevista, se ele passar, a primeira pergunta é a que falta. Você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda, por que o banco vale só no primeiro ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case?
+Nota 3,13 com vídeo em branco. Considerando só o que dá para avaliar, 3,48.
+Indício de IA: Baixo (consultivo, não afeta nota). Evidência de propriedade praticamente incontestável, ao lado da pasta 05. Seis páginas de caderno fotografadas sob luz ruim, com os 3C's aplicados à mão e cada conta desenvolvida passo a passo. A anotação "apenas 1º ano" documenta decisão consciente. A observação sobre a duração das conexões traz informação de fora do case, o que texto gerado a partir do enunciado não produz porque não questiona o input. A ausência de recomendação é falta de tempo, não artefato.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -26472,7 +26615,7 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>Candidato 14 — pasta entregas-candidatos/14 (case BagHub 2026.2)</t>
+          <t>Rafael Rodrigues Moreira</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
@@ -26482,9 +26625,14 @@
       </c>
       <c r="F39" s="73" t="inlineStr">
         <is>
-          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso é difícil de pontuar de forma justa. O que ele fez de melhor ninguém mais fez: derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 h, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa — mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central "interceptando o cliente antes de todo mundo". É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez. E então ele não recomenda nada. O índice promete uma seção "Recomendação do lançamento" que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher — e o problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos. No cálculo há um deslize instrutivo: na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita — e usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude. Na entrevista eu faria três perguntas, e a primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? (Dá 5,04 h, e a resposta expõe a contradição do slide 8.) Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios — qual você recomenda e por quê? Nota 5,20 com V1 e V2 em branco; considerando só o que dá para avaliar, 5,78.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios fortes de autoria própria, e o mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações; conferi e o valor está certo (7,06 h). Isso é raciocínio original, não recuperação de padrão. A contagem de adjacência exige abrir a imagem do mapa e olhar as fronteiras. A regra de robustez com limiares é um instrumento construído por ele. Do outro lado, os erros são humanos: typos ("perídodo", "font única"), numeração de página repetida (07 duas vezes, 09 duas vezes), a contradição entre o slide 6 e o slide 8 sobre qual bairro guarda itens por mais tempo, e o 920 contra 900 aparecendo nas duas colunas do mesmo slide. Esse último é assinatura de conta feita à mão. Pergunta de propriedade para a entrevista: como você chegou nas 7 horas de permanência, e quanto dá no Centro Histórico?
-[IDENTIFICAÇÃO] Nome na capa: Rafael Rodrigues Moreira. V1/V2 nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1).</t>
+          <t>Tem a melhor análise e a pior conclusão do conjunto, e isso foi difícil de pontuar de forma justa.
+O que ele fez de melhor ninguém mais fez. Derivou o tempo de permanência das malas a partir da utilização, das posições e das transações, chegando a cerca de 7 horas na Estação Central. Recalculei e dá 7,06 horas, exato. Isso explica a causa do indicador em vez de só ler o número, e ele usa a conclusão certa, que é mais capital imobilizado por transação. Junte a isso quatro critérios declarados e todos de fato operacionalizados, incluindo uma regra de robustez com limiares numéricos escritos e aplicada corretamente aos quatro bairros, que é o critério qualitativo mais rigoroso que vi em todas as pastas. E a leitura de jornada do cliente no slide 20, classificando os bairros em Origem, Corredor e Destino, com a Estação Central interceptando o cliente antes de todo mundo. É pensamento estratégico de verdade, e ele leu o mapa do Anexo A, algo que só a pasta 12 também fez.
+E então ele não recomenda nada. O índice promete uma seção de recomendação do lançamento que não existe. O slide 21 termina dizendo que a Estação ganha em rentabilidade bruta e o Centro Histórico em eficiência e constância, sem escolher. O problema é maior que estilo, porque a tabela dele mostra o Centro Histórico ganhando em três dos quatro critérios contra o critério que ele mesmo declarou como principal. Essa contradição é o coração da entrega e fica sem resposta. Não há riscos, não há próximos passos.
+No cálculo há um deslize instrutivo. Na Arena ele acertou os 23 bancos, que é onde a maioria escorrega, e depois aplicou os custos por posição a 920 posições em vez de 900, contrariando instrução explícita. E usou 900 corretamente na coluna de parceiros do mesmo slide. O valor ficou na tolerância por sorte de magnitude.
+Na entrevista eu faço três perguntas. A primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? Dá 5,04 horas, e a resposta expõe a contradição do slide 8. Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios, qual você recomenda e por quê?
+Nota 5,20 com vídeo em branco. Considerando só o que dá para avaliar, 5,78.
+Indício de IA: Baixo (consultivo, não afeta nota). O indício mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações, e conferi que o valor está certo. Isso é raciocínio original. A contagem de adjacência exige olhar o mapa. A regra de robustez com limiares é instrumento construído por ele. Do outro lado, os erros são humanos: typos, numeração de página repetida, a contradição entre slides 6 e 8, e o 920 contra 900 nas duas colunas do mesmo slide.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Rafael Rodrigues Moreira. As notas de vídeo dele estão nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -26505,7 +26653,7 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>Candidato 15 — pasta entregas-candidatos/15 (case BagHub 2026.2)</t>
+          <t>Candidato 15 (anônimo)</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
@@ -26515,9 +26663,15 @@
       </c>
       <c r="F40" s="73" t="inlineStr">
         <is>
-          <t>O cálculo está perfeito e é praticamente tudo o que existe. Os oito cenários estão certos, desenvolvidos à mão, e a Arena — onde a maioria escorrega — está não só correta como autocorrigida: ele escreveu a divisão 900/40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo. O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo. O formato agrava: são oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável. O que existe de análise qualitativa está no rascunho, e é melhor do que parece — a lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível; faltou transformar em entrega. Na entrevista, se ele avançar, a pergunta é direta e vale tudo: você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade: por que a Arena arredonda para 23 e não fica em 22,5? Nota 2,63 com V1 e V2 em branco; considerando só o que dá para avaliar, 2,93.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Evidência de propriedade praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos do case à mão e as contas desenvolvidas passo a passo. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta — erro cometido e corrigido no próprio papel, o que não é fabricável. A ausência de recomendação é falha de execução de quem ficou sem tempo ou não entendeu o escopo do entregável, e não artefato de geração: texto gerado entrega a conclusão e economiza no desenvolvimento, exatamente o contrário do que ocorreu aqui. Pergunta de propriedade para a entrevista: por que a Arena arredonda para 23, e qual bairro e modelo você escolheria?
-[IDENTIFICAÇÃO] Sem nome em nenhum dos arquivos — pasta permanece anônima.</t>
+          <t>O cálculo está perfeito e é praticamente tudo o que existe.
+Os oito cenários estão certos, desenvolvidos à mão, e a Arena, onde a maioria escorrega, está não só correta como autocorrigida. Ele escreveu a divisão 900 por 40, riscou o primeiro resultado e anotou acima, com seta, "arredondando para 23". Ver a correção acontecendo na página é, para mim, a melhor prova de domínio de todo o processo seletivo.
+O problema é que a entrega para aí. Não há comparação entre bairros, não há critério de atratividade, não há escolha de bairro, não há escolha de modelo, não há riscos da recomendação, não há próximos passos e não há uma única tabela ou gráfico. Das quatro tarefas do enunciado, uma foi entregue por completo.
+O formato agrava. São oito páginas manuscritas digitalizadas e um dos arquivos se chama "rascunho", ou seja, ele enviou material de trabalho em vez de entregável.
+O que existe de análise qualitativa está no rascunho, e é melhor do que parece. A lista de prós e contras dos dois modelos inclui uma observação que ninguém mais fez, a de que nos pontos parceiros pode ser mais difícil o cliente achar e conhecer o BagHub, que é um ponto real de descoberta e conversão. Isso mostra que havia raciocínio disponível. Faltou transformar em entrega.
+Na entrevista, se ele avançar, a pergunta é direta e vale tudo. Você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade, por que a Arena arredonda para 23 e não fica em 22,5?
+Nota 2,63 com vídeo em branco. Considerando só o que dá para avaliar, 2,93.
+Indício de IA: Baixo (consultivo, não afeta nota). Evidência praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos à mão. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta. Erro cometido e corrigido no próprio papel não é fabricável. A ausência de recomendação é falha de execução, e texto gerado faz o contrário, entrega a conclusão e economiza no desenvolvimento.
+IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -26538,7 +26692,7 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>Candidato 16 — pasta entregas-candidatos/16 (case BagHub 2026.2)</t>
+          <t>Vagner Ássimos Gomes Carlos Filho</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
@@ -26548,9 +26702,15 @@
       </c>
       <c r="F41" s="73" t="inlineStr">
         <is>
-          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido? No slide 4 ele cria um critério de "fit com o serviço" e usa para questionar a própria demanda do material — observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade, e que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é uma leitura crítica de verdade, e ela reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição. O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso — reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade. As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável. Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes. Na entrevista eu iria atrás do melhor insight dele: você escreveu que o público de Noite Alta não carrega bagagem — então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo: a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000. Nota 7,70 com V1 e V2 em branco; considerando só o que dá para avaliar, 8,56.
-INDÍCIO DE IA (advisory, não afeta nota): Baixo. Indícios consistentes de autoria própria. O critério de "fit com o serviço" questiona os dados de demanda do próprio enunciado, e essa é justamente a coisa que saída gerada não faz, porque tende a aceitar o input como verdade — aqui ele confronta a projeção com comportamento real do público (quem vai a bar não leva mala, quem está em hotel não precisa de guarda-volumes). As mitigações são invenções operacionais concretas, como colocar staff da BagHub dentro do comércio parceiro no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos: a numeração da expansão recomeçando em 1º no slide 10 e conflitando com o slide 9, e a fórmula do slide 6 omitindo o arredondamento que o anexo do slide 13 declara e o valor da Arena comprova — inconsistência típica de documento escrito em duas passadas. Pergunta de propriedade para a entrevista: o que você faz com as 20 mil transações de Noite Alta se o público de lá não carrega bagagem?
-[IDENTIFICAÇÃO] Nome na capa: Vagner Ássimos Gomes Carlos Filho. V1/V2 nas linhas 15 (victor 2/3) e 37 (Proc 3/1).</t>
+          <t>Entrega madura, e o que a distingue é fazer a pergunta que o case não faz: as transações projetadas fazem sentido?
+No slide 4 ele cria um critério de fit com o serviço e usa para questionar a própria demanda do material. Observa que grande parte de quem frequenta bares e casas de show não carrega mala, o que põe em dúvida as 20 mil transações semanais de Noite Alta apesar de ser o segundo maior volume da cidade. E que turista hospedado em hotel do Centro Histórico não precisa de guarda-volumes. Essa é leitura crítica de verdade, e reforça a escolha da Estação Central por um caminho que os números não mostram: é o único bairro onde o público carrega bagagem por definição.
+O segundo ponto forte é a honestidade do slide 8, que recomenda parceiros e então lista o que se perde com isso. Reserva local, serviço não padronizado porque é executado por funcionário do parceiro, e mais burocracia no suporte. Nomear o custo da própria recomendação é sinal de maturidade.
+As mitigações do slide 11 são as mais concretas de todo o conjunto, com destaque para a plataforma que indica quais parceiros estão lotados e qual o mais próximo, que ataca diretamente o risco de fila que ele mesmo identificou. E o anexo do slide 13, com premissas declaradas uma a uma, é o tipo de coisa que torna a entrega auditável.
+Os reparos são de forma e de escopo. A recomendação chega no slide 9 de 13, quando poderia abrir o deck. Três slides são parágrafo corrido e o slide 4 em especial é denso demais para o volume de informação que carrega. Faltou prazo em qualquer parte dos riscos e próximos passos, e só dois riscos foram mapeados. Há também um deslize de numeração: o slide 9 ordena a expansão de 1º a 4º e o slide 10 recomeça a contagem em 1º para os três restantes.
+Na entrevista eu vou atrás do melhor insight dele. Você escreveu que o público de Noite Alta não carrega bagagem, então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo, a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000.
+Nota 7,70 com vídeo em branco. Considerando só o que dá para avaliar, 8,56.
+Indício de IA: Baixo (consultivo, não afeta nota). O critério de fit com o serviço questiona os dados de demanda do próprio enunciado, e isso é justamente o que saída gerada não faz, porque tende a aceitar o input como verdade. As mitigações são invenções operacionais concretas, como staff da BagHub dentro do comércio no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos, a numeração da expansão recomeçando no slide 10 e a fórmula do slide 6 omitindo o arredondamento que o anexo declara.
+IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Vagner Ássimos Gomes Carlos Filho. As notas de vídeo dele estão nas linhas 15 (victor 2/3) e 37 (Proc 3/1) e precisam ser transcritas.</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">

--- a/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
+++ b/prints/Planilha de Avaliação - Modelo Quantitativo (v2).xlsx
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Candidato 02 (pasta entregas-candidatos/02, case BagHub 2026.2)</t>
+          <t>02 · Aslan Rodrigues Maia (pasta entregas-candidatos/02, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8306,7 +8306,7 @@
 Na entrevista eu pergunto: se o banco custasse R$ 50.000, o que muda? A resposta é que o rateio cai para R$ 1.250, fica abaixo do prêmio de R$ 1.400 da alta complexidade, e os armários passam a ganhar em Noite Alta. Quem montou aquela seção responde em um minuto.
 Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
 Indício de IA: Baixo (consultivo, não afeta nota). Vários sinais de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural deste case, não leitura dos oito números. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento. A profundidade é desigual de propósito: o anexo faz a Estação por extenso e resume os outros três, o corte de quem tinha um fim de semana. O acabamento do anexo em LaTeX poderia levantar dúvida, mas acabamento não é evidência, e compor em LaTeX aponta para o contrário.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Aslan Rodrigues Maia. As notas de vídeo dele estão nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Aslan Rodrigues Maia, a266739@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome dos dois arquivos e no titulo interno do PDF ("Apresentação - Aslan Maia - Case CCU"). As notas de vídeo dele estão nas linhas 17 e 39 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Candidato 03 (pasta entregas-candidatos/03, case BagHub 2026.2)</t>
+          <t>03 · Bruno Heberth Oliveira Bastos (pasta entregas-candidatos/03, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8435,7 +8435,7 @@
 Na entrevista eu peço a conta que ele se recusou a fazer: a partir de que custo de banco os armários ganham na Estação? Sai da planilha dele, o banco teria que cair para R$ 24.000.
 Nota 7,13 com vídeo em branco. Considerando só o que dá para avaliar, 7,93.
 Indício de IA: Baixo (consultivo, não afeta nota). A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não tabela renderizada. É o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na página 5 e se recusa a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. Profundidade desigual entre as páginas.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Bruno Heberth Oliveira Bastos. As notas de vídeo dele estão nas linhas 8 (victor 3/1) e 30 (Fred 3/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Bruno Heberth Oliveira Bastos, b309603@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome dos dois arquivos dele. As notas de vídeo dele estão nas linhas 8 e 30 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Candidato 04 (pasta entregas-candidatos/04, case BagHub 2026.2)</t>
+          <t>04 · Caio Augusto Saab (pasta entregas-candidatos/04, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8564,7 +8564,7 @@
 Na entrevista eu faço duas perguntas diretas, as mesmas que revelam se ele enxerga o problema. Você disse que a métrica principal é a margem, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação tem complexidade moderada na página 1 e alta na página 4, qual das duas?
 Nota 2,97 com vídeo em branco. Considerando só o que dá para avaliar, 3,30.
 Indício de IA: Baixo (consultivo, não afeta nota). O padrão de erros aponta para autoria própria sem assistência. A contradição entre página 1 e página 4 sobre a complexidade da Estação é inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural para singular na última frase. Deixou de arredondar os bancos apesar da instrução escrita, e IA tende a seguir instrução explícita. A ausência total de tabela e estrutura é o oposto da over-estruturação típica de texto gerado.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: Caio Augusto Saab, c258388@dac.unicamp.br. Confiança media, confirmar. Como cheguei nisso: campo Author do metadado do PDF, gerado no Microsoft Word. O arquivo nao traz o nome no texto nem no nome do arquivo. As notas de vídeo dele estão nas linhas 25 e 47 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero. Atenção: esta identificação vem só do metadado, não do conteúdo. Metadado pode vir de computador compartilhado ou de modelo reaproveitado, então confirmem com o registro de envio antes de usar numa decisão.</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Candidato 05 (pasta entregas-candidatos/05, case BagHub 2026.2)</t>
+          <t>05 · Eduardo Alves Henrique (pasta entregas-candidatos/05, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8694,7 +8694,7 @@
 Na entrevista eu faço duas perguntas. Por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora.
 Nota 6,03 com vídeo em branco. Considerando só o que dá para avaliar, 6,70.
 Indício de IA: Baixo (consultivo, não afeta nota). As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Mostram o processo, não o resultado: estrutura do case transcrita à mão, derivação da fórmula por banco e a conta de Noite Alta passo a passo, batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta decisão de modelagem deliberada. Os typos e o nome do bairro trocado em todas as tabelas são descuidos humanos.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Eduardo Alves Henrique. As notas de vídeo dele estão nas linhas 13 (victor 2/0) e 35 (Proc 2/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Eduardo Alves Henrique, e221509@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome escrito na capa do deck. As notas de vídeo dele estão nas linhas 13 e 35 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Candidato 06 (pasta entregas-candidatos/06, case BagHub 2026.2)</t>
+          <t>06 · Enrico Tristão e Mello de Oliveira (pasta entregas-candidatos/06, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8825,7 +8825,7 @@
 Na entrevista eu vou direto no que prova propriedade. O breakeven da Arena deu R$ 23.478, um número não redondo, de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a recomendação? Quem montou o modelo responde as duas em três minutos.
 Nota 8,33 com vídeo em branco. Considerando só o que dá para avaliar, 9,26.
 Indício de IA: Baixo (consultivo, não afeta nota). Foi a leitura mais difícil, porque o acabamento é alto e o vocabulário é bem de consultoria. Mas a planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes, e ninguém constrói autoconferência num modelo que não montou. O breakeven da Arena saiu R$ 23.478,26, não redondo, e ele não arredondou para embelezar. O R$ 1,15 mil por posição aparece encadeado em três artefatos. Somam-se o "hhh" no nome do arquivo e a numeração trocada.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Enrico Tristão e Mello de Oliveira. As notas de vídeo dele estão nas linhas 12 (victor 2/1) e 34 (Ferro 2/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Enrico Tristão e Mello de Oliveira, e278588@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome do arquivo e campo lastModifiedBy do pptx e do xlsx ("Enrico Mello"). As notas de vídeo dele estão nas linhas 12 e 34 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Candidato 07 (pasta entregas-candidatos/07, case BagHub 2026.2)</t>
+          <t>07 · não identificado (pasta entregas-candidatos/07, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8955,7 +8955,7 @@
 Na entrevista eu pergunto: por que a queda admissível até zerar, 77,3%, é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora. Quem só preencheu a planilha trava.
 Nota 8,60 com vídeo em branco. Considerando só o que dá para avaliar, 9,56.
 Indício de IA: Baixo (consultivo, não afeta nota). A disciplina do modelo é o indício. Bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade. A aba de premissas documenta convenção de cores e deixa nota de manutenção para quem usar o modelo depois, escrita para um leitor futuro e não para um avaliador. Ele marca sistematicamente o que não pode saber: distâncias não informadas, hipótese a validar, médias diárias como normalização. Esse hábito é o oposto de texto gerado.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: metadados completamente vazios nos dois arquivos. A planilha foi feita no Excel Online. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Candidato 08 (pasta entregas-candidatos/08, case BagHub 2026.2)</t>
+          <t>08 · Gabrielle Cristofani do Rosario (pasta entregas-candidatos/08, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -9084,7 +9084,7 @@
 Nota 7,33 com vídeo em branco. Considerando só o que dá para avaliar, 8,15.
 Indício de IA: Baixo (consultivo, não afeta nota). A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor, "900:40 = 22,5 ≈ 23". O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é assinatura de erro humano de transcrição, porque saída gerada seria consistente nos dois lugares. A referência a um relatório escrito que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado.
 ATENÇÃO: URGENTE, o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Gabrielle Cristofani do Rosario. As notas de vídeo dele estão nas linhas 7 (victor 2/2) e 29 (Fred 3/2) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Gabrielle Cristofani do Rosario, g278083@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa, no nome do arquivo e no campo Author do metadado. As notas de vídeo dele estão nas linhas 7 e 29 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Candidato 09 (pasta entregas-candidatos/09, case BagHub 2026.2)</t>
+          <t>09 · não identificado (pasta entregas-candidatos/09, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -9213,7 +9213,7 @@
 Na entrevista eu faço uma pergunta só, e ela vale a etapa toda. O Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2, por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai.
 Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
 Indício de IA: Baixo (consultivo, não afeta nota). O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três usam fórmula. É alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente. A planilha tem marcas de trabalho manual, com células escritas como "IDEM" e "Noite alta" em minúscula contra "Noite Alta" no deck. E o erro central, tratar custo anual como investimento, é falha de interpretação de quem leu rápido, não artefato de geração.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: pptx exportado por "Walnut Exporter" e planilha no Excel Online. Criado em 17/09/2026 as 23:17 UTC. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Candidato 10 (pasta entregas-candidatos/10, case BagHub 2026.2)</t>
+          <t>10 · não identificado (pasta entregas-candidatos/10, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -9342,7 +9342,7 @@
 Na entrevista eu faço as duas perguntas que fecham os buracos. Se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros?
 Nota 6,57 com vídeo em branco. Considerando só o que dá para avaliar, 7,30.
 Indício de IA: Baixo (consultivo, não afeta nota). O rascunho enviado junto é material de trabalho pessoal, com anotações em caixa alta separadas por linhas de "######". Ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se" em vez de afirmar.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: rascunho impresso pelo Google Docs Renderer. No docx, o campo de autor foi preenchido com o titulo do documento e o lastModifiedBy esta como "Un-named". Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Candidato 11 (pasta entregas-candidatos/11, case BagHub 2026.2)</t>
+          <t>11 · Leandra Cunha de Souza (pasta entregas-candidatos/11, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -9471,7 +9471,7 @@
 Na entrevista eu faço duas perguntas. Na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31%, qual é a certa? E você colocou a Arena, R$ 14,94 milhões, à frente de Noite Alta, R$ 19,20 milhões, no ranking, qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita.
 Nota 6,07 com vídeo em branco. Considerando só o que dá para avaliar, 6,74.
 Indício de IA: Baixo (consultivo, não afeta nota). Todos os sinais vêm do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento. O texto de template "BACK TO AGENDA" esquecido indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Leandra Cunha de Souza. As notas de vídeo dele estão nas linhas 14 (victor 2/2) e 36 (Proc 2/2) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Leandra Cunha de Souza, l304532@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa, e-mail no ultimo slide e campo Author do metadado ("Leandra Cunha"). As notas de vídeo dele estão nas linhas 14 e 36 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Candidato 12 (pasta entregas-candidatos/12, case BagHub 2026.2)</t>
+          <t>12 · Mariana Nunes Galvão Sant'Anna (pasta entregas-candidatos/12, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -9601,7 +9601,7 @@
 Na entrevista eu faço as duas perguntas. Como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou.
 Nota 7,93 com vídeo em branco. Considerando só o que dá para avaliar, 8,81.
 Indício de IA: Baixo (consultivo, não afeta nota). A aba Rascunho é material cru, com a estrutura do case em abreviações e typos de digitação rápida. Ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas. E o risco de baixa conversão pela pressa é observação idiossincrática sobre o público.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Mariana Nunes Galvão Sant'Anna. As notas de vídeo dele estão nas linhas 16 (luis 3/2) e 38 (Proc 2/3) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Mariana Nunes Galvão Sant'Anna, m277865@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome do arquivo, no slide de fechamento e no campo Author do metadado. As notas de vídeo dele estão nas linhas 16 e 38 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Candidato 13 (pasta entregas-candidatos/13, case BagHub 2026.2)</t>
+          <t>13 · não identificado (pasta entregas-candidatos/13, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -9730,7 +9730,7 @@
 Na entrevista, se ele passar, a primeira pergunta é a que falta. Você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda, por que o banco vale só no primeiro ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case?
 Nota 3,13 com vídeo em branco. Considerando só o que dá para avaliar, 3,48.
 Indício de IA: Baixo (consultivo, não afeta nota). Evidência de propriedade praticamente incontestável, ao lado da pasta 05. Seis páginas de caderno fotografadas sob luz ruim, com os 3C's aplicados à mão e cada conta desenvolvida passo a passo. A anotação "apenas 1º ano" documenta decisão consciente. A observação sobre a duração das conexões traz informação de fora do case, o que texto gerado a partir do enunciado não produz porque não questiona o input. A ausência de recomendação é falta de tempo, não artefato.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: PDF das contas gerado pelo app Fotos do iOS 26.6.2. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Candidato 14 (pasta entregas-candidatos/14, case BagHub 2026.2)</t>
+          <t>14 · Rafael Rodrigues Moreira (pasta entregas-candidatos/14, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -9859,7 +9859,7 @@
 Na entrevista eu faço três perguntas. A primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? Dá 5,04 horas, e a resposta expõe a contradição do slide 8. Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios, qual você recomenda e por quê?
 Nota 5,20 com vídeo em branco. Considerando só o que dá para avaliar, 5,78.
 Indício de IA: Baixo (consultivo, não afeta nota). O indício mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações, e conferi que o valor está certo. Isso é raciocínio original. A contagem de adjacência exige olhar o mapa. A regra de robustez com limiares é instrumento construído por ele. Do outro lado, os erros são humanos: typos, numeração de página repetida, a contradição entre slides 6 e 8, e o 920 contra 900 nas duas colunas do mesmo slide.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Rafael Rodrigues Moreira. As notas de vídeo dele estão nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Rafael Rodrigues Moreira, r302729@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa e no nome do arquivo. As notas de vídeo dele estão nas linhas 24 e 46 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Candidato 15 (pasta entregas-candidatos/15, case BagHub 2026.2)</t>
+          <t>15 · não identificado (pasta entregas-candidatos/15, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -9989,7 +9989,7 @@
 Na entrevista, se ele avançar, a pergunta é direta e vale tudo. Você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade, por que a Arena arredonda para 23 e não fica em 22,5?
 Nota 2,63 com vídeo em branco. Considerando só o que dá para avaliar, 2,93.
 Indício de IA: Baixo (consultivo, não afeta nota). Evidência praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos à mão. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta. Erro cometido e corrigido no próprio papel não é fabricável. A ausência de recomendação é falha de execução, e texto gerado faz o contrário, entrega a conclusão e economiza no desenvolvimento.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: os dois PDFs foram gerados pelo CamScanner. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Candidato 16 (pasta entregas-candidatos/16, case BagHub 2026.2)</t>
+          <t>16 · Vagner Ássimos Gomes Carlos Filho (pasta entregas-candidatos/16, case BagHub 2026.2)</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -10119,7 +10119,7 @@
 Na entrevista eu vou atrás do melhor insight dele. Você escreveu que o público de Noite Alta não carrega bagagem, então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo, a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000.
 Nota 7,70 com vídeo em branco. Considerando só o que dá para avaliar, 8,56.
 Indício de IA: Baixo (consultivo, não afeta nota). O critério de fit com o serviço questiona os dados de demanda do próprio enunciado, e isso é justamente o que saída gerada não faz, porque tende a aceitar o input como verdade. As mitigações são invenções operacionais concretas, como staff da BagHub dentro do comércio no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos, a numeração da expansão recomeçando no slide 10 e a fórmula do slide 6 omitindo o arredondamento que o anexo declara.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Vagner Ássimos Gomes Carlos Filho. As notas de vídeo dele estão nas linhas 15 (victor 2/3) e 37 (Proc 3/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Vagner Ássimos Gomes Carlos Filho, v188630@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa e campo Author do metadado ("Vagner"). As notas de vídeo dele estão nas linhas 15 e 37 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>a266739@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -26171,7 +26171,7 @@
 Na entrevista eu pergunto: se o banco custasse R$ 50.000, o que muda? A resposta é que o rateio cai para R$ 1.250, fica abaixo do prêmio de R$ 1.400 da alta complexidade, e os armários passam a ganhar em Noite Alta. Quem montou aquela seção responde em um minuto.
 Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
 Indício de IA: Baixo (consultivo, não afeta nota). Vários sinais de autoria própria. A prova de dominância da seção 5.1 é um achado estrutural deste case, não leitura dos oito números. Ele nota que a vantagem dos parceiros em Noite Alta é de só R$ 350 por posição e transforma isso em ponto de monitoramento. A profundidade é desigual de propósito: o anexo faz a Estação por extenso e resume os outros três, o corte de quem tinha um fim de semana. O acabamento do anexo em LaTeX poderia levantar dúvida, mas acabamento não é evidência, e compor em LaTeX aponta para o contrário.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Aslan Rodrigues Maia. As notas de vídeo dele estão nas linhas 17 (Ferro 1/2) e 39 (Proc 2/3) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Aslan Rodrigues Maia, a266739@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome dos dois arquivos e no titulo interno do PDF ("Apresentação - Aslan Maia - Case CCU"). As notas de vídeo dele estão nas linhas 17 e 39 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>b309603@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -26209,7 +26209,7 @@
 Na entrevista eu peço a conta que ele se recusou a fazer: a partir de que custo de banco os armários ganham na Estação? Sai da planilha dele, o banco teria que cair para R$ 24.000.
 Nota 7,13 com vídeo em branco. Considerando só o que dá para avaliar, 7,93.
 Indício de IA: Baixo (consultivo, não afeta nota). A planilha é um modelo que funciona, com fórmulas encadeadas entre abas e ROUNDUP, não tabela renderizada. É o artefato mais difícil de terceirizar. Ele relata o próprio processo de conferência na página 5 e se recusa a preencher lacuna de dado com estimativa inventada, que é o oposto da tendência de IA de completar tudo. Profundidade desigual entre as páginas.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Bruno Heberth Oliveira Bastos. As notas de vídeo dele estão nas linhas 8 (victor 3/1) e 30 (Fred 3/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Bruno Heberth Oliveira Bastos, b309603@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome dos dois arquivos dele. As notas de vídeo dele estão nas linhas 8 e 30 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
@@ -26225,12 +26225,12 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>c258388@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>Candidato 04 (anônimo)</t>
+          <t>Caio Augusto Saab</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -26247,7 +26247,7 @@
 Na entrevista eu faço duas perguntas diretas, as mesmas que revelam se ele enxerga o problema. Você disse que a métrica principal é a margem, então por que escolheu armários a 85,7% e não parceiros a 90,7% no mesmo bairro? E a Estação tem complexidade moderada na página 1 e alta na página 4, qual das duas?
 Nota 2,97 com vídeo em branco. Considerando só o que dá para avaliar, 3,30.
 Indício de IA: Baixo (consultivo, não afeta nota). O padrão de erros aponta para autoria própria sem assistência. A contradição entre página 1 e página 4 sobre a complexidade da Estação é inconsistência de quem escreveu em sessões diferentes sem reler. O registro oscila de primeira pessoa do plural para singular na última frase. Deixou de arredondar os bancos apesar da instrução escrita, e IA tende a seguir instrução explícita. A ausência total de tabela e estrutura é o oposto da over-estruturação típica de texto gerado.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: Caio Augusto Saab, c258388@dac.unicamp.br. Confiança media, confirmar. Como cheguei nisso: campo Author do metadado do PDF, gerado no Microsoft Word. O arquivo nao traz o nome no texto nem no nome do arquivo. As notas de vídeo dele estão nas linhas 25 e 47 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero. Atenção: esta identificação vem só do metadado, não do conteúdo. Metadado pode vir de computador compartilhado ou de modelo reaproveitado, então confirmem com o registro de envio antes de usar numa decisão.</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
@@ -26263,7 +26263,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>e221509@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -26286,7 +26286,7 @@
 Na entrevista eu faço duas perguntas. Por que o breakeven trata o banco como investimento se o Anexo E diz que é custo anual? E por que, no rollout do slide 14, os bairros 2 a 4 usam armários se a sua tabela mostra parceiros ganhando nos quatro? Quem entendeu o próprio breakeven conecta as duas respostas na hora.
 Nota 6,03 com vídeo em branco. Considerando só o que dá para avaliar, 6,70.
 Indício de IA: Baixo (consultivo, não afeta nota). As nove fotos de caderno são a evidência de propriedade mais forte do conjunto. Mostram o processo, não o resultado: estrutura do case transcrita à mão, derivação da fórmula por banco e a conta de Noite Alta passo a passo, batendo com o deck. A anotação "1º ano" em cima do termo de R$ 70.000 documenta decisão de modelagem deliberada. Os typos e o nome do bairro trocado em todas as tabelas são descuidos humanos.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Eduardo Alves Henrique. As notas de vídeo dele estão nas linhas 13 (victor 2/0) e 35 (Proc 2/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Eduardo Alves Henrique, e221509@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome escrito na capa do deck. As notas de vídeo dele estão nas linhas 13 e 35 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>e278588@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -26326,7 +26326,7 @@
 Na entrevista eu vou direto no que prova propriedade. O breakeven da Arena deu R$ 23.478, um número não redondo, de onde vem o 23 no denominador? E se o overhead real der R$ 1,4 mil por posição em vez de R$ 1,15 mil, o que acontece com a recomendação? Quem montou o modelo responde as duas em três minutos.
 Nota 8,33 com vídeo em branco. Considerando só o que dá para avaliar, 9,26.
 Indício de IA: Baixo (consultivo, não afeta nota). Foi a leitura mais difícil, porque o acabamento é alto e o vocabulário é bem de consultoria. Mas a planilha tem uma coluna de reconciliação que cruza a economia por dois caminhos independentes, e ninguém constrói autoconferência num modelo que não montou. O breakeven da Arena saiu R$ 23.478,26, não redondo, e ele não arredondou para embelezar. O R$ 1,15 mil por posição aparece encadeado em três artefatos. Somam-se o "hhh" no nome do arquivo e a numeração trocada.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Enrico Tristão e Mello de Oliveira. As notas de vídeo dele estão nas linhas 12 (victor 2/1) e 34 (Ferro 2/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Enrico Tristão e Mello de Oliveira, e278588@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome do arquivo e campo lastModifiedBy do pptx e do xlsx ("Enrico Mello"). As notas de vídeo dele estão nas linhas 12 e 34 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -26365,7 +26365,7 @@
 Na entrevista eu pergunto: por que a queda admissível até zerar, 77,3%, é exatamente igual à sua margem operacional? Quem entendeu que todo custo do case é fixo responde na hora. Quem só preencheu a planilha trava.
 Nota 8,60 com vídeo em branco. Considerando só o que dá para avaliar, 9,56.
 Indício de IA: Baixo (consultivo, não afeta nota). A disciplina do modelo é o indício. Bloco de Conferências com três identidades que devem zerar e um validador condicional de capacidade. A aba de premissas documenta convenção de cores e deixa nota de manutenção para quem usar o modelo depois, escrita para um leitor futuro e não para um avaliador. Ele marca sistematicamente o que não pode saber: distâncias não informadas, hipótese a validar, médias diárias como normalização. Esse hábito é o oposto de texto gerado.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: metadados completamente vazios nos dois arquivos. A planilha foi feita no Excel Online. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
       <c r="G32" s="30" t="inlineStr">
@@ -26381,7 +26381,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>g278083@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -26403,7 +26403,7 @@
 Nota 7,33 com vídeo em branco. Considerando só o que dá para avaliar, 8,15.
 Indício de IA: Baixo (consultivo, não afeta nota). A memória de cálculo manuscrita mostra o processo, não só o resultado, com as premissas anotadas, o Anexo E transcrito à mão e o arredondamento resolvido na frente do leitor, "900:40 = 22,5 ≈ 23". O erro de complexidade do slide 4 convivendo com contas que usam o valor correto é assinatura de erro humano de transcrição, porque saída gerada seria consistente nos dois lugares. A referência a um relatório escrito que não foi anexado, e um arquivo pessoal que entrou por engano na pasta, indicam upload apressado.
 ATENÇÃO: URGENTE, o arquivo IMG-20260918-WA0254.jpg não tem relação com o case: é a captura de tela de um comprovante de compra parcelada, com valores, datas de vencimento e dados financeiros pessoais. Foi anexado por engano. Recomendo remover do repositório antes de qualquer coisa, porque o repositório chegou a ficar público. Não avaliei esse arquivo e não reproduzi seu conteúdo.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Gabrielle Cristofani do Rosario. As notas de vídeo dele estão nas linhas 7 (victor 2/2) e 29 (Fred 3/2) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Gabrielle Cristofani do Rosario, g278083@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa, no nome do arquivo e no campo Author do metadado. As notas de vídeo dele estão nas linhas 7 e 29 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
@@ -26441,7 +26441,7 @@
 Na entrevista eu faço uma pergunta só, e ela vale a etapa toda. O Anexo E diz que todos os custos são anuais, inclusive os R$ 70.000 por banco. Seu modelo remove esse custo a partir do Ano 2, por quê, e o que acontece com a sua recomendação se ele for mesmo anual? Quem entendeu o próprio modelo reconhece na hora que o roadmap cai.
 Nota 8,30 com vídeo em branco. Considerando só o que dá para avaliar, 9,22.
 Indício de IA: Baixo (consultivo, não afeta nota). O mais claro é a Arena com 23 bancos digitados à mão enquanto os outros três usam fórmula. É alguém que rodou o modelo, viu 22,5 aparecer e corrigiu pontualmente. A planilha tem marcas de trabalho manual, com células escritas como "IDEM" e "Noite alta" em minúscula contra "Noite Alta" no deck. E o erro central, tratar custo anual como investimento, é falha de interpretação de quem leu rápido, não artefato de geração.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: pptx exportado por "Walnut Exporter" e planilha no Excel Online. Criado em 17/09/2026 as 23:17 UTC. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
       <c r="G34" s="30" t="inlineStr">
@@ -26479,7 +26479,7 @@
 Na entrevista eu faço as duas perguntas que fecham os buracos. Se a decisão é só sobre a Estação, quanto você está abdicando de fato? E quais são os riscos de escolher armários, já que você só listou os de parceiros?
 Nota 6,57 com vídeo em branco. Considerando só o que dá para avaliar, 7,30.
 Indício de IA: Baixo (consultivo, não afeta nota). O rascunho enviado junto é material de trabalho pessoal, com anotações em caixa alta separadas por linhas de "######". Ninguém gera isso, e a progressão rascunho para relatório final deixa o processo de escrita visível. O raciocínio de Noite Alta é idiossincrático e coloquial de um jeito que texto gerado raramente é. Ele marca a própria suposição na Arena com "supõe-se" em vez de afirmar.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: rascunho impresso pelo Google Docs Renderer. No docx, o campo de autor foi preenchido com o titulo do documento e o lastModifiedBy esta como "Un-named". Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>l304532@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -26517,7 +26517,7 @@
 Na entrevista eu faço duas perguntas. Na página 3 a Arena aparece com 33% de utilização e na 12 você diz que ela tem a mais baixa, 31%, qual é a certa? E você colocou a Arena, R$ 14,94 milhões, à frente de Noite Alta, R$ 19,20 milhões, no ranking, qual é o critério? A segunda ela deve responder bem, porque a lógica de margem e volatilidade está escrita.
 Nota 6,07 com vídeo em branco. Considerando só o que dá para avaliar, 6,74.
 Indício de IA: Baixo (consultivo, não afeta nota). Todos os sinais vêm do padrão de erro. "Armários inteligententes" repetido igual nas quatro tabelas é copy-paste de um typo humano. "Bag Huby" na capa, "calcúlos" e "Operacao" sem acento. O texto de template "BACK TO AGENDA" esquecido indica deck montado sobre modelo e não revisado. E a utilização trocada no slide 3 convivendo com o valor correto no slide 12 é inconsistência interna de transcrição.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Leandra Cunha de Souza. As notas de vídeo dele estão nas linhas 14 (victor 2/2) e 36 (Proc 2/2) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Leandra Cunha de Souza, l304532@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa, e-mail no ultimo slide e campo Author do metadado ("Leandra Cunha"). As notas de vídeo dele estão nas linhas 14 e 36 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
@@ -26533,7 +26533,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>m277865@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -26556,7 +26556,7 @@
 Na entrevista eu faço as duas perguntas. Como os 58% de horas ociosas se transformariam em lucro, se a demanda já está dada? E quais são os 5 bairros de fronteira da Estação Central? A segunda ela responde de imediato se olhou o mapa, e olhou.
 Nota 7,93 com vídeo em branco. Considerando só o que dá para avaliar, 8,81.
 Indício de IA: Baixo (consultivo, não afeta nota). A aba Rascunho é material cru, com a estrutura do case em abreviações e typos de digitação rápida. Ninguém gera uma aba de rascunho assim. O critério de potencial de fronteira exige abrir a imagem do mapa e contar adjacências, um ato físico de leitura de anexo. As contagens de banco estão fixadas bairro a bairro dentro das fórmulas. E o risco de baixa conversão pela pressa é observação idiossincrática sobre o público.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Mariana Nunes Galvão Sant'Anna. As notas de vídeo dele estão nas linhas 16 (luis 3/2) e 38 (Proc 2/3) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Mariana Nunes Galvão Sant'Anna, m277865@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome no nome do arquivo, no slide de fechamento e no campo Author do metadado. As notas de vídeo dele estão nas linhas 16 e 38 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -26594,7 +26594,7 @@
 Na entrevista, se ele passar, a primeira pergunta é a que falta. Você calculou tudo, então qual bairro e qual modelo você escolhe, e por quê? A segunda, por que o banco vale só no primeiro ano? A terceira eu faria por interesse genuíno: sua observação sobre a conexão de 1h30 é boa, o que ela faz com a demanda de 24 mil transações do case?
 Nota 3,13 com vídeo em branco. Considerando só o que dá para avaliar, 3,48.
 Indício de IA: Baixo (consultivo, não afeta nota). Evidência de propriedade praticamente incontestável, ao lado da pasta 05. Seis páginas de caderno fotografadas sob luz ruim, com os 3C's aplicados à mão e cada conta desenvolvida passo a passo. A anotação "apenas 1º ano" documenta decisão consciente. A observação sobre a duração das conexões traz informação de fora do case, o que texto gerado a partir do enunciado não produz porque não questiona o input. A ausência de recomendação é falta de tempo, não artefato.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: PDF das contas gerado pelo app Fotos do iOS 26.6.2. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>r302729@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -26632,7 +26632,7 @@
 Na entrevista eu faço três perguntas. A primeira é de propriedade pura: como você chegou nas 7 horas, e quanto dá no Centro Histórico? Dá 5,04 horas, e a resposta expõe a contradição do slide 8. Segunda: na Arena, 920 ou 900 posições? Terceira, a que decide: seu critério principal é rentabilidade e a Estação ganha, mas o Centro Histórico ganha em três dos quatro critérios, qual você recomenda e por quê?
 Nota 5,20 com vídeo em branco. Considerando só o que dá para avaliar, 5,78.
 Indício de IA: Baixo (consultivo, não afeta nota). O indício mais forte é quantitativo. Derivar as 7 horas de permanência exige manipular a definição de utilização contra posições e transações, e conferi que o valor está certo. Isso é raciocínio original. A contagem de adjacência exige olhar o mapa. A regra de robustez com limiares é instrumento construído por ele. Do outro lado, os erros são humanos: typos, numeração de página repetida, a contradição entre slides 6 e 8, e o 920 contra 900 nas duas colunas do mesmo slide.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Rafael Rodrigues Moreira. As notas de vídeo dele estão nas linhas 24 (Ferro 2/3) e 46 (Proc 0/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Rafael Rodrigues Moreira, r302729@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa e no nome do arquivo. As notas de vídeo dele estão nas linhas 24 e 46 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -26671,7 +26671,7 @@
 Na entrevista, se ele avançar, a pergunta é direta e vale tudo. Você calculou os oito cenários corretamente, então qual bairro e qual modelo você recomenda, e por quê? E, para confirmar propriedade, por que a Arena arredonda para 23 e não fica em 22,5?
 Nota 2,63 com vídeo em branco. Considerando só o que dá para avaliar, 2,93.
 Indício de IA: Baixo (consultivo, não afeta nota). Evidência praticamente incontestável. Oito páginas manuscritas digitalizadas, com o rascunho transcrevendo os anexos à mão. O ponto decisivo é a autocorreção visível na página da Arena: valor riscado e a anotação "arredondando para 23" acrescentada acima com seta. Erro cometido e corrigido no próprio papel não é fabricável. A ausência de recomendação é falha de execução, e texto gerado faz o contrário, entrega a conclusão e economiza no desenvolvimento.
-IDENTIFICAÇÃO: pasta anônima, nenhum arquivo traz nome. Precisa do mapa número para candidato para trazer V1 e V2.</t>
+IDENTIFICAÇÃO: pasta anônima. Nenhum arquivo traz nome no texto, no nome do arquivo ou no metadado. Rastro de ferramenta que pode ajudar a estreitar: os dois PDFs foram gerados pelo CamScanner. Sem o mapa número para candidato, V1 e V2 não podem ser transcritos e o bloco Vídeo fica valendo zero. Candidatos inscritos ainda não pareados a nenhuma pasta: João Pedro Mendes Stama, Rafael Ponciano Rodrigues dos Santos, Enzo Chofakian Gagliardi, João Gabriel de Oliveira Morcelli, Raphael Negrini Saggioro, Gustavo Daher Pereira, Ricardo Augusto Schmitt Filho, Matheus Dias Freitas, Klaus Augusto Santos da Silva, José Vitor Dias Tutu, Isadora Kluge Dorigan.</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -26687,7 +26687,7 @@
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>v188630@dac.unicamp.br</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -26710,7 +26710,7 @@
 Na entrevista eu vou atrás do melhor insight dele. Você escreveu que o público de Noite Alta não carrega bagagem, então o que você faz com as 20 mil transações que o case projeta para lá? E, para checar propriedade do modelo, a partir de que custo de banco os armários passariam a ganhar na Estação Central? A resposta é R$ 24.000.
 Nota 7,70 com vídeo em branco. Considerando só o que dá para avaliar, 8,56.
 Indício de IA: Baixo (consultivo, não afeta nota). O critério de fit com o serviço questiona os dados de demanda do próprio enunciado, e isso é justamente o que saída gerada não faz, porque tende a aceitar o input como verdade. As mitigações são invenções operacionais concretas, como staff da BagHub dentro do comércio no pico e a plataforma que sinaliza parceiro lotado. Do lado dos deslizes humanos, a numeração da expansão recomeçando no slide 10 e a fórmula do slide 6 omitindo o arredondamento que o anexo declara.
-IDENTIFICAÇÃO: a pasta tem o nome no arquivo, Vagner Ássimos Gomes Carlos Filho. As notas de vídeo dele estão nas linhas 15 (victor 2/3) e 37 (Proc 3/1) e precisam ser transcritas.</t>
+IDENTIFICAÇÃO: Vagner Ássimos Gomes Carlos Filho, v188630@dac.unicamp.br. Confiança alta. Como cheguei nisso: nome na capa e campo Author do metadado ("Vagner"). As notas de vídeo dele estão nas linhas 15 e 37 desta aba e precisam ser transcritas para cá, porque valem 10 pontos e hoje entram como zero.</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
